--- a/public/Ananbay_template.xlsx
+++ b/public/Ananbay_template.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\TebGroup\teb-express-tunghoang\public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAC1F4B-4783-450E-B5CD-9171A40708E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="14640" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -196,15 +202,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="General\,"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General\,"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -252,158 +254,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,194 +275,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -626,253 +299,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -890,64 +321,22 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1205,33 +594,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.5546875" customWidth="1"/>
-    <col min="2" max="2" width="17.3359375" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="17.5546875" customWidth="1"/>
     <col min="7" max="7" width="12.5546875" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.890625" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="12" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="8.3359375" customWidth="1"/>
-    <col min="13" max="13" width="9.890625" customWidth="1"/>
-    <col min="15" max="15" width="10.4453125" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" customWidth="1"/>
+    <col min="15" max="15" width="10.44140625" customWidth="1"/>
     <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="19" max="19" width="13.015625" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="21" max="21" width="11.6640625" customWidth="1"/>
     <col min="1023" max="1023" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.75" spans="1:22">
+    <row r="1" spans="1:22" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1256,7 +645,7 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -1299,7 +688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="14.75" spans="1:22">
+    <row r="2" spans="1:22">
       <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
@@ -1319,7 +708,7 @@
       <c r="H2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="12">
         <v>3210752301</v>
       </c>
       <c r="J2" s="7" t="s">
@@ -1351,7 +740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="27.75" spans="1:22">
+    <row r="3" spans="1:22" ht="28.2">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
@@ -1371,7 +760,7 @@
       <c r="H3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="12">
         <v>3211869019</v>
       </c>
       <c r="J3" s="7" t="s">
@@ -1403,8 +792,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/public/Ananbay_template.xlsx
+++ b/public/Ananbay_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\TebGroup\teb-express-tunghoang\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAC1F4B-4783-450E-B5CD-9171A40708E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B175DCA8-7116-4B2F-AA89-04222F9CE259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>Tên người nhận</t>
   </si>
@@ -71,12 +71,6 @@
   </si>
   <si>
     <t>Pin</t>
-  </si>
-  <si>
-    <t>Label url</t>
-  </si>
-  <si>
-    <t>Ngày scan</t>
   </si>
   <si>
     <t>Tên SP</t>
@@ -146,21 +140,7 @@
     <t>Acrylic</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>Shirt</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Jennifer Brown</t>
-    </r>
   </si>
   <si>
     <r>
@@ -197,6 +177,51 @@
   </si>
   <si>
     <t>Ornament</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Scan sớm (1$)</t>
+  </si>
+  <si>
+    <t>Mã nhãn Tiktok</t>
+  </si>
+  <si>
+    <t>Express</t>
+  </si>
+  <si>
+    <t>Tiktok</t>
+  </si>
+  <si>
+    <t>Jennifer Brown</t>
+  </si>
+  <si>
+    <t>321075232</t>
+  </si>
+  <si>
+    <t>321075233</t>
+  </si>
+  <si>
+    <t>321186904</t>
+  </si>
+  <si>
+    <t>321186905</t>
+  </si>
+  <si>
+    <t>321186906</t>
+  </si>
+  <si>
+    <t>Code3</t>
+  </si>
+  <si>
+    <t>OG2123122</t>
+  </si>
+  <si>
+    <t>12312312331</t>
   </si>
 </sst>
 </file>
@@ -303,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -325,6 +350,12 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,7 +631,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V3"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:V531"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.5546875" customWidth="1"/>
@@ -615,7 +647,9 @@
     <col min="13" max="13" width="9.88671875" customWidth="1"/>
     <col min="15" max="15" width="10.44140625" customWidth="1"/>
     <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="17" max="17" width="7.77734375" style="14" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="13.109375" style="14" customWidth="1"/>
     <col min="21" max="21" width="11.6640625" customWidth="1"/>
     <col min="1023" max="1023" width="11.5546875" customWidth="1"/>
   </cols>
@@ -673,46 +707,46 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:22" ht="15" thickBot="1">
+      <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="6">
         <v>19033</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="12">
-        <v>3210752301</v>
+        <v>24</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K2" s="8">
         <v>85</v>
@@ -727,11 +761,12 @@
         <v>3</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="P2" s="10"/>
+      <c r="R2" s="12"/>
       <c r="T2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U2">
         <v>1</v>
@@ -740,58 +775,1817 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="28.2">
+    <row r="3" spans="1:22" ht="15" thickBot="1">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G3" s="6">
-        <v>20619</v>
+        <v>19033</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="12">
-        <v>3211869019</v>
+        <v>24</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K3" s="8">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="L3" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M3" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N3" s="8">
         <v>3</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>28</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="P3" s="10"/>
+      <c r="R3" s="12"/>
       <c r="T3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="U3">
         <v>1</v>
       </c>
       <c r="V3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="6">
+        <v>20619</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="8">
+        <v>70</v>
+      </c>
+      <c r="L4" s="8">
+        <v>13</v>
+      </c>
+      <c r="M4" s="8">
+        <v>13</v>
+      </c>
+      <c r="N4" s="8">
+        <v>3</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" t="s">
+        <v>30</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
         <v>12</v>
       </c>
     </row>
+    <row r="5" spans="1:22" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="6">
+        <v>20619</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="8">
+        <v>70</v>
+      </c>
+      <c r="L5" s="8">
+        <v>13</v>
+      </c>
+      <c r="M5" s="8">
+        <v>13</v>
+      </c>
+      <c r="N5" s="8">
+        <v>3</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" t="s">
+        <v>26</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="16.8" customHeight="1" thickBot="1">
+      <c r="A6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="6">
+        <v>20619</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="8">
+        <v>70</v>
+      </c>
+      <c r="L6" s="8">
+        <v>13</v>
+      </c>
+      <c r="M6" s="8">
+        <v>13</v>
+      </c>
+      <c r="N6" s="8">
+        <v>3</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" t="s">
+        <v>30</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="R8" s="12"/>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="R9" s="12"/>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="R10" s="12"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="R11" s="12"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="R12" s="12"/>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="R13" s="12"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="R14" s="12"/>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="R15" s="12"/>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="R16" s="12"/>
+    </row>
+    <row r="17" spans="18:18">
+      <c r="R17" s="12"/>
+    </row>
+    <row r="18" spans="18:18">
+      <c r="R18" s="12"/>
+    </row>
+    <row r="19" spans="18:18">
+      <c r="R19" s="12"/>
+    </row>
+    <row r="20" spans="18:18">
+      <c r="R20" s="12"/>
+    </row>
+    <row r="21" spans="18:18">
+      <c r="R21" s="12"/>
+    </row>
+    <row r="22" spans="18:18">
+      <c r="R22" s="12"/>
+    </row>
+    <row r="23" spans="18:18">
+      <c r="R23" s="12"/>
+    </row>
+    <row r="24" spans="18:18">
+      <c r="R24" s="12"/>
+    </row>
+    <row r="25" spans="18:18">
+      <c r="R25" s="12"/>
+    </row>
+    <row r="26" spans="18:18">
+      <c r="R26" s="12"/>
+    </row>
+    <row r="27" spans="18:18">
+      <c r="R27" s="12"/>
+    </row>
+    <row r="28" spans="18:18">
+      <c r="R28" s="12"/>
+    </row>
+    <row r="29" spans="18:18">
+      <c r="R29" s="12"/>
+    </row>
+    <row r="30" spans="18:18">
+      <c r="R30" s="12"/>
+    </row>
+    <row r="31" spans="18:18">
+      <c r="R31" s="12"/>
+    </row>
+    <row r="32" spans="18:18">
+      <c r="R32" s="12"/>
+    </row>
+    <row r="33" spans="18:18">
+      <c r="R33" s="12"/>
+    </row>
+    <row r="34" spans="18:18">
+      <c r="R34" s="12"/>
+    </row>
+    <row r="35" spans="18:18">
+      <c r="R35" s="12"/>
+    </row>
+    <row r="36" spans="18:18">
+      <c r="R36" s="12"/>
+    </row>
+    <row r="37" spans="18:18">
+      <c r="R37" s="12"/>
+    </row>
+    <row r="38" spans="18:18">
+      <c r="R38" s="12"/>
+    </row>
+    <row r="39" spans="18:18">
+      <c r="R39" s="12"/>
+    </row>
+    <row r="40" spans="18:18">
+      <c r="R40" s="12"/>
+    </row>
+    <row r="41" spans="18:18">
+      <c r="R41" s="12"/>
+    </row>
+    <row r="42" spans="18:18">
+      <c r="R42" s="12"/>
+    </row>
+    <row r="43" spans="18:18">
+      <c r="R43" s="12"/>
+    </row>
+    <row r="44" spans="18:18">
+      <c r="R44" s="12"/>
+    </row>
+    <row r="45" spans="18:18">
+      <c r="R45" s="12"/>
+    </row>
+    <row r="46" spans="18:18">
+      <c r="R46" s="12"/>
+    </row>
+    <row r="47" spans="18:18">
+      <c r="R47" s="12"/>
+    </row>
+    <row r="48" spans="18:18">
+      <c r="R48" s="12"/>
+    </row>
+    <row r="49" spans="18:18">
+      <c r="R49" s="12"/>
+    </row>
+    <row r="50" spans="18:18">
+      <c r="R50" s="12"/>
+    </row>
+    <row r="51" spans="18:18">
+      <c r="R51" s="12"/>
+    </row>
+    <row r="52" spans="18:18">
+      <c r="R52" s="12"/>
+    </row>
+    <row r="53" spans="18:18">
+      <c r="R53" s="12"/>
+    </row>
+    <row r="54" spans="18:18">
+      <c r="R54" s="12"/>
+    </row>
+    <row r="55" spans="18:18">
+      <c r="R55" s="12"/>
+    </row>
+    <row r="56" spans="18:18">
+      <c r="R56" s="12"/>
+    </row>
+    <row r="57" spans="18:18">
+      <c r="R57" s="12"/>
+    </row>
+    <row r="58" spans="18:18">
+      <c r="R58" s="12"/>
+    </row>
+    <row r="59" spans="18:18">
+      <c r="R59" s="12"/>
+    </row>
+    <row r="60" spans="18:18">
+      <c r="R60" s="12"/>
+    </row>
+    <row r="61" spans="18:18">
+      <c r="R61" s="12"/>
+    </row>
+    <row r="62" spans="18:18">
+      <c r="R62" s="12"/>
+    </row>
+    <row r="63" spans="18:18">
+      <c r="R63" s="12"/>
+    </row>
+    <row r="64" spans="18:18">
+      <c r="R64" s="12"/>
+    </row>
+    <row r="65" spans="18:18">
+      <c r="R65" s="12"/>
+    </row>
+    <row r="66" spans="18:18">
+      <c r="R66" s="12"/>
+    </row>
+    <row r="67" spans="18:18">
+      <c r="R67" s="12"/>
+    </row>
+    <row r="68" spans="18:18">
+      <c r="R68" s="12"/>
+    </row>
+    <row r="69" spans="18:18">
+      <c r="R69" s="12"/>
+    </row>
+    <row r="70" spans="18:18">
+      <c r="R70" s="12"/>
+    </row>
+    <row r="71" spans="18:18">
+      <c r="R71" s="12"/>
+    </row>
+    <row r="72" spans="18:18">
+      <c r="R72" s="12"/>
+    </row>
+    <row r="73" spans="18:18">
+      <c r="R73" s="12"/>
+    </row>
+    <row r="74" spans="18:18">
+      <c r="R74" s="12"/>
+    </row>
+    <row r="75" spans="18:18">
+      <c r="R75" s="12"/>
+    </row>
+    <row r="76" spans="18:18">
+      <c r="R76" s="12"/>
+    </row>
+    <row r="77" spans="18:18">
+      <c r="R77" s="12"/>
+    </row>
+    <row r="78" spans="18:18">
+      <c r="R78" s="12"/>
+    </row>
+    <row r="79" spans="18:18">
+      <c r="R79" s="12"/>
+    </row>
+    <row r="80" spans="18:18">
+      <c r="R80" s="12"/>
+    </row>
+    <row r="81" spans="18:18">
+      <c r="R81" s="12"/>
+    </row>
+    <row r="82" spans="18:18">
+      <c r="R82" s="12"/>
+    </row>
+    <row r="83" spans="18:18">
+      <c r="R83" s="12"/>
+    </row>
+    <row r="84" spans="18:18">
+      <c r="R84" s="12"/>
+    </row>
+    <row r="85" spans="18:18">
+      <c r="R85" s="12"/>
+    </row>
+    <row r="86" spans="18:18">
+      <c r="R86" s="12"/>
+    </row>
+    <row r="87" spans="18:18">
+      <c r="R87" s="12"/>
+    </row>
+    <row r="88" spans="18:18">
+      <c r="R88" s="12"/>
+    </row>
+    <row r="89" spans="18:18">
+      <c r="R89" s="12"/>
+    </row>
+    <row r="90" spans="18:18">
+      <c r="R90" s="12"/>
+    </row>
+    <row r="91" spans="18:18">
+      <c r="R91" s="12"/>
+    </row>
+    <row r="92" spans="18:18">
+      <c r="R92" s="12"/>
+    </row>
+    <row r="93" spans="18:18">
+      <c r="R93" s="12"/>
+    </row>
+    <row r="94" spans="18:18">
+      <c r="R94" s="12"/>
+    </row>
+    <row r="95" spans="18:18">
+      <c r="R95" s="12"/>
+    </row>
+    <row r="96" spans="18:18">
+      <c r="R96" s="12"/>
+    </row>
+    <row r="97" spans="18:18">
+      <c r="R97" s="12"/>
+    </row>
+    <row r="98" spans="18:18">
+      <c r="R98" s="12"/>
+    </row>
+    <row r="99" spans="18:18">
+      <c r="R99" s="12"/>
+    </row>
+    <row r="100" spans="18:18">
+      <c r="R100" s="12"/>
+    </row>
+    <row r="101" spans="18:18">
+      <c r="R101" s="12"/>
+    </row>
+    <row r="102" spans="18:18">
+      <c r="R102" s="12"/>
+    </row>
+    <row r="103" spans="18:18">
+      <c r="R103" s="12"/>
+    </row>
+    <row r="104" spans="18:18">
+      <c r="R104" s="12"/>
+    </row>
+    <row r="105" spans="18:18">
+      <c r="R105" s="12"/>
+    </row>
+    <row r="106" spans="18:18">
+      <c r="R106" s="12"/>
+    </row>
+    <row r="107" spans="18:18">
+      <c r="R107" s="12"/>
+    </row>
+    <row r="108" spans="18:18">
+      <c r="R108" s="12"/>
+    </row>
+    <row r="109" spans="18:18">
+      <c r="R109" s="12"/>
+    </row>
+    <row r="110" spans="18:18">
+      <c r="R110" s="12"/>
+    </row>
+    <row r="111" spans="18:18">
+      <c r="R111" s="12"/>
+    </row>
+    <row r="112" spans="18:18">
+      <c r="R112" s="12"/>
+    </row>
+    <row r="113" spans="18:18">
+      <c r="R113" s="12"/>
+    </row>
+    <row r="114" spans="18:18">
+      <c r="R114" s="12"/>
+    </row>
+    <row r="115" spans="18:18">
+      <c r="R115" s="12"/>
+    </row>
+    <row r="116" spans="18:18">
+      <c r="R116" s="12"/>
+    </row>
+    <row r="117" spans="18:18">
+      <c r="R117" s="12"/>
+    </row>
+    <row r="118" spans="18:18">
+      <c r="R118" s="12"/>
+    </row>
+    <row r="119" spans="18:18">
+      <c r="R119" s="12"/>
+    </row>
+    <row r="120" spans="18:18">
+      <c r="R120" s="12"/>
+    </row>
+    <row r="121" spans="18:18">
+      <c r="R121" s="12"/>
+    </row>
+    <row r="122" spans="18:18">
+      <c r="R122" s="12"/>
+    </row>
+    <row r="123" spans="18:18">
+      <c r="R123" s="12"/>
+    </row>
+    <row r="124" spans="18:18">
+      <c r="R124" s="12"/>
+    </row>
+    <row r="125" spans="18:18">
+      <c r="R125" s="12"/>
+    </row>
+    <row r="126" spans="18:18">
+      <c r="R126" s="12"/>
+    </row>
+    <row r="127" spans="18:18">
+      <c r="R127" s="12"/>
+    </row>
+    <row r="128" spans="18:18">
+      <c r="R128" s="12"/>
+    </row>
+    <row r="129" spans="18:18">
+      <c r="R129" s="12"/>
+    </row>
+    <row r="130" spans="18:18">
+      <c r="R130" s="12"/>
+    </row>
+    <row r="131" spans="18:18">
+      <c r="R131" s="12"/>
+    </row>
+    <row r="132" spans="18:18">
+      <c r="R132" s="12"/>
+    </row>
+    <row r="133" spans="18:18">
+      <c r="R133" s="12"/>
+    </row>
+    <row r="134" spans="18:18">
+      <c r="R134" s="12"/>
+    </row>
+    <row r="135" spans="18:18">
+      <c r="R135" s="12"/>
+    </row>
+    <row r="136" spans="18:18">
+      <c r="R136" s="12"/>
+    </row>
+    <row r="137" spans="18:18">
+      <c r="R137" s="12"/>
+    </row>
+    <row r="138" spans="18:18">
+      <c r="R138" s="12"/>
+    </row>
+    <row r="139" spans="18:18">
+      <c r="R139" s="12"/>
+    </row>
+    <row r="140" spans="18:18">
+      <c r="R140" s="12"/>
+    </row>
+    <row r="141" spans="18:18">
+      <c r="R141" s="12"/>
+    </row>
+    <row r="142" spans="18:18">
+      <c r="R142" s="12"/>
+    </row>
+    <row r="143" spans="18:18">
+      <c r="R143" s="12"/>
+    </row>
+    <row r="144" spans="18:18">
+      <c r="R144" s="12"/>
+    </row>
+    <row r="145" spans="18:18">
+      <c r="R145" s="12"/>
+    </row>
+    <row r="146" spans="18:18">
+      <c r="R146" s="12"/>
+    </row>
+    <row r="147" spans="18:18">
+      <c r="R147" s="12"/>
+    </row>
+    <row r="148" spans="18:18">
+      <c r="R148" s="12"/>
+    </row>
+    <row r="149" spans="18:18">
+      <c r="R149" s="12"/>
+    </row>
+    <row r="150" spans="18:18">
+      <c r="R150" s="12"/>
+    </row>
+    <row r="151" spans="18:18">
+      <c r="R151" s="12"/>
+    </row>
+    <row r="152" spans="18:18">
+      <c r="R152" s="12"/>
+    </row>
+    <row r="153" spans="18:18">
+      <c r="R153" s="12"/>
+    </row>
+    <row r="154" spans="18:18">
+      <c r="R154" s="12"/>
+    </row>
+    <row r="155" spans="18:18">
+      <c r="R155" s="12"/>
+    </row>
+    <row r="156" spans="18:18">
+      <c r="R156" s="12"/>
+    </row>
+    <row r="157" spans="18:18">
+      <c r="R157" s="12"/>
+    </row>
+    <row r="158" spans="18:18">
+      <c r="R158" s="12"/>
+    </row>
+    <row r="159" spans="18:18">
+      <c r="R159" s="12"/>
+    </row>
+    <row r="160" spans="18:18">
+      <c r="R160" s="12"/>
+    </row>
+    <row r="161" spans="18:18">
+      <c r="R161" s="12"/>
+    </row>
+    <row r="162" spans="18:18">
+      <c r="R162" s="12"/>
+    </row>
+    <row r="163" spans="18:18">
+      <c r="R163" s="12"/>
+    </row>
+    <row r="164" spans="18:18">
+      <c r="R164" s="12"/>
+    </row>
+    <row r="165" spans="18:18">
+      <c r="R165" s="12"/>
+    </row>
+    <row r="166" spans="18:18">
+      <c r="R166" s="12"/>
+    </row>
+    <row r="167" spans="18:18">
+      <c r="R167" s="12"/>
+    </row>
+    <row r="168" spans="18:18">
+      <c r="R168" s="12"/>
+    </row>
+    <row r="169" spans="18:18">
+      <c r="R169" s="12"/>
+    </row>
+    <row r="170" spans="18:18">
+      <c r="R170" s="12"/>
+    </row>
+    <row r="171" spans="18:18">
+      <c r="R171" s="12"/>
+    </row>
+    <row r="172" spans="18:18">
+      <c r="R172" s="12"/>
+    </row>
+    <row r="173" spans="18:18">
+      <c r="R173" s="12"/>
+    </row>
+    <row r="174" spans="18:18">
+      <c r="R174" s="12"/>
+    </row>
+    <row r="175" spans="18:18">
+      <c r="R175" s="12"/>
+    </row>
+    <row r="176" spans="18:18">
+      <c r="R176" s="12"/>
+    </row>
+    <row r="177" spans="18:18">
+      <c r="R177" s="12"/>
+    </row>
+    <row r="178" spans="18:18">
+      <c r="R178" s="12"/>
+    </row>
+    <row r="179" spans="18:18">
+      <c r="R179" s="12"/>
+    </row>
+    <row r="180" spans="18:18">
+      <c r="R180" s="12"/>
+    </row>
+    <row r="181" spans="18:18">
+      <c r="R181" s="12"/>
+    </row>
+    <row r="182" spans="18:18">
+      <c r="R182" s="12"/>
+    </row>
+    <row r="183" spans="18:18">
+      <c r="R183" s="12"/>
+    </row>
+    <row r="184" spans="18:18">
+      <c r="R184" s="12"/>
+    </row>
+    <row r="185" spans="18:18">
+      <c r="R185" s="12"/>
+    </row>
+    <row r="186" spans="18:18">
+      <c r="R186" s="12"/>
+    </row>
+    <row r="187" spans="18:18">
+      <c r="R187" s="12"/>
+    </row>
+    <row r="188" spans="18:18">
+      <c r="R188" s="12"/>
+    </row>
+    <row r="189" spans="18:18">
+      <c r="R189" s="12"/>
+    </row>
+    <row r="190" spans="18:18">
+      <c r="R190" s="12"/>
+    </row>
+    <row r="191" spans="18:18">
+      <c r="R191" s="12"/>
+    </row>
+    <row r="192" spans="18:18">
+      <c r="R192" s="12"/>
+    </row>
+    <row r="193" spans="18:18">
+      <c r="R193" s="12"/>
+    </row>
+    <row r="194" spans="18:18">
+      <c r="R194" s="12"/>
+    </row>
+    <row r="195" spans="18:18">
+      <c r="R195" s="12"/>
+    </row>
+    <row r="196" spans="18:18">
+      <c r="R196" s="12"/>
+    </row>
+    <row r="197" spans="18:18">
+      <c r="R197" s="12"/>
+    </row>
+    <row r="198" spans="18:18">
+      <c r="R198" s="12"/>
+    </row>
+    <row r="199" spans="18:18">
+      <c r="R199" s="12"/>
+    </row>
+    <row r="200" spans="18:18">
+      <c r="R200" s="12"/>
+    </row>
+    <row r="201" spans="18:18">
+      <c r="R201" s="12"/>
+    </row>
+    <row r="202" spans="18:18">
+      <c r="R202" s="12"/>
+    </row>
+    <row r="203" spans="18:18">
+      <c r="R203" s="12"/>
+    </row>
+    <row r="204" spans="18:18">
+      <c r="R204" s="12"/>
+    </row>
+    <row r="205" spans="18:18">
+      <c r="R205" s="12"/>
+    </row>
+    <row r="206" spans="18:18">
+      <c r="R206" s="12"/>
+    </row>
+    <row r="207" spans="18:18">
+      <c r="R207" s="12"/>
+    </row>
+    <row r="208" spans="18:18">
+      <c r="R208" s="12"/>
+    </row>
+    <row r="209" spans="18:18">
+      <c r="R209" s="12"/>
+    </row>
+    <row r="210" spans="18:18">
+      <c r="R210" s="12"/>
+    </row>
+    <row r="211" spans="18:18">
+      <c r="R211" s="12"/>
+    </row>
+    <row r="212" spans="18:18">
+      <c r="R212" s="12"/>
+    </row>
+    <row r="213" spans="18:18">
+      <c r="R213" s="12"/>
+    </row>
+    <row r="214" spans="18:18">
+      <c r="R214" s="12"/>
+    </row>
+    <row r="215" spans="18:18">
+      <c r="R215" s="12"/>
+    </row>
+    <row r="216" spans="18:18">
+      <c r="R216" s="12"/>
+    </row>
+    <row r="217" spans="18:18">
+      <c r="R217" s="12"/>
+    </row>
+    <row r="218" spans="18:18">
+      <c r="R218" s="12"/>
+    </row>
+    <row r="219" spans="18:18">
+      <c r="R219" s="12"/>
+    </row>
+    <row r="220" spans="18:18">
+      <c r="R220" s="12"/>
+    </row>
+    <row r="221" spans="18:18">
+      <c r="R221" s="12"/>
+    </row>
+    <row r="222" spans="18:18">
+      <c r="R222" s="12"/>
+    </row>
+    <row r="223" spans="18:18">
+      <c r="R223" s="12"/>
+    </row>
+    <row r="224" spans="18:18">
+      <c r="R224" s="12"/>
+    </row>
+    <row r="225" spans="18:18">
+      <c r="R225" s="12"/>
+    </row>
+    <row r="226" spans="18:18">
+      <c r="R226" s="12"/>
+    </row>
+    <row r="227" spans="18:18">
+      <c r="R227" s="12"/>
+    </row>
+    <row r="228" spans="18:18">
+      <c r="R228" s="12"/>
+    </row>
+    <row r="229" spans="18:18">
+      <c r="R229" s="12"/>
+    </row>
+    <row r="230" spans="18:18">
+      <c r="R230" s="12"/>
+    </row>
+    <row r="231" spans="18:18">
+      <c r="R231" s="12"/>
+    </row>
+    <row r="232" spans="18:18">
+      <c r="R232" s="12"/>
+    </row>
+    <row r="233" spans="18:18">
+      <c r="R233" s="12"/>
+    </row>
+    <row r="234" spans="18:18">
+      <c r="R234" s="12"/>
+    </row>
+    <row r="235" spans="18:18">
+      <c r="R235" s="12"/>
+    </row>
+    <row r="236" spans="18:18">
+      <c r="R236" s="12"/>
+    </row>
+    <row r="237" spans="18:18">
+      <c r="R237" s="12"/>
+    </row>
+    <row r="238" spans="18:18">
+      <c r="R238" s="12"/>
+    </row>
+    <row r="239" spans="18:18">
+      <c r="R239" s="12"/>
+    </row>
+    <row r="240" spans="18:18">
+      <c r="R240" s="12"/>
+    </row>
+    <row r="241" spans="18:18">
+      <c r="R241" s="12"/>
+    </row>
+    <row r="242" spans="18:18">
+      <c r="R242" s="12"/>
+    </row>
+    <row r="243" spans="18:18">
+      <c r="R243" s="12"/>
+    </row>
+    <row r="244" spans="18:18">
+      <c r="R244" s="12"/>
+    </row>
+    <row r="245" spans="18:18">
+      <c r="R245" s="12"/>
+    </row>
+    <row r="246" spans="18:18">
+      <c r="R246" s="12"/>
+    </row>
+    <row r="247" spans="18:18">
+      <c r="R247" s="12"/>
+    </row>
+    <row r="248" spans="18:18">
+      <c r="R248" s="12"/>
+    </row>
+    <row r="249" spans="18:18">
+      <c r="R249" s="12"/>
+    </row>
+    <row r="250" spans="18:18">
+      <c r="R250" s="12"/>
+    </row>
+    <row r="251" spans="18:18">
+      <c r="R251" s="12"/>
+    </row>
+    <row r="252" spans="18:18">
+      <c r="R252" s="12"/>
+    </row>
+    <row r="253" spans="18:18">
+      <c r="R253" s="12"/>
+    </row>
+    <row r="254" spans="18:18">
+      <c r="R254" s="12"/>
+    </row>
+    <row r="255" spans="18:18">
+      <c r="R255" s="12"/>
+    </row>
+    <row r="256" spans="18:18">
+      <c r="R256" s="12"/>
+    </row>
+    <row r="257" spans="18:18">
+      <c r="R257" s="12"/>
+    </row>
+    <row r="258" spans="18:18">
+      <c r="R258" s="12"/>
+    </row>
+    <row r="259" spans="18:18">
+      <c r="R259" s="12"/>
+    </row>
+    <row r="260" spans="18:18">
+      <c r="R260" s="12"/>
+    </row>
+    <row r="261" spans="18:18">
+      <c r="R261" s="12"/>
+    </row>
+    <row r="262" spans="18:18">
+      <c r="R262" s="12"/>
+    </row>
+    <row r="263" spans="18:18">
+      <c r="R263" s="12"/>
+    </row>
+    <row r="264" spans="18:18">
+      <c r="R264" s="12"/>
+    </row>
+    <row r="265" spans="18:18">
+      <c r="R265" s="12"/>
+    </row>
+    <row r="266" spans="18:18">
+      <c r="R266" s="12"/>
+    </row>
+    <row r="267" spans="18:18">
+      <c r="R267" s="12"/>
+    </row>
+    <row r="268" spans="18:18">
+      <c r="R268" s="12"/>
+    </row>
+    <row r="269" spans="18:18">
+      <c r="R269" s="12"/>
+    </row>
+    <row r="270" spans="18:18">
+      <c r="R270" s="12"/>
+    </row>
+    <row r="271" spans="18:18">
+      <c r="R271" s="12"/>
+    </row>
+    <row r="272" spans="18:18">
+      <c r="R272" s="12"/>
+    </row>
+    <row r="273" spans="18:18">
+      <c r="R273" s="12"/>
+    </row>
+    <row r="274" spans="18:18">
+      <c r="R274" s="12"/>
+    </row>
+    <row r="275" spans="18:18">
+      <c r="R275" s="12"/>
+    </row>
+    <row r="276" spans="18:18">
+      <c r="R276" s="12"/>
+    </row>
+    <row r="277" spans="18:18">
+      <c r="R277" s="12"/>
+    </row>
+    <row r="278" spans="18:18">
+      <c r="R278" s="12"/>
+    </row>
+    <row r="279" spans="18:18">
+      <c r="R279" s="12"/>
+    </row>
+    <row r="280" spans="18:18">
+      <c r="R280" s="12"/>
+    </row>
+    <row r="281" spans="18:18">
+      <c r="R281" s="12"/>
+    </row>
+    <row r="282" spans="18:18">
+      <c r="R282" s="12"/>
+    </row>
+    <row r="283" spans="18:18">
+      <c r="R283" s="12"/>
+    </row>
+    <row r="284" spans="18:18">
+      <c r="R284" s="12"/>
+    </row>
+    <row r="285" spans="18:18">
+      <c r="R285" s="12"/>
+    </row>
+    <row r="286" spans="18:18">
+      <c r="R286" s="12"/>
+    </row>
+    <row r="287" spans="18:18">
+      <c r="R287" s="12"/>
+    </row>
+    <row r="288" spans="18:18">
+      <c r="R288" s="12"/>
+    </row>
+    <row r="289" spans="18:18">
+      <c r="R289" s="12"/>
+    </row>
+    <row r="290" spans="18:18">
+      <c r="R290" s="12"/>
+    </row>
+    <row r="291" spans="18:18">
+      <c r="R291" s="12"/>
+    </row>
+    <row r="292" spans="18:18">
+      <c r="R292" s="12"/>
+    </row>
+    <row r="293" spans="18:18">
+      <c r="R293" s="12"/>
+    </row>
+    <row r="294" spans="18:18">
+      <c r="R294" s="12"/>
+    </row>
+    <row r="295" spans="18:18">
+      <c r="R295" s="12"/>
+    </row>
+    <row r="296" spans="18:18">
+      <c r="R296" s="12"/>
+    </row>
+    <row r="297" spans="18:18">
+      <c r="R297" s="12"/>
+    </row>
+    <row r="298" spans="18:18">
+      <c r="R298" s="12"/>
+    </row>
+    <row r="299" spans="18:18">
+      <c r="R299" s="12"/>
+    </row>
+    <row r="300" spans="18:18">
+      <c r="R300" s="12"/>
+    </row>
+    <row r="301" spans="18:18">
+      <c r="R301" s="12"/>
+    </row>
+    <row r="302" spans="18:18">
+      <c r="R302" s="12"/>
+    </row>
+    <row r="303" spans="18:18">
+      <c r="R303" s="12"/>
+    </row>
+    <row r="304" spans="18:18">
+      <c r="R304" s="12"/>
+    </row>
+    <row r="305" spans="18:18">
+      <c r="R305" s="12"/>
+    </row>
+    <row r="306" spans="18:18">
+      <c r="R306" s="12"/>
+    </row>
+    <row r="307" spans="18:18">
+      <c r="R307" s="12"/>
+    </row>
+    <row r="308" spans="18:18">
+      <c r="R308" s="12"/>
+    </row>
+    <row r="309" spans="18:18">
+      <c r="R309" s="12"/>
+    </row>
+    <row r="310" spans="18:18">
+      <c r="R310" s="12"/>
+    </row>
+    <row r="311" spans="18:18">
+      <c r="R311" s="12"/>
+    </row>
+    <row r="312" spans="18:18">
+      <c r="R312" s="12"/>
+    </row>
+    <row r="313" spans="18:18">
+      <c r="R313" s="12"/>
+    </row>
+    <row r="314" spans="18:18">
+      <c r="R314" s="12"/>
+    </row>
+    <row r="315" spans="18:18">
+      <c r="R315" s="12"/>
+    </row>
+    <row r="316" spans="18:18">
+      <c r="R316" s="12"/>
+    </row>
+    <row r="317" spans="18:18">
+      <c r="R317" s="12"/>
+    </row>
+    <row r="318" spans="18:18">
+      <c r="R318" s="12"/>
+    </row>
+    <row r="319" spans="18:18">
+      <c r="R319" s="12"/>
+    </row>
+    <row r="320" spans="18:18">
+      <c r="R320" s="12"/>
+    </row>
+    <row r="321" spans="18:18">
+      <c r="R321" s="12"/>
+    </row>
+    <row r="322" spans="18:18">
+      <c r="R322" s="12"/>
+    </row>
+    <row r="323" spans="18:18">
+      <c r="R323" s="12"/>
+    </row>
+    <row r="324" spans="18:18">
+      <c r="R324" s="12"/>
+    </row>
+    <row r="325" spans="18:18">
+      <c r="R325" s="12"/>
+    </row>
+    <row r="326" spans="18:18">
+      <c r="R326" s="12"/>
+    </row>
+    <row r="327" spans="18:18">
+      <c r="R327" s="12"/>
+    </row>
+    <row r="328" spans="18:18">
+      <c r="R328" s="12"/>
+    </row>
+    <row r="329" spans="18:18">
+      <c r="R329" s="12"/>
+    </row>
+    <row r="330" spans="18:18">
+      <c r="R330" s="12"/>
+    </row>
+    <row r="331" spans="18:18">
+      <c r="R331" s="12"/>
+    </row>
+    <row r="332" spans="18:18">
+      <c r="R332" s="12"/>
+    </row>
+    <row r="333" spans="18:18">
+      <c r="R333" s="12"/>
+    </row>
+    <row r="334" spans="18:18">
+      <c r="R334" s="12"/>
+    </row>
+    <row r="335" spans="18:18">
+      <c r="R335" s="12"/>
+    </row>
+    <row r="336" spans="18:18">
+      <c r="R336" s="12"/>
+    </row>
+    <row r="337" spans="18:18">
+      <c r="R337" s="12"/>
+    </row>
+    <row r="338" spans="18:18">
+      <c r="R338" s="12"/>
+    </row>
+    <row r="339" spans="18:18">
+      <c r="R339" s="12"/>
+    </row>
+    <row r="340" spans="18:18">
+      <c r="R340" s="12"/>
+    </row>
+    <row r="341" spans="18:18">
+      <c r="R341" s="12"/>
+    </row>
+    <row r="342" spans="18:18">
+      <c r="R342" s="12"/>
+    </row>
+    <row r="343" spans="18:18">
+      <c r="R343" s="12"/>
+    </row>
+    <row r="344" spans="18:18">
+      <c r="R344" s="12"/>
+    </row>
+    <row r="345" spans="18:18">
+      <c r="R345" s="12"/>
+    </row>
+    <row r="346" spans="18:18">
+      <c r="R346" s="12"/>
+    </row>
+    <row r="347" spans="18:18">
+      <c r="R347" s="12"/>
+    </row>
+    <row r="348" spans="18:18">
+      <c r="R348" s="12"/>
+    </row>
+    <row r="349" spans="18:18">
+      <c r="R349" s="12"/>
+    </row>
+    <row r="350" spans="18:18">
+      <c r="R350" s="12"/>
+    </row>
+    <row r="351" spans="18:18">
+      <c r="R351" s="12"/>
+    </row>
+    <row r="352" spans="18:18">
+      <c r="R352" s="12"/>
+    </row>
+    <row r="353" spans="18:18">
+      <c r="R353" s="12"/>
+    </row>
+    <row r="354" spans="18:18">
+      <c r="R354" s="12"/>
+    </row>
+    <row r="355" spans="18:18">
+      <c r="R355" s="12"/>
+    </row>
+    <row r="356" spans="18:18">
+      <c r="R356" s="12"/>
+    </row>
+    <row r="357" spans="18:18">
+      <c r="R357" s="12"/>
+    </row>
+    <row r="358" spans="18:18">
+      <c r="R358" s="12"/>
+    </row>
+    <row r="359" spans="18:18">
+      <c r="R359" s="12"/>
+    </row>
+    <row r="360" spans="18:18">
+      <c r="R360" s="12"/>
+    </row>
+    <row r="361" spans="18:18">
+      <c r="R361" s="12"/>
+    </row>
+    <row r="362" spans="18:18">
+      <c r="R362" s="12"/>
+    </row>
+    <row r="363" spans="18:18">
+      <c r="R363" s="12"/>
+    </row>
+    <row r="364" spans="18:18">
+      <c r="R364" s="12"/>
+    </row>
+    <row r="365" spans="18:18">
+      <c r="R365" s="12"/>
+    </row>
+    <row r="366" spans="18:18">
+      <c r="R366" s="12"/>
+    </row>
+    <row r="367" spans="18:18">
+      <c r="R367" s="12"/>
+    </row>
+    <row r="368" spans="18:18">
+      <c r="R368" s="12"/>
+    </row>
+    <row r="369" spans="18:18">
+      <c r="R369" s="12"/>
+    </row>
+    <row r="370" spans="18:18">
+      <c r="R370" s="12"/>
+    </row>
+    <row r="371" spans="18:18">
+      <c r="R371" s="12"/>
+    </row>
+    <row r="372" spans="18:18">
+      <c r="R372" s="12"/>
+    </row>
+    <row r="373" spans="18:18">
+      <c r="R373" s="12"/>
+    </row>
+    <row r="374" spans="18:18">
+      <c r="R374" s="12"/>
+    </row>
+    <row r="375" spans="18:18">
+      <c r="R375" s="12"/>
+    </row>
+    <row r="376" spans="18:18">
+      <c r="R376" s="12"/>
+    </row>
+    <row r="377" spans="18:18">
+      <c r="R377" s="12"/>
+    </row>
+    <row r="378" spans="18:18">
+      <c r="R378" s="12"/>
+    </row>
+    <row r="379" spans="18:18">
+      <c r="R379" s="12"/>
+    </row>
+    <row r="380" spans="18:18">
+      <c r="R380" s="12"/>
+    </row>
+    <row r="381" spans="18:18">
+      <c r="R381" s="12"/>
+    </row>
+    <row r="382" spans="18:18">
+      <c r="R382" s="12"/>
+    </row>
+    <row r="383" spans="18:18">
+      <c r="R383" s="12"/>
+    </row>
+    <row r="384" spans="18:18">
+      <c r="R384" s="12"/>
+    </row>
+    <row r="385" spans="18:18">
+      <c r="R385" s="12"/>
+    </row>
+    <row r="386" spans="18:18">
+      <c r="R386" s="12"/>
+    </row>
+    <row r="387" spans="18:18">
+      <c r="R387" s="12"/>
+    </row>
+    <row r="388" spans="18:18">
+      <c r="R388" s="12"/>
+    </row>
+    <row r="389" spans="18:18">
+      <c r="R389" s="12"/>
+    </row>
+    <row r="390" spans="18:18">
+      <c r="R390" s="12"/>
+    </row>
+    <row r="391" spans="18:18">
+      <c r="R391" s="12"/>
+    </row>
+    <row r="392" spans="18:18">
+      <c r="R392" s="12"/>
+    </row>
+    <row r="393" spans="18:18">
+      <c r="R393" s="12"/>
+    </row>
+    <row r="394" spans="18:18">
+      <c r="R394" s="12"/>
+    </row>
+    <row r="395" spans="18:18">
+      <c r="R395" s="12"/>
+    </row>
+    <row r="396" spans="18:18">
+      <c r="R396" s="12"/>
+    </row>
+    <row r="397" spans="18:18">
+      <c r="R397" s="12"/>
+    </row>
+    <row r="398" spans="18:18">
+      <c r="R398" s="12"/>
+    </row>
+    <row r="399" spans="18:18">
+      <c r="R399" s="12"/>
+    </row>
+    <row r="400" spans="18:18">
+      <c r="R400" s="12"/>
+    </row>
+    <row r="401" spans="18:18">
+      <c r="R401" s="12"/>
+    </row>
+    <row r="402" spans="18:18">
+      <c r="R402" s="12"/>
+    </row>
+    <row r="403" spans="18:18">
+      <c r="R403" s="12"/>
+    </row>
+    <row r="404" spans="18:18">
+      <c r="R404" s="12"/>
+    </row>
+    <row r="405" spans="18:18">
+      <c r="R405" s="12"/>
+    </row>
+    <row r="406" spans="18:18">
+      <c r="R406" s="12"/>
+    </row>
+    <row r="407" spans="18:18">
+      <c r="R407" s="12"/>
+    </row>
+    <row r="408" spans="18:18">
+      <c r="R408" s="12"/>
+    </row>
+    <row r="409" spans="18:18">
+      <c r="R409" s="12"/>
+    </row>
+    <row r="410" spans="18:18">
+      <c r="R410" s="12"/>
+    </row>
+    <row r="411" spans="18:18">
+      <c r="R411" s="12"/>
+    </row>
+    <row r="412" spans="18:18">
+      <c r="R412" s="12"/>
+    </row>
+    <row r="413" spans="18:18">
+      <c r="R413" s="12"/>
+    </row>
+    <row r="414" spans="18:18">
+      <c r="R414" s="12"/>
+    </row>
+    <row r="415" spans="18:18">
+      <c r="R415" s="12"/>
+    </row>
+    <row r="416" spans="18:18">
+      <c r="R416" s="12"/>
+    </row>
+    <row r="417" spans="18:18">
+      <c r="R417" s="12"/>
+    </row>
+    <row r="418" spans="18:18">
+      <c r="R418" s="12"/>
+    </row>
+    <row r="419" spans="18:18">
+      <c r="R419" s="12"/>
+    </row>
+    <row r="420" spans="18:18">
+      <c r="R420" s="12"/>
+    </row>
+    <row r="421" spans="18:18">
+      <c r="R421" s="12"/>
+    </row>
+    <row r="422" spans="18:18">
+      <c r="R422" s="12"/>
+    </row>
+    <row r="423" spans="18:18">
+      <c r="R423" s="12"/>
+    </row>
+    <row r="424" spans="18:18">
+      <c r="R424" s="12"/>
+    </row>
+    <row r="425" spans="18:18">
+      <c r="R425" s="12"/>
+    </row>
+    <row r="426" spans="18:18">
+      <c r="R426" s="12"/>
+    </row>
+    <row r="427" spans="18:18">
+      <c r="R427" s="12"/>
+    </row>
+    <row r="428" spans="18:18">
+      <c r="R428" s="12"/>
+    </row>
+    <row r="429" spans="18:18">
+      <c r="R429" s="12"/>
+    </row>
+    <row r="430" spans="18:18">
+      <c r="R430" s="12"/>
+    </row>
+    <row r="431" spans="18:18">
+      <c r="R431" s="12"/>
+    </row>
+    <row r="432" spans="18:18">
+      <c r="R432" s="12"/>
+    </row>
+    <row r="433" spans="18:18">
+      <c r="R433" s="12"/>
+    </row>
+    <row r="434" spans="18:18">
+      <c r="R434" s="12"/>
+    </row>
+    <row r="435" spans="18:18">
+      <c r="R435" s="12"/>
+    </row>
+    <row r="436" spans="18:18">
+      <c r="R436" s="12"/>
+    </row>
+    <row r="437" spans="18:18">
+      <c r="R437" s="12"/>
+    </row>
+    <row r="438" spans="18:18">
+      <c r="R438" s="12"/>
+    </row>
+    <row r="439" spans="18:18">
+      <c r="R439" s="12"/>
+    </row>
+    <row r="440" spans="18:18">
+      <c r="R440" s="12"/>
+    </row>
+    <row r="441" spans="18:18">
+      <c r="R441" s="12"/>
+    </row>
+    <row r="442" spans="18:18">
+      <c r="R442" s="12"/>
+    </row>
+    <row r="443" spans="18:18">
+      <c r="R443" s="12"/>
+    </row>
+    <row r="444" spans="18:18">
+      <c r="R444" s="12"/>
+    </row>
+    <row r="445" spans="18:18">
+      <c r="R445" s="12"/>
+    </row>
+    <row r="446" spans="18:18">
+      <c r="R446" s="12"/>
+    </row>
+    <row r="447" spans="18:18">
+      <c r="R447" s="12"/>
+    </row>
+    <row r="448" spans="18:18">
+      <c r="R448" s="12"/>
+    </row>
+    <row r="449" spans="18:18">
+      <c r="R449" s="12"/>
+    </row>
+    <row r="450" spans="18:18">
+      <c r="R450" s="12"/>
+    </row>
+    <row r="451" spans="18:18">
+      <c r="R451" s="12"/>
+    </row>
+    <row r="452" spans="18:18">
+      <c r="R452" s="12"/>
+    </row>
+    <row r="453" spans="18:18">
+      <c r="R453" s="12"/>
+    </row>
+    <row r="454" spans="18:18">
+      <c r="R454" s="12"/>
+    </row>
+    <row r="455" spans="18:18">
+      <c r="R455" s="12"/>
+    </row>
+    <row r="456" spans="18:18">
+      <c r="R456" s="12"/>
+    </row>
+    <row r="457" spans="18:18">
+      <c r="R457" s="12"/>
+    </row>
+    <row r="458" spans="18:18">
+      <c r="R458" s="12"/>
+    </row>
+    <row r="459" spans="18:18">
+      <c r="R459" s="12"/>
+    </row>
+    <row r="460" spans="18:18">
+      <c r="R460" s="12"/>
+    </row>
+    <row r="461" spans="18:18">
+      <c r="R461" s="12"/>
+    </row>
+    <row r="462" spans="18:18">
+      <c r="R462" s="12"/>
+    </row>
+    <row r="463" spans="18:18">
+      <c r="R463" s="12"/>
+    </row>
+    <row r="464" spans="18:18">
+      <c r="R464" s="12"/>
+    </row>
+    <row r="465" spans="18:18">
+      <c r="R465" s="12"/>
+    </row>
+    <row r="466" spans="18:18">
+      <c r="R466" s="12"/>
+    </row>
+    <row r="467" spans="18:18">
+      <c r="R467" s="12"/>
+    </row>
+    <row r="468" spans="18:18">
+      <c r="R468" s="12"/>
+    </row>
+    <row r="469" spans="18:18">
+      <c r="R469" s="12"/>
+    </row>
+    <row r="470" spans="18:18">
+      <c r="R470" s="12"/>
+    </row>
+    <row r="471" spans="18:18">
+      <c r="R471" s="12"/>
+    </row>
+    <row r="472" spans="18:18">
+      <c r="R472" s="12"/>
+    </row>
+    <row r="473" spans="18:18">
+      <c r="R473" s="12"/>
+    </row>
+    <row r="474" spans="18:18">
+      <c r="R474" s="12"/>
+    </row>
+    <row r="475" spans="18:18">
+      <c r="R475" s="12"/>
+    </row>
+    <row r="476" spans="18:18">
+      <c r="R476" s="12"/>
+    </row>
+    <row r="477" spans="18:18">
+      <c r="R477" s="12"/>
+    </row>
+    <row r="478" spans="18:18">
+      <c r="R478" s="12"/>
+    </row>
+    <row r="479" spans="18:18">
+      <c r="R479" s="12"/>
+    </row>
+    <row r="480" spans="18:18">
+      <c r="R480" s="12"/>
+    </row>
+    <row r="481" spans="18:18">
+      <c r="R481" s="12"/>
+    </row>
+    <row r="482" spans="18:18">
+      <c r="R482" s="12"/>
+    </row>
+    <row r="483" spans="18:18">
+      <c r="R483" s="12"/>
+    </row>
+    <row r="484" spans="18:18">
+      <c r="R484" s="12"/>
+    </row>
+    <row r="485" spans="18:18">
+      <c r="R485" s="12"/>
+    </row>
+    <row r="486" spans="18:18">
+      <c r="R486" s="12"/>
+    </row>
+    <row r="487" spans="18:18">
+      <c r="R487" s="12"/>
+    </row>
+    <row r="488" spans="18:18">
+      <c r="R488" s="12"/>
+    </row>
+    <row r="489" spans="18:18">
+      <c r="R489" s="12"/>
+    </row>
+    <row r="490" spans="18:18">
+      <c r="R490" s="12"/>
+    </row>
+    <row r="491" spans="18:18">
+      <c r="R491" s="12"/>
+    </row>
+    <row r="492" spans="18:18">
+      <c r="R492" s="12"/>
+    </row>
+    <row r="493" spans="18:18">
+      <c r="R493" s="12"/>
+    </row>
+    <row r="494" spans="18:18">
+      <c r="R494" s="12"/>
+    </row>
+    <row r="495" spans="18:18">
+      <c r="R495" s="12"/>
+    </row>
+    <row r="496" spans="18:18">
+      <c r="R496" s="12"/>
+    </row>
+    <row r="497" spans="18:18">
+      <c r="R497" s="12"/>
+    </row>
+    <row r="498" spans="18:18">
+      <c r="R498" s="12"/>
+    </row>
+    <row r="499" spans="18:18">
+      <c r="R499" s="12"/>
+    </row>
+    <row r="500" spans="18:18">
+      <c r="R500" s="12"/>
+    </row>
+    <row r="501" spans="18:18">
+      <c r="R501" s="12"/>
+    </row>
+    <row r="502" spans="18:18">
+      <c r="R502" s="12"/>
+    </row>
+    <row r="503" spans="18:18">
+      <c r="R503" s="12"/>
+    </row>
+    <row r="504" spans="18:18">
+      <c r="R504" s="12"/>
+    </row>
+    <row r="505" spans="18:18">
+      <c r="R505" s="12"/>
+    </row>
+    <row r="506" spans="18:18">
+      <c r="R506" s="12"/>
+    </row>
+    <row r="507" spans="18:18">
+      <c r="R507" s="12"/>
+    </row>
+    <row r="508" spans="18:18">
+      <c r="R508" s="12"/>
+    </row>
+    <row r="509" spans="18:18">
+      <c r="R509" s="12"/>
+    </row>
+    <row r="510" spans="18:18">
+      <c r="R510" s="12"/>
+    </row>
+    <row r="511" spans="18:18">
+      <c r="R511" s="12"/>
+    </row>
+    <row r="512" spans="18:18">
+      <c r="R512" s="12"/>
+    </row>
+    <row r="513" spans="18:18">
+      <c r="R513" s="12"/>
+    </row>
+    <row r="514" spans="18:18">
+      <c r="R514" s="12"/>
+    </row>
+    <row r="515" spans="18:18">
+      <c r="R515" s="12"/>
+    </row>
+    <row r="516" spans="18:18">
+      <c r="R516" s="12"/>
+    </row>
+    <row r="517" spans="18:18">
+      <c r="R517" s="12"/>
+    </row>
+    <row r="518" spans="18:18">
+      <c r="R518" s="12"/>
+    </row>
+    <row r="519" spans="18:18">
+      <c r="R519" s="12"/>
+    </row>
+    <row r="520" spans="18:18">
+      <c r="R520" s="12"/>
+    </row>
+    <row r="521" spans="18:18">
+      <c r="R521" s="12"/>
+    </row>
+    <row r="522" spans="18:18">
+      <c r="R522" s="12"/>
+    </row>
+    <row r="523" spans="18:18">
+      <c r="R523" s="12"/>
+    </row>
+    <row r="524" spans="18:18">
+      <c r="R524" s="12"/>
+    </row>
+    <row r="525" spans="18:18">
+      <c r="R525" s="12"/>
+    </row>
+    <row r="526" spans="18:18">
+      <c r="R526" s="12"/>
+    </row>
+    <row r="527" spans="18:18">
+      <c r="R527" s="12"/>
+    </row>
+    <row r="528" spans="18:18">
+      <c r="R528" s="12"/>
+    </row>
+    <row r="529" spans="18:18">
+      <c r="R529" s="12"/>
+    </row>
+    <row r="530" spans="18:18">
+      <c r="R530" s="12"/>
+    </row>
+    <row r="531" spans="18:18">
+      <c r="R531" s="12"/>
+    </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R530:R531" xr:uid="{709BC68A-C242-4787-A4C8-EA4F2DF4203E}">
+      <formula1>IF($O530="Tiktok", R530&lt;&gt;"", TRUE)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O6 O8:O1048576" xr:uid="{10C1B1BA-30A4-43AA-B6F4-A5F0B0F55982}">
+      <formula1>"Express, Tiktok"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S6 S8:S1048576" xr:uid="{F8BCA374-D361-4313-9C59-CF82877BB18A}">
+      <formula1>", YES, NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6 Q8:Q1048576" xr:uid="{16DEDA22-1651-49B2-AAF1-65C50FFEDD2D}">
+      <formula1>"YES, NO"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="R2:R6 R8:R529" xr:uid="{AB023EC7-7443-46B0-A956-FA2A83A11DFD}">
+      <formula1>IF($O2="Tiktok", R2&lt;&gt;"", TRUE)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/public/Ananbay_template.xlsx
+++ b/public/Ananbay_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\TebGroup\teb-express-tunghoang\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B175DCA8-7116-4B2F-AA89-04222F9CE259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283DEACE-114F-40F0-B70E-CCF220E14BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="46">
   <si>
     <t>Tên người nhận</t>
   </si>
@@ -194,9 +194,6 @@
     <t>Express</t>
   </si>
   <si>
-    <t>Tiktok</t>
-  </si>
-  <si>
     <t>Jennifer Brown</t>
   </si>
   <si>
@@ -215,13 +212,16 @@
     <t>321186906</t>
   </si>
   <si>
-    <t>Code3</t>
-  </si>
-  <si>
-    <t>OG2123122</t>
-  </si>
-  <si>
-    <t>12312312331</t>
+    <t>https://s3-fsg-1.fecom.io/labels1/0a4ba38c-dbda-4e30-a1fd-example.pdf</t>
+  </si>
+  <si>
+    <t>https://seller-us.tiktok.com/wsos_v2/oec_fulfillment_doc_tts/object/wsos67e648f023c08b2b?expire=1743231678&amp;skipCookie=true&amp;timeStamp=1743145278&amp;sign=ec6024dfc8a63c6ee6d987234503f0f730fe44c15cc06b2757363a40d2a2c9b4</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HvxQsXIGeox-XxargWYcAHVeKAHanxGI/view</t>
+  </si>
+  <si>
+    <t>Ship By Tiktok</t>
   </si>
 </sst>
 </file>
@@ -231,7 +231,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General\,"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -286,6 +286,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -325,10 +332,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -356,8 +364,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -743,7 +753,7 @@
         <v>24</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>25</v>
@@ -796,7 +806,7 @@
         <v>24</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>25</v>
@@ -817,7 +827,12 @@
         <v>35</v>
       </c>
       <c r="P3" s="10"/>
-      <c r="R3" s="12"/>
+      <c r="R3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="14" t="s">
+        <v>31</v>
+      </c>
       <c r="T3" t="s">
         <v>30</v>
       </c>
@@ -830,7 +845,7 @@
     </row>
     <row r="4" spans="1:22" ht="15.6" customHeight="1" thickBot="1">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>27</v>
@@ -849,7 +864,7 @@
         <v>24</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>25</v>
@@ -867,10 +882,10 @@
         <v>3</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="R4" s="15" t="s">
+        <v>42</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>31</v>
@@ -887,7 +902,7 @@
     </row>
     <row r="5" spans="1:22" ht="15.6" customHeight="1" thickBot="1">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>27</v>
@@ -906,7 +921,7 @@
         <v>24</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>25</v>
@@ -924,10 +939,10 @@
         <v>3</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="S5" s="14" t="s">
         <v>32</v>
@@ -944,7 +959,7 @@
     </row>
     <row r="6" spans="1:22" ht="16.8" customHeight="1" thickBot="1">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>27</v>
@@ -963,7 +978,7 @@
         <v>24</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>25</v>
@@ -981,10 +996,13 @@
         <v>3</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" s="12" t="s">
         <v>45</v>
+      </c>
+      <c r="R6" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="S6" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="T6" t="s">
         <v>30</v>
@@ -996,1567 +1014,2084 @@
         <v>12</v>
       </c>
     </row>
+    <row r="7" spans="1:22">
+      <c r="O7" s="7"/>
+    </row>
     <row r="8" spans="1:22">
+      <c r="O8" s="7"/>
       <c r="R8" s="12"/>
     </row>
     <row r="9" spans="1:22">
+      <c r="O9" s="7"/>
       <c r="R9" s="12"/>
     </row>
     <row r="10" spans="1:22">
+      <c r="O10" s="7"/>
       <c r="R10" s="12"/>
     </row>
     <row r="11" spans="1:22">
+      <c r="O11" s="7"/>
       <c r="R11" s="12"/>
     </row>
     <row r="12" spans="1:22">
+      <c r="O12" s="7"/>
       <c r="R12" s="12"/>
     </row>
     <row r="13" spans="1:22">
+      <c r="O13" s="7"/>
       <c r="R13" s="12"/>
     </row>
     <row r="14" spans="1:22">
+      <c r="O14" s="7"/>
       <c r="R14" s="12"/>
     </row>
     <row r="15" spans="1:22">
+      <c r="O15" s="7"/>
       <c r="R15" s="12"/>
     </row>
     <row r="16" spans="1:22">
+      <c r="O16" s="7"/>
       <c r="R16" s="12"/>
     </row>
-    <row r="17" spans="18:18">
+    <row r="17" spans="15:18">
+      <c r="O17" s="7"/>
       <c r="R17" s="12"/>
     </row>
-    <row r="18" spans="18:18">
+    <row r="18" spans="15:18">
+      <c r="O18" s="7"/>
       <c r="R18" s="12"/>
     </row>
-    <row r="19" spans="18:18">
+    <row r="19" spans="15:18">
+      <c r="O19" s="7"/>
       <c r="R19" s="12"/>
     </row>
-    <row r="20" spans="18:18">
+    <row r="20" spans="15:18">
+      <c r="O20" s="7"/>
       <c r="R20" s="12"/>
     </row>
-    <row r="21" spans="18:18">
+    <row r="21" spans="15:18">
+      <c r="O21" s="7"/>
       <c r="R21" s="12"/>
     </row>
-    <row r="22" spans="18:18">
+    <row r="22" spans="15:18">
+      <c r="O22" s="7"/>
       <c r="R22" s="12"/>
     </row>
-    <row r="23" spans="18:18">
+    <row r="23" spans="15:18">
+      <c r="O23" s="7"/>
       <c r="R23" s="12"/>
     </row>
-    <row r="24" spans="18:18">
+    <row r="24" spans="15:18">
+      <c r="O24" s="7"/>
       <c r="R24" s="12"/>
     </row>
-    <row r="25" spans="18:18">
+    <row r="25" spans="15:18">
+      <c r="O25" s="7"/>
       <c r="R25" s="12"/>
     </row>
-    <row r="26" spans="18:18">
+    <row r="26" spans="15:18">
+      <c r="O26" s="7"/>
       <c r="R26" s="12"/>
     </row>
-    <row r="27" spans="18:18">
+    <row r="27" spans="15:18">
+      <c r="O27" s="7"/>
       <c r="R27" s="12"/>
     </row>
-    <row r="28" spans="18:18">
+    <row r="28" spans="15:18">
+      <c r="O28" s="7"/>
       <c r="R28" s="12"/>
     </row>
-    <row r="29" spans="18:18">
+    <row r="29" spans="15:18">
+      <c r="O29" s="7"/>
       <c r="R29" s="12"/>
     </row>
-    <row r="30" spans="18:18">
+    <row r="30" spans="15:18">
+      <c r="O30" s="7"/>
       <c r="R30" s="12"/>
     </row>
-    <row r="31" spans="18:18">
+    <row r="31" spans="15:18">
+      <c r="O31" s="7"/>
       <c r="R31" s="12"/>
     </row>
-    <row r="32" spans="18:18">
+    <row r="32" spans="15:18">
+      <c r="O32" s="7"/>
       <c r="R32" s="12"/>
     </row>
-    <row r="33" spans="18:18">
+    <row r="33" spans="15:18">
+      <c r="O33" s="7"/>
       <c r="R33" s="12"/>
     </row>
-    <row r="34" spans="18:18">
+    <row r="34" spans="15:18">
+      <c r="O34" s="7"/>
       <c r="R34" s="12"/>
     </row>
-    <row r="35" spans="18:18">
+    <row r="35" spans="15:18">
+      <c r="O35" s="7"/>
       <c r="R35" s="12"/>
     </row>
-    <row r="36" spans="18:18">
+    <row r="36" spans="15:18">
+      <c r="O36" s="7"/>
       <c r="R36" s="12"/>
     </row>
-    <row r="37" spans="18:18">
+    <row r="37" spans="15:18">
+      <c r="O37" s="7"/>
       <c r="R37" s="12"/>
     </row>
-    <row r="38" spans="18:18">
+    <row r="38" spans="15:18">
+      <c r="O38" s="7"/>
       <c r="R38" s="12"/>
     </row>
-    <row r="39" spans="18:18">
+    <row r="39" spans="15:18">
+      <c r="O39" s="7"/>
       <c r="R39" s="12"/>
     </row>
-    <row r="40" spans="18:18">
+    <row r="40" spans="15:18">
+      <c r="O40" s="7"/>
       <c r="R40" s="12"/>
     </row>
-    <row r="41" spans="18:18">
+    <row r="41" spans="15:18">
+      <c r="O41" s="7"/>
       <c r="R41" s="12"/>
     </row>
-    <row r="42" spans="18:18">
+    <row r="42" spans="15:18">
+      <c r="O42" s="7"/>
       <c r="R42" s="12"/>
     </row>
-    <row r="43" spans="18:18">
+    <row r="43" spans="15:18">
+      <c r="O43" s="7"/>
       <c r="R43" s="12"/>
     </row>
-    <row r="44" spans="18:18">
+    <row r="44" spans="15:18">
+      <c r="O44" s="7"/>
       <c r="R44" s="12"/>
     </row>
-    <row r="45" spans="18:18">
+    <row r="45" spans="15:18">
+      <c r="O45" s="7"/>
       <c r="R45" s="12"/>
     </row>
-    <row r="46" spans="18:18">
+    <row r="46" spans="15:18">
+      <c r="O46" s="7"/>
       <c r="R46" s="12"/>
     </row>
-    <row r="47" spans="18:18">
+    <row r="47" spans="15:18">
+      <c r="O47" s="7"/>
       <c r="R47" s="12"/>
     </row>
-    <row r="48" spans="18:18">
+    <row r="48" spans="15:18">
+      <c r="O48" s="7"/>
       <c r="R48" s="12"/>
     </row>
-    <row r="49" spans="18:18">
+    <row r="49" spans="15:18">
+      <c r="O49" s="7"/>
       <c r="R49" s="12"/>
     </row>
-    <row r="50" spans="18:18">
+    <row r="50" spans="15:18">
+      <c r="O50" s="7"/>
       <c r="R50" s="12"/>
     </row>
-    <row r="51" spans="18:18">
+    <row r="51" spans="15:18">
+      <c r="O51" s="7"/>
       <c r="R51" s="12"/>
     </row>
-    <row r="52" spans="18:18">
+    <row r="52" spans="15:18">
+      <c r="O52" s="7"/>
       <c r="R52" s="12"/>
     </row>
-    <row r="53" spans="18:18">
+    <row r="53" spans="15:18">
+      <c r="O53" s="7"/>
       <c r="R53" s="12"/>
     </row>
-    <row r="54" spans="18:18">
+    <row r="54" spans="15:18">
+      <c r="O54" s="7"/>
       <c r="R54" s="12"/>
     </row>
-    <row r="55" spans="18:18">
+    <row r="55" spans="15:18">
+      <c r="O55" s="7"/>
       <c r="R55" s="12"/>
     </row>
-    <row r="56" spans="18:18">
+    <row r="56" spans="15:18">
+      <c r="O56" s="7"/>
       <c r="R56" s="12"/>
     </row>
-    <row r="57" spans="18:18">
+    <row r="57" spans="15:18">
+      <c r="O57" s="7"/>
       <c r="R57" s="12"/>
     </row>
-    <row r="58" spans="18:18">
+    <row r="58" spans="15:18">
+      <c r="O58" s="7"/>
       <c r="R58" s="12"/>
     </row>
-    <row r="59" spans="18:18">
+    <row r="59" spans="15:18">
+      <c r="O59" s="7"/>
       <c r="R59" s="12"/>
     </row>
-    <row r="60" spans="18:18">
+    <row r="60" spans="15:18">
+      <c r="O60" s="7"/>
       <c r="R60" s="12"/>
     </row>
-    <row r="61" spans="18:18">
+    <row r="61" spans="15:18">
+      <c r="O61" s="7"/>
       <c r="R61" s="12"/>
     </row>
-    <row r="62" spans="18:18">
+    <row r="62" spans="15:18">
+      <c r="O62" s="7"/>
       <c r="R62" s="12"/>
     </row>
-    <row r="63" spans="18:18">
+    <row r="63" spans="15:18">
+      <c r="O63" s="7"/>
       <c r="R63" s="12"/>
     </row>
-    <row r="64" spans="18:18">
+    <row r="64" spans="15:18">
+      <c r="O64" s="7"/>
       <c r="R64" s="12"/>
     </row>
-    <row r="65" spans="18:18">
+    <row r="65" spans="15:18">
+      <c r="O65" s="7"/>
       <c r="R65" s="12"/>
     </row>
-    <row r="66" spans="18:18">
+    <row r="66" spans="15:18">
+      <c r="O66" s="7"/>
       <c r="R66" s="12"/>
     </row>
-    <row r="67" spans="18:18">
+    <row r="67" spans="15:18">
+      <c r="O67" s="7"/>
       <c r="R67" s="12"/>
     </row>
-    <row r="68" spans="18:18">
+    <row r="68" spans="15:18">
+      <c r="O68" s="7"/>
       <c r="R68" s="12"/>
     </row>
-    <row r="69" spans="18:18">
+    <row r="69" spans="15:18">
+      <c r="O69" s="7"/>
       <c r="R69" s="12"/>
     </row>
-    <row r="70" spans="18:18">
+    <row r="70" spans="15:18">
+      <c r="O70" s="7"/>
       <c r="R70" s="12"/>
     </row>
-    <row r="71" spans="18:18">
+    <row r="71" spans="15:18">
+      <c r="O71" s="7"/>
       <c r="R71" s="12"/>
     </row>
-    <row r="72" spans="18:18">
+    <row r="72" spans="15:18">
+      <c r="O72" s="7"/>
       <c r="R72" s="12"/>
     </row>
-    <row r="73" spans="18:18">
+    <row r="73" spans="15:18">
+      <c r="O73" s="7"/>
       <c r="R73" s="12"/>
     </row>
-    <row r="74" spans="18:18">
+    <row r="74" spans="15:18">
+      <c r="O74" s="7"/>
       <c r="R74" s="12"/>
     </row>
-    <row r="75" spans="18:18">
+    <row r="75" spans="15:18">
+      <c r="O75" s="7"/>
       <c r="R75" s="12"/>
     </row>
-    <row r="76" spans="18:18">
+    <row r="76" spans="15:18">
+      <c r="O76" s="7"/>
       <c r="R76" s="12"/>
     </row>
-    <row r="77" spans="18:18">
+    <row r="77" spans="15:18">
+      <c r="O77" s="7"/>
       <c r="R77" s="12"/>
     </row>
-    <row r="78" spans="18:18">
+    <row r="78" spans="15:18">
+      <c r="O78" s="7"/>
       <c r="R78" s="12"/>
     </row>
-    <row r="79" spans="18:18">
+    <row r="79" spans="15:18">
+      <c r="O79" s="7"/>
       <c r="R79" s="12"/>
     </row>
-    <row r="80" spans="18:18">
+    <row r="80" spans="15:18">
+      <c r="O80" s="7"/>
       <c r="R80" s="12"/>
     </row>
-    <row r="81" spans="18:18">
+    <row r="81" spans="15:18">
+      <c r="O81" s="7"/>
       <c r="R81" s="12"/>
     </row>
-    <row r="82" spans="18:18">
+    <row r="82" spans="15:18">
+      <c r="O82" s="7"/>
       <c r="R82" s="12"/>
     </row>
-    <row r="83" spans="18:18">
+    <row r="83" spans="15:18">
+      <c r="O83" s="7"/>
       <c r="R83" s="12"/>
     </row>
-    <row r="84" spans="18:18">
+    <row r="84" spans="15:18">
+      <c r="O84" s="7"/>
       <c r="R84" s="12"/>
     </row>
-    <row r="85" spans="18:18">
+    <row r="85" spans="15:18">
+      <c r="O85" s="7"/>
       <c r="R85" s="12"/>
     </row>
-    <row r="86" spans="18:18">
+    <row r="86" spans="15:18">
+      <c r="O86" s="7"/>
       <c r="R86" s="12"/>
     </row>
-    <row r="87" spans="18:18">
+    <row r="87" spans="15:18">
+      <c r="O87" s="7"/>
       <c r="R87" s="12"/>
     </row>
-    <row r="88" spans="18:18">
+    <row r="88" spans="15:18">
+      <c r="O88" s="7"/>
       <c r="R88" s="12"/>
     </row>
-    <row r="89" spans="18:18">
+    <row r="89" spans="15:18">
+      <c r="O89" s="7"/>
       <c r="R89" s="12"/>
     </row>
-    <row r="90" spans="18:18">
+    <row r="90" spans="15:18">
+      <c r="O90" s="7"/>
       <c r="R90" s="12"/>
     </row>
-    <row r="91" spans="18:18">
+    <row r="91" spans="15:18">
+      <c r="O91" s="7"/>
       <c r="R91" s="12"/>
     </row>
-    <row r="92" spans="18:18">
+    <row r="92" spans="15:18">
+      <c r="O92" s="7"/>
       <c r="R92" s="12"/>
     </row>
-    <row r="93" spans="18:18">
+    <row r="93" spans="15:18">
+      <c r="O93" s="7"/>
       <c r="R93" s="12"/>
     </row>
-    <row r="94" spans="18:18">
+    <row r="94" spans="15:18">
+      <c r="O94" s="7"/>
       <c r="R94" s="12"/>
     </row>
-    <row r="95" spans="18:18">
+    <row r="95" spans="15:18">
+      <c r="O95" s="7"/>
       <c r="R95" s="12"/>
     </row>
-    <row r="96" spans="18:18">
+    <row r="96" spans="15:18">
+      <c r="O96" s="7"/>
       <c r="R96" s="12"/>
     </row>
-    <row r="97" spans="18:18">
+    <row r="97" spans="15:18">
+      <c r="O97" s="7"/>
       <c r="R97" s="12"/>
     </row>
-    <row r="98" spans="18:18">
+    <row r="98" spans="15:18">
+      <c r="O98" s="7"/>
       <c r="R98" s="12"/>
     </row>
-    <row r="99" spans="18:18">
+    <row r="99" spans="15:18">
+      <c r="O99" s="7"/>
       <c r="R99" s="12"/>
     </row>
-    <row r="100" spans="18:18">
+    <row r="100" spans="15:18">
+      <c r="O100" s="7"/>
       <c r="R100" s="12"/>
     </row>
-    <row r="101" spans="18:18">
+    <row r="101" spans="15:18">
+      <c r="O101" s="7"/>
       <c r="R101" s="12"/>
     </row>
-    <row r="102" spans="18:18">
+    <row r="102" spans="15:18">
+      <c r="O102" s="7"/>
       <c r="R102" s="12"/>
     </row>
-    <row r="103" spans="18:18">
+    <row r="103" spans="15:18">
+      <c r="O103" s="7"/>
       <c r="R103" s="12"/>
     </row>
-    <row r="104" spans="18:18">
+    <row r="104" spans="15:18">
+      <c r="O104" s="7"/>
       <c r="R104" s="12"/>
     </row>
-    <row r="105" spans="18:18">
+    <row r="105" spans="15:18">
+      <c r="O105" s="7"/>
       <c r="R105" s="12"/>
     </row>
-    <row r="106" spans="18:18">
+    <row r="106" spans="15:18">
+      <c r="O106" s="7"/>
       <c r="R106" s="12"/>
     </row>
-    <row r="107" spans="18:18">
+    <row r="107" spans="15:18">
+      <c r="O107" s="7"/>
       <c r="R107" s="12"/>
     </row>
-    <row r="108" spans="18:18">
+    <row r="108" spans="15:18">
+      <c r="O108" s="7"/>
       <c r="R108" s="12"/>
     </row>
-    <row r="109" spans="18:18">
+    <row r="109" spans="15:18">
+      <c r="O109" s="7"/>
       <c r="R109" s="12"/>
     </row>
-    <row r="110" spans="18:18">
+    <row r="110" spans="15:18">
+      <c r="O110" s="7"/>
       <c r="R110" s="12"/>
     </row>
-    <row r="111" spans="18:18">
+    <row r="111" spans="15:18">
+      <c r="O111" s="7"/>
       <c r="R111" s="12"/>
     </row>
-    <row r="112" spans="18:18">
+    <row r="112" spans="15:18">
+      <c r="O112" s="7"/>
       <c r="R112" s="12"/>
     </row>
-    <row r="113" spans="18:18">
+    <row r="113" spans="15:18">
+      <c r="O113" s="7"/>
       <c r="R113" s="12"/>
     </row>
-    <row r="114" spans="18:18">
+    <row r="114" spans="15:18">
+      <c r="O114" s="7"/>
       <c r="R114" s="12"/>
     </row>
-    <row r="115" spans="18:18">
+    <row r="115" spans="15:18">
+      <c r="O115" s="7"/>
       <c r="R115" s="12"/>
     </row>
-    <row r="116" spans="18:18">
+    <row r="116" spans="15:18">
+      <c r="O116" s="7"/>
       <c r="R116" s="12"/>
     </row>
-    <row r="117" spans="18:18">
+    <row r="117" spans="15:18">
+      <c r="O117" s="7"/>
       <c r="R117" s="12"/>
     </row>
-    <row r="118" spans="18:18">
+    <row r="118" spans="15:18">
+      <c r="O118" s="7"/>
       <c r="R118" s="12"/>
     </row>
-    <row r="119" spans="18:18">
+    <row r="119" spans="15:18">
+      <c r="O119" s="7"/>
       <c r="R119" s="12"/>
     </row>
-    <row r="120" spans="18:18">
+    <row r="120" spans="15:18">
+      <c r="O120" s="7"/>
       <c r="R120" s="12"/>
     </row>
-    <row r="121" spans="18:18">
+    <row r="121" spans="15:18">
+      <c r="O121" s="7"/>
       <c r="R121" s="12"/>
     </row>
-    <row r="122" spans="18:18">
+    <row r="122" spans="15:18">
+      <c r="O122" s="7"/>
       <c r="R122" s="12"/>
     </row>
-    <row r="123" spans="18:18">
+    <row r="123" spans="15:18">
+      <c r="O123" s="7"/>
       <c r="R123" s="12"/>
     </row>
-    <row r="124" spans="18:18">
+    <row r="124" spans="15:18">
+      <c r="O124" s="7"/>
       <c r="R124" s="12"/>
     </row>
-    <row r="125" spans="18:18">
+    <row r="125" spans="15:18">
+      <c r="O125" s="7"/>
       <c r="R125" s="12"/>
     </row>
-    <row r="126" spans="18:18">
+    <row r="126" spans="15:18">
+      <c r="O126" s="7"/>
       <c r="R126" s="12"/>
     </row>
-    <row r="127" spans="18:18">
+    <row r="127" spans="15:18">
+      <c r="O127" s="7"/>
       <c r="R127" s="12"/>
     </row>
-    <row r="128" spans="18:18">
+    <row r="128" spans="15:18">
+      <c r="O128" s="7"/>
       <c r="R128" s="12"/>
     </row>
-    <row r="129" spans="18:18">
+    <row r="129" spans="15:18">
+      <c r="O129" s="7"/>
       <c r="R129" s="12"/>
     </row>
-    <row r="130" spans="18:18">
+    <row r="130" spans="15:18">
+      <c r="O130" s="7"/>
       <c r="R130" s="12"/>
     </row>
-    <row r="131" spans="18:18">
+    <row r="131" spans="15:18">
+      <c r="O131" s="7"/>
       <c r="R131" s="12"/>
     </row>
-    <row r="132" spans="18:18">
+    <row r="132" spans="15:18">
+      <c r="O132" s="7"/>
       <c r="R132" s="12"/>
     </row>
-    <row r="133" spans="18:18">
+    <row r="133" spans="15:18">
+      <c r="O133" s="7"/>
       <c r="R133" s="12"/>
     </row>
-    <row r="134" spans="18:18">
+    <row r="134" spans="15:18">
+      <c r="O134" s="7"/>
       <c r="R134" s="12"/>
     </row>
-    <row r="135" spans="18:18">
+    <row r="135" spans="15:18">
+      <c r="O135" s="7"/>
       <c r="R135" s="12"/>
     </row>
-    <row r="136" spans="18:18">
+    <row r="136" spans="15:18">
+      <c r="O136" s="7"/>
       <c r="R136" s="12"/>
     </row>
-    <row r="137" spans="18:18">
+    <row r="137" spans="15:18">
+      <c r="O137" s="7"/>
       <c r="R137" s="12"/>
     </row>
-    <row r="138" spans="18:18">
+    <row r="138" spans="15:18">
+      <c r="O138" s="7"/>
       <c r="R138" s="12"/>
     </row>
-    <row r="139" spans="18:18">
+    <row r="139" spans="15:18">
+      <c r="O139" s="7"/>
       <c r="R139" s="12"/>
     </row>
-    <row r="140" spans="18:18">
+    <row r="140" spans="15:18">
+      <c r="O140" s="7"/>
       <c r="R140" s="12"/>
     </row>
-    <row r="141" spans="18:18">
+    <row r="141" spans="15:18">
+      <c r="O141" s="7"/>
       <c r="R141" s="12"/>
     </row>
-    <row r="142" spans="18:18">
+    <row r="142" spans="15:18">
+      <c r="O142" s="7"/>
       <c r="R142" s="12"/>
     </row>
-    <row r="143" spans="18:18">
+    <row r="143" spans="15:18">
+      <c r="O143" s="7"/>
       <c r="R143" s="12"/>
     </row>
-    <row r="144" spans="18:18">
+    <row r="144" spans="15:18">
+      <c r="O144" s="7"/>
       <c r="R144" s="12"/>
     </row>
-    <row r="145" spans="18:18">
+    <row r="145" spans="15:18">
+      <c r="O145" s="7"/>
       <c r="R145" s="12"/>
     </row>
-    <row r="146" spans="18:18">
+    <row r="146" spans="15:18">
+      <c r="O146" s="7"/>
       <c r="R146" s="12"/>
     </row>
-    <row r="147" spans="18:18">
+    <row r="147" spans="15:18">
+      <c r="O147" s="7"/>
       <c r="R147" s="12"/>
     </row>
-    <row r="148" spans="18:18">
+    <row r="148" spans="15:18">
+      <c r="O148" s="7"/>
       <c r="R148" s="12"/>
     </row>
-    <row r="149" spans="18:18">
+    <row r="149" spans="15:18">
+      <c r="O149" s="7"/>
       <c r="R149" s="12"/>
     </row>
-    <row r="150" spans="18:18">
+    <row r="150" spans="15:18">
+      <c r="O150" s="7"/>
       <c r="R150" s="12"/>
     </row>
-    <row r="151" spans="18:18">
+    <row r="151" spans="15:18">
+      <c r="O151" s="7"/>
       <c r="R151" s="12"/>
     </row>
-    <row r="152" spans="18:18">
+    <row r="152" spans="15:18">
+      <c r="O152" s="7"/>
       <c r="R152" s="12"/>
     </row>
-    <row r="153" spans="18:18">
+    <row r="153" spans="15:18">
+      <c r="O153" s="7"/>
       <c r="R153" s="12"/>
     </row>
-    <row r="154" spans="18:18">
+    <row r="154" spans="15:18">
+      <c r="O154" s="7"/>
       <c r="R154" s="12"/>
     </row>
-    <row r="155" spans="18:18">
+    <row r="155" spans="15:18">
+      <c r="O155" s="7"/>
       <c r="R155" s="12"/>
     </row>
-    <row r="156" spans="18:18">
+    <row r="156" spans="15:18">
+      <c r="O156" s="7"/>
       <c r="R156" s="12"/>
     </row>
-    <row r="157" spans="18:18">
+    <row r="157" spans="15:18">
+      <c r="O157" s="7"/>
       <c r="R157" s="12"/>
     </row>
-    <row r="158" spans="18:18">
+    <row r="158" spans="15:18">
+      <c r="O158" s="7"/>
       <c r="R158" s="12"/>
     </row>
-    <row r="159" spans="18:18">
+    <row r="159" spans="15:18">
+      <c r="O159" s="7"/>
       <c r="R159" s="12"/>
     </row>
-    <row r="160" spans="18:18">
+    <row r="160" spans="15:18">
+      <c r="O160" s="7"/>
       <c r="R160" s="12"/>
     </row>
-    <row r="161" spans="18:18">
+    <row r="161" spans="15:18">
+      <c r="O161" s="7"/>
       <c r="R161" s="12"/>
     </row>
-    <row r="162" spans="18:18">
+    <row r="162" spans="15:18">
+      <c r="O162" s="7"/>
       <c r="R162" s="12"/>
     </row>
-    <row r="163" spans="18:18">
+    <row r="163" spans="15:18">
+      <c r="O163" s="7"/>
       <c r="R163" s="12"/>
     </row>
-    <row r="164" spans="18:18">
+    <row r="164" spans="15:18">
+      <c r="O164" s="7"/>
       <c r="R164" s="12"/>
     </row>
-    <row r="165" spans="18:18">
+    <row r="165" spans="15:18">
+      <c r="O165" s="7"/>
       <c r="R165" s="12"/>
     </row>
-    <row r="166" spans="18:18">
+    <row r="166" spans="15:18">
+      <c r="O166" s="7"/>
       <c r="R166" s="12"/>
     </row>
-    <row r="167" spans="18:18">
+    <row r="167" spans="15:18">
+      <c r="O167" s="7"/>
       <c r="R167" s="12"/>
     </row>
-    <row r="168" spans="18:18">
+    <row r="168" spans="15:18">
+      <c r="O168" s="7"/>
       <c r="R168" s="12"/>
     </row>
-    <row r="169" spans="18:18">
+    <row r="169" spans="15:18">
+      <c r="O169" s="7"/>
       <c r="R169" s="12"/>
     </row>
-    <row r="170" spans="18:18">
+    <row r="170" spans="15:18">
+      <c r="O170" s="7"/>
       <c r="R170" s="12"/>
     </row>
-    <row r="171" spans="18:18">
+    <row r="171" spans="15:18">
+      <c r="O171" s="7"/>
       <c r="R171" s="12"/>
     </row>
-    <row r="172" spans="18:18">
+    <row r="172" spans="15:18">
+      <c r="O172" s="7"/>
       <c r="R172" s="12"/>
     </row>
-    <row r="173" spans="18:18">
+    <row r="173" spans="15:18">
+      <c r="O173" s="7"/>
       <c r="R173" s="12"/>
     </row>
-    <row r="174" spans="18:18">
+    <row r="174" spans="15:18">
+      <c r="O174" s="7"/>
       <c r="R174" s="12"/>
     </row>
-    <row r="175" spans="18:18">
+    <row r="175" spans="15:18">
+      <c r="O175" s="7"/>
       <c r="R175" s="12"/>
     </row>
-    <row r="176" spans="18:18">
+    <row r="176" spans="15:18">
+      <c r="O176" s="7"/>
       <c r="R176" s="12"/>
     </row>
-    <row r="177" spans="18:18">
+    <row r="177" spans="15:18">
+      <c r="O177" s="7"/>
       <c r="R177" s="12"/>
     </row>
-    <row r="178" spans="18:18">
+    <row r="178" spans="15:18">
+      <c r="O178" s="7"/>
       <c r="R178" s="12"/>
     </row>
-    <row r="179" spans="18:18">
+    <row r="179" spans="15:18">
+      <c r="O179" s="7"/>
       <c r="R179" s="12"/>
     </row>
-    <row r="180" spans="18:18">
+    <row r="180" spans="15:18">
+      <c r="O180" s="7"/>
       <c r="R180" s="12"/>
     </row>
-    <row r="181" spans="18:18">
+    <row r="181" spans="15:18">
+      <c r="O181" s="7"/>
       <c r="R181" s="12"/>
     </row>
-    <row r="182" spans="18:18">
+    <row r="182" spans="15:18">
+      <c r="O182" s="7"/>
       <c r="R182" s="12"/>
     </row>
-    <row r="183" spans="18:18">
+    <row r="183" spans="15:18">
+      <c r="O183" s="7"/>
       <c r="R183" s="12"/>
     </row>
-    <row r="184" spans="18:18">
+    <row r="184" spans="15:18">
+      <c r="O184" s="7"/>
       <c r="R184" s="12"/>
     </row>
-    <row r="185" spans="18:18">
+    <row r="185" spans="15:18">
+      <c r="O185" s="7"/>
       <c r="R185" s="12"/>
     </row>
-    <row r="186" spans="18:18">
+    <row r="186" spans="15:18">
+      <c r="O186" s="7"/>
       <c r="R186" s="12"/>
     </row>
-    <row r="187" spans="18:18">
+    <row r="187" spans="15:18">
+      <c r="O187" s="7"/>
       <c r="R187" s="12"/>
     </row>
-    <row r="188" spans="18:18">
+    <row r="188" spans="15:18">
+      <c r="O188" s="7"/>
       <c r="R188" s="12"/>
     </row>
-    <row r="189" spans="18:18">
+    <row r="189" spans="15:18">
+      <c r="O189" s="7"/>
       <c r="R189" s="12"/>
     </row>
-    <row r="190" spans="18:18">
+    <row r="190" spans="15:18">
+      <c r="O190" s="7"/>
       <c r="R190" s="12"/>
     </row>
-    <row r="191" spans="18:18">
+    <row r="191" spans="15:18">
+      <c r="O191" s="7"/>
       <c r="R191" s="12"/>
     </row>
-    <row r="192" spans="18:18">
+    <row r="192" spans="15:18">
+      <c r="O192" s="7"/>
       <c r="R192" s="12"/>
     </row>
-    <row r="193" spans="18:18">
+    <row r="193" spans="15:18">
+      <c r="O193" s="7"/>
       <c r="R193" s="12"/>
     </row>
-    <row r="194" spans="18:18">
+    <row r="194" spans="15:18">
+      <c r="O194" s="7"/>
       <c r="R194" s="12"/>
     </row>
-    <row r="195" spans="18:18">
+    <row r="195" spans="15:18">
+      <c r="O195" s="7"/>
       <c r="R195" s="12"/>
     </row>
-    <row r="196" spans="18:18">
+    <row r="196" spans="15:18">
+      <c r="O196" s="7"/>
       <c r="R196" s="12"/>
     </row>
-    <row r="197" spans="18:18">
+    <row r="197" spans="15:18">
+      <c r="O197" s="7"/>
       <c r="R197" s="12"/>
     </row>
-    <row r="198" spans="18:18">
+    <row r="198" spans="15:18">
+      <c r="O198" s="7"/>
       <c r="R198" s="12"/>
     </row>
-    <row r="199" spans="18:18">
+    <row r="199" spans="15:18">
+      <c r="O199" s="7"/>
       <c r="R199" s="12"/>
     </row>
-    <row r="200" spans="18:18">
+    <row r="200" spans="15:18">
+      <c r="O200" s="7"/>
       <c r="R200" s="12"/>
     </row>
-    <row r="201" spans="18:18">
+    <row r="201" spans="15:18">
+      <c r="O201" s="7"/>
       <c r="R201" s="12"/>
     </row>
-    <row r="202" spans="18:18">
+    <row r="202" spans="15:18">
+      <c r="O202" s="7"/>
       <c r="R202" s="12"/>
     </row>
-    <row r="203" spans="18:18">
+    <row r="203" spans="15:18">
+      <c r="O203" s="7"/>
       <c r="R203" s="12"/>
     </row>
-    <row r="204" spans="18:18">
+    <row r="204" spans="15:18">
+      <c r="O204" s="7"/>
       <c r="R204" s="12"/>
     </row>
-    <row r="205" spans="18:18">
+    <row r="205" spans="15:18">
+      <c r="O205" s="7"/>
       <c r="R205" s="12"/>
     </row>
-    <row r="206" spans="18:18">
+    <row r="206" spans="15:18">
+      <c r="O206" s="7"/>
       <c r="R206" s="12"/>
     </row>
-    <row r="207" spans="18:18">
+    <row r="207" spans="15:18">
+      <c r="O207" s="7"/>
       <c r="R207" s="12"/>
     </row>
-    <row r="208" spans="18:18">
+    <row r="208" spans="15:18">
+      <c r="O208" s="7"/>
       <c r="R208" s="12"/>
     </row>
-    <row r="209" spans="18:18">
+    <row r="209" spans="15:18">
+      <c r="O209" s="7"/>
       <c r="R209" s="12"/>
     </row>
-    <row r="210" spans="18:18">
+    <row r="210" spans="15:18">
+      <c r="O210" s="7"/>
       <c r="R210" s="12"/>
     </row>
-    <row r="211" spans="18:18">
+    <row r="211" spans="15:18">
+      <c r="O211" s="7"/>
       <c r="R211" s="12"/>
     </row>
-    <row r="212" spans="18:18">
+    <row r="212" spans="15:18">
+      <c r="O212" s="7"/>
       <c r="R212" s="12"/>
     </row>
-    <row r="213" spans="18:18">
+    <row r="213" spans="15:18">
+      <c r="O213" s="7"/>
       <c r="R213" s="12"/>
     </row>
-    <row r="214" spans="18:18">
+    <row r="214" spans="15:18">
+      <c r="O214" s="7"/>
       <c r="R214" s="12"/>
     </row>
-    <row r="215" spans="18:18">
+    <row r="215" spans="15:18">
+      <c r="O215" s="7"/>
       <c r="R215" s="12"/>
     </row>
-    <row r="216" spans="18:18">
+    <row r="216" spans="15:18">
+      <c r="O216" s="7"/>
       <c r="R216" s="12"/>
     </row>
-    <row r="217" spans="18:18">
+    <row r="217" spans="15:18">
+      <c r="O217" s="7"/>
       <c r="R217" s="12"/>
     </row>
-    <row r="218" spans="18:18">
+    <row r="218" spans="15:18">
+      <c r="O218" s="7"/>
       <c r="R218" s="12"/>
     </row>
-    <row r="219" spans="18:18">
+    <row r="219" spans="15:18">
+      <c r="O219" s="7"/>
       <c r="R219" s="12"/>
     </row>
-    <row r="220" spans="18:18">
+    <row r="220" spans="15:18">
+      <c r="O220" s="7"/>
       <c r="R220" s="12"/>
     </row>
-    <row r="221" spans="18:18">
+    <row r="221" spans="15:18">
+      <c r="O221" s="7"/>
       <c r="R221" s="12"/>
     </row>
-    <row r="222" spans="18:18">
+    <row r="222" spans="15:18">
+      <c r="O222" s="7"/>
       <c r="R222" s="12"/>
     </row>
-    <row r="223" spans="18:18">
+    <row r="223" spans="15:18">
+      <c r="O223" s="7"/>
       <c r="R223" s="12"/>
     </row>
-    <row r="224" spans="18:18">
+    <row r="224" spans="15:18">
+      <c r="O224" s="7"/>
       <c r="R224" s="12"/>
     </row>
-    <row r="225" spans="18:18">
+    <row r="225" spans="15:18">
+      <c r="O225" s="7"/>
       <c r="R225" s="12"/>
     </row>
-    <row r="226" spans="18:18">
+    <row r="226" spans="15:18">
+      <c r="O226" s="7"/>
       <c r="R226" s="12"/>
     </row>
-    <row r="227" spans="18:18">
+    <row r="227" spans="15:18">
+      <c r="O227" s="7"/>
       <c r="R227" s="12"/>
     </row>
-    <row r="228" spans="18:18">
+    <row r="228" spans="15:18">
+      <c r="O228" s="7"/>
       <c r="R228" s="12"/>
     </row>
-    <row r="229" spans="18:18">
+    <row r="229" spans="15:18">
+      <c r="O229" s="7"/>
       <c r="R229" s="12"/>
     </row>
-    <row r="230" spans="18:18">
+    <row r="230" spans="15:18">
+      <c r="O230" s="7"/>
       <c r="R230" s="12"/>
     </row>
-    <row r="231" spans="18:18">
+    <row r="231" spans="15:18">
+      <c r="O231" s="7"/>
       <c r="R231" s="12"/>
     </row>
-    <row r="232" spans="18:18">
+    <row r="232" spans="15:18">
+      <c r="O232" s="7"/>
       <c r="R232" s="12"/>
     </row>
-    <row r="233" spans="18:18">
+    <row r="233" spans="15:18">
+      <c r="O233" s="7"/>
       <c r="R233" s="12"/>
     </row>
-    <row r="234" spans="18:18">
+    <row r="234" spans="15:18">
+      <c r="O234" s="7"/>
       <c r="R234" s="12"/>
     </row>
-    <row r="235" spans="18:18">
+    <row r="235" spans="15:18">
+      <c r="O235" s="7"/>
       <c r="R235" s="12"/>
     </row>
-    <row r="236" spans="18:18">
+    <row r="236" spans="15:18">
+      <c r="O236" s="7"/>
       <c r="R236" s="12"/>
     </row>
-    <row r="237" spans="18:18">
+    <row r="237" spans="15:18">
+      <c r="O237" s="7"/>
       <c r="R237" s="12"/>
     </row>
-    <row r="238" spans="18:18">
+    <row r="238" spans="15:18">
+      <c r="O238" s="7"/>
       <c r="R238" s="12"/>
     </row>
-    <row r="239" spans="18:18">
+    <row r="239" spans="15:18">
+      <c r="O239" s="7"/>
       <c r="R239" s="12"/>
     </row>
-    <row r="240" spans="18:18">
+    <row r="240" spans="15:18">
+      <c r="O240" s="7"/>
       <c r="R240" s="12"/>
     </row>
-    <row r="241" spans="18:18">
+    <row r="241" spans="15:18">
+      <c r="O241" s="7"/>
       <c r="R241" s="12"/>
     </row>
-    <row r="242" spans="18:18">
+    <row r="242" spans="15:18">
+      <c r="O242" s="7"/>
       <c r="R242" s="12"/>
     </row>
-    <row r="243" spans="18:18">
+    <row r="243" spans="15:18">
+      <c r="O243" s="7"/>
       <c r="R243" s="12"/>
     </row>
-    <row r="244" spans="18:18">
+    <row r="244" spans="15:18">
+      <c r="O244" s="7"/>
       <c r="R244" s="12"/>
     </row>
-    <row r="245" spans="18:18">
+    <row r="245" spans="15:18">
+      <c r="O245" s="7"/>
       <c r="R245" s="12"/>
     </row>
-    <row r="246" spans="18:18">
+    <row r="246" spans="15:18">
+      <c r="O246" s="7"/>
       <c r="R246" s="12"/>
     </row>
-    <row r="247" spans="18:18">
+    <row r="247" spans="15:18">
+      <c r="O247" s="7"/>
       <c r="R247" s="12"/>
     </row>
-    <row r="248" spans="18:18">
+    <row r="248" spans="15:18">
+      <c r="O248" s="7"/>
       <c r="R248" s="12"/>
     </row>
-    <row r="249" spans="18:18">
+    <row r="249" spans="15:18">
+      <c r="O249" s="7"/>
       <c r="R249" s="12"/>
     </row>
-    <row r="250" spans="18:18">
+    <row r="250" spans="15:18">
+      <c r="O250" s="7"/>
       <c r="R250" s="12"/>
     </row>
-    <row r="251" spans="18:18">
+    <row r="251" spans="15:18">
+      <c r="O251" s="7"/>
       <c r="R251" s="12"/>
     </row>
-    <row r="252" spans="18:18">
+    <row r="252" spans="15:18">
+      <c r="O252" s="7"/>
       <c r="R252" s="12"/>
     </row>
-    <row r="253" spans="18:18">
+    <row r="253" spans="15:18">
+      <c r="O253" s="7"/>
       <c r="R253" s="12"/>
     </row>
-    <row r="254" spans="18:18">
+    <row r="254" spans="15:18">
+      <c r="O254" s="7"/>
       <c r="R254" s="12"/>
     </row>
-    <row r="255" spans="18:18">
+    <row r="255" spans="15:18">
+      <c r="O255" s="7"/>
       <c r="R255" s="12"/>
     </row>
-    <row r="256" spans="18:18">
+    <row r="256" spans="15:18">
+      <c r="O256" s="7"/>
       <c r="R256" s="12"/>
     </row>
-    <row r="257" spans="18:18">
+    <row r="257" spans="15:18">
+      <c r="O257" s="7"/>
       <c r="R257" s="12"/>
     </row>
-    <row r="258" spans="18:18">
+    <row r="258" spans="15:18">
+      <c r="O258" s="7"/>
       <c r="R258" s="12"/>
     </row>
-    <row r="259" spans="18:18">
+    <row r="259" spans="15:18">
+      <c r="O259" s="7"/>
       <c r="R259" s="12"/>
     </row>
-    <row r="260" spans="18:18">
+    <row r="260" spans="15:18">
+      <c r="O260" s="7"/>
       <c r="R260" s="12"/>
     </row>
-    <row r="261" spans="18:18">
+    <row r="261" spans="15:18">
+      <c r="O261" s="7"/>
       <c r="R261" s="12"/>
     </row>
-    <row r="262" spans="18:18">
+    <row r="262" spans="15:18">
+      <c r="O262" s="7"/>
       <c r="R262" s="12"/>
     </row>
-    <row r="263" spans="18:18">
+    <row r="263" spans="15:18">
+      <c r="O263" s="7"/>
       <c r="R263" s="12"/>
     </row>
-    <row r="264" spans="18:18">
+    <row r="264" spans="15:18">
+      <c r="O264" s="7"/>
       <c r="R264" s="12"/>
     </row>
-    <row r="265" spans="18:18">
+    <row r="265" spans="15:18">
+      <c r="O265" s="7"/>
       <c r="R265" s="12"/>
     </row>
-    <row r="266" spans="18:18">
+    <row r="266" spans="15:18">
+      <c r="O266" s="7"/>
       <c r="R266" s="12"/>
     </row>
-    <row r="267" spans="18:18">
+    <row r="267" spans="15:18">
+      <c r="O267" s="7"/>
       <c r="R267" s="12"/>
     </row>
-    <row r="268" spans="18:18">
+    <row r="268" spans="15:18">
+      <c r="O268" s="7"/>
       <c r="R268" s="12"/>
     </row>
-    <row r="269" spans="18:18">
+    <row r="269" spans="15:18">
+      <c r="O269" s="7"/>
       <c r="R269" s="12"/>
     </row>
-    <row r="270" spans="18:18">
+    <row r="270" spans="15:18">
+      <c r="O270" s="7"/>
       <c r="R270" s="12"/>
     </row>
-    <row r="271" spans="18:18">
+    <row r="271" spans="15:18">
+      <c r="O271" s="7"/>
       <c r="R271" s="12"/>
     </row>
-    <row r="272" spans="18:18">
+    <row r="272" spans="15:18">
+      <c r="O272" s="7"/>
       <c r="R272" s="12"/>
     </row>
-    <row r="273" spans="18:18">
+    <row r="273" spans="15:18">
+      <c r="O273" s="7"/>
       <c r="R273" s="12"/>
     </row>
-    <row r="274" spans="18:18">
+    <row r="274" spans="15:18">
+      <c r="O274" s="7"/>
       <c r="R274" s="12"/>
     </row>
-    <row r="275" spans="18:18">
+    <row r="275" spans="15:18">
+      <c r="O275" s="7"/>
       <c r="R275" s="12"/>
     </row>
-    <row r="276" spans="18:18">
+    <row r="276" spans="15:18">
+      <c r="O276" s="7"/>
       <c r="R276" s="12"/>
     </row>
-    <row r="277" spans="18:18">
+    <row r="277" spans="15:18">
+      <c r="O277" s="7"/>
       <c r="R277" s="12"/>
     </row>
-    <row r="278" spans="18:18">
+    <row r="278" spans="15:18">
+      <c r="O278" s="7"/>
       <c r="R278" s="12"/>
     </row>
-    <row r="279" spans="18:18">
+    <row r="279" spans="15:18">
+      <c r="O279" s="7"/>
       <c r="R279" s="12"/>
     </row>
-    <row r="280" spans="18:18">
+    <row r="280" spans="15:18">
+      <c r="O280" s="7"/>
       <c r="R280" s="12"/>
     </row>
-    <row r="281" spans="18:18">
+    <row r="281" spans="15:18">
+      <c r="O281" s="7"/>
       <c r="R281" s="12"/>
     </row>
-    <row r="282" spans="18:18">
+    <row r="282" spans="15:18">
+      <c r="O282" s="7"/>
       <c r="R282" s="12"/>
     </row>
-    <row r="283" spans="18:18">
+    <row r="283" spans="15:18">
+      <c r="O283" s="7"/>
       <c r="R283" s="12"/>
     </row>
-    <row r="284" spans="18:18">
+    <row r="284" spans="15:18">
+      <c r="O284" s="7"/>
       <c r="R284" s="12"/>
     </row>
-    <row r="285" spans="18:18">
+    <row r="285" spans="15:18">
+      <c r="O285" s="7"/>
       <c r="R285" s="12"/>
     </row>
-    <row r="286" spans="18:18">
+    <row r="286" spans="15:18">
+      <c r="O286" s="7"/>
       <c r="R286" s="12"/>
     </row>
-    <row r="287" spans="18:18">
+    <row r="287" spans="15:18">
+      <c r="O287" s="7"/>
       <c r="R287" s="12"/>
     </row>
-    <row r="288" spans="18:18">
+    <row r="288" spans="15:18">
+      <c r="O288" s="7"/>
       <c r="R288" s="12"/>
     </row>
-    <row r="289" spans="18:18">
+    <row r="289" spans="15:18">
+      <c r="O289" s="7"/>
       <c r="R289" s="12"/>
     </row>
-    <row r="290" spans="18:18">
+    <row r="290" spans="15:18">
+      <c r="O290" s="7"/>
       <c r="R290" s="12"/>
     </row>
-    <row r="291" spans="18:18">
+    <row r="291" spans="15:18">
+      <c r="O291" s="7"/>
       <c r="R291" s="12"/>
     </row>
-    <row r="292" spans="18:18">
+    <row r="292" spans="15:18">
+      <c r="O292" s="7"/>
       <c r="R292" s="12"/>
     </row>
-    <row r="293" spans="18:18">
+    <row r="293" spans="15:18">
+      <c r="O293" s="7"/>
       <c r="R293" s="12"/>
     </row>
-    <row r="294" spans="18:18">
+    <row r="294" spans="15:18">
+      <c r="O294" s="7"/>
       <c r="R294" s="12"/>
     </row>
-    <row r="295" spans="18:18">
+    <row r="295" spans="15:18">
+      <c r="O295" s="7"/>
       <c r="R295" s="12"/>
     </row>
-    <row r="296" spans="18:18">
+    <row r="296" spans="15:18">
+      <c r="O296" s="7"/>
       <c r="R296" s="12"/>
     </row>
-    <row r="297" spans="18:18">
+    <row r="297" spans="15:18">
+      <c r="O297" s="7"/>
       <c r="R297" s="12"/>
     </row>
-    <row r="298" spans="18:18">
+    <row r="298" spans="15:18">
+      <c r="O298" s="7"/>
       <c r="R298" s="12"/>
     </row>
-    <row r="299" spans="18:18">
+    <row r="299" spans="15:18">
+      <c r="O299" s="7"/>
       <c r="R299" s="12"/>
     </row>
-    <row r="300" spans="18:18">
+    <row r="300" spans="15:18">
+      <c r="O300" s="7"/>
       <c r="R300" s="12"/>
     </row>
-    <row r="301" spans="18:18">
+    <row r="301" spans="15:18">
+      <c r="O301" s="7"/>
       <c r="R301" s="12"/>
     </row>
-    <row r="302" spans="18:18">
+    <row r="302" spans="15:18">
+      <c r="O302" s="7"/>
       <c r="R302" s="12"/>
     </row>
-    <row r="303" spans="18:18">
+    <row r="303" spans="15:18">
+      <c r="O303" s="7"/>
       <c r="R303" s="12"/>
     </row>
-    <row r="304" spans="18:18">
+    <row r="304" spans="15:18">
+      <c r="O304" s="7"/>
       <c r="R304" s="12"/>
     </row>
-    <row r="305" spans="18:18">
+    <row r="305" spans="15:18">
+      <c r="O305" s="7"/>
       <c r="R305" s="12"/>
     </row>
-    <row r="306" spans="18:18">
+    <row r="306" spans="15:18">
+      <c r="O306" s="7"/>
       <c r="R306" s="12"/>
     </row>
-    <row r="307" spans="18:18">
+    <row r="307" spans="15:18">
+      <c r="O307" s="7"/>
       <c r="R307" s="12"/>
     </row>
-    <row r="308" spans="18:18">
+    <row r="308" spans="15:18">
+      <c r="O308" s="7"/>
       <c r="R308" s="12"/>
     </row>
-    <row r="309" spans="18:18">
+    <row r="309" spans="15:18">
+      <c r="O309" s="7"/>
       <c r="R309" s="12"/>
     </row>
-    <row r="310" spans="18:18">
+    <row r="310" spans="15:18">
+      <c r="O310" s="7"/>
       <c r="R310" s="12"/>
     </row>
-    <row r="311" spans="18:18">
+    <row r="311" spans="15:18">
+      <c r="O311" s="7"/>
       <c r="R311" s="12"/>
     </row>
-    <row r="312" spans="18:18">
+    <row r="312" spans="15:18">
+      <c r="O312" s="7"/>
       <c r="R312" s="12"/>
     </row>
-    <row r="313" spans="18:18">
+    <row r="313" spans="15:18">
+      <c r="O313" s="7"/>
       <c r="R313" s="12"/>
     </row>
-    <row r="314" spans="18:18">
+    <row r="314" spans="15:18">
+      <c r="O314" s="7"/>
       <c r="R314" s="12"/>
     </row>
-    <row r="315" spans="18:18">
+    <row r="315" spans="15:18">
+      <c r="O315" s="7"/>
       <c r="R315" s="12"/>
     </row>
-    <row r="316" spans="18:18">
+    <row r="316" spans="15:18">
+      <c r="O316" s="7"/>
       <c r="R316" s="12"/>
     </row>
-    <row r="317" spans="18:18">
+    <row r="317" spans="15:18">
+      <c r="O317" s="7"/>
       <c r="R317" s="12"/>
     </row>
-    <row r="318" spans="18:18">
+    <row r="318" spans="15:18">
+      <c r="O318" s="7"/>
       <c r="R318" s="12"/>
     </row>
-    <row r="319" spans="18:18">
+    <row r="319" spans="15:18">
+      <c r="O319" s="7"/>
       <c r="R319" s="12"/>
     </row>
-    <row r="320" spans="18:18">
+    <row r="320" spans="15:18">
+      <c r="O320" s="7"/>
       <c r="R320" s="12"/>
     </row>
-    <row r="321" spans="18:18">
+    <row r="321" spans="15:18">
+      <c r="O321" s="7"/>
       <c r="R321" s="12"/>
     </row>
-    <row r="322" spans="18:18">
+    <row r="322" spans="15:18">
+      <c r="O322" s="7"/>
       <c r="R322" s="12"/>
     </row>
-    <row r="323" spans="18:18">
+    <row r="323" spans="15:18">
+      <c r="O323" s="7"/>
       <c r="R323" s="12"/>
     </row>
-    <row r="324" spans="18:18">
+    <row r="324" spans="15:18">
+      <c r="O324" s="7"/>
       <c r="R324" s="12"/>
     </row>
-    <row r="325" spans="18:18">
+    <row r="325" spans="15:18">
+      <c r="O325" s="7"/>
       <c r="R325" s="12"/>
     </row>
-    <row r="326" spans="18:18">
+    <row r="326" spans="15:18">
+      <c r="O326" s="7"/>
       <c r="R326" s="12"/>
     </row>
-    <row r="327" spans="18:18">
+    <row r="327" spans="15:18">
+      <c r="O327" s="7"/>
       <c r="R327" s="12"/>
     </row>
-    <row r="328" spans="18:18">
+    <row r="328" spans="15:18">
+      <c r="O328" s="7"/>
       <c r="R328" s="12"/>
     </row>
-    <row r="329" spans="18:18">
+    <row r="329" spans="15:18">
+      <c r="O329" s="7"/>
       <c r="R329" s="12"/>
     </row>
-    <row r="330" spans="18:18">
+    <row r="330" spans="15:18">
+      <c r="O330" s="7"/>
       <c r="R330" s="12"/>
     </row>
-    <row r="331" spans="18:18">
+    <row r="331" spans="15:18">
+      <c r="O331" s="7"/>
       <c r="R331" s="12"/>
     </row>
-    <row r="332" spans="18:18">
+    <row r="332" spans="15:18">
+      <c r="O332" s="7"/>
       <c r="R332" s="12"/>
     </row>
-    <row r="333" spans="18:18">
+    <row r="333" spans="15:18">
+      <c r="O333" s="7"/>
       <c r="R333" s="12"/>
     </row>
-    <row r="334" spans="18:18">
+    <row r="334" spans="15:18">
+      <c r="O334" s="7"/>
       <c r="R334" s="12"/>
     </row>
-    <row r="335" spans="18:18">
+    <row r="335" spans="15:18">
+      <c r="O335" s="7"/>
       <c r="R335" s="12"/>
     </row>
-    <row r="336" spans="18:18">
+    <row r="336" spans="15:18">
+      <c r="O336" s="7"/>
       <c r="R336" s="12"/>
     </row>
-    <row r="337" spans="18:18">
+    <row r="337" spans="15:18">
+      <c r="O337" s="7"/>
       <c r="R337" s="12"/>
     </row>
-    <row r="338" spans="18:18">
+    <row r="338" spans="15:18">
+      <c r="O338" s="7"/>
       <c r="R338" s="12"/>
     </row>
-    <row r="339" spans="18:18">
+    <row r="339" spans="15:18">
+      <c r="O339" s="7"/>
       <c r="R339" s="12"/>
     </row>
-    <row r="340" spans="18:18">
+    <row r="340" spans="15:18">
+      <c r="O340" s="7"/>
       <c r="R340" s="12"/>
     </row>
-    <row r="341" spans="18:18">
+    <row r="341" spans="15:18">
+      <c r="O341" s="7"/>
       <c r="R341" s="12"/>
     </row>
-    <row r="342" spans="18:18">
+    <row r="342" spans="15:18">
+      <c r="O342" s="7"/>
       <c r="R342" s="12"/>
     </row>
-    <row r="343" spans="18:18">
+    <row r="343" spans="15:18">
+      <c r="O343" s="7"/>
       <c r="R343" s="12"/>
     </row>
-    <row r="344" spans="18:18">
+    <row r="344" spans="15:18">
+      <c r="O344" s="7"/>
       <c r="R344" s="12"/>
     </row>
-    <row r="345" spans="18:18">
+    <row r="345" spans="15:18">
+      <c r="O345" s="7"/>
       <c r="R345" s="12"/>
     </row>
-    <row r="346" spans="18:18">
+    <row r="346" spans="15:18">
+      <c r="O346" s="7"/>
       <c r="R346" s="12"/>
     </row>
-    <row r="347" spans="18:18">
+    <row r="347" spans="15:18">
+      <c r="O347" s="7"/>
       <c r="R347" s="12"/>
     </row>
-    <row r="348" spans="18:18">
+    <row r="348" spans="15:18">
+      <c r="O348" s="7"/>
       <c r="R348" s="12"/>
     </row>
-    <row r="349" spans="18:18">
+    <row r="349" spans="15:18">
+      <c r="O349" s="7"/>
       <c r="R349" s="12"/>
     </row>
-    <row r="350" spans="18:18">
+    <row r="350" spans="15:18">
+      <c r="O350" s="7"/>
       <c r="R350" s="12"/>
     </row>
-    <row r="351" spans="18:18">
+    <row r="351" spans="15:18">
+      <c r="O351" s="7"/>
       <c r="R351" s="12"/>
     </row>
-    <row r="352" spans="18:18">
+    <row r="352" spans="15:18">
+      <c r="O352" s="7"/>
       <c r="R352" s="12"/>
     </row>
-    <row r="353" spans="18:18">
+    <row r="353" spans="15:18">
+      <c r="O353" s="7"/>
       <c r="R353" s="12"/>
     </row>
-    <row r="354" spans="18:18">
+    <row r="354" spans="15:18">
+      <c r="O354" s="7"/>
       <c r="R354" s="12"/>
     </row>
-    <row r="355" spans="18:18">
+    <row r="355" spans="15:18">
+      <c r="O355" s="7"/>
       <c r="R355" s="12"/>
     </row>
-    <row r="356" spans="18:18">
+    <row r="356" spans="15:18">
+      <c r="O356" s="7"/>
       <c r="R356" s="12"/>
     </row>
-    <row r="357" spans="18:18">
+    <row r="357" spans="15:18">
+      <c r="O357" s="7"/>
       <c r="R357" s="12"/>
     </row>
-    <row r="358" spans="18:18">
+    <row r="358" spans="15:18">
+      <c r="O358" s="7"/>
       <c r="R358" s="12"/>
     </row>
-    <row r="359" spans="18:18">
+    <row r="359" spans="15:18">
+      <c r="O359" s="7"/>
       <c r="R359" s="12"/>
     </row>
-    <row r="360" spans="18:18">
+    <row r="360" spans="15:18">
+      <c r="O360" s="7"/>
       <c r="R360" s="12"/>
     </row>
-    <row r="361" spans="18:18">
+    <row r="361" spans="15:18">
+      <c r="O361" s="7"/>
       <c r="R361" s="12"/>
     </row>
-    <row r="362" spans="18:18">
+    <row r="362" spans="15:18">
+      <c r="O362" s="7"/>
       <c r="R362" s="12"/>
     </row>
-    <row r="363" spans="18:18">
+    <row r="363" spans="15:18">
+      <c r="O363" s="7"/>
       <c r="R363" s="12"/>
     </row>
-    <row r="364" spans="18:18">
+    <row r="364" spans="15:18">
+      <c r="O364" s="7"/>
       <c r="R364" s="12"/>
     </row>
-    <row r="365" spans="18:18">
+    <row r="365" spans="15:18">
+      <c r="O365" s="7"/>
       <c r="R365" s="12"/>
     </row>
-    <row r="366" spans="18:18">
+    <row r="366" spans="15:18">
+      <c r="O366" s="7"/>
       <c r="R366" s="12"/>
     </row>
-    <row r="367" spans="18:18">
+    <row r="367" spans="15:18">
+      <c r="O367" s="7"/>
       <c r="R367" s="12"/>
     </row>
-    <row r="368" spans="18:18">
+    <row r="368" spans="15:18">
+      <c r="O368" s="7"/>
       <c r="R368" s="12"/>
     </row>
-    <row r="369" spans="18:18">
+    <row r="369" spans="15:18">
+      <c r="O369" s="7"/>
       <c r="R369" s="12"/>
     </row>
-    <row r="370" spans="18:18">
+    <row r="370" spans="15:18">
+      <c r="O370" s="7"/>
       <c r="R370" s="12"/>
     </row>
-    <row r="371" spans="18:18">
+    <row r="371" spans="15:18">
+      <c r="O371" s="7"/>
       <c r="R371" s="12"/>
     </row>
-    <row r="372" spans="18:18">
+    <row r="372" spans="15:18">
+      <c r="O372" s="7"/>
       <c r="R372" s="12"/>
     </row>
-    <row r="373" spans="18:18">
+    <row r="373" spans="15:18">
+      <c r="O373" s="7"/>
       <c r="R373" s="12"/>
     </row>
-    <row r="374" spans="18:18">
+    <row r="374" spans="15:18">
+      <c r="O374" s="7"/>
       <c r="R374" s="12"/>
     </row>
-    <row r="375" spans="18:18">
+    <row r="375" spans="15:18">
+      <c r="O375" s="7"/>
       <c r="R375" s="12"/>
     </row>
-    <row r="376" spans="18:18">
+    <row r="376" spans="15:18">
+      <c r="O376" s="7"/>
       <c r="R376" s="12"/>
     </row>
-    <row r="377" spans="18:18">
+    <row r="377" spans="15:18">
+      <c r="O377" s="7"/>
       <c r="R377" s="12"/>
     </row>
-    <row r="378" spans="18:18">
+    <row r="378" spans="15:18">
+      <c r="O378" s="7"/>
       <c r="R378" s="12"/>
     </row>
-    <row r="379" spans="18:18">
+    <row r="379" spans="15:18">
+      <c r="O379" s="7"/>
       <c r="R379" s="12"/>
     </row>
-    <row r="380" spans="18:18">
+    <row r="380" spans="15:18">
+      <c r="O380" s="7"/>
       <c r="R380" s="12"/>
     </row>
-    <row r="381" spans="18:18">
+    <row r="381" spans="15:18">
+      <c r="O381" s="7"/>
       <c r="R381" s="12"/>
     </row>
-    <row r="382" spans="18:18">
+    <row r="382" spans="15:18">
+      <c r="O382" s="7"/>
       <c r="R382" s="12"/>
     </row>
-    <row r="383" spans="18:18">
+    <row r="383" spans="15:18">
+      <c r="O383" s="7"/>
       <c r="R383" s="12"/>
     </row>
-    <row r="384" spans="18:18">
+    <row r="384" spans="15:18">
+      <c r="O384" s="7"/>
       <c r="R384" s="12"/>
     </row>
-    <row r="385" spans="18:18">
+    <row r="385" spans="15:18">
+      <c r="O385" s="7"/>
       <c r="R385" s="12"/>
     </row>
-    <row r="386" spans="18:18">
+    <row r="386" spans="15:18">
+      <c r="O386" s="7"/>
       <c r="R386" s="12"/>
     </row>
-    <row r="387" spans="18:18">
+    <row r="387" spans="15:18">
+      <c r="O387" s="7"/>
       <c r="R387" s="12"/>
     </row>
-    <row r="388" spans="18:18">
+    <row r="388" spans="15:18">
+      <c r="O388" s="7"/>
       <c r="R388" s="12"/>
     </row>
-    <row r="389" spans="18:18">
+    <row r="389" spans="15:18">
+      <c r="O389" s="7"/>
       <c r="R389" s="12"/>
     </row>
-    <row r="390" spans="18:18">
+    <row r="390" spans="15:18">
+      <c r="O390" s="7"/>
       <c r="R390" s="12"/>
     </row>
-    <row r="391" spans="18:18">
+    <row r="391" spans="15:18">
+      <c r="O391" s="7"/>
       <c r="R391" s="12"/>
     </row>
-    <row r="392" spans="18:18">
+    <row r="392" spans="15:18">
+      <c r="O392" s="7"/>
       <c r="R392" s="12"/>
     </row>
-    <row r="393" spans="18:18">
+    <row r="393" spans="15:18">
+      <c r="O393" s="7"/>
       <c r="R393" s="12"/>
     </row>
-    <row r="394" spans="18:18">
+    <row r="394" spans="15:18">
+      <c r="O394" s="7"/>
       <c r="R394" s="12"/>
     </row>
-    <row r="395" spans="18:18">
+    <row r="395" spans="15:18">
+      <c r="O395" s="7"/>
       <c r="R395" s="12"/>
     </row>
-    <row r="396" spans="18:18">
+    <row r="396" spans="15:18">
+      <c r="O396" s="7"/>
       <c r="R396" s="12"/>
     </row>
-    <row r="397" spans="18:18">
+    <row r="397" spans="15:18">
+      <c r="O397" s="7"/>
       <c r="R397" s="12"/>
     </row>
-    <row r="398" spans="18:18">
+    <row r="398" spans="15:18">
+      <c r="O398" s="7"/>
       <c r="R398" s="12"/>
     </row>
-    <row r="399" spans="18:18">
+    <row r="399" spans="15:18">
+      <c r="O399" s="7"/>
       <c r="R399" s="12"/>
     </row>
-    <row r="400" spans="18:18">
+    <row r="400" spans="15:18">
+      <c r="O400" s="7"/>
       <c r="R400" s="12"/>
     </row>
-    <row r="401" spans="18:18">
+    <row r="401" spans="15:18">
+      <c r="O401" s="7"/>
       <c r="R401" s="12"/>
     </row>
-    <row r="402" spans="18:18">
+    <row r="402" spans="15:18">
+      <c r="O402" s="7"/>
       <c r="R402" s="12"/>
     </row>
-    <row r="403" spans="18:18">
+    <row r="403" spans="15:18">
+      <c r="O403" s="7"/>
       <c r="R403" s="12"/>
     </row>
-    <row r="404" spans="18:18">
+    <row r="404" spans="15:18">
+      <c r="O404" s="7"/>
       <c r="R404" s="12"/>
     </row>
-    <row r="405" spans="18:18">
+    <row r="405" spans="15:18">
+      <c r="O405" s="7"/>
       <c r="R405" s="12"/>
     </row>
-    <row r="406" spans="18:18">
+    <row r="406" spans="15:18">
+      <c r="O406" s="7"/>
       <c r="R406" s="12"/>
     </row>
-    <row r="407" spans="18:18">
+    <row r="407" spans="15:18">
+      <c r="O407" s="7"/>
       <c r="R407" s="12"/>
     </row>
-    <row r="408" spans="18:18">
+    <row r="408" spans="15:18">
+      <c r="O408" s="7"/>
       <c r="R408" s="12"/>
     </row>
-    <row r="409" spans="18:18">
+    <row r="409" spans="15:18">
+      <c r="O409" s="7"/>
       <c r="R409" s="12"/>
     </row>
-    <row r="410" spans="18:18">
+    <row r="410" spans="15:18">
+      <c r="O410" s="7"/>
       <c r="R410" s="12"/>
     </row>
-    <row r="411" spans="18:18">
+    <row r="411" spans="15:18">
+      <c r="O411" s="7"/>
       <c r="R411" s="12"/>
     </row>
-    <row r="412" spans="18:18">
+    <row r="412" spans="15:18">
+      <c r="O412" s="7"/>
       <c r="R412" s="12"/>
     </row>
-    <row r="413" spans="18:18">
+    <row r="413" spans="15:18">
+      <c r="O413" s="7"/>
       <c r="R413" s="12"/>
     </row>
-    <row r="414" spans="18:18">
+    <row r="414" spans="15:18">
+      <c r="O414" s="7"/>
       <c r="R414" s="12"/>
     </row>
-    <row r="415" spans="18:18">
+    <row r="415" spans="15:18">
+      <c r="O415" s="7"/>
       <c r="R415" s="12"/>
     </row>
-    <row r="416" spans="18:18">
+    <row r="416" spans="15:18">
+      <c r="O416" s="7"/>
       <c r="R416" s="12"/>
     </row>
-    <row r="417" spans="18:18">
+    <row r="417" spans="15:18">
+      <c r="O417" s="7"/>
       <c r="R417" s="12"/>
     </row>
-    <row r="418" spans="18:18">
+    <row r="418" spans="15:18">
+      <c r="O418" s="7"/>
       <c r="R418" s="12"/>
     </row>
-    <row r="419" spans="18:18">
+    <row r="419" spans="15:18">
+      <c r="O419" s="7"/>
       <c r="R419" s="12"/>
     </row>
-    <row r="420" spans="18:18">
+    <row r="420" spans="15:18">
+      <c r="O420" s="7"/>
       <c r="R420" s="12"/>
     </row>
-    <row r="421" spans="18:18">
+    <row r="421" spans="15:18">
+      <c r="O421" s="7"/>
       <c r="R421" s="12"/>
     </row>
-    <row r="422" spans="18:18">
+    <row r="422" spans="15:18">
+      <c r="O422" s="7"/>
       <c r="R422" s="12"/>
     </row>
-    <row r="423" spans="18:18">
+    <row r="423" spans="15:18">
+      <c r="O423" s="7"/>
       <c r="R423" s="12"/>
     </row>
-    <row r="424" spans="18:18">
+    <row r="424" spans="15:18">
+      <c r="O424" s="7"/>
       <c r="R424" s="12"/>
     </row>
-    <row r="425" spans="18:18">
+    <row r="425" spans="15:18">
+      <c r="O425" s="7"/>
       <c r="R425" s="12"/>
     </row>
-    <row r="426" spans="18:18">
+    <row r="426" spans="15:18">
+      <c r="O426" s="7"/>
       <c r="R426" s="12"/>
     </row>
-    <row r="427" spans="18:18">
+    <row r="427" spans="15:18">
+      <c r="O427" s="7"/>
       <c r="R427" s="12"/>
     </row>
-    <row r="428" spans="18:18">
+    <row r="428" spans="15:18">
+      <c r="O428" s="7"/>
       <c r="R428" s="12"/>
     </row>
-    <row r="429" spans="18:18">
+    <row r="429" spans="15:18">
+      <c r="O429" s="7"/>
       <c r="R429" s="12"/>
     </row>
-    <row r="430" spans="18:18">
+    <row r="430" spans="15:18">
+      <c r="O430" s="7"/>
       <c r="R430" s="12"/>
     </row>
-    <row r="431" spans="18:18">
+    <row r="431" spans="15:18">
+      <c r="O431" s="7"/>
       <c r="R431" s="12"/>
     </row>
-    <row r="432" spans="18:18">
+    <row r="432" spans="15:18">
+      <c r="O432" s="7"/>
       <c r="R432" s="12"/>
     </row>
-    <row r="433" spans="18:18">
+    <row r="433" spans="15:18">
+      <c r="O433" s="7"/>
       <c r="R433" s="12"/>
     </row>
-    <row r="434" spans="18:18">
+    <row r="434" spans="15:18">
+      <c r="O434" s="7"/>
       <c r="R434" s="12"/>
     </row>
-    <row r="435" spans="18:18">
+    <row r="435" spans="15:18">
+      <c r="O435" s="7"/>
       <c r="R435" s="12"/>
     </row>
-    <row r="436" spans="18:18">
+    <row r="436" spans="15:18">
+      <c r="O436" s="7"/>
       <c r="R436" s="12"/>
     </row>
-    <row r="437" spans="18:18">
+    <row r="437" spans="15:18">
+      <c r="O437" s="7"/>
       <c r="R437" s="12"/>
     </row>
-    <row r="438" spans="18:18">
+    <row r="438" spans="15:18">
+      <c r="O438" s="7"/>
       <c r="R438" s="12"/>
     </row>
-    <row r="439" spans="18:18">
+    <row r="439" spans="15:18">
+      <c r="O439" s="7"/>
       <c r="R439" s="12"/>
     </row>
-    <row r="440" spans="18:18">
+    <row r="440" spans="15:18">
+      <c r="O440" s="7"/>
       <c r="R440" s="12"/>
     </row>
-    <row r="441" spans="18:18">
+    <row r="441" spans="15:18">
+      <c r="O441" s="7"/>
       <c r="R441" s="12"/>
     </row>
-    <row r="442" spans="18:18">
+    <row r="442" spans="15:18">
+      <c r="O442" s="7"/>
       <c r="R442" s="12"/>
     </row>
-    <row r="443" spans="18:18">
+    <row r="443" spans="15:18">
+      <c r="O443" s="7"/>
       <c r="R443" s="12"/>
     </row>
-    <row r="444" spans="18:18">
+    <row r="444" spans="15:18">
+      <c r="O444" s="7"/>
       <c r="R444" s="12"/>
     </row>
-    <row r="445" spans="18:18">
+    <row r="445" spans="15:18">
+      <c r="O445" s="7"/>
       <c r="R445" s="12"/>
     </row>
-    <row r="446" spans="18:18">
+    <row r="446" spans="15:18">
+      <c r="O446" s="7"/>
       <c r="R446" s="12"/>
     </row>
-    <row r="447" spans="18:18">
+    <row r="447" spans="15:18">
+      <c r="O447" s="7"/>
       <c r="R447" s="12"/>
     </row>
-    <row r="448" spans="18:18">
+    <row r="448" spans="15:18">
+      <c r="O448" s="7"/>
       <c r="R448" s="12"/>
     </row>
-    <row r="449" spans="18:18">
+    <row r="449" spans="15:18">
+      <c r="O449" s="7"/>
       <c r="R449" s="12"/>
     </row>
-    <row r="450" spans="18:18">
+    <row r="450" spans="15:18">
+      <c r="O450" s="7"/>
       <c r="R450" s="12"/>
     </row>
-    <row r="451" spans="18:18">
+    <row r="451" spans="15:18">
+      <c r="O451" s="7"/>
       <c r="R451" s="12"/>
     </row>
-    <row r="452" spans="18:18">
+    <row r="452" spans="15:18">
+      <c r="O452" s="7"/>
       <c r="R452" s="12"/>
     </row>
-    <row r="453" spans="18:18">
+    <row r="453" spans="15:18">
+      <c r="O453" s="7"/>
       <c r="R453" s="12"/>
     </row>
-    <row r="454" spans="18:18">
+    <row r="454" spans="15:18">
+      <c r="O454" s="7"/>
       <c r="R454" s="12"/>
     </row>
-    <row r="455" spans="18:18">
+    <row r="455" spans="15:18">
+      <c r="O455" s="7"/>
       <c r="R455" s="12"/>
     </row>
-    <row r="456" spans="18:18">
+    <row r="456" spans="15:18">
+      <c r="O456" s="7"/>
       <c r="R456" s="12"/>
     </row>
-    <row r="457" spans="18:18">
+    <row r="457" spans="15:18">
+      <c r="O457" s="7"/>
       <c r="R457" s="12"/>
     </row>
-    <row r="458" spans="18:18">
+    <row r="458" spans="15:18">
+      <c r="O458" s="7"/>
       <c r="R458" s="12"/>
     </row>
-    <row r="459" spans="18:18">
+    <row r="459" spans="15:18">
+      <c r="O459" s="7"/>
       <c r="R459" s="12"/>
     </row>
-    <row r="460" spans="18:18">
+    <row r="460" spans="15:18">
+      <c r="O460" s="7"/>
       <c r="R460" s="12"/>
     </row>
-    <row r="461" spans="18:18">
+    <row r="461" spans="15:18">
+      <c r="O461" s="7"/>
       <c r="R461" s="12"/>
     </row>
-    <row r="462" spans="18:18">
+    <row r="462" spans="15:18">
+      <c r="O462" s="7"/>
       <c r="R462" s="12"/>
     </row>
-    <row r="463" spans="18:18">
+    <row r="463" spans="15:18">
+      <c r="O463" s="7"/>
       <c r="R463" s="12"/>
     </row>
-    <row r="464" spans="18:18">
+    <row r="464" spans="15:18">
+      <c r="O464" s="7"/>
       <c r="R464" s="12"/>
     </row>
-    <row r="465" spans="18:18">
+    <row r="465" spans="15:18">
+      <c r="O465" s="7"/>
       <c r="R465" s="12"/>
     </row>
-    <row r="466" spans="18:18">
+    <row r="466" spans="15:18">
+      <c r="O466" s="7"/>
       <c r="R466" s="12"/>
     </row>
-    <row r="467" spans="18:18">
+    <row r="467" spans="15:18">
+      <c r="O467" s="7"/>
       <c r="R467" s="12"/>
     </row>
-    <row r="468" spans="18:18">
+    <row r="468" spans="15:18">
+      <c r="O468" s="7"/>
       <c r="R468" s="12"/>
     </row>
-    <row r="469" spans="18:18">
+    <row r="469" spans="15:18">
+      <c r="O469" s="7"/>
       <c r="R469" s="12"/>
     </row>
-    <row r="470" spans="18:18">
+    <row r="470" spans="15:18">
+      <c r="O470" s="7"/>
       <c r="R470" s="12"/>
     </row>
-    <row r="471" spans="18:18">
+    <row r="471" spans="15:18">
+      <c r="O471" s="7"/>
       <c r="R471" s="12"/>
     </row>
-    <row r="472" spans="18:18">
+    <row r="472" spans="15:18">
+      <c r="O472" s="7"/>
       <c r="R472" s="12"/>
     </row>
-    <row r="473" spans="18:18">
+    <row r="473" spans="15:18">
+      <c r="O473" s="7"/>
       <c r="R473" s="12"/>
     </row>
-    <row r="474" spans="18:18">
+    <row r="474" spans="15:18">
+      <c r="O474" s="7"/>
       <c r="R474" s="12"/>
     </row>
-    <row r="475" spans="18:18">
+    <row r="475" spans="15:18">
+      <c r="O475" s="7"/>
       <c r="R475" s="12"/>
     </row>
-    <row r="476" spans="18:18">
+    <row r="476" spans="15:18">
+      <c r="O476" s="7"/>
       <c r="R476" s="12"/>
     </row>
-    <row r="477" spans="18:18">
+    <row r="477" spans="15:18">
+      <c r="O477" s="7"/>
       <c r="R477" s="12"/>
     </row>
-    <row r="478" spans="18:18">
+    <row r="478" spans="15:18">
+      <c r="O478" s="7"/>
       <c r="R478" s="12"/>
     </row>
-    <row r="479" spans="18:18">
+    <row r="479" spans="15:18">
+      <c r="O479" s="7"/>
       <c r="R479" s="12"/>
     </row>
-    <row r="480" spans="18:18">
+    <row r="480" spans="15:18">
+      <c r="O480" s="7"/>
       <c r="R480" s="12"/>
     </row>
-    <row r="481" spans="18:18">
+    <row r="481" spans="15:18">
+      <c r="O481" s="7"/>
       <c r="R481" s="12"/>
     </row>
-    <row r="482" spans="18:18">
+    <row r="482" spans="15:18">
+      <c r="O482" s="7"/>
       <c r="R482" s="12"/>
     </row>
-    <row r="483" spans="18:18">
+    <row r="483" spans="15:18">
+      <c r="O483" s="7"/>
       <c r="R483" s="12"/>
     </row>
-    <row r="484" spans="18:18">
+    <row r="484" spans="15:18">
+      <c r="O484" s="7"/>
       <c r="R484" s="12"/>
     </row>
-    <row r="485" spans="18:18">
+    <row r="485" spans="15:18">
+      <c r="O485" s="7"/>
       <c r="R485" s="12"/>
     </row>
-    <row r="486" spans="18:18">
+    <row r="486" spans="15:18">
+      <c r="O486" s="7"/>
       <c r="R486" s="12"/>
     </row>
-    <row r="487" spans="18:18">
+    <row r="487" spans="15:18">
+      <c r="O487" s="7"/>
       <c r="R487" s="12"/>
     </row>
-    <row r="488" spans="18:18">
+    <row r="488" spans="15:18">
+      <c r="O488" s="7"/>
       <c r="R488" s="12"/>
     </row>
-    <row r="489" spans="18:18">
+    <row r="489" spans="15:18">
+      <c r="O489" s="7"/>
       <c r="R489" s="12"/>
     </row>
-    <row r="490" spans="18:18">
+    <row r="490" spans="15:18">
+      <c r="O490" s="7"/>
       <c r="R490" s="12"/>
     </row>
-    <row r="491" spans="18:18">
+    <row r="491" spans="15:18">
+      <c r="O491" s="7"/>
       <c r="R491" s="12"/>
     </row>
-    <row r="492" spans="18:18">
+    <row r="492" spans="15:18">
+      <c r="O492" s="7"/>
       <c r="R492" s="12"/>
     </row>
-    <row r="493" spans="18:18">
+    <row r="493" spans="15:18">
+      <c r="O493" s="7"/>
       <c r="R493" s="12"/>
     </row>
-    <row r="494" spans="18:18">
+    <row r="494" spans="15:18">
+      <c r="O494" s="7"/>
       <c r="R494" s="12"/>
     </row>
-    <row r="495" spans="18:18">
+    <row r="495" spans="15:18">
+      <c r="O495" s="7"/>
       <c r="R495" s="12"/>
     </row>
-    <row r="496" spans="18:18">
+    <row r="496" spans="15:18">
+      <c r="O496" s="7"/>
       <c r="R496" s="12"/>
     </row>
-    <row r="497" spans="18:18">
+    <row r="497" spans="15:18">
+      <c r="O497" s="7"/>
       <c r="R497" s="12"/>
     </row>
-    <row r="498" spans="18:18">
+    <row r="498" spans="15:18">
+      <c r="O498" s="7"/>
       <c r="R498" s="12"/>
     </row>
-    <row r="499" spans="18:18">
+    <row r="499" spans="15:18">
+      <c r="O499" s="7"/>
       <c r="R499" s="12"/>
     </row>
-    <row r="500" spans="18:18">
+    <row r="500" spans="15:18">
+      <c r="O500" s="7"/>
       <c r="R500" s="12"/>
     </row>
-    <row r="501" spans="18:18">
+    <row r="501" spans="15:18">
+      <c r="O501" s="7"/>
       <c r="R501" s="12"/>
     </row>
-    <row r="502" spans="18:18">
+    <row r="502" spans="15:18">
+      <c r="O502" s="7"/>
       <c r="R502" s="12"/>
     </row>
-    <row r="503" spans="18:18">
+    <row r="503" spans="15:18">
+      <c r="O503" s="7"/>
       <c r="R503" s="12"/>
     </row>
-    <row r="504" spans="18:18">
+    <row r="504" spans="15:18">
+      <c r="O504" s="7"/>
       <c r="R504" s="12"/>
     </row>
-    <row r="505" spans="18:18">
+    <row r="505" spans="15:18">
+      <c r="O505" s="7"/>
       <c r="R505" s="12"/>
     </row>
-    <row r="506" spans="18:18">
+    <row r="506" spans="15:18">
+      <c r="O506" s="7"/>
       <c r="R506" s="12"/>
     </row>
-    <row r="507" spans="18:18">
+    <row r="507" spans="15:18">
+      <c r="O507" s="7"/>
       <c r="R507" s="12"/>
     </row>
-    <row r="508" spans="18:18">
+    <row r="508" spans="15:18">
+      <c r="O508" s="7"/>
       <c r="R508" s="12"/>
     </row>
-    <row r="509" spans="18:18">
+    <row r="509" spans="15:18">
+      <c r="O509" s="7"/>
       <c r="R509" s="12"/>
     </row>
-    <row r="510" spans="18:18">
+    <row r="510" spans="15:18">
+      <c r="O510" s="7"/>
       <c r="R510" s="12"/>
     </row>
-    <row r="511" spans="18:18">
+    <row r="511" spans="15:18">
+      <c r="O511" s="7"/>
       <c r="R511" s="12"/>
     </row>
-    <row r="512" spans="18:18">
+    <row r="512" spans="15:18">
+      <c r="O512" s="7"/>
       <c r="R512" s="12"/>
     </row>
-    <row r="513" spans="18:18">
+    <row r="513" spans="15:18">
+      <c r="O513" s="7"/>
       <c r="R513" s="12"/>
     </row>
-    <row r="514" spans="18:18">
+    <row r="514" spans="15:18">
+      <c r="O514" s="7"/>
       <c r="R514" s="12"/>
     </row>
-    <row r="515" spans="18:18">
+    <row r="515" spans="15:18">
+      <c r="O515" s="7"/>
       <c r="R515" s="12"/>
     </row>
-    <row r="516" spans="18:18">
+    <row r="516" spans="15:18">
+      <c r="O516" s="7"/>
       <c r="R516" s="12"/>
     </row>
-    <row r="517" spans="18:18">
+    <row r="517" spans="15:18">
+      <c r="O517" s="7"/>
       <c r="R517" s="12"/>
     </row>
-    <row r="518" spans="18:18">
+    <row r="518" spans="15:18">
+      <c r="O518" s="7"/>
       <c r="R518" s="12"/>
     </row>
-    <row r="519" spans="18:18">
+    <row r="519" spans="15:18">
+      <c r="O519" s="7"/>
       <c r="R519" s="12"/>
     </row>
-    <row r="520" spans="18:18">
+    <row r="520" spans="15:18">
+      <c r="O520" s="7"/>
       <c r="R520" s="12"/>
     </row>
-    <row r="521" spans="18:18">
+    <row r="521" spans="15:18">
+      <c r="O521" s="7"/>
       <c r="R521" s="12"/>
     </row>
-    <row r="522" spans="18:18">
+    <row r="522" spans="15:18">
       <c r="R522" s="12"/>
     </row>
-    <row r="523" spans="18:18">
+    <row r="523" spans="15:18">
       <c r="R523" s="12"/>
     </row>
-    <row r="524" spans="18:18">
+    <row r="524" spans="15:18">
       <c r="R524" s="12"/>
     </row>
-    <row r="525" spans="18:18">
+    <row r="525" spans="15:18">
       <c r="R525" s="12"/>
     </row>
-    <row r="526" spans="18:18">
+    <row r="526" spans="15:18">
       <c r="R526" s="12"/>
     </row>
-    <row r="527" spans="18:18">
+    <row r="527" spans="15:18">
       <c r="R527" s="12"/>
     </row>
-    <row r="528" spans="18:18">
+    <row r="528" spans="15:18">
       <c r="R528" s="12"/>
     </row>
     <row r="529" spans="18:18">
@@ -2569,23 +3104,32 @@
       <c r="R531" s="12"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R530:R531" xr:uid="{709BC68A-C242-4787-A4C8-EA4F2DF4203E}">
       <formula1>IF($O530="Tiktok", R530&lt;&gt;"", TRUE)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O6 O8:O1048576" xr:uid="{10C1B1BA-30A4-43AA-B6F4-A5F0B0F55982}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O522:O1048576" xr:uid="{10C1B1BA-30A4-43AA-B6F4-A5F0B0F55982}">
       <formula1>"Express, Tiktok"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S6 S8:S1048576" xr:uid="{F8BCA374-D361-4313-9C59-CF82877BB18A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S6 S8:S9 S11:S1048576" xr:uid="{F8BCA374-D361-4313-9C59-CF82877BB18A}">
       <formula1>", YES, NO"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6 Q8:Q1048576" xr:uid="{16DEDA22-1651-49B2-AAF1-65C50FFEDD2D}">
       <formula1>"YES, NO"</formula1>
     </dataValidation>
-    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="R2:R6 R8:R529" xr:uid="{AB023EC7-7443-46B0-A956-FA2A83A11DFD}">
+    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="R8:R529 R2:R6" xr:uid="{AB023EC7-7443-46B0-A956-FA2A83A11DFD}">
       <formula1>IF($O2="Tiktok", R2&lt;&gt;"", TRUE)</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O521" xr:uid="{8664190F-EA7C-4D2F-AC04-A222D6E43D96}">
+      <formula1>"Express, Ship By Tiktok"</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="R4" r:id="rId1" xr:uid="{76E30326-4126-47A2-B998-13BFF5AC8CB0}"/>
+    <hyperlink ref="R5" r:id="rId2" xr:uid="{1BA6FB39-2A12-4199-9359-4A92E9981534}"/>
+    <hyperlink ref="R6" r:id="rId3" xr:uid="{407B0B84-A534-457B-A8CA-A1CE178CC981}"/>
+    <hyperlink ref="R3" r:id="rId4" xr:uid="{C7B06EFA-603B-4084-A643-C12280E2CECC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/public/Ananbay_template.xlsx
+++ b/public/Ananbay_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\TebGroup\teb-express-tunghoang\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283DEACE-114F-40F0-B70E-CCF220E14BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE8AA35-A6D8-489F-B658-43B3BAF7C960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
   <si>
     <t>Tên người nhận</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>Dịch vụ</t>
-  </si>
-  <si>
-    <t>Products</t>
   </si>
   <si>
     <t>Pin</t>
@@ -223,6 +220,9 @@
   <si>
     <t>Ship By Tiktok</t>
   </si>
+  <si>
+    <t>Hàng TradeMark</t>
+  </si>
 </sst>
 </file>
 
@@ -231,7 +231,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General\,"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -271,12 +271,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -334,9 +328,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -355,8 +349,7 @@
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -364,7 +357,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -650,16 +643,16 @@
     <col min="3" max="3" width="17.5546875" customWidth="1"/>
     <col min="7" max="7" width="12.5546875" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="11" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="8.33203125" customWidth="1"/>
     <col min="13" max="13" width="9.88671875" customWidth="1"/>
     <col min="15" max="15" width="10.44140625" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="7.77734375" style="14" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" customWidth="1"/>
+    <col min="17" max="17" width="7.77734375" style="13" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="13.109375" style="14" customWidth="1"/>
+    <col min="19" max="19" width="13.109375" style="13" customWidth="1"/>
     <col min="21" max="21" width="11.6640625" customWidth="1"/>
     <col min="1023" max="1023" width="11.5546875" customWidth="1"/>
   </cols>
@@ -689,7 +682,7 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -711,52 +704,52 @@
         <v>14</v>
       </c>
       <c r="P1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S1" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="15" thickBot="1">
       <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="G2" s="6">
         <v>19033</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="K2" s="8">
         <v>85</v>
@@ -771,12 +764,14 @@
         <v>3</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="10"/>
-      <c r="R2" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="11"/>
       <c r="T2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U2">
         <v>1</v>
@@ -787,29 +782,29 @@
     </row>
     <row r="3" spans="1:22" ht="15" thickBot="1">
       <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="G3" s="6">
         <v>19033</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="K3" s="8">
         <v>85</v>
@@ -824,17 +819,17 @@
         <v>3</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="10"/>
-      <c r="R3" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="P3" s="13"/>
+      <c r="R3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="T3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U3">
         <v>1</v>
@@ -845,29 +840,29 @@
     </row>
     <row r="4" spans="1:22" ht="15.6" customHeight="1" thickBot="1">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="G4" s="6">
         <v>20619</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="K4" s="8">
         <v>70</v>
@@ -882,16 +877,19 @@
         <v>3</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="R4" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="S4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="13" t="s">
         <v>31</v>
       </c>
+      <c r="R4" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="T4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U4">
         <v>1</v>
@@ -902,29 +900,29 @@
     </row>
     <row r="5" spans="1:22" ht="15.6" customHeight="1" thickBot="1">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="G5" s="6">
         <v>20619</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="K5" s="8">
         <v>70</v>
@@ -939,16 +937,17 @@
         <v>3</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="R5" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>32</v>
+        <v>44</v>
+      </c>
+      <c r="P5" s="13"/>
+      <c r="R5" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="S5" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="T5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U5">
         <v>1</v>
@@ -959,29 +958,29 @@
     </row>
     <row r="6" spans="1:22" ht="16.8" customHeight="1" thickBot="1">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="G6" s="6">
         <v>20619</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="K6" s="8">
         <v>70</v>
@@ -996,16 +995,17 @@
         <v>3</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="R6" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="S6" s="14" t="s">
-        <v>31</v>
+      <c r="P6" s="13"/>
+      <c r="R6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="T6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U6">
         <v>1</v>
@@ -1016,2092 +1016,2609 @@
     </row>
     <row r="7" spans="1:22">
       <c r="O7" s="7"/>
+      <c r="P7" s="13"/>
     </row>
     <row r="8" spans="1:22">
       <c r="O8" s="7"/>
-      <c r="R8" s="12"/>
+      <c r="P8" s="13"/>
+      <c r="R8" s="11"/>
     </row>
     <row r="9" spans="1:22">
       <c r="O9" s="7"/>
-      <c r="R9" s="12"/>
+      <c r="P9" s="13"/>
+      <c r="R9" s="11"/>
     </row>
     <row r="10" spans="1:22">
       <c r="O10" s="7"/>
-      <c r="R10" s="12"/>
+      <c r="P10" s="13"/>
+      <c r="R10" s="11"/>
     </row>
     <row r="11" spans="1:22">
       <c r="O11" s="7"/>
-      <c r="R11" s="12"/>
+      <c r="P11" s="13"/>
+      <c r="R11" s="11"/>
     </row>
     <row r="12" spans="1:22">
       <c r="O12" s="7"/>
-      <c r="R12" s="12"/>
+      <c r="P12" s="13"/>
+      <c r="R12" s="11"/>
     </row>
     <row r="13" spans="1:22">
       <c r="O13" s="7"/>
-      <c r="R13" s="12"/>
+      <c r="P13" s="13"/>
+      <c r="R13" s="11"/>
     </row>
     <row r="14" spans="1:22">
       <c r="O14" s="7"/>
-      <c r="R14" s="12"/>
+      <c r="P14" s="13"/>
+      <c r="R14" s="11"/>
     </row>
     <row r="15" spans="1:22">
       <c r="O15" s="7"/>
-      <c r="R15" s="12"/>
+      <c r="P15" s="13"/>
+      <c r="R15" s="11"/>
     </row>
     <row r="16" spans="1:22">
       <c r="O16" s="7"/>
-      <c r="R16" s="12"/>
+      <c r="P16" s="13"/>
+      <c r="R16" s="11"/>
     </row>
     <row r="17" spans="15:18">
       <c r="O17" s="7"/>
-      <c r="R17" s="12"/>
+      <c r="P17" s="13"/>
+      <c r="R17" s="11"/>
     </row>
     <row r="18" spans="15:18">
       <c r="O18" s="7"/>
-      <c r="R18" s="12"/>
+      <c r="P18" s="13"/>
+      <c r="R18" s="11"/>
     </row>
     <row r="19" spans="15:18">
       <c r="O19" s="7"/>
-      <c r="R19" s="12"/>
+      <c r="P19" s="13"/>
+      <c r="R19" s="11"/>
     </row>
     <row r="20" spans="15:18">
       <c r="O20" s="7"/>
-      <c r="R20" s="12"/>
+      <c r="P20" s="13"/>
+      <c r="R20" s="11"/>
     </row>
     <row r="21" spans="15:18">
       <c r="O21" s="7"/>
-      <c r="R21" s="12"/>
+      <c r="P21" s="13"/>
+      <c r="R21" s="11"/>
     </row>
     <row r="22" spans="15:18">
       <c r="O22" s="7"/>
-      <c r="R22" s="12"/>
+      <c r="P22" s="13"/>
+      <c r="R22" s="11"/>
     </row>
     <row r="23" spans="15:18">
       <c r="O23" s="7"/>
-      <c r="R23" s="12"/>
+      <c r="P23" s="13"/>
+      <c r="R23" s="11"/>
     </row>
     <row r="24" spans="15:18">
       <c r="O24" s="7"/>
-      <c r="R24" s="12"/>
+      <c r="P24" s="13"/>
+      <c r="R24" s="11"/>
     </row>
     <row r="25" spans="15:18">
       <c r="O25" s="7"/>
-      <c r="R25" s="12"/>
+      <c r="P25" s="13"/>
+      <c r="R25" s="11"/>
     </row>
     <row r="26" spans="15:18">
       <c r="O26" s="7"/>
-      <c r="R26" s="12"/>
+      <c r="P26" s="13"/>
+      <c r="R26" s="11"/>
     </row>
     <row r="27" spans="15:18">
       <c r="O27" s="7"/>
-      <c r="R27" s="12"/>
+      <c r="P27" s="13"/>
+      <c r="R27" s="11"/>
     </row>
     <row r="28" spans="15:18">
       <c r="O28" s="7"/>
-      <c r="R28" s="12"/>
+      <c r="P28" s="13"/>
+      <c r="R28" s="11"/>
     </row>
     <row r="29" spans="15:18">
       <c r="O29" s="7"/>
-      <c r="R29" s="12"/>
+      <c r="P29" s="13"/>
+      <c r="R29" s="11"/>
     </row>
     <row r="30" spans="15:18">
       <c r="O30" s="7"/>
-      <c r="R30" s="12"/>
+      <c r="P30" s="13"/>
+      <c r="R30" s="11"/>
     </row>
     <row r="31" spans="15:18">
       <c r="O31" s="7"/>
-      <c r="R31" s="12"/>
+      <c r="P31" s="13"/>
+      <c r="R31" s="11"/>
     </row>
     <row r="32" spans="15:18">
       <c r="O32" s="7"/>
-      <c r="R32" s="12"/>
+      <c r="P32" s="13"/>
+      <c r="R32" s="11"/>
     </row>
     <row r="33" spans="15:18">
       <c r="O33" s="7"/>
-      <c r="R33" s="12"/>
+      <c r="P33" s="13"/>
+      <c r="R33" s="11"/>
     </row>
     <row r="34" spans="15:18">
       <c r="O34" s="7"/>
-      <c r="R34" s="12"/>
+      <c r="P34" s="13"/>
+      <c r="R34" s="11"/>
     </row>
     <row r="35" spans="15:18">
       <c r="O35" s="7"/>
-      <c r="R35" s="12"/>
+      <c r="P35" s="13"/>
+      <c r="R35" s="11"/>
     </row>
     <row r="36" spans="15:18">
       <c r="O36" s="7"/>
-      <c r="R36" s="12"/>
+      <c r="P36" s="13"/>
+      <c r="R36" s="11"/>
     </row>
     <row r="37" spans="15:18">
       <c r="O37" s="7"/>
-      <c r="R37" s="12"/>
+      <c r="P37" s="13"/>
+      <c r="R37" s="11"/>
     </row>
     <row r="38" spans="15:18">
       <c r="O38" s="7"/>
-      <c r="R38" s="12"/>
+      <c r="P38" s="13"/>
+      <c r="R38" s="11"/>
     </row>
     <row r="39" spans="15:18">
       <c r="O39" s="7"/>
-      <c r="R39" s="12"/>
+      <c r="P39" s="13"/>
+      <c r="R39" s="11"/>
     </row>
     <row r="40" spans="15:18">
       <c r="O40" s="7"/>
-      <c r="R40" s="12"/>
+      <c r="P40" s="13"/>
+      <c r="R40" s="11"/>
     </row>
     <row r="41" spans="15:18">
       <c r="O41" s="7"/>
-      <c r="R41" s="12"/>
+      <c r="P41" s="13"/>
+      <c r="R41" s="11"/>
     </row>
     <row r="42" spans="15:18">
       <c r="O42" s="7"/>
-      <c r="R42" s="12"/>
+      <c r="P42" s="13"/>
+      <c r="R42" s="11"/>
     </row>
     <row r="43" spans="15:18">
       <c r="O43" s="7"/>
-      <c r="R43" s="12"/>
+      <c r="P43" s="13"/>
+      <c r="R43" s="11"/>
     </row>
     <row r="44" spans="15:18">
       <c r="O44" s="7"/>
-      <c r="R44" s="12"/>
+      <c r="P44" s="13"/>
+      <c r="R44" s="11"/>
     </row>
     <row r="45" spans="15:18">
       <c r="O45" s="7"/>
-      <c r="R45" s="12"/>
+      <c r="P45" s="13"/>
+      <c r="R45" s="11"/>
     </row>
     <row r="46" spans="15:18">
       <c r="O46" s="7"/>
-      <c r="R46" s="12"/>
+      <c r="P46" s="13"/>
+      <c r="R46" s="11"/>
     </row>
     <row r="47" spans="15:18">
       <c r="O47" s="7"/>
-      <c r="R47" s="12"/>
+      <c r="P47" s="13"/>
+      <c r="R47" s="11"/>
     </row>
     <row r="48" spans="15:18">
       <c r="O48" s="7"/>
-      <c r="R48" s="12"/>
+      <c r="P48" s="13"/>
+      <c r="R48" s="11"/>
     </row>
     <row r="49" spans="15:18">
       <c r="O49" s="7"/>
-      <c r="R49" s="12"/>
+      <c r="P49" s="13"/>
+      <c r="R49" s="11"/>
     </row>
     <row r="50" spans="15:18">
       <c r="O50" s="7"/>
-      <c r="R50" s="12"/>
+      <c r="P50" s="13"/>
+      <c r="R50" s="11"/>
     </row>
     <row r="51" spans="15:18">
       <c r="O51" s="7"/>
-      <c r="R51" s="12"/>
+      <c r="P51" s="13"/>
+      <c r="R51" s="11"/>
     </row>
     <row r="52" spans="15:18">
       <c r="O52" s="7"/>
-      <c r="R52" s="12"/>
+      <c r="P52" s="13"/>
+      <c r="R52" s="11"/>
     </row>
     <row r="53" spans="15:18">
       <c r="O53" s="7"/>
-      <c r="R53" s="12"/>
+      <c r="P53" s="13"/>
+      <c r="R53" s="11"/>
     </row>
     <row r="54" spans="15:18">
       <c r="O54" s="7"/>
-      <c r="R54" s="12"/>
+      <c r="P54" s="13"/>
+      <c r="R54" s="11"/>
     </row>
     <row r="55" spans="15:18">
       <c r="O55" s="7"/>
-      <c r="R55" s="12"/>
+      <c r="P55" s="13"/>
+      <c r="R55" s="11"/>
     </row>
     <row r="56" spans="15:18">
       <c r="O56" s="7"/>
-      <c r="R56" s="12"/>
+      <c r="P56" s="13"/>
+      <c r="R56" s="11"/>
     </row>
     <row r="57" spans="15:18">
       <c r="O57" s="7"/>
-      <c r="R57" s="12"/>
+      <c r="P57" s="13"/>
+      <c r="R57" s="11"/>
     </row>
     <row r="58" spans="15:18">
       <c r="O58" s="7"/>
-      <c r="R58" s="12"/>
+      <c r="P58" s="13"/>
+      <c r="R58" s="11"/>
     </row>
     <row r="59" spans="15:18">
       <c r="O59" s="7"/>
-      <c r="R59" s="12"/>
+      <c r="P59" s="13"/>
+      <c r="R59" s="11"/>
     </row>
     <row r="60" spans="15:18">
       <c r="O60" s="7"/>
-      <c r="R60" s="12"/>
+      <c r="P60" s="13"/>
+      <c r="R60" s="11"/>
     </row>
     <row r="61" spans="15:18">
       <c r="O61" s="7"/>
-      <c r="R61" s="12"/>
+      <c r="P61" s="13"/>
+      <c r="R61" s="11"/>
     </row>
     <row r="62" spans="15:18">
       <c r="O62" s="7"/>
-      <c r="R62" s="12"/>
+      <c r="P62" s="13"/>
+      <c r="R62" s="11"/>
     </row>
     <row r="63" spans="15:18">
       <c r="O63" s="7"/>
-      <c r="R63" s="12"/>
+      <c r="P63" s="13"/>
+      <c r="R63" s="11"/>
     </row>
     <row r="64" spans="15:18">
       <c r="O64" s="7"/>
-      <c r="R64" s="12"/>
+      <c r="P64" s="13"/>
+      <c r="R64" s="11"/>
     </row>
     <row r="65" spans="15:18">
       <c r="O65" s="7"/>
-      <c r="R65" s="12"/>
+      <c r="P65" s="13"/>
+      <c r="R65" s="11"/>
     </row>
     <row r="66" spans="15:18">
       <c r="O66" s="7"/>
-      <c r="R66" s="12"/>
+      <c r="P66" s="13"/>
+      <c r="R66" s="11"/>
     </row>
     <row r="67" spans="15:18">
       <c r="O67" s="7"/>
-      <c r="R67" s="12"/>
+      <c r="P67" s="13"/>
+      <c r="R67" s="11"/>
     </row>
     <row r="68" spans="15:18">
       <c r="O68" s="7"/>
-      <c r="R68" s="12"/>
+      <c r="P68" s="13"/>
+      <c r="R68" s="11"/>
     </row>
     <row r="69" spans="15:18">
       <c r="O69" s="7"/>
-      <c r="R69" s="12"/>
+      <c r="P69" s="13"/>
+      <c r="R69" s="11"/>
     </row>
     <row r="70" spans="15:18">
       <c r="O70" s="7"/>
-      <c r="R70" s="12"/>
+      <c r="P70" s="13"/>
+      <c r="R70" s="11"/>
     </row>
     <row r="71" spans="15:18">
       <c r="O71" s="7"/>
-      <c r="R71" s="12"/>
+      <c r="P71" s="13"/>
+      <c r="R71" s="11"/>
     </row>
     <row r="72" spans="15:18">
       <c r="O72" s="7"/>
-      <c r="R72" s="12"/>
+      <c r="P72" s="13"/>
+      <c r="R72" s="11"/>
     </row>
     <row r="73" spans="15:18">
       <c r="O73" s="7"/>
-      <c r="R73" s="12"/>
+      <c r="P73" s="13"/>
+      <c r="R73" s="11"/>
     </row>
     <row r="74" spans="15:18">
       <c r="O74" s="7"/>
-      <c r="R74" s="12"/>
+      <c r="P74" s="13"/>
+      <c r="R74" s="11"/>
     </row>
     <row r="75" spans="15:18">
       <c r="O75" s="7"/>
-      <c r="R75" s="12"/>
+      <c r="P75" s="13"/>
+      <c r="R75" s="11"/>
     </row>
     <row r="76" spans="15:18">
       <c r="O76" s="7"/>
-      <c r="R76" s="12"/>
+      <c r="P76" s="13"/>
+      <c r="R76" s="11"/>
     </row>
     <row r="77" spans="15:18">
       <c r="O77" s="7"/>
-      <c r="R77" s="12"/>
+      <c r="P77" s="13"/>
+      <c r="R77" s="11"/>
     </row>
     <row r="78" spans="15:18">
       <c r="O78" s="7"/>
-      <c r="R78" s="12"/>
+      <c r="P78" s="13"/>
+      <c r="R78" s="11"/>
     </row>
     <row r="79" spans="15:18">
       <c r="O79" s="7"/>
-      <c r="R79" s="12"/>
+      <c r="P79" s="13"/>
+      <c r="R79" s="11"/>
     </row>
     <row r="80" spans="15:18">
       <c r="O80" s="7"/>
-      <c r="R80" s="12"/>
+      <c r="P80" s="13"/>
+      <c r="R80" s="11"/>
     </row>
     <row r="81" spans="15:18">
       <c r="O81" s="7"/>
-      <c r="R81" s="12"/>
+      <c r="P81" s="13"/>
+      <c r="R81" s="11"/>
     </row>
     <row r="82" spans="15:18">
       <c r="O82" s="7"/>
-      <c r="R82" s="12"/>
+      <c r="P82" s="13"/>
+      <c r="R82" s="11"/>
     </row>
     <row r="83" spans="15:18">
       <c r="O83" s="7"/>
-      <c r="R83" s="12"/>
+      <c r="P83" s="13"/>
+      <c r="R83" s="11"/>
     </row>
     <row r="84" spans="15:18">
       <c r="O84" s="7"/>
-      <c r="R84" s="12"/>
+      <c r="P84" s="13"/>
+      <c r="R84" s="11"/>
     </row>
     <row r="85" spans="15:18">
       <c r="O85" s="7"/>
-      <c r="R85" s="12"/>
+      <c r="P85" s="13"/>
+      <c r="R85" s="11"/>
     </row>
     <row r="86" spans="15:18">
       <c r="O86" s="7"/>
-      <c r="R86" s="12"/>
+      <c r="P86" s="13"/>
+      <c r="R86" s="11"/>
     </row>
     <row r="87" spans="15:18">
       <c r="O87" s="7"/>
-      <c r="R87" s="12"/>
+      <c r="P87" s="13"/>
+      <c r="R87" s="11"/>
     </row>
     <row r="88" spans="15:18">
       <c r="O88" s="7"/>
-      <c r="R88" s="12"/>
+      <c r="P88" s="13"/>
+      <c r="R88" s="11"/>
     </row>
     <row r="89" spans="15:18">
       <c r="O89" s="7"/>
-      <c r="R89" s="12"/>
+      <c r="P89" s="13"/>
+      <c r="R89" s="11"/>
     </row>
     <row r="90" spans="15:18">
       <c r="O90" s="7"/>
-      <c r="R90" s="12"/>
+      <c r="P90" s="13"/>
+      <c r="R90" s="11"/>
     </row>
     <row r="91" spans="15:18">
       <c r="O91" s="7"/>
-      <c r="R91" s="12"/>
+      <c r="P91" s="13"/>
+      <c r="R91" s="11"/>
     </row>
     <row r="92" spans="15:18">
       <c r="O92" s="7"/>
-      <c r="R92" s="12"/>
+      <c r="P92" s="13"/>
+      <c r="R92" s="11"/>
     </row>
     <row r="93" spans="15:18">
       <c r="O93" s="7"/>
-      <c r="R93" s="12"/>
+      <c r="P93" s="13"/>
+      <c r="R93" s="11"/>
     </row>
     <row r="94" spans="15:18">
       <c r="O94" s="7"/>
-      <c r="R94" s="12"/>
+      <c r="P94" s="13"/>
+      <c r="R94" s="11"/>
     </row>
     <row r="95" spans="15:18">
       <c r="O95" s="7"/>
-      <c r="R95" s="12"/>
+      <c r="P95" s="13"/>
+      <c r="R95" s="11"/>
     </row>
     <row r="96" spans="15:18">
       <c r="O96" s="7"/>
-      <c r="R96" s="12"/>
+      <c r="P96" s="13"/>
+      <c r="R96" s="11"/>
     </row>
     <row r="97" spans="15:18">
       <c r="O97" s="7"/>
-      <c r="R97" s="12"/>
+      <c r="P97" s="13"/>
+      <c r="R97" s="11"/>
     </row>
     <row r="98" spans="15:18">
       <c r="O98" s="7"/>
-      <c r="R98" s="12"/>
+      <c r="P98" s="13"/>
+      <c r="R98" s="11"/>
     </row>
     <row r="99" spans="15:18">
       <c r="O99" s="7"/>
-      <c r="R99" s="12"/>
+      <c r="P99" s="13"/>
+      <c r="R99" s="11"/>
     </row>
     <row r="100" spans="15:18">
       <c r="O100" s="7"/>
-      <c r="R100" s="12"/>
+      <c r="P100" s="13"/>
+      <c r="R100" s="11"/>
     </row>
     <row r="101" spans="15:18">
       <c r="O101" s="7"/>
-      <c r="R101" s="12"/>
+      <c r="P101" s="13"/>
+      <c r="R101" s="11"/>
     </row>
     <row r="102" spans="15:18">
       <c r="O102" s="7"/>
-      <c r="R102" s="12"/>
+      <c r="P102" s="13"/>
+      <c r="R102" s="11"/>
     </row>
     <row r="103" spans="15:18">
       <c r="O103" s="7"/>
-      <c r="R103" s="12"/>
+      <c r="P103" s="13"/>
+      <c r="R103" s="11"/>
     </row>
     <row r="104" spans="15:18">
       <c r="O104" s="7"/>
-      <c r="R104" s="12"/>
+      <c r="P104" s="13"/>
+      <c r="R104" s="11"/>
     </row>
     <row r="105" spans="15:18">
       <c r="O105" s="7"/>
-      <c r="R105" s="12"/>
+      <c r="P105" s="13"/>
+      <c r="R105" s="11"/>
     </row>
     <row r="106" spans="15:18">
       <c r="O106" s="7"/>
-      <c r="R106" s="12"/>
+      <c r="P106" s="13"/>
+      <c r="R106" s="11"/>
     </row>
     <row r="107" spans="15:18">
       <c r="O107" s="7"/>
-      <c r="R107" s="12"/>
+      <c r="P107" s="13"/>
+      <c r="R107" s="11"/>
     </row>
     <row r="108" spans="15:18">
       <c r="O108" s="7"/>
-      <c r="R108" s="12"/>
+      <c r="P108" s="13"/>
+      <c r="R108" s="11"/>
     </row>
     <row r="109" spans="15:18">
       <c r="O109" s="7"/>
-      <c r="R109" s="12"/>
+      <c r="P109" s="13"/>
+      <c r="R109" s="11"/>
     </row>
     <row r="110" spans="15:18">
       <c r="O110" s="7"/>
-      <c r="R110" s="12"/>
+      <c r="P110" s="13"/>
+      <c r="R110" s="11"/>
     </row>
     <row r="111" spans="15:18">
       <c r="O111" s="7"/>
-      <c r="R111" s="12"/>
+      <c r="P111" s="13"/>
+      <c r="R111" s="11"/>
     </row>
     <row r="112" spans="15:18">
       <c r="O112" s="7"/>
-      <c r="R112" s="12"/>
+      <c r="P112" s="13"/>
+      <c r="R112" s="11"/>
     </row>
     <row r="113" spans="15:18">
       <c r="O113" s="7"/>
-      <c r="R113" s="12"/>
+      <c r="P113" s="13"/>
+      <c r="R113" s="11"/>
     </row>
     <row r="114" spans="15:18">
       <c r="O114" s="7"/>
-      <c r="R114" s="12"/>
+      <c r="P114" s="13"/>
+      <c r="R114" s="11"/>
     </row>
     <row r="115" spans="15:18">
       <c r="O115" s="7"/>
-      <c r="R115" s="12"/>
+      <c r="P115" s="13"/>
+      <c r="R115" s="11"/>
     </row>
     <row r="116" spans="15:18">
       <c r="O116" s="7"/>
-      <c r="R116" s="12"/>
+      <c r="P116" s="13"/>
+      <c r="R116" s="11"/>
     </row>
     <row r="117" spans="15:18">
       <c r="O117" s="7"/>
-      <c r="R117" s="12"/>
+      <c r="P117" s="13"/>
+      <c r="R117" s="11"/>
     </row>
     <row r="118" spans="15:18">
       <c r="O118" s="7"/>
-      <c r="R118" s="12"/>
+      <c r="P118" s="13"/>
+      <c r="R118" s="11"/>
     </row>
     <row r="119" spans="15:18">
       <c r="O119" s="7"/>
-      <c r="R119" s="12"/>
+      <c r="P119" s="13"/>
+      <c r="R119" s="11"/>
     </row>
     <row r="120" spans="15:18">
       <c r="O120" s="7"/>
-      <c r="R120" s="12"/>
+      <c r="P120" s="13"/>
+      <c r="R120" s="11"/>
     </row>
     <row r="121" spans="15:18">
       <c r="O121" s="7"/>
-      <c r="R121" s="12"/>
+      <c r="P121" s="13"/>
+      <c r="R121" s="11"/>
     </row>
     <row r="122" spans="15:18">
       <c r="O122" s="7"/>
-      <c r="R122" s="12"/>
+      <c r="P122" s="13"/>
+      <c r="R122" s="11"/>
     </row>
     <row r="123" spans="15:18">
       <c r="O123" s="7"/>
-      <c r="R123" s="12"/>
+      <c r="P123" s="13"/>
+      <c r="R123" s="11"/>
     </row>
     <row r="124" spans="15:18">
       <c r="O124" s="7"/>
-      <c r="R124" s="12"/>
+      <c r="P124" s="13"/>
+      <c r="R124" s="11"/>
     </row>
     <row r="125" spans="15:18">
       <c r="O125" s="7"/>
-      <c r="R125" s="12"/>
+      <c r="P125" s="13"/>
+      <c r="R125" s="11"/>
     </row>
     <row r="126" spans="15:18">
       <c r="O126" s="7"/>
-      <c r="R126" s="12"/>
+      <c r="P126" s="13"/>
+      <c r="R126" s="11"/>
     </row>
     <row r="127" spans="15:18">
       <c r="O127" s="7"/>
-      <c r="R127" s="12"/>
+      <c r="P127" s="13"/>
+      <c r="R127" s="11"/>
     </row>
     <row r="128" spans="15:18">
       <c r="O128" s="7"/>
-      <c r="R128" s="12"/>
+      <c r="P128" s="13"/>
+      <c r="R128" s="11"/>
     </row>
     <row r="129" spans="15:18">
       <c r="O129" s="7"/>
-      <c r="R129" s="12"/>
+      <c r="P129" s="13"/>
+      <c r="R129" s="11"/>
     </row>
     <row r="130" spans="15:18">
       <c r="O130" s="7"/>
-      <c r="R130" s="12"/>
+      <c r="P130" s="13"/>
+      <c r="R130" s="11"/>
     </row>
     <row r="131" spans="15:18">
       <c r="O131" s="7"/>
-      <c r="R131" s="12"/>
+      <c r="P131" s="13"/>
+      <c r="R131" s="11"/>
     </row>
     <row r="132" spans="15:18">
       <c r="O132" s="7"/>
-      <c r="R132" s="12"/>
+      <c r="P132" s="13"/>
+      <c r="R132" s="11"/>
     </row>
     <row r="133" spans="15:18">
       <c r="O133" s="7"/>
-      <c r="R133" s="12"/>
+      <c r="P133" s="13"/>
+      <c r="R133" s="11"/>
     </row>
     <row r="134" spans="15:18">
       <c r="O134" s="7"/>
-      <c r="R134" s="12"/>
+      <c r="P134" s="13"/>
+      <c r="R134" s="11"/>
     </row>
     <row r="135" spans="15:18">
       <c r="O135" s="7"/>
-      <c r="R135" s="12"/>
+      <c r="P135" s="13"/>
+      <c r="R135" s="11"/>
     </row>
     <row r="136" spans="15:18">
       <c r="O136" s="7"/>
-      <c r="R136" s="12"/>
+      <c r="P136" s="13"/>
+      <c r="R136" s="11"/>
     </row>
     <row r="137" spans="15:18">
       <c r="O137" s="7"/>
-      <c r="R137" s="12"/>
+      <c r="P137" s="13"/>
+      <c r="R137" s="11"/>
     </row>
     <row r="138" spans="15:18">
       <c r="O138" s="7"/>
-      <c r="R138" s="12"/>
+      <c r="P138" s="13"/>
+      <c r="R138" s="11"/>
     </row>
     <row r="139" spans="15:18">
       <c r="O139" s="7"/>
-      <c r="R139" s="12"/>
+      <c r="P139" s="13"/>
+      <c r="R139" s="11"/>
     </row>
     <row r="140" spans="15:18">
       <c r="O140" s="7"/>
-      <c r="R140" s="12"/>
+      <c r="P140" s="13"/>
+      <c r="R140" s="11"/>
     </row>
     <row r="141" spans="15:18">
       <c r="O141" s="7"/>
-      <c r="R141" s="12"/>
+      <c r="P141" s="13"/>
+      <c r="R141" s="11"/>
     </row>
     <row r="142" spans="15:18">
       <c r="O142" s="7"/>
-      <c r="R142" s="12"/>
+      <c r="P142" s="13"/>
+      <c r="R142" s="11"/>
     </row>
     <row r="143" spans="15:18">
       <c r="O143" s="7"/>
-      <c r="R143" s="12"/>
+      <c r="P143" s="13"/>
+      <c r="R143" s="11"/>
     </row>
     <row r="144" spans="15:18">
       <c r="O144" s="7"/>
-      <c r="R144" s="12"/>
+      <c r="P144" s="13"/>
+      <c r="R144" s="11"/>
     </row>
     <row r="145" spans="15:18">
       <c r="O145" s="7"/>
-      <c r="R145" s="12"/>
+      <c r="P145" s="13"/>
+      <c r="R145" s="11"/>
     </row>
     <row r="146" spans="15:18">
       <c r="O146" s="7"/>
-      <c r="R146" s="12"/>
+      <c r="P146" s="13"/>
+      <c r="R146" s="11"/>
     </row>
     <row r="147" spans="15:18">
       <c r="O147" s="7"/>
-      <c r="R147" s="12"/>
+      <c r="P147" s="13"/>
+      <c r="R147" s="11"/>
     </row>
     <row r="148" spans="15:18">
       <c r="O148" s="7"/>
-      <c r="R148" s="12"/>
+      <c r="P148" s="13"/>
+      <c r="R148" s="11"/>
     </row>
     <row r="149" spans="15:18">
       <c r="O149" s="7"/>
-      <c r="R149" s="12"/>
+      <c r="P149" s="13"/>
+      <c r="R149" s="11"/>
     </row>
     <row r="150" spans="15:18">
       <c r="O150" s="7"/>
-      <c r="R150" s="12"/>
+      <c r="P150" s="13"/>
+      <c r="R150" s="11"/>
     </row>
     <row r="151" spans="15:18">
       <c r="O151" s="7"/>
-      <c r="R151" s="12"/>
+      <c r="P151" s="13"/>
+      <c r="R151" s="11"/>
     </row>
     <row r="152" spans="15:18">
       <c r="O152" s="7"/>
-      <c r="R152" s="12"/>
+      <c r="P152" s="13"/>
+      <c r="R152" s="11"/>
     </row>
     <row r="153" spans="15:18">
       <c r="O153" s="7"/>
-      <c r="R153" s="12"/>
+      <c r="P153" s="13"/>
+      <c r="R153" s="11"/>
     </row>
     <row r="154" spans="15:18">
       <c r="O154" s="7"/>
-      <c r="R154" s="12"/>
+      <c r="P154" s="13"/>
+      <c r="R154" s="11"/>
     </row>
     <row r="155" spans="15:18">
       <c r="O155" s="7"/>
-      <c r="R155" s="12"/>
+      <c r="P155" s="13"/>
+      <c r="R155" s="11"/>
     </row>
     <row r="156" spans="15:18">
       <c r="O156" s="7"/>
-      <c r="R156" s="12"/>
+      <c r="P156" s="13"/>
+      <c r="R156" s="11"/>
     </row>
     <row r="157" spans="15:18">
       <c r="O157" s="7"/>
-      <c r="R157" s="12"/>
+      <c r="P157" s="13"/>
+      <c r="R157" s="11"/>
     </row>
     <row r="158" spans="15:18">
       <c r="O158" s="7"/>
-      <c r="R158" s="12"/>
+      <c r="P158" s="13"/>
+      <c r="R158" s="11"/>
     </row>
     <row r="159" spans="15:18">
       <c r="O159" s="7"/>
-      <c r="R159" s="12"/>
+      <c r="P159" s="13"/>
+      <c r="R159" s="11"/>
     </row>
     <row r="160" spans="15:18">
       <c r="O160" s="7"/>
-      <c r="R160" s="12"/>
+      <c r="P160" s="13"/>
+      <c r="R160" s="11"/>
     </row>
     <row r="161" spans="15:18">
       <c r="O161" s="7"/>
-      <c r="R161" s="12"/>
+      <c r="P161" s="13"/>
+      <c r="R161" s="11"/>
     </row>
     <row r="162" spans="15:18">
       <c r="O162" s="7"/>
-      <c r="R162" s="12"/>
+      <c r="P162" s="13"/>
+      <c r="R162" s="11"/>
     </row>
     <row r="163" spans="15:18">
       <c r="O163" s="7"/>
-      <c r="R163" s="12"/>
+      <c r="P163" s="13"/>
+      <c r="R163" s="11"/>
     </row>
     <row r="164" spans="15:18">
       <c r="O164" s="7"/>
-      <c r="R164" s="12"/>
+      <c r="P164" s="13"/>
+      <c r="R164" s="11"/>
     </row>
     <row r="165" spans="15:18">
       <c r="O165" s="7"/>
-      <c r="R165" s="12"/>
+      <c r="P165" s="13"/>
+      <c r="R165" s="11"/>
     </row>
     <row r="166" spans="15:18">
       <c r="O166" s="7"/>
-      <c r="R166" s="12"/>
+      <c r="P166" s="13"/>
+      <c r="R166" s="11"/>
     </row>
     <row r="167" spans="15:18">
       <c r="O167" s="7"/>
-      <c r="R167" s="12"/>
+      <c r="P167" s="13"/>
+      <c r="R167" s="11"/>
     </row>
     <row r="168" spans="15:18">
       <c r="O168" s="7"/>
-      <c r="R168" s="12"/>
+      <c r="P168" s="13"/>
+      <c r="R168" s="11"/>
     </row>
     <row r="169" spans="15:18">
       <c r="O169" s="7"/>
-      <c r="R169" s="12"/>
+      <c r="P169" s="13"/>
+      <c r="R169" s="11"/>
     </row>
     <row r="170" spans="15:18">
       <c r="O170" s="7"/>
-      <c r="R170" s="12"/>
+      <c r="P170" s="13"/>
+      <c r="R170" s="11"/>
     </row>
     <row r="171" spans="15:18">
       <c r="O171" s="7"/>
-      <c r="R171" s="12"/>
+      <c r="P171" s="13"/>
+      <c r="R171" s="11"/>
     </row>
     <row r="172" spans="15:18">
       <c r="O172" s="7"/>
-      <c r="R172" s="12"/>
+      <c r="P172" s="13"/>
+      <c r="R172" s="11"/>
     </row>
     <row r="173" spans="15:18">
       <c r="O173" s="7"/>
-      <c r="R173" s="12"/>
+      <c r="P173" s="13"/>
+      <c r="R173" s="11"/>
     </row>
     <row r="174" spans="15:18">
       <c r="O174" s="7"/>
-      <c r="R174" s="12"/>
+      <c r="P174" s="13"/>
+      <c r="R174" s="11"/>
     </row>
     <row r="175" spans="15:18">
       <c r="O175" s="7"/>
-      <c r="R175" s="12"/>
+      <c r="P175" s="13"/>
+      <c r="R175" s="11"/>
     </row>
     <row r="176" spans="15:18">
       <c r="O176" s="7"/>
-      <c r="R176" s="12"/>
+      <c r="P176" s="13"/>
+      <c r="R176" s="11"/>
     </row>
     <row r="177" spans="15:18">
       <c r="O177" s="7"/>
-      <c r="R177" s="12"/>
+      <c r="P177" s="13"/>
+      <c r="R177" s="11"/>
     </row>
     <row r="178" spans="15:18">
       <c r="O178" s="7"/>
-      <c r="R178" s="12"/>
+      <c r="P178" s="13"/>
+      <c r="R178" s="11"/>
     </row>
     <row r="179" spans="15:18">
       <c r="O179" s="7"/>
-      <c r="R179" s="12"/>
+      <c r="P179" s="13"/>
+      <c r="R179" s="11"/>
     </row>
     <row r="180" spans="15:18">
       <c r="O180" s="7"/>
-      <c r="R180" s="12"/>
+      <c r="P180" s="13"/>
+      <c r="R180" s="11"/>
     </row>
     <row r="181" spans="15:18">
       <c r="O181" s="7"/>
-      <c r="R181" s="12"/>
+      <c r="P181" s="13"/>
+      <c r="R181" s="11"/>
     </row>
     <row r="182" spans="15:18">
       <c r="O182" s="7"/>
-      <c r="R182" s="12"/>
+      <c r="P182" s="13"/>
+      <c r="R182" s="11"/>
     </row>
     <row r="183" spans="15:18">
       <c r="O183" s="7"/>
-      <c r="R183" s="12"/>
+      <c r="P183" s="13"/>
+      <c r="R183" s="11"/>
     </row>
     <row r="184" spans="15:18">
       <c r="O184" s="7"/>
-      <c r="R184" s="12"/>
+      <c r="P184" s="13"/>
+      <c r="R184" s="11"/>
     </row>
     <row r="185" spans="15:18">
       <c r="O185" s="7"/>
-      <c r="R185" s="12"/>
+      <c r="P185" s="13"/>
+      <c r="R185" s="11"/>
     </row>
     <row r="186" spans="15:18">
       <c r="O186" s="7"/>
-      <c r="R186" s="12"/>
+      <c r="P186" s="13"/>
+      <c r="R186" s="11"/>
     </row>
     <row r="187" spans="15:18">
       <c r="O187" s="7"/>
-      <c r="R187" s="12"/>
+      <c r="P187" s="13"/>
+      <c r="R187" s="11"/>
     </row>
     <row r="188" spans="15:18">
       <c r="O188" s="7"/>
-      <c r="R188" s="12"/>
+      <c r="P188" s="13"/>
+      <c r="R188" s="11"/>
     </row>
     <row r="189" spans="15:18">
       <c r="O189" s="7"/>
-      <c r="R189" s="12"/>
+      <c r="P189" s="13"/>
+      <c r="R189" s="11"/>
     </row>
     <row r="190" spans="15:18">
       <c r="O190" s="7"/>
-      <c r="R190" s="12"/>
+      <c r="P190" s="13"/>
+      <c r="R190" s="11"/>
     </row>
     <row r="191" spans="15:18">
       <c r="O191" s="7"/>
-      <c r="R191" s="12"/>
+      <c r="P191" s="13"/>
+      <c r="R191" s="11"/>
     </row>
     <row r="192" spans="15:18">
       <c r="O192" s="7"/>
-      <c r="R192" s="12"/>
+      <c r="P192" s="13"/>
+      <c r="R192" s="11"/>
     </row>
     <row r="193" spans="15:18">
       <c r="O193" s="7"/>
-      <c r="R193" s="12"/>
+      <c r="P193" s="13"/>
+      <c r="R193" s="11"/>
     </row>
     <row r="194" spans="15:18">
       <c r="O194" s="7"/>
-      <c r="R194" s="12"/>
+      <c r="P194" s="13"/>
+      <c r="R194" s="11"/>
     </row>
     <row r="195" spans="15:18">
       <c r="O195" s="7"/>
-      <c r="R195" s="12"/>
+      <c r="P195" s="13"/>
+      <c r="R195" s="11"/>
     </row>
     <row r="196" spans="15:18">
       <c r="O196" s="7"/>
-      <c r="R196" s="12"/>
+      <c r="P196" s="13"/>
+      <c r="R196" s="11"/>
     </row>
     <row r="197" spans="15:18">
       <c r="O197" s="7"/>
-      <c r="R197" s="12"/>
+      <c r="P197" s="13"/>
+      <c r="R197" s="11"/>
     </row>
     <row r="198" spans="15:18">
       <c r="O198" s="7"/>
-      <c r="R198" s="12"/>
+      <c r="P198" s="13"/>
+      <c r="R198" s="11"/>
     </row>
     <row r="199" spans="15:18">
       <c r="O199" s="7"/>
-      <c r="R199" s="12"/>
+      <c r="P199" s="13"/>
+      <c r="R199" s="11"/>
     </row>
     <row r="200" spans="15:18">
       <c r="O200" s="7"/>
-      <c r="R200" s="12"/>
+      <c r="P200" s="13"/>
+      <c r="R200" s="11"/>
     </row>
     <row r="201" spans="15:18">
       <c r="O201" s="7"/>
-      <c r="R201" s="12"/>
+      <c r="P201" s="13"/>
+      <c r="R201" s="11"/>
     </row>
     <row r="202" spans="15:18">
       <c r="O202" s="7"/>
-      <c r="R202" s="12"/>
+      <c r="P202" s="13"/>
+      <c r="R202" s="11"/>
     </row>
     <row r="203" spans="15:18">
       <c r="O203" s="7"/>
-      <c r="R203" s="12"/>
+      <c r="P203" s="13"/>
+      <c r="R203" s="11"/>
     </row>
     <row r="204" spans="15:18">
       <c r="O204" s="7"/>
-      <c r="R204" s="12"/>
+      <c r="P204" s="13"/>
+      <c r="R204" s="11"/>
     </row>
     <row r="205" spans="15:18">
       <c r="O205" s="7"/>
-      <c r="R205" s="12"/>
+      <c r="P205" s="13"/>
+      <c r="R205" s="11"/>
     </row>
     <row r="206" spans="15:18">
       <c r="O206" s="7"/>
-      <c r="R206" s="12"/>
+      <c r="P206" s="13"/>
+      <c r="R206" s="11"/>
     </row>
     <row r="207" spans="15:18">
       <c r="O207" s="7"/>
-      <c r="R207" s="12"/>
+      <c r="P207" s="13"/>
+      <c r="R207" s="11"/>
     </row>
     <row r="208" spans="15:18">
       <c r="O208" s="7"/>
-      <c r="R208" s="12"/>
+      <c r="P208" s="13"/>
+      <c r="R208" s="11"/>
     </row>
     <row r="209" spans="15:18">
       <c r="O209" s="7"/>
-      <c r="R209" s="12"/>
+      <c r="P209" s="13"/>
+      <c r="R209" s="11"/>
     </row>
     <row r="210" spans="15:18">
       <c r="O210" s="7"/>
-      <c r="R210" s="12"/>
+      <c r="P210" s="13"/>
+      <c r="R210" s="11"/>
     </row>
     <row r="211" spans="15:18">
       <c r="O211" s="7"/>
-      <c r="R211" s="12"/>
+      <c r="P211" s="13"/>
+      <c r="R211" s="11"/>
     </row>
     <row r="212" spans="15:18">
       <c r="O212" s="7"/>
-      <c r="R212" s="12"/>
+      <c r="P212" s="13"/>
+      <c r="R212" s="11"/>
     </row>
     <row r="213" spans="15:18">
       <c r="O213" s="7"/>
-      <c r="R213" s="12"/>
+      <c r="P213" s="13"/>
+      <c r="R213" s="11"/>
     </row>
     <row r="214" spans="15:18">
       <c r="O214" s="7"/>
-      <c r="R214" s="12"/>
+      <c r="P214" s="13"/>
+      <c r="R214" s="11"/>
     </row>
     <row r="215" spans="15:18">
       <c r="O215" s="7"/>
-      <c r="R215" s="12"/>
+      <c r="P215" s="13"/>
+      <c r="R215" s="11"/>
     </row>
     <row r="216" spans="15:18">
       <c r="O216" s="7"/>
-      <c r="R216" s="12"/>
+      <c r="P216" s="13"/>
+      <c r="R216" s="11"/>
     </row>
     <row r="217" spans="15:18">
       <c r="O217" s="7"/>
-      <c r="R217" s="12"/>
+      <c r="P217" s="13"/>
+      <c r="R217" s="11"/>
     </row>
     <row r="218" spans="15:18">
       <c r="O218" s="7"/>
-      <c r="R218" s="12"/>
+      <c r="P218" s="13"/>
+      <c r="R218" s="11"/>
     </row>
     <row r="219" spans="15:18">
       <c r="O219" s="7"/>
-      <c r="R219" s="12"/>
+      <c r="P219" s="13"/>
+      <c r="R219" s="11"/>
     </row>
     <row r="220" spans="15:18">
       <c r="O220" s="7"/>
-      <c r="R220" s="12"/>
+      <c r="P220" s="13"/>
+      <c r="R220" s="11"/>
     </row>
     <row r="221" spans="15:18">
       <c r="O221" s="7"/>
-      <c r="R221" s="12"/>
+      <c r="P221" s="13"/>
+      <c r="R221" s="11"/>
     </row>
     <row r="222" spans="15:18">
       <c r="O222" s="7"/>
-      <c r="R222" s="12"/>
+      <c r="P222" s="13"/>
+      <c r="R222" s="11"/>
     </row>
     <row r="223" spans="15:18">
       <c r="O223" s="7"/>
-      <c r="R223" s="12"/>
+      <c r="P223" s="13"/>
+      <c r="R223" s="11"/>
     </row>
     <row r="224" spans="15:18">
       <c r="O224" s="7"/>
-      <c r="R224" s="12"/>
+      <c r="P224" s="13"/>
+      <c r="R224" s="11"/>
     </row>
     <row r="225" spans="15:18">
       <c r="O225" s="7"/>
-      <c r="R225" s="12"/>
+      <c r="P225" s="13"/>
+      <c r="R225" s="11"/>
     </row>
     <row r="226" spans="15:18">
       <c r="O226" s="7"/>
-      <c r="R226" s="12"/>
+      <c r="P226" s="13"/>
+      <c r="R226" s="11"/>
     </row>
     <row r="227" spans="15:18">
       <c r="O227" s="7"/>
-      <c r="R227" s="12"/>
+      <c r="P227" s="13"/>
+      <c r="R227" s="11"/>
     </row>
     <row r="228" spans="15:18">
       <c r="O228" s="7"/>
-      <c r="R228" s="12"/>
+      <c r="P228" s="13"/>
+      <c r="R228" s="11"/>
     </row>
     <row r="229" spans="15:18">
       <c r="O229" s="7"/>
-      <c r="R229" s="12"/>
+      <c r="P229" s="13"/>
+      <c r="R229" s="11"/>
     </row>
     <row r="230" spans="15:18">
       <c r="O230" s="7"/>
-      <c r="R230" s="12"/>
+      <c r="P230" s="13"/>
+      <c r="R230" s="11"/>
     </row>
     <row r="231" spans="15:18">
       <c r="O231" s="7"/>
-      <c r="R231" s="12"/>
+      <c r="P231" s="13"/>
+      <c r="R231" s="11"/>
     </row>
     <row r="232" spans="15:18">
       <c r="O232" s="7"/>
-      <c r="R232" s="12"/>
+      <c r="P232" s="13"/>
+      <c r="R232" s="11"/>
     </row>
     <row r="233" spans="15:18">
       <c r="O233" s="7"/>
-      <c r="R233" s="12"/>
+      <c r="P233" s="13"/>
+      <c r="R233" s="11"/>
     </row>
     <row r="234" spans="15:18">
       <c r="O234" s="7"/>
-      <c r="R234" s="12"/>
+      <c r="P234" s="13"/>
+      <c r="R234" s="11"/>
     </row>
     <row r="235" spans="15:18">
       <c r="O235" s="7"/>
-      <c r="R235" s="12"/>
+      <c r="P235" s="13"/>
+      <c r="R235" s="11"/>
     </row>
     <row r="236" spans="15:18">
       <c r="O236" s="7"/>
-      <c r="R236" s="12"/>
+      <c r="P236" s="13"/>
+      <c r="R236" s="11"/>
     </row>
     <row r="237" spans="15:18">
       <c r="O237" s="7"/>
-      <c r="R237" s="12"/>
+      <c r="P237" s="13"/>
+      <c r="R237" s="11"/>
     </row>
     <row r="238" spans="15:18">
       <c r="O238" s="7"/>
-      <c r="R238" s="12"/>
+      <c r="P238" s="13"/>
+      <c r="R238" s="11"/>
     </row>
     <row r="239" spans="15:18">
       <c r="O239" s="7"/>
-      <c r="R239" s="12"/>
+      <c r="P239" s="13"/>
+      <c r="R239" s="11"/>
     </row>
     <row r="240" spans="15:18">
       <c r="O240" s="7"/>
-      <c r="R240" s="12"/>
+      <c r="P240" s="13"/>
+      <c r="R240" s="11"/>
     </row>
     <row r="241" spans="15:18">
       <c r="O241" s="7"/>
-      <c r="R241" s="12"/>
+      <c r="P241" s="13"/>
+      <c r="R241" s="11"/>
     </row>
     <row r="242" spans="15:18">
       <c r="O242" s="7"/>
-      <c r="R242" s="12"/>
+      <c r="P242" s="13"/>
+      <c r="R242" s="11"/>
     </row>
     <row r="243" spans="15:18">
       <c r="O243" s="7"/>
-      <c r="R243" s="12"/>
+      <c r="P243" s="13"/>
+      <c r="R243" s="11"/>
     </row>
     <row r="244" spans="15:18">
       <c r="O244" s="7"/>
-      <c r="R244" s="12"/>
+      <c r="P244" s="13"/>
+      <c r="R244" s="11"/>
     </row>
     <row r="245" spans="15:18">
       <c r="O245" s="7"/>
-      <c r="R245" s="12"/>
+      <c r="P245" s="13"/>
+      <c r="R245" s="11"/>
     </row>
     <row r="246" spans="15:18">
       <c r="O246" s="7"/>
-      <c r="R246" s="12"/>
+      <c r="P246" s="13"/>
+      <c r="R246" s="11"/>
     </row>
     <row r="247" spans="15:18">
       <c r="O247" s="7"/>
-      <c r="R247" s="12"/>
+      <c r="P247" s="13"/>
+      <c r="R247" s="11"/>
     </row>
     <row r="248" spans="15:18">
       <c r="O248" s="7"/>
-      <c r="R248" s="12"/>
+      <c r="P248" s="13"/>
+      <c r="R248" s="11"/>
     </row>
     <row r="249" spans="15:18">
       <c r="O249" s="7"/>
-      <c r="R249" s="12"/>
+      <c r="P249" s="13"/>
+      <c r="R249" s="11"/>
     </row>
     <row r="250" spans="15:18">
       <c r="O250" s="7"/>
-      <c r="R250" s="12"/>
+      <c r="P250" s="13"/>
+      <c r="R250" s="11"/>
     </row>
     <row r="251" spans="15:18">
       <c r="O251" s="7"/>
-      <c r="R251" s="12"/>
+      <c r="P251" s="13"/>
+      <c r="R251" s="11"/>
     </row>
     <row r="252" spans="15:18">
       <c r="O252" s="7"/>
-      <c r="R252" s="12"/>
+      <c r="P252" s="13"/>
+      <c r="R252" s="11"/>
     </row>
     <row r="253" spans="15:18">
       <c r="O253" s="7"/>
-      <c r="R253" s="12"/>
+      <c r="P253" s="13"/>
+      <c r="R253" s="11"/>
     </row>
     <row r="254" spans="15:18">
       <c r="O254" s="7"/>
-      <c r="R254" s="12"/>
+      <c r="P254" s="13"/>
+      <c r="R254" s="11"/>
     </row>
     <row r="255" spans="15:18">
       <c r="O255" s="7"/>
-      <c r="R255" s="12"/>
+      <c r="P255" s="13"/>
+      <c r="R255" s="11"/>
     </row>
     <row r="256" spans="15:18">
       <c r="O256" s="7"/>
-      <c r="R256" s="12"/>
+      <c r="P256" s="13"/>
+      <c r="R256" s="11"/>
     </row>
     <row r="257" spans="15:18">
       <c r="O257" s="7"/>
-      <c r="R257" s="12"/>
+      <c r="P257" s="13"/>
+      <c r="R257" s="11"/>
     </row>
     <row r="258" spans="15:18">
       <c r="O258" s="7"/>
-      <c r="R258" s="12"/>
+      <c r="P258" s="13"/>
+      <c r="R258" s="11"/>
     </row>
     <row r="259" spans="15:18">
       <c r="O259" s="7"/>
-      <c r="R259" s="12"/>
+      <c r="P259" s="13"/>
+      <c r="R259" s="11"/>
     </row>
     <row r="260" spans="15:18">
       <c r="O260" s="7"/>
-      <c r="R260" s="12"/>
+      <c r="P260" s="13"/>
+      <c r="R260" s="11"/>
     </row>
     <row r="261" spans="15:18">
       <c r="O261" s="7"/>
-      <c r="R261" s="12"/>
+      <c r="P261" s="13"/>
+      <c r="R261" s="11"/>
     </row>
     <row r="262" spans="15:18">
       <c r="O262" s="7"/>
-      <c r="R262" s="12"/>
+      <c r="P262" s="13"/>
+      <c r="R262" s="11"/>
     </row>
     <row r="263" spans="15:18">
       <c r="O263" s="7"/>
-      <c r="R263" s="12"/>
+      <c r="P263" s="13"/>
+      <c r="R263" s="11"/>
     </row>
     <row r="264" spans="15:18">
       <c r="O264" s="7"/>
-      <c r="R264" s="12"/>
+      <c r="P264" s="13"/>
+      <c r="R264" s="11"/>
     </row>
     <row r="265" spans="15:18">
       <c r="O265" s="7"/>
-      <c r="R265" s="12"/>
+      <c r="P265" s="13"/>
+      <c r="R265" s="11"/>
     </row>
     <row r="266" spans="15:18">
       <c r="O266" s="7"/>
-      <c r="R266" s="12"/>
+      <c r="P266" s="13"/>
+      <c r="R266" s="11"/>
     </row>
     <row r="267" spans="15:18">
       <c r="O267" s="7"/>
-      <c r="R267" s="12"/>
+      <c r="P267" s="13"/>
+      <c r="R267" s="11"/>
     </row>
     <row r="268" spans="15:18">
       <c r="O268" s="7"/>
-      <c r="R268" s="12"/>
+      <c r="P268" s="13"/>
+      <c r="R268" s="11"/>
     </row>
     <row r="269" spans="15:18">
       <c r="O269" s="7"/>
-      <c r="R269" s="12"/>
+      <c r="P269" s="13"/>
+      <c r="R269" s="11"/>
     </row>
     <row r="270" spans="15:18">
       <c r="O270" s="7"/>
-      <c r="R270" s="12"/>
+      <c r="P270" s="13"/>
+      <c r="R270" s="11"/>
     </row>
     <row r="271" spans="15:18">
       <c r="O271" s="7"/>
-      <c r="R271" s="12"/>
+      <c r="P271" s="13"/>
+      <c r="R271" s="11"/>
     </row>
     <row r="272" spans="15:18">
       <c r="O272" s="7"/>
-      <c r="R272" s="12"/>
+      <c r="P272" s="13"/>
+      <c r="R272" s="11"/>
     </row>
     <row r="273" spans="15:18">
       <c r="O273" s="7"/>
-      <c r="R273" s="12"/>
+      <c r="P273" s="13"/>
+      <c r="R273" s="11"/>
     </row>
     <row r="274" spans="15:18">
       <c r="O274" s="7"/>
-      <c r="R274" s="12"/>
+      <c r="P274" s="13"/>
+      <c r="R274" s="11"/>
     </row>
     <row r="275" spans="15:18">
       <c r="O275" s="7"/>
-      <c r="R275" s="12"/>
+      <c r="P275" s="13"/>
+      <c r="R275" s="11"/>
     </row>
     <row r="276" spans="15:18">
       <c r="O276" s="7"/>
-      <c r="R276" s="12"/>
+      <c r="P276" s="13"/>
+      <c r="R276" s="11"/>
     </row>
     <row r="277" spans="15:18">
       <c r="O277" s="7"/>
-      <c r="R277" s="12"/>
+      <c r="P277" s="13"/>
+      <c r="R277" s="11"/>
     </row>
     <row r="278" spans="15:18">
       <c r="O278" s="7"/>
-      <c r="R278" s="12"/>
+      <c r="P278" s="13"/>
+      <c r="R278" s="11"/>
     </row>
     <row r="279" spans="15:18">
       <c r="O279" s="7"/>
-      <c r="R279" s="12"/>
+      <c r="P279" s="13"/>
+      <c r="R279" s="11"/>
     </row>
     <row r="280" spans="15:18">
       <c r="O280" s="7"/>
-      <c r="R280" s="12"/>
+      <c r="P280" s="13"/>
+      <c r="R280" s="11"/>
     </row>
     <row r="281" spans="15:18">
       <c r="O281" s="7"/>
-      <c r="R281" s="12"/>
+      <c r="P281" s="13"/>
+      <c r="R281" s="11"/>
     </row>
     <row r="282" spans="15:18">
       <c r="O282" s="7"/>
-      <c r="R282" s="12"/>
+      <c r="P282" s="13"/>
+      <c r="R282" s="11"/>
     </row>
     <row r="283" spans="15:18">
       <c r="O283" s="7"/>
-      <c r="R283" s="12"/>
+      <c r="P283" s="13"/>
+      <c r="R283" s="11"/>
     </row>
     <row r="284" spans="15:18">
       <c r="O284" s="7"/>
-      <c r="R284" s="12"/>
+      <c r="P284" s="13"/>
+      <c r="R284" s="11"/>
     </row>
     <row r="285" spans="15:18">
       <c r="O285" s="7"/>
-      <c r="R285" s="12"/>
+      <c r="P285" s="13"/>
+      <c r="R285" s="11"/>
     </row>
     <row r="286" spans="15:18">
       <c r="O286" s="7"/>
-      <c r="R286" s="12"/>
+      <c r="P286" s="13"/>
+      <c r="R286" s="11"/>
     </row>
     <row r="287" spans="15:18">
       <c r="O287" s="7"/>
-      <c r="R287" s="12"/>
+      <c r="P287" s="13"/>
+      <c r="R287" s="11"/>
     </row>
     <row r="288" spans="15:18">
       <c r="O288" s="7"/>
-      <c r="R288" s="12"/>
+      <c r="P288" s="13"/>
+      <c r="R288" s="11"/>
     </row>
     <row r="289" spans="15:18">
       <c r="O289" s="7"/>
-      <c r="R289" s="12"/>
+      <c r="P289" s="13"/>
+      <c r="R289" s="11"/>
     </row>
     <row r="290" spans="15:18">
       <c r="O290" s="7"/>
-      <c r="R290" s="12"/>
+      <c r="P290" s="13"/>
+      <c r="R290" s="11"/>
     </row>
     <row r="291" spans="15:18">
       <c r="O291" s="7"/>
-      <c r="R291" s="12"/>
+      <c r="P291" s="13"/>
+      <c r="R291" s="11"/>
     </row>
     <row r="292" spans="15:18">
       <c r="O292" s="7"/>
-      <c r="R292" s="12"/>
+      <c r="P292" s="13"/>
+      <c r="R292" s="11"/>
     </row>
     <row r="293" spans="15:18">
       <c r="O293" s="7"/>
-      <c r="R293" s="12"/>
+      <c r="P293" s="13"/>
+      <c r="R293" s="11"/>
     </row>
     <row r="294" spans="15:18">
       <c r="O294" s="7"/>
-      <c r="R294" s="12"/>
+      <c r="P294" s="13"/>
+      <c r="R294" s="11"/>
     </row>
     <row r="295" spans="15:18">
       <c r="O295" s="7"/>
-      <c r="R295" s="12"/>
+      <c r="P295" s="13"/>
+      <c r="R295" s="11"/>
     </row>
     <row r="296" spans="15:18">
       <c r="O296" s="7"/>
-      <c r="R296" s="12"/>
+      <c r="P296" s="13"/>
+      <c r="R296" s="11"/>
     </row>
     <row r="297" spans="15:18">
       <c r="O297" s="7"/>
-      <c r="R297" s="12"/>
+      <c r="P297" s="13"/>
+      <c r="R297" s="11"/>
     </row>
     <row r="298" spans="15:18">
       <c r="O298" s="7"/>
-      <c r="R298" s="12"/>
+      <c r="P298" s="13"/>
+      <c r="R298" s="11"/>
     </row>
     <row r="299" spans="15:18">
       <c r="O299" s="7"/>
-      <c r="R299" s="12"/>
+      <c r="P299" s="13"/>
+      <c r="R299" s="11"/>
     </row>
     <row r="300" spans="15:18">
       <c r="O300" s="7"/>
-      <c r="R300" s="12"/>
+      <c r="P300" s="13"/>
+      <c r="R300" s="11"/>
     </row>
     <row r="301" spans="15:18">
       <c r="O301" s="7"/>
-      <c r="R301" s="12"/>
+      <c r="P301" s="13"/>
+      <c r="R301" s="11"/>
     </row>
     <row r="302" spans="15:18">
       <c r="O302" s="7"/>
-      <c r="R302" s="12"/>
+      <c r="P302" s="13"/>
+      <c r="R302" s="11"/>
     </row>
     <row r="303" spans="15:18">
       <c r="O303" s="7"/>
-      <c r="R303" s="12"/>
+      <c r="P303" s="13"/>
+      <c r="R303" s="11"/>
     </row>
     <row r="304" spans="15:18">
       <c r="O304" s="7"/>
-      <c r="R304" s="12"/>
+      <c r="P304" s="13"/>
+      <c r="R304" s="11"/>
     </row>
     <row r="305" spans="15:18">
       <c r="O305" s="7"/>
-      <c r="R305" s="12"/>
+      <c r="P305" s="13"/>
+      <c r="R305" s="11"/>
     </row>
     <row r="306" spans="15:18">
       <c r="O306" s="7"/>
-      <c r="R306" s="12"/>
+      <c r="P306" s="13"/>
+      <c r="R306" s="11"/>
     </row>
     <row r="307" spans="15:18">
       <c r="O307" s="7"/>
-      <c r="R307" s="12"/>
+      <c r="P307" s="13"/>
+      <c r="R307" s="11"/>
     </row>
     <row r="308" spans="15:18">
       <c r="O308" s="7"/>
-      <c r="R308" s="12"/>
+      <c r="P308" s="13"/>
+      <c r="R308" s="11"/>
     </row>
     <row r="309" spans="15:18">
       <c r="O309" s="7"/>
-      <c r="R309" s="12"/>
+      <c r="P309" s="13"/>
+      <c r="R309" s="11"/>
     </row>
     <row r="310" spans="15:18">
       <c r="O310" s="7"/>
-      <c r="R310" s="12"/>
+      <c r="P310" s="13"/>
+      <c r="R310" s="11"/>
     </row>
     <row r="311" spans="15:18">
       <c r="O311" s="7"/>
-      <c r="R311" s="12"/>
+      <c r="P311" s="13"/>
+      <c r="R311" s="11"/>
     </row>
     <row r="312" spans="15:18">
       <c r="O312" s="7"/>
-      <c r="R312" s="12"/>
+      <c r="P312" s="13"/>
+      <c r="R312" s="11"/>
     </row>
     <row r="313" spans="15:18">
       <c r="O313" s="7"/>
-      <c r="R313" s="12"/>
+      <c r="P313" s="13"/>
+      <c r="R313" s="11"/>
     </row>
     <row r="314" spans="15:18">
       <c r="O314" s="7"/>
-      <c r="R314" s="12"/>
+      <c r="P314" s="13"/>
+      <c r="R314" s="11"/>
     </row>
     <row r="315" spans="15:18">
       <c r="O315" s="7"/>
-      <c r="R315" s="12"/>
+      <c r="P315" s="13"/>
+      <c r="R315" s="11"/>
     </row>
     <row r="316" spans="15:18">
       <c r="O316" s="7"/>
-      <c r="R316" s="12"/>
+      <c r="P316" s="13"/>
+      <c r="R316" s="11"/>
     </row>
     <row r="317" spans="15:18">
       <c r="O317" s="7"/>
-      <c r="R317" s="12"/>
+      <c r="P317" s="13"/>
+      <c r="R317" s="11"/>
     </row>
     <row r="318" spans="15:18">
       <c r="O318" s="7"/>
-      <c r="R318" s="12"/>
+      <c r="P318" s="13"/>
+      <c r="R318" s="11"/>
     </row>
     <row r="319" spans="15:18">
       <c r="O319" s="7"/>
-      <c r="R319" s="12"/>
+      <c r="P319" s="13"/>
+      <c r="R319" s="11"/>
     </row>
     <row r="320" spans="15:18">
       <c r="O320" s="7"/>
-      <c r="R320" s="12"/>
+      <c r="P320" s="13"/>
+      <c r="R320" s="11"/>
     </row>
     <row r="321" spans="15:18">
       <c r="O321" s="7"/>
-      <c r="R321" s="12"/>
+      <c r="P321" s="13"/>
+      <c r="R321" s="11"/>
     </row>
     <row r="322" spans="15:18">
       <c r="O322" s="7"/>
-      <c r="R322" s="12"/>
+      <c r="P322" s="13"/>
+      <c r="R322" s="11"/>
     </row>
     <row r="323" spans="15:18">
       <c r="O323" s="7"/>
-      <c r="R323" s="12"/>
+      <c r="P323" s="13"/>
+      <c r="R323" s="11"/>
     </row>
     <row r="324" spans="15:18">
       <c r="O324" s="7"/>
-      <c r="R324" s="12"/>
+      <c r="P324" s="13"/>
+      <c r="R324" s="11"/>
     </row>
     <row r="325" spans="15:18">
       <c r="O325" s="7"/>
-      <c r="R325" s="12"/>
+      <c r="P325" s="13"/>
+      <c r="R325" s="11"/>
     </row>
     <row r="326" spans="15:18">
       <c r="O326" s="7"/>
-      <c r="R326" s="12"/>
+      <c r="P326" s="13"/>
+      <c r="R326" s="11"/>
     </row>
     <row r="327" spans="15:18">
       <c r="O327" s="7"/>
-      <c r="R327" s="12"/>
+      <c r="P327" s="13"/>
+      <c r="R327" s="11"/>
     </row>
     <row r="328" spans="15:18">
       <c r="O328" s="7"/>
-      <c r="R328" s="12"/>
+      <c r="P328" s="13"/>
+      <c r="R328" s="11"/>
     </row>
     <row r="329" spans="15:18">
       <c r="O329" s="7"/>
-      <c r="R329" s="12"/>
+      <c r="P329" s="13"/>
+      <c r="R329" s="11"/>
     </row>
     <row r="330" spans="15:18">
       <c r="O330" s="7"/>
-      <c r="R330" s="12"/>
+      <c r="P330" s="13"/>
+      <c r="R330" s="11"/>
     </row>
     <row r="331" spans="15:18">
       <c r="O331" s="7"/>
-      <c r="R331" s="12"/>
+      <c r="P331" s="13"/>
+      <c r="R331" s="11"/>
     </row>
     <row r="332" spans="15:18">
       <c r="O332" s="7"/>
-      <c r="R332" s="12"/>
+      <c r="P332" s="13"/>
+      <c r="R332" s="11"/>
     </row>
     <row r="333" spans="15:18">
       <c r="O333" s="7"/>
-      <c r="R333" s="12"/>
+      <c r="P333" s="13"/>
+      <c r="R333" s="11"/>
     </row>
     <row r="334" spans="15:18">
       <c r="O334" s="7"/>
-      <c r="R334" s="12"/>
+      <c r="P334" s="13"/>
+      <c r="R334" s="11"/>
     </row>
     <row r="335" spans="15:18">
       <c r="O335" s="7"/>
-      <c r="R335" s="12"/>
+      <c r="P335" s="13"/>
+      <c r="R335" s="11"/>
     </row>
     <row r="336" spans="15:18">
       <c r="O336" s="7"/>
-      <c r="R336" s="12"/>
+      <c r="P336" s="13"/>
+      <c r="R336" s="11"/>
     </row>
     <row r="337" spans="15:18">
       <c r="O337" s="7"/>
-      <c r="R337" s="12"/>
+      <c r="P337" s="13"/>
+      <c r="R337" s="11"/>
     </row>
     <row r="338" spans="15:18">
       <c r="O338" s="7"/>
-      <c r="R338" s="12"/>
+      <c r="P338" s="13"/>
+      <c r="R338" s="11"/>
     </row>
     <row r="339" spans="15:18">
       <c r="O339" s="7"/>
-      <c r="R339" s="12"/>
+      <c r="P339" s="13"/>
+      <c r="R339" s="11"/>
     </row>
     <row r="340" spans="15:18">
       <c r="O340" s="7"/>
-      <c r="R340" s="12"/>
+      <c r="P340" s="13"/>
+      <c r="R340" s="11"/>
     </row>
     <row r="341" spans="15:18">
       <c r="O341" s="7"/>
-      <c r="R341" s="12"/>
+      <c r="P341" s="13"/>
+      <c r="R341" s="11"/>
     </row>
     <row r="342" spans="15:18">
       <c r="O342" s="7"/>
-      <c r="R342" s="12"/>
+      <c r="P342" s="13"/>
+      <c r="R342" s="11"/>
     </row>
     <row r="343" spans="15:18">
       <c r="O343" s="7"/>
-      <c r="R343" s="12"/>
+      <c r="P343" s="13"/>
+      <c r="R343" s="11"/>
     </row>
     <row r="344" spans="15:18">
       <c r="O344" s="7"/>
-      <c r="R344" s="12"/>
+      <c r="P344" s="13"/>
+      <c r="R344" s="11"/>
     </row>
     <row r="345" spans="15:18">
       <c r="O345" s="7"/>
-      <c r="R345" s="12"/>
+      <c r="P345" s="13"/>
+      <c r="R345" s="11"/>
     </row>
     <row r="346" spans="15:18">
       <c r="O346" s="7"/>
-      <c r="R346" s="12"/>
+      <c r="P346" s="13"/>
+      <c r="R346" s="11"/>
     </row>
     <row r="347" spans="15:18">
       <c r="O347" s="7"/>
-      <c r="R347" s="12"/>
+      <c r="P347" s="13"/>
+      <c r="R347" s="11"/>
     </row>
     <row r="348" spans="15:18">
       <c r="O348" s="7"/>
-      <c r="R348" s="12"/>
+      <c r="P348" s="13"/>
+      <c r="R348" s="11"/>
     </row>
     <row r="349" spans="15:18">
       <c r="O349" s="7"/>
-      <c r="R349" s="12"/>
+      <c r="P349" s="13"/>
+      <c r="R349" s="11"/>
     </row>
     <row r="350" spans="15:18">
       <c r="O350" s="7"/>
-      <c r="R350" s="12"/>
+      <c r="P350" s="13"/>
+      <c r="R350" s="11"/>
     </row>
     <row r="351" spans="15:18">
       <c r="O351" s="7"/>
-      <c r="R351" s="12"/>
+      <c r="P351" s="13"/>
+      <c r="R351" s="11"/>
     </row>
     <row r="352" spans="15:18">
       <c r="O352" s="7"/>
-      <c r="R352" s="12"/>
+      <c r="P352" s="13"/>
+      <c r="R352" s="11"/>
     </row>
     <row r="353" spans="15:18">
       <c r="O353" s="7"/>
-      <c r="R353" s="12"/>
+      <c r="P353" s="13"/>
+      <c r="R353" s="11"/>
     </row>
     <row r="354" spans="15:18">
       <c r="O354" s="7"/>
-      <c r="R354" s="12"/>
+      <c r="P354" s="13"/>
+      <c r="R354" s="11"/>
     </row>
     <row r="355" spans="15:18">
       <c r="O355" s="7"/>
-      <c r="R355" s="12"/>
+      <c r="P355" s="13"/>
+      <c r="R355" s="11"/>
     </row>
     <row r="356" spans="15:18">
       <c r="O356" s="7"/>
-      <c r="R356" s="12"/>
+      <c r="P356" s="13"/>
+      <c r="R356" s="11"/>
     </row>
     <row r="357" spans="15:18">
       <c r="O357" s="7"/>
-      <c r="R357" s="12"/>
+      <c r="P357" s="13"/>
+      <c r="R357" s="11"/>
     </row>
     <row r="358" spans="15:18">
       <c r="O358" s="7"/>
-      <c r="R358" s="12"/>
+      <c r="P358" s="13"/>
+      <c r="R358" s="11"/>
     </row>
     <row r="359" spans="15:18">
       <c r="O359" s="7"/>
-      <c r="R359" s="12"/>
+      <c r="P359" s="13"/>
+      <c r="R359" s="11"/>
     </row>
     <row r="360" spans="15:18">
       <c r="O360" s="7"/>
-      <c r="R360" s="12"/>
+      <c r="P360" s="13"/>
+      <c r="R360" s="11"/>
     </row>
     <row r="361" spans="15:18">
       <c r="O361" s="7"/>
-      <c r="R361" s="12"/>
+      <c r="P361" s="13"/>
+      <c r="R361" s="11"/>
     </row>
     <row r="362" spans="15:18">
       <c r="O362" s="7"/>
-      <c r="R362" s="12"/>
+      <c r="P362" s="13"/>
+      <c r="R362" s="11"/>
     </row>
     <row r="363" spans="15:18">
       <c r="O363" s="7"/>
-      <c r="R363" s="12"/>
+      <c r="P363" s="13"/>
+      <c r="R363" s="11"/>
     </row>
     <row r="364" spans="15:18">
       <c r="O364" s="7"/>
-      <c r="R364" s="12"/>
+      <c r="P364" s="13"/>
+      <c r="R364" s="11"/>
     </row>
     <row r="365" spans="15:18">
       <c r="O365" s="7"/>
-      <c r="R365" s="12"/>
+      <c r="P365" s="13"/>
+      <c r="R365" s="11"/>
     </row>
     <row r="366" spans="15:18">
       <c r="O366" s="7"/>
-      <c r="R366" s="12"/>
+      <c r="P366" s="13"/>
+      <c r="R366" s="11"/>
     </row>
     <row r="367" spans="15:18">
       <c r="O367" s="7"/>
-      <c r="R367" s="12"/>
+      <c r="P367" s="13"/>
+      <c r="R367" s="11"/>
     </row>
     <row r="368" spans="15:18">
       <c r="O368" s="7"/>
-      <c r="R368" s="12"/>
+      <c r="P368" s="13"/>
+      <c r="R368" s="11"/>
     </row>
     <row r="369" spans="15:18">
       <c r="O369" s="7"/>
-      <c r="R369" s="12"/>
+      <c r="P369" s="13"/>
+      <c r="R369" s="11"/>
     </row>
     <row r="370" spans="15:18">
       <c r="O370" s="7"/>
-      <c r="R370" s="12"/>
+      <c r="P370" s="13"/>
+      <c r="R370" s="11"/>
     </row>
     <row r="371" spans="15:18">
       <c r="O371" s="7"/>
-      <c r="R371" s="12"/>
+      <c r="P371" s="13"/>
+      <c r="R371" s="11"/>
     </row>
     <row r="372" spans="15:18">
       <c r="O372" s="7"/>
-      <c r="R372" s="12"/>
+      <c r="P372" s="13"/>
+      <c r="R372" s="11"/>
     </row>
     <row r="373" spans="15:18">
       <c r="O373" s="7"/>
-      <c r="R373" s="12"/>
+      <c r="P373" s="13"/>
+      <c r="R373" s="11"/>
     </row>
     <row r="374" spans="15:18">
       <c r="O374" s="7"/>
-      <c r="R374" s="12"/>
+      <c r="P374" s="13"/>
+      <c r="R374" s="11"/>
     </row>
     <row r="375" spans="15:18">
       <c r="O375" s="7"/>
-      <c r="R375" s="12"/>
+      <c r="P375" s="13"/>
+      <c r="R375" s="11"/>
     </row>
     <row r="376" spans="15:18">
       <c r="O376" s="7"/>
-      <c r="R376" s="12"/>
+      <c r="P376" s="13"/>
+      <c r="R376" s="11"/>
     </row>
     <row r="377" spans="15:18">
       <c r="O377" s="7"/>
-      <c r="R377" s="12"/>
+      <c r="P377" s="13"/>
+      <c r="R377" s="11"/>
     </row>
     <row r="378" spans="15:18">
       <c r="O378" s="7"/>
-      <c r="R378" s="12"/>
+      <c r="P378" s="13"/>
+      <c r="R378" s="11"/>
     </row>
     <row r="379" spans="15:18">
       <c r="O379" s="7"/>
-      <c r="R379" s="12"/>
+      <c r="P379" s="13"/>
+      <c r="R379" s="11"/>
     </row>
     <row r="380" spans="15:18">
       <c r="O380" s="7"/>
-      <c r="R380" s="12"/>
+      <c r="P380" s="13"/>
+      <c r="R380" s="11"/>
     </row>
     <row r="381" spans="15:18">
       <c r="O381" s="7"/>
-      <c r="R381" s="12"/>
+      <c r="P381" s="13"/>
+      <c r="R381" s="11"/>
     </row>
     <row r="382" spans="15:18">
       <c r="O382" s="7"/>
-      <c r="R382" s="12"/>
+      <c r="P382" s="13"/>
+      <c r="R382" s="11"/>
     </row>
     <row r="383" spans="15:18">
       <c r="O383" s="7"/>
-      <c r="R383" s="12"/>
+      <c r="P383" s="13"/>
+      <c r="R383" s="11"/>
     </row>
     <row r="384" spans="15:18">
       <c r="O384" s="7"/>
-      <c r="R384" s="12"/>
+      <c r="P384" s="13"/>
+      <c r="R384" s="11"/>
     </row>
     <row r="385" spans="15:18">
       <c r="O385" s="7"/>
-      <c r="R385" s="12"/>
+      <c r="P385" s="13"/>
+      <c r="R385" s="11"/>
     </row>
     <row r="386" spans="15:18">
       <c r="O386" s="7"/>
-      <c r="R386" s="12"/>
+      <c r="P386" s="13"/>
+      <c r="R386" s="11"/>
     </row>
     <row r="387" spans="15:18">
       <c r="O387" s="7"/>
-      <c r="R387" s="12"/>
+      <c r="P387" s="13"/>
+      <c r="R387" s="11"/>
     </row>
     <row r="388" spans="15:18">
       <c r="O388" s="7"/>
-      <c r="R388" s="12"/>
+      <c r="P388" s="13"/>
+      <c r="R388" s="11"/>
     </row>
     <row r="389" spans="15:18">
       <c r="O389" s="7"/>
-      <c r="R389" s="12"/>
+      <c r="P389" s="13"/>
+      <c r="R389" s="11"/>
     </row>
     <row r="390" spans="15:18">
       <c r="O390" s="7"/>
-      <c r="R390" s="12"/>
+      <c r="P390" s="13"/>
+      <c r="R390" s="11"/>
     </row>
     <row r="391" spans="15:18">
       <c r="O391" s="7"/>
-      <c r="R391" s="12"/>
+      <c r="P391" s="13"/>
+      <c r="R391" s="11"/>
     </row>
     <row r="392" spans="15:18">
       <c r="O392" s="7"/>
-      <c r="R392" s="12"/>
+      <c r="P392" s="13"/>
+      <c r="R392" s="11"/>
     </row>
     <row r="393" spans="15:18">
       <c r="O393" s="7"/>
-      <c r="R393" s="12"/>
+      <c r="P393" s="13"/>
+      <c r="R393" s="11"/>
     </row>
     <row r="394" spans="15:18">
       <c r="O394" s="7"/>
-      <c r="R394" s="12"/>
+      <c r="P394" s="13"/>
+      <c r="R394" s="11"/>
     </row>
     <row r="395" spans="15:18">
       <c r="O395" s="7"/>
-      <c r="R395" s="12"/>
+      <c r="P395" s="13"/>
+      <c r="R395" s="11"/>
     </row>
     <row r="396" spans="15:18">
       <c r="O396" s="7"/>
-      <c r="R396" s="12"/>
+      <c r="P396" s="13"/>
+      <c r="R396" s="11"/>
     </row>
     <row r="397" spans="15:18">
       <c r="O397" s="7"/>
-      <c r="R397" s="12"/>
+      <c r="P397" s="13"/>
+      <c r="R397" s="11"/>
     </row>
     <row r="398" spans="15:18">
       <c r="O398" s="7"/>
-      <c r="R398" s="12"/>
+      <c r="P398" s="13"/>
+      <c r="R398" s="11"/>
     </row>
     <row r="399" spans="15:18">
       <c r="O399" s="7"/>
-      <c r="R399" s="12"/>
+      <c r="P399" s="13"/>
+      <c r="R399" s="11"/>
     </row>
     <row r="400" spans="15:18">
       <c r="O400" s="7"/>
-      <c r="R400" s="12"/>
+      <c r="P400" s="13"/>
+      <c r="R400" s="11"/>
     </row>
     <row r="401" spans="15:18">
       <c r="O401" s="7"/>
-      <c r="R401" s="12"/>
+      <c r="P401" s="13"/>
+      <c r="R401" s="11"/>
     </row>
     <row r="402" spans="15:18">
       <c r="O402" s="7"/>
-      <c r="R402" s="12"/>
+      <c r="P402" s="13"/>
+      <c r="R402" s="11"/>
     </row>
     <row r="403" spans="15:18">
       <c r="O403" s="7"/>
-      <c r="R403" s="12"/>
+      <c r="P403" s="13"/>
+      <c r="R403" s="11"/>
     </row>
     <row r="404" spans="15:18">
       <c r="O404" s="7"/>
-      <c r="R404" s="12"/>
+      <c r="P404" s="13"/>
+      <c r="R404" s="11"/>
     </row>
     <row r="405" spans="15:18">
       <c r="O405" s="7"/>
-      <c r="R405" s="12"/>
+      <c r="P405" s="13"/>
+      <c r="R405" s="11"/>
     </row>
     <row r="406" spans="15:18">
       <c r="O406" s="7"/>
-      <c r="R406" s="12"/>
+      <c r="P406" s="13"/>
+      <c r="R406" s="11"/>
     </row>
     <row r="407" spans="15:18">
       <c r="O407" s="7"/>
-      <c r="R407" s="12"/>
+      <c r="P407" s="13"/>
+      <c r="R407" s="11"/>
     </row>
     <row r="408" spans="15:18">
       <c r="O408" s="7"/>
-      <c r="R408" s="12"/>
+      <c r="P408" s="13"/>
+      <c r="R408" s="11"/>
     </row>
     <row r="409" spans="15:18">
       <c r="O409" s="7"/>
-      <c r="R409" s="12"/>
+      <c r="P409" s="13"/>
+      <c r="R409" s="11"/>
     </row>
     <row r="410" spans="15:18">
       <c r="O410" s="7"/>
-      <c r="R410" s="12"/>
+      <c r="P410" s="13"/>
+      <c r="R410" s="11"/>
     </row>
     <row r="411" spans="15:18">
       <c r="O411" s="7"/>
-      <c r="R411" s="12"/>
+      <c r="P411" s="13"/>
+      <c r="R411" s="11"/>
     </row>
     <row r="412" spans="15:18">
       <c r="O412" s="7"/>
-      <c r="R412" s="12"/>
+      <c r="P412" s="13"/>
+      <c r="R412" s="11"/>
     </row>
     <row r="413" spans="15:18">
       <c r="O413" s="7"/>
-      <c r="R413" s="12"/>
+      <c r="P413" s="13"/>
+      <c r="R413" s="11"/>
     </row>
     <row r="414" spans="15:18">
       <c r="O414" s="7"/>
-      <c r="R414" s="12"/>
+      <c r="P414" s="13"/>
+      <c r="R414" s="11"/>
     </row>
     <row r="415" spans="15:18">
       <c r="O415" s="7"/>
-      <c r="R415" s="12"/>
+      <c r="P415" s="13"/>
+      <c r="R415" s="11"/>
     </row>
     <row r="416" spans="15:18">
       <c r="O416" s="7"/>
-      <c r="R416" s="12"/>
+      <c r="P416" s="13"/>
+      <c r="R416" s="11"/>
     </row>
     <row r="417" spans="15:18">
       <c r="O417" s="7"/>
-      <c r="R417" s="12"/>
+      <c r="P417" s="13"/>
+      <c r="R417" s="11"/>
     </row>
     <row r="418" spans="15:18">
       <c r="O418" s="7"/>
-      <c r="R418" s="12"/>
+      <c r="P418" s="13"/>
+      <c r="R418" s="11"/>
     </row>
     <row r="419" spans="15:18">
       <c r="O419" s="7"/>
-      <c r="R419" s="12"/>
+      <c r="P419" s="13"/>
+      <c r="R419" s="11"/>
     </row>
     <row r="420" spans="15:18">
       <c r="O420" s="7"/>
-      <c r="R420" s="12"/>
+      <c r="P420" s="13"/>
+      <c r="R420" s="11"/>
     </row>
     <row r="421" spans="15:18">
       <c r="O421" s="7"/>
-      <c r="R421" s="12"/>
+      <c r="P421" s="13"/>
+      <c r="R421" s="11"/>
     </row>
     <row r="422" spans="15:18">
       <c r="O422" s="7"/>
-      <c r="R422" s="12"/>
+      <c r="P422" s="13"/>
+      <c r="R422" s="11"/>
     </row>
     <row r="423" spans="15:18">
       <c r="O423" s="7"/>
-      <c r="R423" s="12"/>
+      <c r="P423" s="13"/>
+      <c r="R423" s="11"/>
     </row>
     <row r="424" spans="15:18">
       <c r="O424" s="7"/>
-      <c r="R424" s="12"/>
+      <c r="P424" s="13"/>
+      <c r="R424" s="11"/>
     </row>
     <row r="425" spans="15:18">
       <c r="O425" s="7"/>
-      <c r="R425" s="12"/>
+      <c r="P425" s="13"/>
+      <c r="R425" s="11"/>
     </row>
     <row r="426" spans="15:18">
       <c r="O426" s="7"/>
-      <c r="R426" s="12"/>
+      <c r="P426" s="13"/>
+      <c r="R426" s="11"/>
     </row>
     <row r="427" spans="15:18">
       <c r="O427" s="7"/>
-      <c r="R427" s="12"/>
+      <c r="P427" s="13"/>
+      <c r="R427" s="11"/>
     </row>
     <row r="428" spans="15:18">
       <c r="O428" s="7"/>
-      <c r="R428" s="12"/>
+      <c r="P428" s="13"/>
+      <c r="R428" s="11"/>
     </row>
     <row r="429" spans="15:18">
       <c r="O429" s="7"/>
-      <c r="R429" s="12"/>
+      <c r="P429" s="13"/>
+      <c r="R429" s="11"/>
     </row>
     <row r="430" spans="15:18">
       <c r="O430" s="7"/>
-      <c r="R430" s="12"/>
+      <c r="P430" s="13"/>
+      <c r="R430" s="11"/>
     </row>
     <row r="431" spans="15:18">
       <c r="O431" s="7"/>
-      <c r="R431" s="12"/>
+      <c r="P431" s="13"/>
+      <c r="R431" s="11"/>
     </row>
     <row r="432" spans="15:18">
       <c r="O432" s="7"/>
-      <c r="R432" s="12"/>
+      <c r="P432" s="13"/>
+      <c r="R432" s="11"/>
     </row>
     <row r="433" spans="15:18">
       <c r="O433" s="7"/>
-      <c r="R433" s="12"/>
+      <c r="P433" s="13"/>
+      <c r="R433" s="11"/>
     </row>
     <row r="434" spans="15:18">
       <c r="O434" s="7"/>
-      <c r="R434" s="12"/>
+      <c r="P434" s="13"/>
+      <c r="R434" s="11"/>
     </row>
     <row r="435" spans="15:18">
       <c r="O435" s="7"/>
-      <c r="R435" s="12"/>
+      <c r="P435" s="13"/>
+      <c r="R435" s="11"/>
     </row>
     <row r="436" spans="15:18">
       <c r="O436" s="7"/>
-      <c r="R436" s="12"/>
+      <c r="P436" s="13"/>
+      <c r="R436" s="11"/>
     </row>
     <row r="437" spans="15:18">
       <c r="O437" s="7"/>
-      <c r="R437" s="12"/>
+      <c r="P437" s="13"/>
+      <c r="R437" s="11"/>
     </row>
     <row r="438" spans="15:18">
       <c r="O438" s="7"/>
-      <c r="R438" s="12"/>
+      <c r="P438" s="13"/>
+      <c r="R438" s="11"/>
     </row>
     <row r="439" spans="15:18">
       <c r="O439" s="7"/>
-      <c r="R439" s="12"/>
+      <c r="P439" s="13"/>
+      <c r="R439" s="11"/>
     </row>
     <row r="440" spans="15:18">
       <c r="O440" s="7"/>
-      <c r="R440" s="12"/>
+      <c r="P440" s="13"/>
+      <c r="R440" s="11"/>
     </row>
     <row r="441" spans="15:18">
       <c r="O441" s="7"/>
-      <c r="R441" s="12"/>
+      <c r="P441" s="13"/>
+      <c r="R441" s="11"/>
     </row>
     <row r="442" spans="15:18">
       <c r="O442" s="7"/>
-      <c r="R442" s="12"/>
+      <c r="P442" s="13"/>
+      <c r="R442" s="11"/>
     </row>
     <row r="443" spans="15:18">
       <c r="O443" s="7"/>
-      <c r="R443" s="12"/>
+      <c r="P443" s="13"/>
+      <c r="R443" s="11"/>
     </row>
     <row r="444" spans="15:18">
       <c r="O444" s="7"/>
-      <c r="R444" s="12"/>
+      <c r="P444" s="13"/>
+      <c r="R444" s="11"/>
     </row>
     <row r="445" spans="15:18">
       <c r="O445" s="7"/>
-      <c r="R445" s="12"/>
+      <c r="P445" s="13"/>
+      <c r="R445" s="11"/>
     </row>
     <row r="446" spans="15:18">
       <c r="O446" s="7"/>
-      <c r="R446" s="12"/>
+      <c r="P446" s="13"/>
+      <c r="R446" s="11"/>
     </row>
     <row r="447" spans="15:18">
       <c r="O447" s="7"/>
-      <c r="R447" s="12"/>
+      <c r="P447" s="13"/>
+      <c r="R447" s="11"/>
     </row>
     <row r="448" spans="15:18">
       <c r="O448" s="7"/>
-      <c r="R448" s="12"/>
+      <c r="P448" s="13"/>
+      <c r="R448" s="11"/>
     </row>
     <row r="449" spans="15:18">
       <c r="O449" s="7"/>
-      <c r="R449" s="12"/>
+      <c r="P449" s="13"/>
+      <c r="R449" s="11"/>
     </row>
     <row r="450" spans="15:18">
       <c r="O450" s="7"/>
-      <c r="R450" s="12"/>
+      <c r="P450" s="13"/>
+      <c r="R450" s="11"/>
     </row>
     <row r="451" spans="15:18">
       <c r="O451" s="7"/>
-      <c r="R451" s="12"/>
+      <c r="P451" s="13"/>
+      <c r="R451" s="11"/>
     </row>
     <row r="452" spans="15:18">
       <c r="O452" s="7"/>
-      <c r="R452" s="12"/>
+      <c r="P452" s="13"/>
+      <c r="R452" s="11"/>
     </row>
     <row r="453" spans="15:18">
       <c r="O453" s="7"/>
-      <c r="R453" s="12"/>
+      <c r="P453" s="13"/>
+      <c r="R453" s="11"/>
     </row>
     <row r="454" spans="15:18">
       <c r="O454" s="7"/>
-      <c r="R454" s="12"/>
+      <c r="P454" s="13"/>
+      <c r="R454" s="11"/>
     </row>
     <row r="455" spans="15:18">
       <c r="O455" s="7"/>
-      <c r="R455" s="12"/>
+      <c r="P455" s="13"/>
+      <c r="R455" s="11"/>
     </row>
     <row r="456" spans="15:18">
       <c r="O456" s="7"/>
-      <c r="R456" s="12"/>
+      <c r="P456" s="13"/>
+      <c r="R456" s="11"/>
     </row>
     <row r="457" spans="15:18">
       <c r="O457" s="7"/>
-      <c r="R457" s="12"/>
+      <c r="P457" s="13"/>
+      <c r="R457" s="11"/>
     </row>
     <row r="458" spans="15:18">
       <c r="O458" s="7"/>
-      <c r="R458" s="12"/>
+      <c r="P458" s="13"/>
+      <c r="R458" s="11"/>
     </row>
     <row r="459" spans="15:18">
       <c r="O459" s="7"/>
-      <c r="R459" s="12"/>
+      <c r="P459" s="13"/>
+      <c r="R459" s="11"/>
     </row>
     <row r="460" spans="15:18">
       <c r="O460" s="7"/>
-      <c r="R460" s="12"/>
+      <c r="P460" s="13"/>
+      <c r="R460" s="11"/>
     </row>
     <row r="461" spans="15:18">
       <c r="O461" s="7"/>
-      <c r="R461" s="12"/>
+      <c r="P461" s="13"/>
+      <c r="R461" s="11"/>
     </row>
     <row r="462" spans="15:18">
       <c r="O462" s="7"/>
-      <c r="R462" s="12"/>
+      <c r="P462" s="13"/>
+      <c r="R462" s="11"/>
     </row>
     <row r="463" spans="15:18">
       <c r="O463" s="7"/>
-      <c r="R463" s="12"/>
+      <c r="P463" s="13"/>
+      <c r="R463" s="11"/>
     </row>
     <row r="464" spans="15:18">
       <c r="O464" s="7"/>
-      <c r="R464" s="12"/>
+      <c r="P464" s="13"/>
+      <c r="R464" s="11"/>
     </row>
     <row r="465" spans="15:18">
       <c r="O465" s="7"/>
-      <c r="R465" s="12"/>
+      <c r="P465" s="13"/>
+      <c r="R465" s="11"/>
     </row>
     <row r="466" spans="15:18">
       <c r="O466" s="7"/>
-      <c r="R466" s="12"/>
+      <c r="P466" s="13"/>
+      <c r="R466" s="11"/>
     </row>
     <row r="467" spans="15:18">
       <c r="O467" s="7"/>
-      <c r="R467" s="12"/>
+      <c r="P467" s="13"/>
+      <c r="R467" s="11"/>
     </row>
     <row r="468" spans="15:18">
       <c r="O468" s="7"/>
-      <c r="R468" s="12"/>
+      <c r="P468" s="13"/>
+      <c r="R468" s="11"/>
     </row>
     <row r="469" spans="15:18">
       <c r="O469" s="7"/>
-      <c r="R469" s="12"/>
+      <c r="P469" s="13"/>
+      <c r="R469" s="11"/>
     </row>
     <row r="470" spans="15:18">
       <c r="O470" s="7"/>
-      <c r="R470" s="12"/>
+      <c r="P470" s="13"/>
+      <c r="R470" s="11"/>
     </row>
     <row r="471" spans="15:18">
       <c r="O471" s="7"/>
-      <c r="R471" s="12"/>
+      <c r="P471" s="13"/>
+      <c r="R471" s="11"/>
     </row>
     <row r="472" spans="15:18">
       <c r="O472" s="7"/>
-      <c r="R472" s="12"/>
+      <c r="P472" s="13"/>
+      <c r="R472" s="11"/>
     </row>
     <row r="473" spans="15:18">
       <c r="O473" s="7"/>
-      <c r="R473" s="12"/>
+      <c r="P473" s="13"/>
+      <c r="R473" s="11"/>
     </row>
     <row r="474" spans="15:18">
       <c r="O474" s="7"/>
-      <c r="R474" s="12"/>
+      <c r="P474" s="13"/>
+      <c r="R474" s="11"/>
     </row>
     <row r="475" spans="15:18">
       <c r="O475" s="7"/>
-      <c r="R475" s="12"/>
+      <c r="P475" s="13"/>
+      <c r="R475" s="11"/>
     </row>
     <row r="476" spans="15:18">
       <c r="O476" s="7"/>
-      <c r="R476" s="12"/>
+      <c r="P476" s="13"/>
+      <c r="R476" s="11"/>
     </row>
     <row r="477" spans="15:18">
       <c r="O477" s="7"/>
-      <c r="R477" s="12"/>
+      <c r="P477" s="13"/>
+      <c r="R477" s="11"/>
     </row>
     <row r="478" spans="15:18">
       <c r="O478" s="7"/>
-      <c r="R478" s="12"/>
+      <c r="P478" s="13"/>
+      <c r="R478" s="11"/>
     </row>
     <row r="479" spans="15:18">
       <c r="O479" s="7"/>
-      <c r="R479" s="12"/>
+      <c r="P479" s="13"/>
+      <c r="R479" s="11"/>
     </row>
     <row r="480" spans="15:18">
       <c r="O480" s="7"/>
-      <c r="R480" s="12"/>
+      <c r="P480" s="13"/>
+      <c r="R480" s="11"/>
     </row>
     <row r="481" spans="15:18">
       <c r="O481" s="7"/>
-      <c r="R481" s="12"/>
+      <c r="P481" s="13"/>
+      <c r="R481" s="11"/>
     </row>
     <row r="482" spans="15:18">
       <c r="O482" s="7"/>
-      <c r="R482" s="12"/>
+      <c r="P482" s="13"/>
+      <c r="R482" s="11"/>
     </row>
     <row r="483" spans="15:18">
       <c r="O483" s="7"/>
-      <c r="R483" s="12"/>
+      <c r="P483" s="13"/>
+      <c r="R483" s="11"/>
     </row>
     <row r="484" spans="15:18">
       <c r="O484" s="7"/>
-      <c r="R484" s="12"/>
+      <c r="P484" s="13"/>
+      <c r="R484" s="11"/>
     </row>
     <row r="485" spans="15:18">
       <c r="O485" s="7"/>
-      <c r="R485" s="12"/>
+      <c r="P485" s="13"/>
+      <c r="R485" s="11"/>
     </row>
     <row r="486" spans="15:18">
       <c r="O486" s="7"/>
-      <c r="R486" s="12"/>
+      <c r="P486" s="13"/>
+      <c r="R486" s="11"/>
     </row>
     <row r="487" spans="15:18">
       <c r="O487" s="7"/>
-      <c r="R487" s="12"/>
+      <c r="P487" s="13"/>
+      <c r="R487" s="11"/>
     </row>
     <row r="488" spans="15:18">
       <c r="O488" s="7"/>
-      <c r="R488" s="12"/>
+      <c r="P488" s="13"/>
+      <c r="R488" s="11"/>
     </row>
     <row r="489" spans="15:18">
       <c r="O489" s="7"/>
-      <c r="R489" s="12"/>
+      <c r="P489" s="13"/>
+      <c r="R489" s="11"/>
     </row>
     <row r="490" spans="15:18">
       <c r="O490" s="7"/>
-      <c r="R490" s="12"/>
+      <c r="P490" s="13"/>
+      <c r="R490" s="11"/>
     </row>
     <row r="491" spans="15:18">
       <c r="O491" s="7"/>
-      <c r="R491" s="12"/>
+      <c r="P491" s="13"/>
+      <c r="R491" s="11"/>
     </row>
     <row r="492" spans="15:18">
       <c r="O492" s="7"/>
-      <c r="R492" s="12"/>
+      <c r="P492" s="13"/>
+      <c r="R492" s="11"/>
     </row>
     <row r="493" spans="15:18">
       <c r="O493" s="7"/>
-      <c r="R493" s="12"/>
+      <c r="P493" s="13"/>
+      <c r="R493" s="11"/>
     </row>
     <row r="494" spans="15:18">
       <c r="O494" s="7"/>
-      <c r="R494" s="12"/>
+      <c r="P494" s="13"/>
+      <c r="R494" s="11"/>
     </row>
     <row r="495" spans="15:18">
       <c r="O495" s="7"/>
-      <c r="R495" s="12"/>
+      <c r="P495" s="13"/>
+      <c r="R495" s="11"/>
     </row>
     <row r="496" spans="15:18">
       <c r="O496" s="7"/>
-      <c r="R496" s="12"/>
+      <c r="P496" s="13"/>
+      <c r="R496" s="11"/>
     </row>
     <row r="497" spans="15:18">
       <c r="O497" s="7"/>
-      <c r="R497" s="12"/>
+      <c r="P497" s="13"/>
+      <c r="R497" s="11"/>
     </row>
     <row r="498" spans="15:18">
       <c r="O498" s="7"/>
-      <c r="R498" s="12"/>
+      <c r="P498" s="13"/>
+      <c r="R498" s="11"/>
     </row>
     <row r="499" spans="15:18">
       <c r="O499" s="7"/>
-      <c r="R499" s="12"/>
+      <c r="P499" s="13"/>
+      <c r="R499" s="11"/>
     </row>
     <row r="500" spans="15:18">
       <c r="O500" s="7"/>
-      <c r="R500" s="12"/>
+      <c r="P500" s="13"/>
+      <c r="R500" s="11"/>
     </row>
     <row r="501" spans="15:18">
       <c r="O501" s="7"/>
-      <c r="R501" s="12"/>
+      <c r="P501" s="13"/>
+      <c r="R501" s="11"/>
     </row>
     <row r="502" spans="15:18">
       <c r="O502" s="7"/>
-      <c r="R502" s="12"/>
+      <c r="P502" s="13"/>
+      <c r="R502" s="11"/>
     </row>
     <row r="503" spans="15:18">
       <c r="O503" s="7"/>
-      <c r="R503" s="12"/>
+      <c r="P503" s="13"/>
+      <c r="R503" s="11"/>
     </row>
     <row r="504" spans="15:18">
       <c r="O504" s="7"/>
-      <c r="R504" s="12"/>
+      <c r="P504" s="13"/>
+      <c r="R504" s="11"/>
     </row>
     <row r="505" spans="15:18">
       <c r="O505" s="7"/>
-      <c r="R505" s="12"/>
+      <c r="P505" s="13"/>
+      <c r="R505" s="11"/>
     </row>
     <row r="506" spans="15:18">
       <c r="O506" s="7"/>
-      <c r="R506" s="12"/>
+      <c r="P506" s="13"/>
+      <c r="R506" s="11"/>
     </row>
     <row r="507" spans="15:18">
       <c r="O507" s="7"/>
-      <c r="R507" s="12"/>
+      <c r="P507" s="13"/>
+      <c r="R507" s="11"/>
     </row>
     <row r="508" spans="15:18">
       <c r="O508" s="7"/>
-      <c r="R508" s="12"/>
+      <c r="P508" s="13"/>
+      <c r="R508" s="11"/>
     </row>
     <row r="509" spans="15:18">
       <c r="O509" s="7"/>
-      <c r="R509" s="12"/>
+      <c r="P509" s="13"/>
+      <c r="R509" s="11"/>
     </row>
     <row r="510" spans="15:18">
       <c r="O510" s="7"/>
-      <c r="R510" s="12"/>
+      <c r="P510" s="13"/>
+      <c r="R510" s="11"/>
     </row>
     <row r="511" spans="15:18">
       <c r="O511" s="7"/>
-      <c r="R511" s="12"/>
+      <c r="P511" s="13"/>
+      <c r="R511" s="11"/>
     </row>
     <row r="512" spans="15:18">
       <c r="O512" s="7"/>
-      <c r="R512" s="12"/>
+      <c r="P512" s="13"/>
+      <c r="R512" s="11"/>
     </row>
     <row r="513" spans="15:18">
       <c r="O513" s="7"/>
-      <c r="R513" s="12"/>
+      <c r="P513" s="13"/>
+      <c r="R513" s="11"/>
     </row>
     <row r="514" spans="15:18">
       <c r="O514" s="7"/>
-      <c r="R514" s="12"/>
+      <c r="P514" s="13"/>
+      <c r="R514" s="11"/>
     </row>
     <row r="515" spans="15:18">
       <c r="O515" s="7"/>
-      <c r="R515" s="12"/>
+      <c r="P515" s="13"/>
+      <c r="R515" s="11"/>
     </row>
     <row r="516" spans="15:18">
       <c r="O516" s="7"/>
-      <c r="R516" s="12"/>
+      <c r="P516" s="13"/>
+      <c r="R516" s="11"/>
     </row>
     <row r="517" spans="15:18">
       <c r="O517" s="7"/>
-      <c r="R517" s="12"/>
+      <c r="P517" s="13"/>
+      <c r="R517" s="11"/>
     </row>
     <row r="518" spans="15:18">
       <c r="O518" s="7"/>
-      <c r="R518" s="12"/>
+      <c r="P518" s="13"/>
+      <c r="R518" s="11"/>
     </row>
     <row r="519" spans="15:18">
       <c r="O519" s="7"/>
-      <c r="R519" s="12"/>
+      <c r="P519" s="13"/>
+      <c r="R519" s="11"/>
     </row>
     <row r="520" spans="15:18">
       <c r="O520" s="7"/>
-      <c r="R520" s="12"/>
+      <c r="P520" s="13"/>
+      <c r="R520" s="11"/>
     </row>
     <row r="521" spans="15:18">
       <c r="O521" s="7"/>
-      <c r="R521" s="12"/>
+      <c r="P521" s="13"/>
+      <c r="R521" s="11"/>
     </row>
     <row r="522" spans="15:18">
-      <c r="R522" s="12"/>
+      <c r="P522" s="13"/>
+      <c r="R522" s="11"/>
     </row>
     <row r="523" spans="15:18">
-      <c r="R523" s="12"/>
+      <c r="P523" s="13"/>
+      <c r="R523" s="11"/>
     </row>
     <row r="524" spans="15:18">
-      <c r="R524" s="12"/>
+      <c r="R524" s="11"/>
     </row>
     <row r="525" spans="15:18">
-      <c r="R525" s="12"/>
+      <c r="R525" s="11"/>
     </row>
     <row r="526" spans="15:18">
-      <c r="R526" s="12"/>
+      <c r="R526" s="11"/>
     </row>
     <row r="527" spans="15:18">
-      <c r="R527" s="12"/>
+      <c r="R527" s="11"/>
     </row>
     <row r="528" spans="15:18">
-      <c r="R528" s="12"/>
+      <c r="R528" s="11"/>
     </row>
     <row r="529" spans="18:18">
-      <c r="R529" s="12"/>
+      <c r="R529" s="11"/>
     </row>
     <row r="530" spans="18:18">
-      <c r="R530" s="12"/>
+      <c r="R530" s="11"/>
     </row>
     <row r="531" spans="18:18">
-      <c r="R531" s="12"/>
+      <c r="R531" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -3114,7 +3631,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S6 S8:S9 S11:S1048576" xr:uid="{F8BCA374-D361-4313-9C59-CF82877BB18A}">
       <formula1>", YES, NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6 Q8:Q1048576" xr:uid="{16DEDA22-1651-49B2-AAF1-65C50FFEDD2D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6 Q8:Q1048576 P2:P523" xr:uid="{16DEDA22-1651-49B2-AAF1-65C50FFEDD2D}">
       <formula1>"YES, NO"</formula1>
     </dataValidation>
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="R8:R529 R2:R6" xr:uid="{AB023EC7-7443-46B0-A956-FA2A83A11DFD}">

--- a/public/Ananbay_template.xlsx
+++ b/public/Ananbay_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\TebGroup\teb-express-tunghoang\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE8AA35-A6D8-489F-B658-43B3BAF7C960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39247435-F6B7-44F9-91D4-1FC35F3080D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Tên người nhận</t>
   </si>
@@ -140,45 +140,6 @@
     <t>Shirt</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>43645 Marguerite st</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>CALIFORNIA</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>MD</t>
-    </r>
-  </si>
-  <si>
-    <t>Ornament</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
@@ -191,31 +152,13 @@
     <t>Express</t>
   </si>
   <si>
-    <t>Jennifer Brown</t>
-  </si>
-  <si>
     <t>321075232</t>
-  </si>
-  <si>
-    <t>321075233</t>
-  </si>
-  <si>
-    <t>321186904</t>
   </si>
   <si>
     <t>321186905</t>
   </si>
   <si>
-    <t>321186906</t>
-  </si>
-  <si>
-    <t>https://s3-fsg-1.fecom.io/labels1/0a4ba38c-dbda-4e30-a1fd-example.pdf</t>
-  </si>
-  <si>
     <t>https://seller-us.tiktok.com/wsos_v2/oec_fulfillment_doc_tts/object/wsos67e648f023c08b2b?expire=1743231678&amp;skipCookie=true&amp;timeStamp=1743145278&amp;sign=ec6024dfc8a63c6ee6d987234503f0f730fe44c15cc06b2757363a40d2a2c9b4</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1HvxQsXIGeox-XxargWYcAHVeKAHanxGI/view</t>
   </si>
   <si>
     <t>Ship By Tiktok</t>
@@ -635,7 +578,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V531"/>
+  <dimension ref="A1:V528"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.5546875" customWidth="1"/>
@@ -704,16 +647,16 @@
         <v>14</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
@@ -746,7 +689,7 @@
         <v>23</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>24</v>
@@ -764,10 +707,10 @@
         <v>3</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R2" s="11"/>
       <c r="T2" t="s">
@@ -780,243 +723,70 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15" thickBot="1">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
+    <row r="3" spans="1:22" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A3" s="3"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="6">
-        <v>19033</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>24</v>
       </c>
       <c r="K3" s="8">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="L3" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M3" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N3" s="8">
         <v>3</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P3" s="13"/>
       <c r="R3" s="14" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="U3">
         <v>1</v>
       </c>
       <c r="V3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="6">
-        <v>20619</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="8">
-        <v>70</v>
-      </c>
-      <c r="L4" s="8">
-        <v>13</v>
-      </c>
-      <c r="M4" s="8">
-        <v>13</v>
-      </c>
-      <c r="N4" s="8">
-        <v>3</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="R4" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="T4" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="6">
-        <v>20619</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="8">
-        <v>70</v>
-      </c>
-      <c r="L5" s="8">
-        <v>13</v>
-      </c>
-      <c r="M5" s="8">
-        <v>13</v>
-      </c>
-      <c r="N5" s="8">
-        <v>3</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>44</v>
-      </c>
+    <row r="4" spans="1:22">
+      <c r="O4" s="7"/>
+      <c r="P4" s="13"/>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="O5" s="7"/>
       <c r="P5" s="13"/>
-      <c r="R5" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="S5" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" t="s">
-        <v>25</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="16.8" customHeight="1" thickBot="1">
-      <c r="A6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="6">
-        <v>20619</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="8">
-        <v>70</v>
-      </c>
-      <c r="L6" s="8">
-        <v>13</v>
-      </c>
-      <c r="M6" s="8">
-        <v>13</v>
-      </c>
-      <c r="N6" s="8">
-        <v>3</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>44</v>
-      </c>
+      <c r="R5" s="11"/>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="O6" s="7"/>
       <c r="P6" s="13"/>
-      <c r="R6" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="S6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="T6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="V6">
-        <v>12</v>
-      </c>
+      <c r="R6" s="11"/>
     </row>
     <row r="7" spans="1:22">
       <c r="O7" s="7"/>
       <c r="P7" s="13"/>
+      <c r="R7" s="11"/>
     </row>
     <row r="8" spans="1:22">
       <c r="O8" s="7"/>
@@ -3574,26 +3344,20 @@
       <c r="R518" s="11"/>
     </row>
     <row r="519" spans="15:18">
-      <c r="O519" s="7"/>
       <c r="P519" s="13"/>
       <c r="R519" s="11"/>
     </row>
     <row r="520" spans="15:18">
-      <c r="O520" s="7"/>
       <c r="P520" s="13"/>
       <c r="R520" s="11"/>
     </row>
     <row r="521" spans="15:18">
-      <c r="O521" s="7"/>
-      <c r="P521" s="13"/>
       <c r="R521" s="11"/>
     </row>
     <row r="522" spans="15:18">
-      <c r="P522" s="13"/>
       <c r="R522" s="11"/>
     </row>
     <row r="523" spans="15:18">
-      <c r="P523" s="13"/>
       <c r="R523" s="11"/>
     </row>
     <row r="524" spans="15:18">
@@ -3611,41 +3375,29 @@
     <row r="528" spans="15:18">
       <c r="R528" s="11"/>
     </row>
-    <row r="529" spans="18:18">
-      <c r="R529" s="11"/>
-    </row>
-    <row r="530" spans="18:18">
-      <c r="R530" s="11"/>
-    </row>
-    <row r="531" spans="18:18">
-      <c r="R531" s="11"/>
-    </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R530:R531" xr:uid="{709BC68A-C242-4787-A4C8-EA4F2DF4203E}">
-      <formula1>IF($O530="Tiktok", R530&lt;&gt;"", TRUE)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R527:R528" xr:uid="{709BC68A-C242-4787-A4C8-EA4F2DF4203E}">
+      <formula1>IF($O527="Tiktok", R527&lt;&gt;"", TRUE)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O522:O1048576" xr:uid="{10C1B1BA-30A4-43AA-B6F4-A5F0B0F55982}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O519:O1048576" xr:uid="{10C1B1BA-30A4-43AA-B6F4-A5F0B0F55982}">
       <formula1>"Express, Tiktok"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S6 S8:S9 S11:S1048576" xr:uid="{F8BCA374-D361-4313-9C59-CF82877BB18A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5:S6 S8:S1048576 S2:S3" xr:uid="{F8BCA374-D361-4313-9C59-CF82877BB18A}">
       <formula1>", YES, NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6 Q8:Q1048576 P2:P523" xr:uid="{16DEDA22-1651-49B2-AAF1-65C50FFEDD2D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q5:Q1048576 Q2:Q3 P2:P520" xr:uid="{16DEDA22-1651-49B2-AAF1-65C50FFEDD2D}">
       <formula1>"YES, NO"</formula1>
     </dataValidation>
-    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="R8:R529 R2:R6" xr:uid="{AB023EC7-7443-46B0-A956-FA2A83A11DFD}">
+    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="R5:R526 R2:R3" xr:uid="{AB023EC7-7443-46B0-A956-FA2A83A11DFD}">
       <formula1>IF($O2="Tiktok", R2&lt;&gt;"", TRUE)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O521" xr:uid="{8664190F-EA7C-4D2F-AC04-A222D6E43D96}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O518" xr:uid="{8664190F-EA7C-4D2F-AC04-A222D6E43D96}">
       <formula1>"Express, Ship By Tiktok"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="R4" r:id="rId1" xr:uid="{76E30326-4126-47A2-B998-13BFF5AC8CB0}"/>
-    <hyperlink ref="R5" r:id="rId2" xr:uid="{1BA6FB39-2A12-4199-9359-4A92E9981534}"/>
-    <hyperlink ref="R6" r:id="rId3" xr:uid="{407B0B84-A534-457B-A8CA-A1CE178CC981}"/>
-    <hyperlink ref="R3" r:id="rId4" xr:uid="{C7B06EFA-603B-4084-A643-C12280E2CECC}"/>
+    <hyperlink ref="R3" r:id="rId1" xr:uid="{1BA6FB39-2A12-4199-9359-4A92E9981534}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/public/Ananbay_template.xlsx
+++ b/public/Ananbay_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\TebGroup\teb-express-tunghoang\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\TebGroup\aTung-tebexpress-cus\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39247435-F6B7-44F9-91D4-1FC35F3080D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877A5DAD-B87D-4855-921A-95FA359540C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,22 +149,22 @@
     <t>Mã nhãn Tiktok</t>
   </si>
   <si>
-    <t>Express</t>
-  </si>
-  <si>
     <t>321075232</t>
   </si>
   <si>
     <t>321186905</t>
   </si>
   <si>
-    <t>https://seller-us.tiktok.com/wsos_v2/oec_fulfillment_doc_tts/object/wsos67e648f023c08b2b?expire=1743231678&amp;skipCookie=true&amp;timeStamp=1743145278&amp;sign=ec6024dfc8a63c6ee6d987234503f0f730fe44c15cc06b2757363a40d2a2c9b4</t>
-  </si>
-  <si>
     <t>Ship By Tiktok</t>
   </si>
   <si>
     <t>Hàng TradeMark</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=download&amp;id=1gTk2GJUmt2k9FGdCRib01Qw9oOTSc0QU</t>
   </si>
 </sst>
 </file>
@@ -647,7 +647,7 @@
         <v>14</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
@@ -689,7 +689,7 @@
         <v>23</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>24</v>
@@ -707,7 +707,7 @@
         <v>3</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P2" s="13" t="s">
         <v>26</v>
@@ -732,7 +732,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="3"/>
       <c r="I3" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>24</v>
@@ -750,11 +750,11 @@
         <v>3</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P3" s="13"/>
       <c r="R3" s="14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S3" s="13" t="s">
         <v>26</v>
@@ -3383,7 +3383,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O519:O1048576" xr:uid="{10C1B1BA-30A4-43AA-B6F4-A5F0B0F55982}">
       <formula1>"Express, Tiktok"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5:S6 S8:S1048576 S2:S3" xr:uid="{F8BCA374-D361-4313-9C59-CF82877BB18A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S8:S1048576 S2:S6" xr:uid="{F8BCA374-D361-4313-9C59-CF82877BB18A}">
       <formula1>", YES, NO"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q5:Q1048576 Q2:Q3 P2:P520" xr:uid="{16DEDA22-1651-49B2-AAF1-65C50FFEDD2D}">
@@ -3392,13 +3392,10 @@
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="R5:R526 R2:R3" xr:uid="{AB023EC7-7443-46B0-A956-FA2A83A11DFD}">
       <formula1>IF($O2="Tiktok", R2&lt;&gt;"", TRUE)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O518" xr:uid="{8664190F-EA7C-4D2F-AC04-A222D6E43D96}">
-      <formula1>"Express, Ship By Tiktok"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O518" xr:uid="{D4F5877A-3FE9-4602-ABFD-C44BAAB259EC}">
+      <formula1>"Standard, Express, Ship By Tiktok, Super Express"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{1BA6FB39-2A12-4199-9359-4A92E9981534}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/public/Ananbay_template.xlsx
+++ b/public/Ananbay_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\TebGroup\aTung-tebexpress-cus\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877A5DAD-B87D-4855-921A-95FA359540C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9450662D-9358-49F2-8FC2-4B4D5CFD9582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Tên người nhận</t>
   </si>
@@ -166,6 +166,9 @@
   <si>
     <t>https://drive.google.com/uc?export=download&amp;id=1gTk2GJUmt2k9FGdCRib01Qw9oOTSc0QU</t>
   </si>
+  <si>
+    <t>04225</t>
+  </si>
 </sst>
 </file>
 
@@ -174,7 +177,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General\,"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -230,6 +233,11 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -273,7 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -283,9 +291,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -301,6 +306,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -584,23 +594,23 @@
     <col min="1" max="1" width="15.5546875" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="10" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="10" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="8.33203125" customWidth="1"/>
     <col min="13" max="13" width="9.88671875" customWidth="1"/>
     <col min="15" max="15" width="10.44140625" customWidth="1"/>
     <col min="16" max="16" width="15.6640625" customWidth="1"/>
-    <col min="17" max="17" width="7.77734375" style="13" customWidth="1"/>
+    <col min="17" max="17" width="7.77734375" style="12" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="13.109375" style="13" customWidth="1"/>
+    <col min="19" max="19" width="13.109375" style="12" customWidth="1"/>
     <col min="21" max="21" width="11.6640625" customWidth="1"/>
     <col min="1023" max="1023" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="15" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -619,13 +629,13 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -646,7 +656,7 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>32</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -655,7 +665,7 @@
       <c r="R1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="S1" s="11" t="s">
         <v>27</v>
       </c>
       <c r="T1" s="1" t="s">
@@ -682,37 +692,37 @@
       <c r="F2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="6">
-        <v>19033</v>
+      <c r="G2" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="7">
         <v>85</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="7">
         <v>15</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="7">
         <v>15</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="7">
         <v>3</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="11"/>
+      <c r="R2" s="10"/>
       <c r="T2" t="s">
         <v>25</v>
       </c>
@@ -729,34 +739,36 @@
       <c r="D3" s="5"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="6"/>
+      <c r="G3" s="14">
+        <v>13423</v>
+      </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="7">
         <v>70</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="7">
         <v>13</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="7">
         <v>13</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="7">
         <v>3</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="R3" s="14" t="s">
+      <c r="P3" s="12"/>
+      <c r="R3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="S3" s="12" t="s">
         <v>26</v>
       </c>
       <c r="T3" t="s">
@@ -770,2612 +782,2614 @@
       </c>
     </row>
     <row r="4" spans="1:22">
-      <c r="O4" s="7"/>
-      <c r="P4" s="13"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="12"/>
     </row>
     <row r="5" spans="1:22">
-      <c r="O5" s="7"/>
-      <c r="P5" s="13"/>
-      <c r="R5" s="11"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="12"/>
+      <c r="R5" s="10"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="O6" s="7"/>
-      <c r="P6" s="13"/>
-      <c r="R6" s="11"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="12"/>
+      <c r="R6" s="10"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="O7" s="7"/>
-      <c r="P7" s="13"/>
-      <c r="R7" s="11"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="12"/>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="O8" s="7"/>
-      <c r="P8" s="13"/>
-      <c r="R8" s="11"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="12"/>
+      <c r="R8" s="10"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="O9" s="7"/>
-      <c r="P9" s="13"/>
-      <c r="R9" s="11"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="12"/>
+      <c r="R9" s="10"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="O10" s="7"/>
-      <c r="P10" s="13"/>
-      <c r="R10" s="11"/>
+      <c r="D10" s="16"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="12"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="O11" s="7"/>
-      <c r="P11" s="13"/>
-      <c r="R11" s="11"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="12"/>
+      <c r="R11" s="10"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="O12" s="7"/>
-      <c r="P12" s="13"/>
-      <c r="R12" s="11"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="12"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" spans="1:22">
-      <c r="O13" s="7"/>
-      <c r="P13" s="13"/>
-      <c r="R13" s="11"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="12"/>
+      <c r="R13" s="10"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="O14" s="7"/>
-      <c r="P14" s="13"/>
-      <c r="R14" s="11"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="12"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="O15" s="7"/>
-      <c r="P15" s="13"/>
-      <c r="R15" s="11"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="12"/>
+      <c r="R15" s="10"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="O16" s="7"/>
-      <c r="P16" s="13"/>
-      <c r="R16" s="11"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="12"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" spans="15:18">
-      <c r="O17" s="7"/>
-      <c r="P17" s="13"/>
-      <c r="R17" s="11"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="12"/>
+      <c r="R17" s="10"/>
     </row>
     <row r="18" spans="15:18">
-      <c r="O18" s="7"/>
-      <c r="P18" s="13"/>
-      <c r="R18" s="11"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="12"/>
+      <c r="R18" s="10"/>
     </row>
     <row r="19" spans="15:18">
-      <c r="O19" s="7"/>
-      <c r="P19" s="13"/>
-      <c r="R19" s="11"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="12"/>
+      <c r="R19" s="10"/>
     </row>
     <row r="20" spans="15:18">
-      <c r="O20" s="7"/>
-      <c r="P20" s="13"/>
-      <c r="R20" s="11"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="12"/>
+      <c r="R20" s="10"/>
     </row>
     <row r="21" spans="15:18">
-      <c r="O21" s="7"/>
-      <c r="P21" s="13"/>
-      <c r="R21" s="11"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="12"/>
+      <c r="R21" s="10"/>
     </row>
     <row r="22" spans="15:18">
-      <c r="O22" s="7"/>
-      <c r="P22" s="13"/>
-      <c r="R22" s="11"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="12"/>
+      <c r="R22" s="10"/>
     </row>
     <row r="23" spans="15:18">
-      <c r="O23" s="7"/>
-      <c r="P23" s="13"/>
-      <c r="R23" s="11"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="12"/>
+      <c r="R23" s="10"/>
     </row>
     <row r="24" spans="15:18">
-      <c r="O24" s="7"/>
-      <c r="P24" s="13"/>
-      <c r="R24" s="11"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="12"/>
+      <c r="R24" s="10"/>
     </row>
     <row r="25" spans="15:18">
-      <c r="O25" s="7"/>
-      <c r="P25" s="13"/>
-      <c r="R25" s="11"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="12"/>
+      <c r="R25" s="10"/>
     </row>
     <row r="26" spans="15:18">
-      <c r="O26" s="7"/>
-      <c r="P26" s="13"/>
-      <c r="R26" s="11"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="12"/>
+      <c r="R26" s="10"/>
     </row>
     <row r="27" spans="15:18">
-      <c r="O27" s="7"/>
-      <c r="P27" s="13"/>
-      <c r="R27" s="11"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="12"/>
+      <c r="R27" s="10"/>
     </row>
     <row r="28" spans="15:18">
-      <c r="O28" s="7"/>
-      <c r="P28" s="13"/>
-      <c r="R28" s="11"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="12"/>
+      <c r="R28" s="10"/>
     </row>
     <row r="29" spans="15:18">
-      <c r="O29" s="7"/>
-      <c r="P29" s="13"/>
-      <c r="R29" s="11"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="12"/>
+      <c r="R29" s="10"/>
     </row>
     <row r="30" spans="15:18">
-      <c r="O30" s="7"/>
-      <c r="P30" s="13"/>
-      <c r="R30" s="11"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="12"/>
+      <c r="R30" s="10"/>
     </row>
     <row r="31" spans="15:18">
-      <c r="O31" s="7"/>
-      <c r="P31" s="13"/>
-      <c r="R31" s="11"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="12"/>
+      <c r="R31" s="10"/>
     </row>
     <row r="32" spans="15:18">
-      <c r="O32" s="7"/>
-      <c r="P32" s="13"/>
-      <c r="R32" s="11"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="12"/>
+      <c r="R32" s="10"/>
     </row>
     <row r="33" spans="15:18">
-      <c r="O33" s="7"/>
-      <c r="P33" s="13"/>
-      <c r="R33" s="11"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="12"/>
+      <c r="R33" s="10"/>
     </row>
     <row r="34" spans="15:18">
-      <c r="O34" s="7"/>
-      <c r="P34" s="13"/>
-      <c r="R34" s="11"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="12"/>
+      <c r="R34" s="10"/>
     </row>
     <row r="35" spans="15:18">
-      <c r="O35" s="7"/>
-      <c r="P35" s="13"/>
-      <c r="R35" s="11"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="12"/>
+      <c r="R35" s="10"/>
     </row>
     <row r="36" spans="15:18">
-      <c r="O36" s="7"/>
-      <c r="P36" s="13"/>
-      <c r="R36" s="11"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="12"/>
+      <c r="R36" s="10"/>
     </row>
     <row r="37" spans="15:18">
-      <c r="O37" s="7"/>
-      <c r="P37" s="13"/>
-      <c r="R37" s="11"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="12"/>
+      <c r="R37" s="10"/>
     </row>
     <row r="38" spans="15:18">
-      <c r="O38" s="7"/>
-      <c r="P38" s="13"/>
-      <c r="R38" s="11"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="12"/>
+      <c r="R38" s="10"/>
     </row>
     <row r="39" spans="15:18">
-      <c r="O39" s="7"/>
-      <c r="P39" s="13"/>
-      <c r="R39" s="11"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="12"/>
+      <c r="R39" s="10"/>
     </row>
     <row r="40" spans="15:18">
-      <c r="O40" s="7"/>
-      <c r="P40" s="13"/>
-      <c r="R40" s="11"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="12"/>
+      <c r="R40" s="10"/>
     </row>
     <row r="41" spans="15:18">
-      <c r="O41" s="7"/>
-      <c r="P41" s="13"/>
-      <c r="R41" s="11"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="12"/>
+      <c r="R41" s="10"/>
     </row>
     <row r="42" spans="15:18">
-      <c r="O42" s="7"/>
-      <c r="P42" s="13"/>
-      <c r="R42" s="11"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="12"/>
+      <c r="R42" s="10"/>
     </row>
     <row r="43" spans="15:18">
-      <c r="O43" s="7"/>
-      <c r="P43" s="13"/>
-      <c r="R43" s="11"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="12"/>
+      <c r="R43" s="10"/>
     </row>
     <row r="44" spans="15:18">
-      <c r="O44" s="7"/>
-      <c r="P44" s="13"/>
-      <c r="R44" s="11"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="12"/>
+      <c r="R44" s="10"/>
     </row>
     <row r="45" spans="15:18">
-      <c r="O45" s="7"/>
-      <c r="P45" s="13"/>
-      <c r="R45" s="11"/>
+      <c r="O45" s="6"/>
+      <c r="P45" s="12"/>
+      <c r="R45" s="10"/>
     </row>
     <row r="46" spans="15:18">
-      <c r="O46" s="7"/>
-      <c r="P46" s="13"/>
-      <c r="R46" s="11"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="12"/>
+      <c r="R46" s="10"/>
     </row>
     <row r="47" spans="15:18">
-      <c r="O47" s="7"/>
-      <c r="P47" s="13"/>
-      <c r="R47" s="11"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="12"/>
+      <c r="R47" s="10"/>
     </row>
     <row r="48" spans="15:18">
-      <c r="O48" s="7"/>
-      <c r="P48" s="13"/>
-      <c r="R48" s="11"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="12"/>
+      <c r="R48" s="10"/>
     </row>
     <row r="49" spans="15:18">
-      <c r="O49" s="7"/>
-      <c r="P49" s="13"/>
-      <c r="R49" s="11"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="12"/>
+      <c r="R49" s="10"/>
     </row>
     <row r="50" spans="15:18">
-      <c r="O50" s="7"/>
-      <c r="P50" s="13"/>
-      <c r="R50" s="11"/>
+      <c r="O50" s="6"/>
+      <c r="P50" s="12"/>
+      <c r="R50" s="10"/>
     </row>
     <row r="51" spans="15:18">
-      <c r="O51" s="7"/>
-      <c r="P51" s="13"/>
-      <c r="R51" s="11"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="12"/>
+      <c r="R51" s="10"/>
     </row>
     <row r="52" spans="15:18">
-      <c r="O52" s="7"/>
-      <c r="P52" s="13"/>
-      <c r="R52" s="11"/>
+      <c r="O52" s="6"/>
+      <c r="P52" s="12"/>
+      <c r="R52" s="10"/>
     </row>
     <row r="53" spans="15:18">
-      <c r="O53" s="7"/>
-      <c r="P53" s="13"/>
-      <c r="R53" s="11"/>
+      <c r="O53" s="6"/>
+      <c r="P53" s="12"/>
+      <c r="R53" s="10"/>
     </row>
     <row r="54" spans="15:18">
-      <c r="O54" s="7"/>
-      <c r="P54" s="13"/>
-      <c r="R54" s="11"/>
+      <c r="O54" s="6"/>
+      <c r="P54" s="12"/>
+      <c r="R54" s="10"/>
     </row>
     <row r="55" spans="15:18">
-      <c r="O55" s="7"/>
-      <c r="P55" s="13"/>
-      <c r="R55" s="11"/>
+      <c r="O55" s="6"/>
+      <c r="P55" s="12"/>
+      <c r="R55" s="10"/>
     </row>
     <row r="56" spans="15:18">
-      <c r="O56" s="7"/>
-      <c r="P56" s="13"/>
-      <c r="R56" s="11"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="12"/>
+      <c r="R56" s="10"/>
     </row>
     <row r="57" spans="15:18">
-      <c r="O57" s="7"/>
-      <c r="P57" s="13"/>
-      <c r="R57" s="11"/>
+      <c r="O57" s="6"/>
+      <c r="P57" s="12"/>
+      <c r="R57" s="10"/>
     </row>
     <row r="58" spans="15:18">
-      <c r="O58" s="7"/>
-      <c r="P58" s="13"/>
-      <c r="R58" s="11"/>
+      <c r="O58" s="6"/>
+      <c r="P58" s="12"/>
+      <c r="R58" s="10"/>
     </row>
     <row r="59" spans="15:18">
-      <c r="O59" s="7"/>
-      <c r="P59" s="13"/>
-      <c r="R59" s="11"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="12"/>
+      <c r="R59" s="10"/>
     </row>
     <row r="60" spans="15:18">
-      <c r="O60" s="7"/>
-      <c r="P60" s="13"/>
-      <c r="R60" s="11"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="12"/>
+      <c r="R60" s="10"/>
     </row>
     <row r="61" spans="15:18">
-      <c r="O61" s="7"/>
-      <c r="P61" s="13"/>
-      <c r="R61" s="11"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="12"/>
+      <c r="R61" s="10"/>
     </row>
     <row r="62" spans="15:18">
-      <c r="O62" s="7"/>
-      <c r="P62" s="13"/>
-      <c r="R62" s="11"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="12"/>
+      <c r="R62" s="10"/>
     </row>
     <row r="63" spans="15:18">
-      <c r="O63" s="7"/>
-      <c r="P63" s="13"/>
-      <c r="R63" s="11"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="12"/>
+      <c r="R63" s="10"/>
     </row>
     <row r="64" spans="15:18">
-      <c r="O64" s="7"/>
-      <c r="P64" s="13"/>
-      <c r="R64" s="11"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="12"/>
+      <c r="R64" s="10"/>
     </row>
     <row r="65" spans="15:18">
-      <c r="O65" s="7"/>
-      <c r="P65" s="13"/>
-      <c r="R65" s="11"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="12"/>
+      <c r="R65" s="10"/>
     </row>
     <row r="66" spans="15:18">
-      <c r="O66" s="7"/>
-      <c r="P66" s="13"/>
-      <c r="R66" s="11"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="12"/>
+      <c r="R66" s="10"/>
     </row>
     <row r="67" spans="15:18">
-      <c r="O67" s="7"/>
-      <c r="P67" s="13"/>
-      <c r="R67" s="11"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="12"/>
+      <c r="R67" s="10"/>
     </row>
     <row r="68" spans="15:18">
-      <c r="O68" s="7"/>
-      <c r="P68" s="13"/>
-      <c r="R68" s="11"/>
+      <c r="O68" s="6"/>
+      <c r="P68" s="12"/>
+      <c r="R68" s="10"/>
     </row>
     <row r="69" spans="15:18">
-      <c r="O69" s="7"/>
-      <c r="P69" s="13"/>
-      <c r="R69" s="11"/>
+      <c r="O69" s="6"/>
+      <c r="P69" s="12"/>
+      <c r="R69" s="10"/>
     </row>
     <row r="70" spans="15:18">
-      <c r="O70" s="7"/>
-      <c r="P70" s="13"/>
-      <c r="R70" s="11"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="12"/>
+      <c r="R70" s="10"/>
     </row>
     <row r="71" spans="15:18">
-      <c r="O71" s="7"/>
-      <c r="P71" s="13"/>
-      <c r="R71" s="11"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="12"/>
+      <c r="R71" s="10"/>
     </row>
     <row r="72" spans="15:18">
-      <c r="O72" s="7"/>
-      <c r="P72" s="13"/>
-      <c r="R72" s="11"/>
+      <c r="O72" s="6"/>
+      <c r="P72" s="12"/>
+      <c r="R72" s="10"/>
     </row>
     <row r="73" spans="15:18">
-      <c r="O73" s="7"/>
-      <c r="P73" s="13"/>
-      <c r="R73" s="11"/>
+      <c r="O73" s="6"/>
+      <c r="P73" s="12"/>
+      <c r="R73" s="10"/>
     </row>
     <row r="74" spans="15:18">
-      <c r="O74" s="7"/>
-      <c r="P74" s="13"/>
-      <c r="R74" s="11"/>
+      <c r="O74" s="6"/>
+      <c r="P74" s="12"/>
+      <c r="R74" s="10"/>
     </row>
     <row r="75" spans="15:18">
-      <c r="O75" s="7"/>
-      <c r="P75" s="13"/>
-      <c r="R75" s="11"/>
+      <c r="O75" s="6"/>
+      <c r="P75" s="12"/>
+      <c r="R75" s="10"/>
     </row>
     <row r="76" spans="15:18">
-      <c r="O76" s="7"/>
-      <c r="P76" s="13"/>
-      <c r="R76" s="11"/>
+      <c r="O76" s="6"/>
+      <c r="P76" s="12"/>
+      <c r="R76" s="10"/>
     </row>
     <row r="77" spans="15:18">
-      <c r="O77" s="7"/>
-      <c r="P77" s="13"/>
-      <c r="R77" s="11"/>
+      <c r="O77" s="6"/>
+      <c r="P77" s="12"/>
+      <c r="R77" s="10"/>
     </row>
     <row r="78" spans="15:18">
-      <c r="O78" s="7"/>
-      <c r="P78" s="13"/>
-      <c r="R78" s="11"/>
+      <c r="O78" s="6"/>
+      <c r="P78" s="12"/>
+      <c r="R78" s="10"/>
     </row>
     <row r="79" spans="15:18">
-      <c r="O79" s="7"/>
-      <c r="P79" s="13"/>
-      <c r="R79" s="11"/>
+      <c r="O79" s="6"/>
+      <c r="P79" s="12"/>
+      <c r="R79" s="10"/>
     </row>
     <row r="80" spans="15:18">
-      <c r="O80" s="7"/>
-      <c r="P80" s="13"/>
-      <c r="R80" s="11"/>
+      <c r="O80" s="6"/>
+      <c r="P80" s="12"/>
+      <c r="R80" s="10"/>
     </row>
     <row r="81" spans="15:18">
-      <c r="O81" s="7"/>
-      <c r="P81" s="13"/>
-      <c r="R81" s="11"/>
+      <c r="O81" s="6"/>
+      <c r="P81" s="12"/>
+      <c r="R81" s="10"/>
     </row>
     <row r="82" spans="15:18">
-      <c r="O82" s="7"/>
-      <c r="P82" s="13"/>
-      <c r="R82" s="11"/>
+      <c r="O82" s="6"/>
+      <c r="P82" s="12"/>
+      <c r="R82" s="10"/>
     </row>
     <row r="83" spans="15:18">
-      <c r="O83" s="7"/>
-      <c r="P83" s="13"/>
-      <c r="R83" s="11"/>
+      <c r="O83" s="6"/>
+      <c r="P83" s="12"/>
+      <c r="R83" s="10"/>
     </row>
     <row r="84" spans="15:18">
-      <c r="O84" s="7"/>
-      <c r="P84" s="13"/>
-      <c r="R84" s="11"/>
+      <c r="O84" s="6"/>
+      <c r="P84" s="12"/>
+      <c r="R84" s="10"/>
     </row>
     <row r="85" spans="15:18">
-      <c r="O85" s="7"/>
-      <c r="P85" s="13"/>
-      <c r="R85" s="11"/>
+      <c r="O85" s="6"/>
+      <c r="P85" s="12"/>
+      <c r="R85" s="10"/>
     </row>
     <row r="86" spans="15:18">
-      <c r="O86" s="7"/>
-      <c r="P86" s="13"/>
-      <c r="R86" s="11"/>
+      <c r="O86" s="6"/>
+      <c r="P86" s="12"/>
+      <c r="R86" s="10"/>
     </row>
     <row r="87" spans="15:18">
-      <c r="O87" s="7"/>
-      <c r="P87" s="13"/>
-      <c r="R87" s="11"/>
+      <c r="O87" s="6"/>
+      <c r="P87" s="12"/>
+      <c r="R87" s="10"/>
     </row>
     <row r="88" spans="15:18">
-      <c r="O88" s="7"/>
-      <c r="P88" s="13"/>
-      <c r="R88" s="11"/>
+      <c r="O88" s="6"/>
+      <c r="P88" s="12"/>
+      <c r="R88" s="10"/>
     </row>
     <row r="89" spans="15:18">
-      <c r="O89" s="7"/>
-      <c r="P89" s="13"/>
-      <c r="R89" s="11"/>
+      <c r="O89" s="6"/>
+      <c r="P89" s="12"/>
+      <c r="R89" s="10"/>
     </row>
     <row r="90" spans="15:18">
-      <c r="O90" s="7"/>
-      <c r="P90" s="13"/>
-      <c r="R90" s="11"/>
+      <c r="O90" s="6"/>
+      <c r="P90" s="12"/>
+      <c r="R90" s="10"/>
     </row>
     <row r="91" spans="15:18">
-      <c r="O91" s="7"/>
-      <c r="P91" s="13"/>
-      <c r="R91" s="11"/>
+      <c r="O91" s="6"/>
+      <c r="P91" s="12"/>
+      <c r="R91" s="10"/>
     </row>
     <row r="92" spans="15:18">
-      <c r="O92" s="7"/>
-      <c r="P92" s="13"/>
-      <c r="R92" s="11"/>
+      <c r="O92" s="6"/>
+      <c r="P92" s="12"/>
+      <c r="R92" s="10"/>
     </row>
     <row r="93" spans="15:18">
-      <c r="O93" s="7"/>
-      <c r="P93" s="13"/>
-      <c r="R93" s="11"/>
+      <c r="O93" s="6"/>
+      <c r="P93" s="12"/>
+      <c r="R93" s="10"/>
     </row>
     <row r="94" spans="15:18">
-      <c r="O94" s="7"/>
-      <c r="P94" s="13"/>
-      <c r="R94" s="11"/>
+      <c r="O94" s="6"/>
+      <c r="P94" s="12"/>
+      <c r="R94" s="10"/>
     </row>
     <row r="95" spans="15:18">
-      <c r="O95" s="7"/>
-      <c r="P95" s="13"/>
-      <c r="R95" s="11"/>
+      <c r="O95" s="6"/>
+      <c r="P95" s="12"/>
+      <c r="R95" s="10"/>
     </row>
     <row r="96" spans="15:18">
-      <c r="O96" s="7"/>
-      <c r="P96" s="13"/>
-      <c r="R96" s="11"/>
+      <c r="O96" s="6"/>
+      <c r="P96" s="12"/>
+      <c r="R96" s="10"/>
     </row>
     <row r="97" spans="15:18">
-      <c r="O97" s="7"/>
-      <c r="P97" s="13"/>
-      <c r="R97" s="11"/>
+      <c r="O97" s="6"/>
+      <c r="P97" s="12"/>
+      <c r="R97" s="10"/>
     </row>
     <row r="98" spans="15:18">
-      <c r="O98" s="7"/>
-      <c r="P98" s="13"/>
-      <c r="R98" s="11"/>
+      <c r="O98" s="6"/>
+      <c r="P98" s="12"/>
+      <c r="R98" s="10"/>
     </row>
     <row r="99" spans="15:18">
-      <c r="O99" s="7"/>
-      <c r="P99" s="13"/>
-      <c r="R99" s="11"/>
+      <c r="O99" s="6"/>
+      <c r="P99" s="12"/>
+      <c r="R99" s="10"/>
     </row>
     <row r="100" spans="15:18">
-      <c r="O100" s="7"/>
-      <c r="P100" s="13"/>
-      <c r="R100" s="11"/>
+      <c r="O100" s="6"/>
+      <c r="P100" s="12"/>
+      <c r="R100" s="10"/>
     </row>
     <row r="101" spans="15:18">
-      <c r="O101" s="7"/>
-      <c r="P101" s="13"/>
-      <c r="R101" s="11"/>
+      <c r="O101" s="6"/>
+      <c r="P101" s="12"/>
+      <c r="R101" s="10"/>
     </row>
     <row r="102" spans="15:18">
-      <c r="O102" s="7"/>
-      <c r="P102" s="13"/>
-      <c r="R102" s="11"/>
+      <c r="O102" s="6"/>
+      <c r="P102" s="12"/>
+      <c r="R102" s="10"/>
     </row>
     <row r="103" spans="15:18">
-      <c r="O103" s="7"/>
-      <c r="P103" s="13"/>
-      <c r="R103" s="11"/>
+      <c r="O103" s="6"/>
+      <c r="P103" s="12"/>
+      <c r="R103" s="10"/>
     </row>
     <row r="104" spans="15:18">
-      <c r="O104" s="7"/>
-      <c r="P104" s="13"/>
-      <c r="R104" s="11"/>
+      <c r="O104" s="6"/>
+      <c r="P104" s="12"/>
+      <c r="R104" s="10"/>
     </row>
     <row r="105" spans="15:18">
-      <c r="O105" s="7"/>
-      <c r="P105" s="13"/>
-      <c r="R105" s="11"/>
+      <c r="O105" s="6"/>
+      <c r="P105" s="12"/>
+      <c r="R105" s="10"/>
     </row>
     <row r="106" spans="15:18">
-      <c r="O106" s="7"/>
-      <c r="P106" s="13"/>
-      <c r="R106" s="11"/>
+      <c r="O106" s="6"/>
+      <c r="P106" s="12"/>
+      <c r="R106" s="10"/>
     </row>
     <row r="107" spans="15:18">
-      <c r="O107" s="7"/>
-      <c r="P107" s="13"/>
-      <c r="R107" s="11"/>
+      <c r="O107" s="6"/>
+      <c r="P107" s="12"/>
+      <c r="R107" s="10"/>
     </row>
     <row r="108" spans="15:18">
-      <c r="O108" s="7"/>
-      <c r="P108" s="13"/>
-      <c r="R108" s="11"/>
+      <c r="O108" s="6"/>
+      <c r="P108" s="12"/>
+      <c r="R108" s="10"/>
     </row>
     <row r="109" spans="15:18">
-      <c r="O109" s="7"/>
-      <c r="P109" s="13"/>
-      <c r="R109" s="11"/>
+      <c r="O109" s="6"/>
+      <c r="P109" s="12"/>
+      <c r="R109" s="10"/>
     </row>
     <row r="110" spans="15:18">
-      <c r="O110" s="7"/>
-      <c r="P110" s="13"/>
-      <c r="R110" s="11"/>
+      <c r="O110" s="6"/>
+      <c r="P110" s="12"/>
+      <c r="R110" s="10"/>
     </row>
     <row r="111" spans="15:18">
-      <c r="O111" s="7"/>
-      <c r="P111" s="13"/>
-      <c r="R111" s="11"/>
+      <c r="O111" s="6"/>
+      <c r="P111" s="12"/>
+      <c r="R111" s="10"/>
     </row>
     <row r="112" spans="15:18">
-      <c r="O112" s="7"/>
-      <c r="P112" s="13"/>
-      <c r="R112" s="11"/>
+      <c r="O112" s="6"/>
+      <c r="P112" s="12"/>
+      <c r="R112" s="10"/>
     </row>
     <row r="113" spans="15:18">
-      <c r="O113" s="7"/>
-      <c r="P113" s="13"/>
-      <c r="R113" s="11"/>
+      <c r="O113" s="6"/>
+      <c r="P113" s="12"/>
+      <c r="R113" s="10"/>
     </row>
     <row r="114" spans="15:18">
-      <c r="O114" s="7"/>
-      <c r="P114" s="13"/>
-      <c r="R114" s="11"/>
+      <c r="O114" s="6"/>
+      <c r="P114" s="12"/>
+      <c r="R114" s="10"/>
     </row>
     <row r="115" spans="15:18">
-      <c r="O115" s="7"/>
-      <c r="P115" s="13"/>
-      <c r="R115" s="11"/>
+      <c r="O115" s="6"/>
+      <c r="P115" s="12"/>
+      <c r="R115" s="10"/>
     </row>
     <row r="116" spans="15:18">
-      <c r="O116" s="7"/>
-      <c r="P116" s="13"/>
-      <c r="R116" s="11"/>
+      <c r="O116" s="6"/>
+      <c r="P116" s="12"/>
+      <c r="R116" s="10"/>
     </row>
     <row r="117" spans="15:18">
-      <c r="O117" s="7"/>
-      <c r="P117" s="13"/>
-      <c r="R117" s="11"/>
+      <c r="O117" s="6"/>
+      <c r="P117" s="12"/>
+      <c r="R117" s="10"/>
     </row>
     <row r="118" spans="15:18">
-      <c r="O118" s="7"/>
-      <c r="P118" s="13"/>
-      <c r="R118" s="11"/>
+      <c r="O118" s="6"/>
+      <c r="P118" s="12"/>
+      <c r="R118" s="10"/>
     </row>
     <row r="119" spans="15:18">
-      <c r="O119" s="7"/>
-      <c r="P119" s="13"/>
-      <c r="R119" s="11"/>
+      <c r="O119" s="6"/>
+      <c r="P119" s="12"/>
+      <c r="R119" s="10"/>
     </row>
     <row r="120" spans="15:18">
-      <c r="O120" s="7"/>
-      <c r="P120" s="13"/>
-      <c r="R120" s="11"/>
+      <c r="O120" s="6"/>
+      <c r="P120" s="12"/>
+      <c r="R120" s="10"/>
     </row>
     <row r="121" spans="15:18">
-      <c r="O121" s="7"/>
-      <c r="P121" s="13"/>
-      <c r="R121" s="11"/>
+      <c r="O121" s="6"/>
+      <c r="P121" s="12"/>
+      <c r="R121" s="10"/>
     </row>
     <row r="122" spans="15:18">
-      <c r="O122" s="7"/>
-      <c r="P122" s="13"/>
-      <c r="R122" s="11"/>
+      <c r="O122" s="6"/>
+      <c r="P122" s="12"/>
+      <c r="R122" s="10"/>
     </row>
     <row r="123" spans="15:18">
-      <c r="O123" s="7"/>
-      <c r="P123" s="13"/>
-      <c r="R123" s="11"/>
+      <c r="O123" s="6"/>
+      <c r="P123" s="12"/>
+      <c r="R123" s="10"/>
     </row>
     <row r="124" spans="15:18">
-      <c r="O124" s="7"/>
-      <c r="P124" s="13"/>
-      <c r="R124" s="11"/>
+      <c r="O124" s="6"/>
+      <c r="P124" s="12"/>
+      <c r="R124" s="10"/>
     </row>
     <row r="125" spans="15:18">
-      <c r="O125" s="7"/>
-      <c r="P125" s="13"/>
-      <c r="R125" s="11"/>
+      <c r="O125" s="6"/>
+      <c r="P125" s="12"/>
+      <c r="R125" s="10"/>
     </row>
     <row r="126" spans="15:18">
-      <c r="O126" s="7"/>
-      <c r="P126" s="13"/>
-      <c r="R126" s="11"/>
+      <c r="O126" s="6"/>
+      <c r="P126" s="12"/>
+      <c r="R126" s="10"/>
     </row>
     <row r="127" spans="15:18">
-      <c r="O127" s="7"/>
-      <c r="P127" s="13"/>
-      <c r="R127" s="11"/>
+      <c r="O127" s="6"/>
+      <c r="P127" s="12"/>
+      <c r="R127" s="10"/>
     </row>
     <row r="128" spans="15:18">
-      <c r="O128" s="7"/>
-      <c r="P128" s="13"/>
-      <c r="R128" s="11"/>
+      <c r="O128" s="6"/>
+      <c r="P128" s="12"/>
+      <c r="R128" s="10"/>
     </row>
     <row r="129" spans="15:18">
-      <c r="O129" s="7"/>
-      <c r="P129" s="13"/>
-      <c r="R129" s="11"/>
+      <c r="O129" s="6"/>
+      <c r="P129" s="12"/>
+      <c r="R129" s="10"/>
     </row>
     <row r="130" spans="15:18">
-      <c r="O130" s="7"/>
-      <c r="P130" s="13"/>
-      <c r="R130" s="11"/>
+      <c r="O130" s="6"/>
+      <c r="P130" s="12"/>
+      <c r="R130" s="10"/>
     </row>
     <row r="131" spans="15:18">
-      <c r="O131" s="7"/>
-      <c r="P131" s="13"/>
-      <c r="R131" s="11"/>
+      <c r="O131" s="6"/>
+      <c r="P131" s="12"/>
+      <c r="R131" s="10"/>
     </row>
     <row r="132" spans="15:18">
-      <c r="O132" s="7"/>
-      <c r="P132" s="13"/>
-      <c r="R132" s="11"/>
+      <c r="O132" s="6"/>
+      <c r="P132" s="12"/>
+      <c r="R132" s="10"/>
     </row>
     <row r="133" spans="15:18">
-      <c r="O133" s="7"/>
-      <c r="P133" s="13"/>
-      <c r="R133" s="11"/>
+      <c r="O133" s="6"/>
+      <c r="P133" s="12"/>
+      <c r="R133" s="10"/>
     </row>
     <row r="134" spans="15:18">
-      <c r="O134" s="7"/>
-      <c r="P134" s="13"/>
-      <c r="R134" s="11"/>
+      <c r="O134" s="6"/>
+      <c r="P134" s="12"/>
+      <c r="R134" s="10"/>
     </row>
     <row r="135" spans="15:18">
-      <c r="O135" s="7"/>
-      <c r="P135" s="13"/>
-      <c r="R135" s="11"/>
+      <c r="O135" s="6"/>
+      <c r="P135" s="12"/>
+      <c r="R135" s="10"/>
     </row>
     <row r="136" spans="15:18">
-      <c r="O136" s="7"/>
-      <c r="P136" s="13"/>
-      <c r="R136" s="11"/>
+      <c r="O136" s="6"/>
+      <c r="P136" s="12"/>
+      <c r="R136" s="10"/>
     </row>
     <row r="137" spans="15:18">
-      <c r="O137" s="7"/>
-      <c r="P137" s="13"/>
-      <c r="R137" s="11"/>
+      <c r="O137" s="6"/>
+      <c r="P137" s="12"/>
+      <c r="R137" s="10"/>
     </row>
     <row r="138" spans="15:18">
-      <c r="O138" s="7"/>
-      <c r="P138" s="13"/>
-      <c r="R138" s="11"/>
+      <c r="O138" s="6"/>
+      <c r="P138" s="12"/>
+      <c r="R138" s="10"/>
     </row>
     <row r="139" spans="15:18">
-      <c r="O139" s="7"/>
-      <c r="P139" s="13"/>
-      <c r="R139" s="11"/>
+      <c r="O139" s="6"/>
+      <c r="P139" s="12"/>
+      <c r="R139" s="10"/>
     </row>
     <row r="140" spans="15:18">
-      <c r="O140" s="7"/>
-      <c r="P140" s="13"/>
-      <c r="R140" s="11"/>
+      <c r="O140" s="6"/>
+      <c r="P140" s="12"/>
+      <c r="R140" s="10"/>
     </row>
     <row r="141" spans="15:18">
-      <c r="O141" s="7"/>
-      <c r="P141" s="13"/>
-      <c r="R141" s="11"/>
+      <c r="O141" s="6"/>
+      <c r="P141" s="12"/>
+      <c r="R141" s="10"/>
     </row>
     <row r="142" spans="15:18">
-      <c r="O142" s="7"/>
-      <c r="P142" s="13"/>
-      <c r="R142" s="11"/>
+      <c r="O142" s="6"/>
+      <c r="P142" s="12"/>
+      <c r="R142" s="10"/>
     </row>
     <row r="143" spans="15:18">
-      <c r="O143" s="7"/>
-      <c r="P143" s="13"/>
-      <c r="R143" s="11"/>
+      <c r="O143" s="6"/>
+      <c r="P143" s="12"/>
+      <c r="R143" s="10"/>
     </row>
     <row r="144" spans="15:18">
-      <c r="O144" s="7"/>
-      <c r="P144" s="13"/>
-      <c r="R144" s="11"/>
+      <c r="O144" s="6"/>
+      <c r="P144" s="12"/>
+      <c r="R144" s="10"/>
     </row>
     <row r="145" spans="15:18">
-      <c r="O145" s="7"/>
-      <c r="P145" s="13"/>
-      <c r="R145" s="11"/>
+      <c r="O145" s="6"/>
+      <c r="P145" s="12"/>
+      <c r="R145" s="10"/>
     </row>
     <row r="146" spans="15:18">
-      <c r="O146" s="7"/>
-      <c r="P146" s="13"/>
-      <c r="R146" s="11"/>
+      <c r="O146" s="6"/>
+      <c r="P146" s="12"/>
+      <c r="R146" s="10"/>
     </row>
     <row r="147" spans="15:18">
-      <c r="O147" s="7"/>
-      <c r="P147" s="13"/>
-      <c r="R147" s="11"/>
+      <c r="O147" s="6"/>
+      <c r="P147" s="12"/>
+      <c r="R147" s="10"/>
     </row>
     <row r="148" spans="15:18">
-      <c r="O148" s="7"/>
-      <c r="P148" s="13"/>
-      <c r="R148" s="11"/>
+      <c r="O148" s="6"/>
+      <c r="P148" s="12"/>
+      <c r="R148" s="10"/>
     </row>
     <row r="149" spans="15:18">
-      <c r="O149" s="7"/>
-      <c r="P149" s="13"/>
-      <c r="R149" s="11"/>
+      <c r="O149" s="6"/>
+      <c r="P149" s="12"/>
+      <c r="R149" s="10"/>
     </row>
     <row r="150" spans="15:18">
-      <c r="O150" s="7"/>
-      <c r="P150" s="13"/>
-      <c r="R150" s="11"/>
+      <c r="O150" s="6"/>
+      <c r="P150" s="12"/>
+      <c r="R150" s="10"/>
     </row>
     <row r="151" spans="15:18">
-      <c r="O151" s="7"/>
-      <c r="P151" s="13"/>
-      <c r="R151" s="11"/>
+      <c r="O151" s="6"/>
+      <c r="P151" s="12"/>
+      <c r="R151" s="10"/>
     </row>
     <row r="152" spans="15:18">
-      <c r="O152" s="7"/>
-      <c r="P152" s="13"/>
-      <c r="R152" s="11"/>
+      <c r="O152" s="6"/>
+      <c r="P152" s="12"/>
+      <c r="R152" s="10"/>
     </row>
     <row r="153" spans="15:18">
-      <c r="O153" s="7"/>
-      <c r="P153" s="13"/>
-      <c r="R153" s="11"/>
+      <c r="O153" s="6"/>
+      <c r="P153" s="12"/>
+      <c r="R153" s="10"/>
     </row>
     <row r="154" spans="15:18">
-      <c r="O154" s="7"/>
-      <c r="P154" s="13"/>
-      <c r="R154" s="11"/>
+      <c r="O154" s="6"/>
+      <c r="P154" s="12"/>
+      <c r="R154" s="10"/>
     </row>
     <row r="155" spans="15:18">
-      <c r="O155" s="7"/>
-      <c r="P155" s="13"/>
-      <c r="R155" s="11"/>
+      <c r="O155" s="6"/>
+      <c r="P155" s="12"/>
+      <c r="R155" s="10"/>
     </row>
     <row r="156" spans="15:18">
-      <c r="O156" s="7"/>
-      <c r="P156" s="13"/>
-      <c r="R156" s="11"/>
+      <c r="O156" s="6"/>
+      <c r="P156" s="12"/>
+      <c r="R156" s="10"/>
     </row>
     <row r="157" spans="15:18">
-      <c r="O157" s="7"/>
-      <c r="P157" s="13"/>
-      <c r="R157" s="11"/>
+      <c r="O157" s="6"/>
+      <c r="P157" s="12"/>
+      <c r="R157" s="10"/>
     </row>
     <row r="158" spans="15:18">
-      <c r="O158" s="7"/>
-      <c r="P158" s="13"/>
-      <c r="R158" s="11"/>
+      <c r="O158" s="6"/>
+      <c r="P158" s="12"/>
+      <c r="R158" s="10"/>
     </row>
     <row r="159" spans="15:18">
-      <c r="O159" s="7"/>
-      <c r="P159" s="13"/>
-      <c r="R159" s="11"/>
+      <c r="O159" s="6"/>
+      <c r="P159" s="12"/>
+      <c r="R159" s="10"/>
     </row>
     <row r="160" spans="15:18">
-      <c r="O160" s="7"/>
-      <c r="P160" s="13"/>
-      <c r="R160" s="11"/>
+      <c r="O160" s="6"/>
+      <c r="P160" s="12"/>
+      <c r="R160" s="10"/>
     </row>
     <row r="161" spans="15:18">
-      <c r="O161" s="7"/>
-      <c r="P161" s="13"/>
-      <c r="R161" s="11"/>
+      <c r="O161" s="6"/>
+      <c r="P161" s="12"/>
+      <c r="R161" s="10"/>
     </row>
     <row r="162" spans="15:18">
-      <c r="O162" s="7"/>
-      <c r="P162" s="13"/>
-      <c r="R162" s="11"/>
+      <c r="O162" s="6"/>
+      <c r="P162" s="12"/>
+      <c r="R162" s="10"/>
     </row>
     <row r="163" spans="15:18">
-      <c r="O163" s="7"/>
-      <c r="P163" s="13"/>
-      <c r="R163" s="11"/>
+      <c r="O163" s="6"/>
+      <c r="P163" s="12"/>
+      <c r="R163" s="10"/>
     </row>
     <row r="164" spans="15:18">
-      <c r="O164" s="7"/>
-      <c r="P164" s="13"/>
-      <c r="R164" s="11"/>
+      <c r="O164" s="6"/>
+      <c r="P164" s="12"/>
+      <c r="R164" s="10"/>
     </row>
     <row r="165" spans="15:18">
-      <c r="O165" s="7"/>
-      <c r="P165" s="13"/>
-      <c r="R165" s="11"/>
+      <c r="O165" s="6"/>
+      <c r="P165" s="12"/>
+      <c r="R165" s="10"/>
     </row>
     <row r="166" spans="15:18">
-      <c r="O166" s="7"/>
-      <c r="P166" s="13"/>
-      <c r="R166" s="11"/>
+      <c r="O166" s="6"/>
+      <c r="P166" s="12"/>
+      <c r="R166" s="10"/>
     </row>
     <row r="167" spans="15:18">
-      <c r="O167" s="7"/>
-      <c r="P167" s="13"/>
-      <c r="R167" s="11"/>
+      <c r="O167" s="6"/>
+      <c r="P167" s="12"/>
+      <c r="R167" s="10"/>
     </row>
     <row r="168" spans="15:18">
-      <c r="O168" s="7"/>
-      <c r="P168" s="13"/>
-      <c r="R168" s="11"/>
+      <c r="O168" s="6"/>
+      <c r="P168" s="12"/>
+      <c r="R168" s="10"/>
     </row>
     <row r="169" spans="15:18">
-      <c r="O169" s="7"/>
-      <c r="P169" s="13"/>
-      <c r="R169" s="11"/>
+      <c r="O169" s="6"/>
+      <c r="P169" s="12"/>
+      <c r="R169" s="10"/>
     </row>
     <row r="170" spans="15:18">
-      <c r="O170" s="7"/>
-      <c r="P170" s="13"/>
-      <c r="R170" s="11"/>
+      <c r="O170" s="6"/>
+      <c r="P170" s="12"/>
+      <c r="R170" s="10"/>
     </row>
     <row r="171" spans="15:18">
-      <c r="O171" s="7"/>
-      <c r="P171" s="13"/>
-      <c r="R171" s="11"/>
+      <c r="O171" s="6"/>
+      <c r="P171" s="12"/>
+      <c r="R171" s="10"/>
     </row>
     <row r="172" spans="15:18">
-      <c r="O172" s="7"/>
-      <c r="P172" s="13"/>
-      <c r="R172" s="11"/>
+      <c r="O172" s="6"/>
+      <c r="P172" s="12"/>
+      <c r="R172" s="10"/>
     </row>
     <row r="173" spans="15:18">
-      <c r="O173" s="7"/>
-      <c r="P173" s="13"/>
-      <c r="R173" s="11"/>
+      <c r="O173" s="6"/>
+      <c r="P173" s="12"/>
+      <c r="R173" s="10"/>
     </row>
     <row r="174" spans="15:18">
-      <c r="O174" s="7"/>
-      <c r="P174" s="13"/>
-      <c r="R174" s="11"/>
+      <c r="O174" s="6"/>
+      <c r="P174" s="12"/>
+      <c r="R174" s="10"/>
     </row>
     <row r="175" spans="15:18">
-      <c r="O175" s="7"/>
-      <c r="P175" s="13"/>
-      <c r="R175" s="11"/>
+      <c r="O175" s="6"/>
+      <c r="P175" s="12"/>
+      <c r="R175" s="10"/>
     </row>
     <row r="176" spans="15:18">
-      <c r="O176" s="7"/>
-      <c r="P176" s="13"/>
-      <c r="R176" s="11"/>
+      <c r="O176" s="6"/>
+      <c r="P176" s="12"/>
+      <c r="R176" s="10"/>
     </row>
     <row r="177" spans="15:18">
-      <c r="O177" s="7"/>
-      <c r="P177" s="13"/>
-      <c r="R177" s="11"/>
+      <c r="O177" s="6"/>
+      <c r="P177" s="12"/>
+      <c r="R177" s="10"/>
     </row>
     <row r="178" spans="15:18">
-      <c r="O178" s="7"/>
-      <c r="P178" s="13"/>
-      <c r="R178" s="11"/>
+      <c r="O178" s="6"/>
+      <c r="P178" s="12"/>
+      <c r="R178" s="10"/>
     </row>
     <row r="179" spans="15:18">
-      <c r="O179" s="7"/>
-      <c r="P179" s="13"/>
-      <c r="R179" s="11"/>
+      <c r="O179" s="6"/>
+      <c r="P179" s="12"/>
+      <c r="R179" s="10"/>
     </row>
     <row r="180" spans="15:18">
-      <c r="O180" s="7"/>
-      <c r="P180" s="13"/>
-      <c r="R180" s="11"/>
+      <c r="O180" s="6"/>
+      <c r="P180" s="12"/>
+      <c r="R180" s="10"/>
     </row>
     <row r="181" spans="15:18">
-      <c r="O181" s="7"/>
-      <c r="P181" s="13"/>
-      <c r="R181" s="11"/>
+      <c r="O181" s="6"/>
+      <c r="P181" s="12"/>
+      <c r="R181" s="10"/>
     </row>
     <row r="182" spans="15:18">
-      <c r="O182" s="7"/>
-      <c r="P182" s="13"/>
-      <c r="R182" s="11"/>
+      <c r="O182" s="6"/>
+      <c r="P182" s="12"/>
+      <c r="R182" s="10"/>
     </row>
     <row r="183" spans="15:18">
-      <c r="O183" s="7"/>
-      <c r="P183" s="13"/>
-      <c r="R183" s="11"/>
+      <c r="O183" s="6"/>
+      <c r="P183" s="12"/>
+      <c r="R183" s="10"/>
     </row>
     <row r="184" spans="15:18">
-      <c r="O184" s="7"/>
-      <c r="P184" s="13"/>
-      <c r="R184" s="11"/>
+      <c r="O184" s="6"/>
+      <c r="P184" s="12"/>
+      <c r="R184" s="10"/>
     </row>
     <row r="185" spans="15:18">
-      <c r="O185" s="7"/>
-      <c r="P185" s="13"/>
-      <c r="R185" s="11"/>
+      <c r="O185" s="6"/>
+      <c r="P185" s="12"/>
+      <c r="R185" s="10"/>
     </row>
     <row r="186" spans="15:18">
-      <c r="O186" s="7"/>
-      <c r="P186" s="13"/>
-      <c r="R186" s="11"/>
+      <c r="O186" s="6"/>
+      <c r="P186" s="12"/>
+      <c r="R186" s="10"/>
     </row>
     <row r="187" spans="15:18">
-      <c r="O187" s="7"/>
-      <c r="P187" s="13"/>
-      <c r="R187" s="11"/>
+      <c r="O187" s="6"/>
+      <c r="P187" s="12"/>
+      <c r="R187" s="10"/>
     </row>
     <row r="188" spans="15:18">
-      <c r="O188" s="7"/>
-      <c r="P188" s="13"/>
-      <c r="R188" s="11"/>
+      <c r="O188" s="6"/>
+      <c r="P188" s="12"/>
+      <c r="R188" s="10"/>
     </row>
     <row r="189" spans="15:18">
-      <c r="O189" s="7"/>
-      <c r="P189" s="13"/>
-      <c r="R189" s="11"/>
+      <c r="O189" s="6"/>
+      <c r="P189" s="12"/>
+      <c r="R189" s="10"/>
     </row>
     <row r="190" spans="15:18">
-      <c r="O190" s="7"/>
-      <c r="P190" s="13"/>
-      <c r="R190" s="11"/>
+      <c r="O190" s="6"/>
+      <c r="P190" s="12"/>
+      <c r="R190" s="10"/>
     </row>
     <row r="191" spans="15:18">
-      <c r="O191" s="7"/>
-      <c r="P191" s="13"/>
-      <c r="R191" s="11"/>
+      <c r="O191" s="6"/>
+      <c r="P191" s="12"/>
+      <c r="R191" s="10"/>
     </row>
     <row r="192" spans="15:18">
-      <c r="O192" s="7"/>
-      <c r="P192" s="13"/>
-      <c r="R192" s="11"/>
+      <c r="O192" s="6"/>
+      <c r="P192" s="12"/>
+      <c r="R192" s="10"/>
     </row>
     <row r="193" spans="15:18">
-      <c r="O193" s="7"/>
-      <c r="P193" s="13"/>
-      <c r="R193" s="11"/>
+      <c r="O193" s="6"/>
+      <c r="P193" s="12"/>
+      <c r="R193" s="10"/>
     </row>
     <row r="194" spans="15:18">
-      <c r="O194" s="7"/>
-      <c r="P194" s="13"/>
-      <c r="R194" s="11"/>
+      <c r="O194" s="6"/>
+      <c r="P194" s="12"/>
+      <c r="R194" s="10"/>
     </row>
     <row r="195" spans="15:18">
-      <c r="O195" s="7"/>
-      <c r="P195" s="13"/>
-      <c r="R195" s="11"/>
+      <c r="O195" s="6"/>
+      <c r="P195" s="12"/>
+      <c r="R195" s="10"/>
     </row>
     <row r="196" spans="15:18">
-      <c r="O196" s="7"/>
-      <c r="P196" s="13"/>
-      <c r="R196" s="11"/>
+      <c r="O196" s="6"/>
+      <c r="P196" s="12"/>
+      <c r="R196" s="10"/>
     </row>
     <row r="197" spans="15:18">
-      <c r="O197" s="7"/>
-      <c r="P197" s="13"/>
-      <c r="R197" s="11"/>
+      <c r="O197" s="6"/>
+      <c r="P197" s="12"/>
+      <c r="R197" s="10"/>
     </row>
     <row r="198" spans="15:18">
-      <c r="O198" s="7"/>
-      <c r="P198" s="13"/>
-      <c r="R198" s="11"/>
+      <c r="O198" s="6"/>
+      <c r="P198" s="12"/>
+      <c r="R198" s="10"/>
     </row>
     <row r="199" spans="15:18">
-      <c r="O199" s="7"/>
-      <c r="P199" s="13"/>
-      <c r="R199" s="11"/>
+      <c r="O199" s="6"/>
+      <c r="P199" s="12"/>
+      <c r="R199" s="10"/>
     </row>
     <row r="200" spans="15:18">
-      <c r="O200" s="7"/>
-      <c r="P200" s="13"/>
-      <c r="R200" s="11"/>
+      <c r="O200" s="6"/>
+      <c r="P200" s="12"/>
+      <c r="R200" s="10"/>
     </row>
     <row r="201" spans="15:18">
-      <c r="O201" s="7"/>
-      <c r="P201" s="13"/>
-      <c r="R201" s="11"/>
+      <c r="O201" s="6"/>
+      <c r="P201" s="12"/>
+      <c r="R201" s="10"/>
     </row>
     <row r="202" spans="15:18">
-      <c r="O202" s="7"/>
-      <c r="P202" s="13"/>
-      <c r="R202" s="11"/>
+      <c r="O202" s="6"/>
+      <c r="P202" s="12"/>
+      <c r="R202" s="10"/>
     </row>
     <row r="203" spans="15:18">
-      <c r="O203" s="7"/>
-      <c r="P203" s="13"/>
-      <c r="R203" s="11"/>
+      <c r="O203" s="6"/>
+      <c r="P203" s="12"/>
+      <c r="R203" s="10"/>
     </row>
     <row r="204" spans="15:18">
-      <c r="O204" s="7"/>
-      <c r="P204" s="13"/>
-      <c r="R204" s="11"/>
+      <c r="O204" s="6"/>
+      <c r="P204" s="12"/>
+      <c r="R204" s="10"/>
     </row>
     <row r="205" spans="15:18">
-      <c r="O205" s="7"/>
-      <c r="P205" s="13"/>
-      <c r="R205" s="11"/>
+      <c r="O205" s="6"/>
+      <c r="P205" s="12"/>
+      <c r="R205" s="10"/>
     </row>
     <row r="206" spans="15:18">
-      <c r="O206" s="7"/>
-      <c r="P206" s="13"/>
-      <c r="R206" s="11"/>
+      <c r="O206" s="6"/>
+      <c r="P206" s="12"/>
+      <c r="R206" s="10"/>
     </row>
     <row r="207" spans="15:18">
-      <c r="O207" s="7"/>
-      <c r="P207" s="13"/>
-      <c r="R207" s="11"/>
+      <c r="O207" s="6"/>
+      <c r="P207" s="12"/>
+      <c r="R207" s="10"/>
     </row>
     <row r="208" spans="15:18">
-      <c r="O208" s="7"/>
-      <c r="P208" s="13"/>
-      <c r="R208" s="11"/>
+      <c r="O208" s="6"/>
+      <c r="P208" s="12"/>
+      <c r="R208" s="10"/>
     </row>
     <row r="209" spans="15:18">
-      <c r="O209" s="7"/>
-      <c r="P209" s="13"/>
-      <c r="R209" s="11"/>
+      <c r="O209" s="6"/>
+      <c r="P209" s="12"/>
+      <c r="R209" s="10"/>
     </row>
     <row r="210" spans="15:18">
-      <c r="O210" s="7"/>
-      <c r="P210" s="13"/>
-      <c r="R210" s="11"/>
+      <c r="O210" s="6"/>
+      <c r="P210" s="12"/>
+      <c r="R210" s="10"/>
     </row>
     <row r="211" spans="15:18">
-      <c r="O211" s="7"/>
-      <c r="P211" s="13"/>
-      <c r="R211" s="11"/>
+      <c r="O211" s="6"/>
+      <c r="P211" s="12"/>
+      <c r="R211" s="10"/>
     </row>
     <row r="212" spans="15:18">
-      <c r="O212" s="7"/>
-      <c r="P212" s="13"/>
-      <c r="R212" s="11"/>
+      <c r="O212" s="6"/>
+      <c r="P212" s="12"/>
+      <c r="R212" s="10"/>
     </row>
     <row r="213" spans="15:18">
-      <c r="O213" s="7"/>
-      <c r="P213" s="13"/>
-      <c r="R213" s="11"/>
+      <c r="O213" s="6"/>
+      <c r="P213" s="12"/>
+      <c r="R213" s="10"/>
     </row>
     <row r="214" spans="15:18">
-      <c r="O214" s="7"/>
-      <c r="P214" s="13"/>
-      <c r="R214" s="11"/>
+      <c r="O214" s="6"/>
+      <c r="P214" s="12"/>
+      <c r="R214" s="10"/>
     </row>
     <row r="215" spans="15:18">
-      <c r="O215" s="7"/>
-      <c r="P215" s="13"/>
-      <c r="R215" s="11"/>
+      <c r="O215" s="6"/>
+      <c r="P215" s="12"/>
+      <c r="R215" s="10"/>
     </row>
     <row r="216" spans="15:18">
-      <c r="O216" s="7"/>
-      <c r="P216" s="13"/>
-      <c r="R216" s="11"/>
+      <c r="O216" s="6"/>
+      <c r="P216" s="12"/>
+      <c r="R216" s="10"/>
     </row>
     <row r="217" spans="15:18">
-      <c r="O217" s="7"/>
-      <c r="P217" s="13"/>
-      <c r="R217" s="11"/>
+      <c r="O217" s="6"/>
+      <c r="P217" s="12"/>
+      <c r="R217" s="10"/>
     </row>
     <row r="218" spans="15:18">
-      <c r="O218" s="7"/>
-      <c r="P218" s="13"/>
-      <c r="R218" s="11"/>
+      <c r="O218" s="6"/>
+      <c r="P218" s="12"/>
+      <c r="R218" s="10"/>
     </row>
     <row r="219" spans="15:18">
-      <c r="O219" s="7"/>
-      <c r="P219" s="13"/>
-      <c r="R219" s="11"/>
+      <c r="O219" s="6"/>
+      <c r="P219" s="12"/>
+      <c r="R219" s="10"/>
     </row>
     <row r="220" spans="15:18">
-      <c r="O220" s="7"/>
-      <c r="P220" s="13"/>
-      <c r="R220" s="11"/>
+      <c r="O220" s="6"/>
+      <c r="P220" s="12"/>
+      <c r="R220" s="10"/>
     </row>
     <row r="221" spans="15:18">
-      <c r="O221" s="7"/>
-      <c r="P221" s="13"/>
-      <c r="R221" s="11"/>
+      <c r="O221" s="6"/>
+      <c r="P221" s="12"/>
+      <c r="R221" s="10"/>
     </row>
     <row r="222" spans="15:18">
-      <c r="O222" s="7"/>
-      <c r="P222" s="13"/>
-      <c r="R222" s="11"/>
+      <c r="O222" s="6"/>
+      <c r="P222" s="12"/>
+      <c r="R222" s="10"/>
     </row>
     <row r="223" spans="15:18">
-      <c r="O223" s="7"/>
-      <c r="P223" s="13"/>
-      <c r="R223" s="11"/>
+      <c r="O223" s="6"/>
+      <c r="P223" s="12"/>
+      <c r="R223" s="10"/>
     </row>
     <row r="224" spans="15:18">
-      <c r="O224" s="7"/>
-      <c r="P224" s="13"/>
-      <c r="R224" s="11"/>
+      <c r="O224" s="6"/>
+      <c r="P224" s="12"/>
+      <c r="R224" s="10"/>
     </row>
     <row r="225" spans="15:18">
-      <c r="O225" s="7"/>
-      <c r="P225" s="13"/>
-      <c r="R225" s="11"/>
+      <c r="O225" s="6"/>
+      <c r="P225" s="12"/>
+      <c r="R225" s="10"/>
     </row>
     <row r="226" spans="15:18">
-      <c r="O226" s="7"/>
-      <c r="P226" s="13"/>
-      <c r="R226" s="11"/>
+      <c r="O226" s="6"/>
+      <c r="P226" s="12"/>
+      <c r="R226" s="10"/>
     </row>
     <row r="227" spans="15:18">
-      <c r="O227" s="7"/>
-      <c r="P227" s="13"/>
-      <c r="R227" s="11"/>
+      <c r="O227" s="6"/>
+      <c r="P227" s="12"/>
+      <c r="R227" s="10"/>
     </row>
     <row r="228" spans="15:18">
-      <c r="O228" s="7"/>
-      <c r="P228" s="13"/>
-      <c r="R228" s="11"/>
+      <c r="O228" s="6"/>
+      <c r="P228" s="12"/>
+      <c r="R228" s="10"/>
     </row>
     <row r="229" spans="15:18">
-      <c r="O229" s="7"/>
-      <c r="P229" s="13"/>
-      <c r="R229" s="11"/>
+      <c r="O229" s="6"/>
+      <c r="P229" s="12"/>
+      <c r="R229" s="10"/>
     </row>
     <row r="230" spans="15:18">
-      <c r="O230" s="7"/>
-      <c r="P230" s="13"/>
-      <c r="R230" s="11"/>
+      <c r="O230" s="6"/>
+      <c r="P230" s="12"/>
+      <c r="R230" s="10"/>
     </row>
     <row r="231" spans="15:18">
-      <c r="O231" s="7"/>
-      <c r="P231" s="13"/>
-      <c r="R231" s="11"/>
+      <c r="O231" s="6"/>
+      <c r="P231" s="12"/>
+      <c r="R231" s="10"/>
     </row>
     <row r="232" spans="15:18">
-      <c r="O232" s="7"/>
-      <c r="P232" s="13"/>
-      <c r="R232" s="11"/>
+      <c r="O232" s="6"/>
+      <c r="P232" s="12"/>
+      <c r="R232" s="10"/>
     </row>
     <row r="233" spans="15:18">
-      <c r="O233" s="7"/>
-      <c r="P233" s="13"/>
-      <c r="R233" s="11"/>
+      <c r="O233" s="6"/>
+      <c r="P233" s="12"/>
+      <c r="R233" s="10"/>
     </row>
     <row r="234" spans="15:18">
-      <c r="O234" s="7"/>
-      <c r="P234" s="13"/>
-      <c r="R234" s="11"/>
+      <c r="O234" s="6"/>
+      <c r="P234" s="12"/>
+      <c r="R234" s="10"/>
     </row>
     <row r="235" spans="15:18">
-      <c r="O235" s="7"/>
-      <c r="P235" s="13"/>
-      <c r="R235" s="11"/>
+      <c r="O235" s="6"/>
+      <c r="P235" s="12"/>
+      <c r="R235" s="10"/>
     </row>
     <row r="236" spans="15:18">
-      <c r="O236" s="7"/>
-      <c r="P236" s="13"/>
-      <c r="R236" s="11"/>
+      <c r="O236" s="6"/>
+      <c r="P236" s="12"/>
+      <c r="R236" s="10"/>
     </row>
     <row r="237" spans="15:18">
-      <c r="O237" s="7"/>
-      <c r="P237" s="13"/>
-      <c r="R237" s="11"/>
+      <c r="O237" s="6"/>
+      <c r="P237" s="12"/>
+      <c r="R237" s="10"/>
     </row>
     <row r="238" spans="15:18">
-      <c r="O238" s="7"/>
-      <c r="P238" s="13"/>
-      <c r="R238" s="11"/>
+      <c r="O238" s="6"/>
+      <c r="P238" s="12"/>
+      <c r="R238" s="10"/>
     </row>
     <row r="239" spans="15:18">
-      <c r="O239" s="7"/>
-      <c r="P239" s="13"/>
-      <c r="R239" s="11"/>
+      <c r="O239" s="6"/>
+      <c r="P239" s="12"/>
+      <c r="R239" s="10"/>
     </row>
     <row r="240" spans="15:18">
-      <c r="O240" s="7"/>
-      <c r="P240" s="13"/>
-      <c r="R240" s="11"/>
+      <c r="O240" s="6"/>
+      <c r="P240" s="12"/>
+      <c r="R240" s="10"/>
     </row>
     <row r="241" spans="15:18">
-      <c r="O241" s="7"/>
-      <c r="P241" s="13"/>
-      <c r="R241" s="11"/>
+      <c r="O241" s="6"/>
+      <c r="P241" s="12"/>
+      <c r="R241" s="10"/>
     </row>
     <row r="242" spans="15:18">
-      <c r="O242" s="7"/>
-      <c r="P242" s="13"/>
-      <c r="R242" s="11"/>
+      <c r="O242" s="6"/>
+      <c r="P242" s="12"/>
+      <c r="R242" s="10"/>
     </row>
     <row r="243" spans="15:18">
-      <c r="O243" s="7"/>
-      <c r="P243" s="13"/>
-      <c r="R243" s="11"/>
+      <c r="O243" s="6"/>
+      <c r="P243" s="12"/>
+      <c r="R243" s="10"/>
     </row>
     <row r="244" spans="15:18">
-      <c r="O244" s="7"/>
-      <c r="P244" s="13"/>
-      <c r="R244" s="11"/>
+      <c r="O244" s="6"/>
+      <c r="P244" s="12"/>
+      <c r="R244" s="10"/>
     </row>
     <row r="245" spans="15:18">
-      <c r="O245" s="7"/>
-      <c r="P245" s="13"/>
-      <c r="R245" s="11"/>
+      <c r="O245" s="6"/>
+      <c r="P245" s="12"/>
+      <c r="R245" s="10"/>
     </row>
     <row r="246" spans="15:18">
-      <c r="O246" s="7"/>
-      <c r="P246" s="13"/>
-      <c r="R246" s="11"/>
+      <c r="O246" s="6"/>
+      <c r="P246" s="12"/>
+      <c r="R246" s="10"/>
     </row>
     <row r="247" spans="15:18">
-      <c r="O247" s="7"/>
-      <c r="P247" s="13"/>
-      <c r="R247" s="11"/>
+      <c r="O247" s="6"/>
+      <c r="P247" s="12"/>
+      <c r="R247" s="10"/>
     </row>
     <row r="248" spans="15:18">
-      <c r="O248" s="7"/>
-      <c r="P248" s="13"/>
-      <c r="R248" s="11"/>
+      <c r="O248" s="6"/>
+      <c r="P248" s="12"/>
+      <c r="R248" s="10"/>
     </row>
     <row r="249" spans="15:18">
-      <c r="O249" s="7"/>
-      <c r="P249" s="13"/>
-      <c r="R249" s="11"/>
+      <c r="O249" s="6"/>
+      <c r="P249" s="12"/>
+      <c r="R249" s="10"/>
     </row>
     <row r="250" spans="15:18">
-      <c r="O250" s="7"/>
-      <c r="P250" s="13"/>
-      <c r="R250" s="11"/>
+      <c r="O250" s="6"/>
+      <c r="P250" s="12"/>
+      <c r="R250" s="10"/>
     </row>
     <row r="251" spans="15:18">
-      <c r="O251" s="7"/>
-      <c r="P251" s="13"/>
-      <c r="R251" s="11"/>
+      <c r="O251" s="6"/>
+      <c r="P251" s="12"/>
+      <c r="R251" s="10"/>
     </row>
     <row r="252" spans="15:18">
-      <c r="O252" s="7"/>
-      <c r="P252" s="13"/>
-      <c r="R252" s="11"/>
+      <c r="O252" s="6"/>
+      <c r="P252" s="12"/>
+      <c r="R252" s="10"/>
     </row>
     <row r="253" spans="15:18">
-      <c r="O253" s="7"/>
-      <c r="P253" s="13"/>
-      <c r="R253" s="11"/>
+      <c r="O253" s="6"/>
+      <c r="P253" s="12"/>
+      <c r="R253" s="10"/>
     </row>
     <row r="254" spans="15:18">
-      <c r="O254" s="7"/>
-      <c r="P254" s="13"/>
-      <c r="R254" s="11"/>
+      <c r="O254" s="6"/>
+      <c r="P254" s="12"/>
+      <c r="R254" s="10"/>
     </row>
     <row r="255" spans="15:18">
-      <c r="O255" s="7"/>
-      <c r="P255" s="13"/>
-      <c r="R255" s="11"/>
+      <c r="O255" s="6"/>
+      <c r="P255" s="12"/>
+      <c r="R255" s="10"/>
     </row>
     <row r="256" spans="15:18">
-      <c r="O256" s="7"/>
-      <c r="P256" s="13"/>
-      <c r="R256" s="11"/>
+      <c r="O256" s="6"/>
+      <c r="P256" s="12"/>
+      <c r="R256" s="10"/>
     </row>
     <row r="257" spans="15:18">
-      <c r="O257" s="7"/>
-      <c r="P257" s="13"/>
-      <c r="R257" s="11"/>
+      <c r="O257" s="6"/>
+      <c r="P257" s="12"/>
+      <c r="R257" s="10"/>
     </row>
     <row r="258" spans="15:18">
-      <c r="O258" s="7"/>
-      <c r="P258" s="13"/>
-      <c r="R258" s="11"/>
+      <c r="O258" s="6"/>
+      <c r="P258" s="12"/>
+      <c r="R258" s="10"/>
     </row>
     <row r="259" spans="15:18">
-      <c r="O259" s="7"/>
-      <c r="P259" s="13"/>
-      <c r="R259" s="11"/>
+      <c r="O259" s="6"/>
+      <c r="P259" s="12"/>
+      <c r="R259" s="10"/>
     </row>
     <row r="260" spans="15:18">
-      <c r="O260" s="7"/>
-      <c r="P260" s="13"/>
-      <c r="R260" s="11"/>
+      <c r="O260" s="6"/>
+      <c r="P260" s="12"/>
+      <c r="R260" s="10"/>
     </row>
     <row r="261" spans="15:18">
-      <c r="O261" s="7"/>
-      <c r="P261" s="13"/>
-      <c r="R261" s="11"/>
+      <c r="O261" s="6"/>
+      <c r="P261" s="12"/>
+      <c r="R261" s="10"/>
     </row>
     <row r="262" spans="15:18">
-      <c r="O262" s="7"/>
-      <c r="P262" s="13"/>
-      <c r="R262" s="11"/>
+      <c r="O262" s="6"/>
+      <c r="P262" s="12"/>
+      <c r="R262" s="10"/>
     </row>
     <row r="263" spans="15:18">
-      <c r="O263" s="7"/>
-      <c r="P263" s="13"/>
-      <c r="R263" s="11"/>
+      <c r="O263" s="6"/>
+      <c r="P263" s="12"/>
+      <c r="R263" s="10"/>
     </row>
     <row r="264" spans="15:18">
-      <c r="O264" s="7"/>
-      <c r="P264" s="13"/>
-      <c r="R264" s="11"/>
+      <c r="O264" s="6"/>
+      <c r="P264" s="12"/>
+      <c r="R264" s="10"/>
     </row>
     <row r="265" spans="15:18">
-      <c r="O265" s="7"/>
-      <c r="P265" s="13"/>
-      <c r="R265" s="11"/>
+      <c r="O265" s="6"/>
+      <c r="P265" s="12"/>
+      <c r="R265" s="10"/>
     </row>
     <row r="266" spans="15:18">
-      <c r="O266" s="7"/>
-      <c r="P266" s="13"/>
-      <c r="R266" s="11"/>
+      <c r="O266" s="6"/>
+      <c r="P266" s="12"/>
+      <c r="R266" s="10"/>
     </row>
     <row r="267" spans="15:18">
-      <c r="O267" s="7"/>
-      <c r="P267" s="13"/>
-      <c r="R267" s="11"/>
+      <c r="O267" s="6"/>
+      <c r="P267" s="12"/>
+      <c r="R267" s="10"/>
     </row>
     <row r="268" spans="15:18">
-      <c r="O268" s="7"/>
-      <c r="P268" s="13"/>
-      <c r="R268" s="11"/>
+      <c r="O268" s="6"/>
+      <c r="P268" s="12"/>
+      <c r="R268" s="10"/>
     </row>
     <row r="269" spans="15:18">
-      <c r="O269" s="7"/>
-      <c r="P269" s="13"/>
-      <c r="R269" s="11"/>
+      <c r="O269" s="6"/>
+      <c r="P269" s="12"/>
+      <c r="R269" s="10"/>
     </row>
     <row r="270" spans="15:18">
-      <c r="O270" s="7"/>
-      <c r="P270" s="13"/>
-      <c r="R270" s="11"/>
+      <c r="O270" s="6"/>
+      <c r="P270" s="12"/>
+      <c r="R270" s="10"/>
     </row>
     <row r="271" spans="15:18">
-      <c r="O271" s="7"/>
-      <c r="P271" s="13"/>
-      <c r="R271" s="11"/>
+      <c r="O271" s="6"/>
+      <c r="P271" s="12"/>
+      <c r="R271" s="10"/>
     </row>
     <row r="272" spans="15:18">
-      <c r="O272" s="7"/>
-      <c r="P272" s="13"/>
-      <c r="R272" s="11"/>
+      <c r="O272" s="6"/>
+      <c r="P272" s="12"/>
+      <c r="R272" s="10"/>
     </row>
     <row r="273" spans="15:18">
-      <c r="O273" s="7"/>
-      <c r="P273" s="13"/>
-      <c r="R273" s="11"/>
+      <c r="O273" s="6"/>
+      <c r="P273" s="12"/>
+      <c r="R273" s="10"/>
     </row>
     <row r="274" spans="15:18">
-      <c r="O274" s="7"/>
-      <c r="P274" s="13"/>
-      <c r="R274" s="11"/>
+      <c r="O274" s="6"/>
+      <c r="P274" s="12"/>
+      <c r="R274" s="10"/>
     </row>
     <row r="275" spans="15:18">
-      <c r="O275" s="7"/>
-      <c r="P275" s="13"/>
-      <c r="R275" s="11"/>
+      <c r="O275" s="6"/>
+      <c r="P275" s="12"/>
+      <c r="R275" s="10"/>
     </row>
     <row r="276" spans="15:18">
-      <c r="O276" s="7"/>
-      <c r="P276" s="13"/>
-      <c r="R276" s="11"/>
+      <c r="O276" s="6"/>
+      <c r="P276" s="12"/>
+      <c r="R276" s="10"/>
     </row>
     <row r="277" spans="15:18">
-      <c r="O277" s="7"/>
-      <c r="P277" s="13"/>
-      <c r="R277" s="11"/>
+      <c r="O277" s="6"/>
+      <c r="P277" s="12"/>
+      <c r="R277" s="10"/>
     </row>
     <row r="278" spans="15:18">
-      <c r="O278" s="7"/>
-      <c r="P278" s="13"/>
-      <c r="R278" s="11"/>
+      <c r="O278" s="6"/>
+      <c r="P278" s="12"/>
+      <c r="R278" s="10"/>
     </row>
     <row r="279" spans="15:18">
-      <c r="O279" s="7"/>
-      <c r="P279" s="13"/>
-      <c r="R279" s="11"/>
+      <c r="O279" s="6"/>
+      <c r="P279" s="12"/>
+      <c r="R279" s="10"/>
     </row>
     <row r="280" spans="15:18">
-      <c r="O280" s="7"/>
-      <c r="P280" s="13"/>
-      <c r="R280" s="11"/>
+      <c r="O280" s="6"/>
+      <c r="P280" s="12"/>
+      <c r="R280" s="10"/>
     </row>
     <row r="281" spans="15:18">
-      <c r="O281" s="7"/>
-      <c r="P281" s="13"/>
-      <c r="R281" s="11"/>
+      <c r="O281" s="6"/>
+      <c r="P281" s="12"/>
+      <c r="R281" s="10"/>
     </row>
     <row r="282" spans="15:18">
-      <c r="O282" s="7"/>
-      <c r="P282" s="13"/>
-      <c r="R282" s="11"/>
+      <c r="O282" s="6"/>
+      <c r="P282" s="12"/>
+      <c r="R282" s="10"/>
     </row>
     <row r="283" spans="15:18">
-      <c r="O283" s="7"/>
-      <c r="P283" s="13"/>
-      <c r="R283" s="11"/>
+      <c r="O283" s="6"/>
+      <c r="P283" s="12"/>
+      <c r="R283" s="10"/>
     </row>
     <row r="284" spans="15:18">
-      <c r="O284" s="7"/>
-      <c r="P284" s="13"/>
-      <c r="R284" s="11"/>
+      <c r="O284" s="6"/>
+      <c r="P284" s="12"/>
+      <c r="R284" s="10"/>
     </row>
     <row r="285" spans="15:18">
-      <c r="O285" s="7"/>
-      <c r="P285" s="13"/>
-      <c r="R285" s="11"/>
+      <c r="O285" s="6"/>
+      <c r="P285" s="12"/>
+      <c r="R285" s="10"/>
     </row>
     <row r="286" spans="15:18">
-      <c r="O286" s="7"/>
-      <c r="P286" s="13"/>
-      <c r="R286" s="11"/>
+      <c r="O286" s="6"/>
+      <c r="P286" s="12"/>
+      <c r="R286" s="10"/>
     </row>
     <row r="287" spans="15:18">
-      <c r="O287" s="7"/>
-      <c r="P287" s="13"/>
-      <c r="R287" s="11"/>
+      <c r="O287" s="6"/>
+      <c r="P287" s="12"/>
+      <c r="R287" s="10"/>
     </row>
     <row r="288" spans="15:18">
-      <c r="O288" s="7"/>
-      <c r="P288" s="13"/>
-      <c r="R288" s="11"/>
+      <c r="O288" s="6"/>
+      <c r="P288" s="12"/>
+      <c r="R288" s="10"/>
     </row>
     <row r="289" spans="15:18">
-      <c r="O289" s="7"/>
-      <c r="P289" s="13"/>
-      <c r="R289" s="11"/>
+      <c r="O289" s="6"/>
+      <c r="P289" s="12"/>
+      <c r="R289" s="10"/>
     </row>
     <row r="290" spans="15:18">
-      <c r="O290" s="7"/>
-      <c r="P290" s="13"/>
-      <c r="R290" s="11"/>
+      <c r="O290" s="6"/>
+      <c r="P290" s="12"/>
+      <c r="R290" s="10"/>
     </row>
     <row r="291" spans="15:18">
-      <c r="O291" s="7"/>
-      <c r="P291" s="13"/>
-      <c r="R291" s="11"/>
+      <c r="O291" s="6"/>
+      <c r="P291" s="12"/>
+      <c r="R291" s="10"/>
     </row>
     <row r="292" spans="15:18">
-      <c r="O292" s="7"/>
-      <c r="P292" s="13"/>
-      <c r="R292" s="11"/>
+      <c r="O292" s="6"/>
+      <c r="P292" s="12"/>
+      <c r="R292" s="10"/>
     </row>
     <row r="293" spans="15:18">
-      <c r="O293" s="7"/>
-      <c r="P293" s="13"/>
-      <c r="R293" s="11"/>
+      <c r="O293" s="6"/>
+      <c r="P293" s="12"/>
+      <c r="R293" s="10"/>
     </row>
     <row r="294" spans="15:18">
-      <c r="O294" s="7"/>
-      <c r="P294" s="13"/>
-      <c r="R294" s="11"/>
+      <c r="O294" s="6"/>
+      <c r="P294" s="12"/>
+      <c r="R294" s="10"/>
     </row>
     <row r="295" spans="15:18">
-      <c r="O295" s="7"/>
-      <c r="P295" s="13"/>
-      <c r="R295" s="11"/>
+      <c r="O295" s="6"/>
+      <c r="P295" s="12"/>
+      <c r="R295" s="10"/>
     </row>
     <row r="296" spans="15:18">
-      <c r="O296" s="7"/>
-      <c r="P296" s="13"/>
-      <c r="R296" s="11"/>
+      <c r="O296" s="6"/>
+      <c r="P296" s="12"/>
+      <c r="R296" s="10"/>
     </row>
     <row r="297" spans="15:18">
-      <c r="O297" s="7"/>
-      <c r="P297" s="13"/>
-      <c r="R297" s="11"/>
+      <c r="O297" s="6"/>
+      <c r="P297" s="12"/>
+      <c r="R297" s="10"/>
     </row>
     <row r="298" spans="15:18">
-      <c r="O298" s="7"/>
-      <c r="P298" s="13"/>
-      <c r="R298" s="11"/>
+      <c r="O298" s="6"/>
+      <c r="P298" s="12"/>
+      <c r="R298" s="10"/>
     </row>
     <row r="299" spans="15:18">
-      <c r="O299" s="7"/>
-      <c r="P299" s="13"/>
-      <c r="R299" s="11"/>
+      <c r="O299" s="6"/>
+      <c r="P299" s="12"/>
+      <c r="R299" s="10"/>
     </row>
     <row r="300" spans="15:18">
-      <c r="O300" s="7"/>
-      <c r="P300" s="13"/>
-      <c r="R300" s="11"/>
+      <c r="O300" s="6"/>
+      <c r="P300" s="12"/>
+      <c r="R300" s="10"/>
     </row>
     <row r="301" spans="15:18">
-      <c r="O301" s="7"/>
-      <c r="P301" s="13"/>
-      <c r="R301" s="11"/>
+      <c r="O301" s="6"/>
+      <c r="P301" s="12"/>
+      <c r="R301" s="10"/>
     </row>
     <row r="302" spans="15:18">
-      <c r="O302" s="7"/>
-      <c r="P302" s="13"/>
-      <c r="R302" s="11"/>
+      <c r="O302" s="6"/>
+      <c r="P302" s="12"/>
+      <c r="R302" s="10"/>
     </row>
     <row r="303" spans="15:18">
-      <c r="O303" s="7"/>
-      <c r="P303" s="13"/>
-      <c r="R303" s="11"/>
+      <c r="O303" s="6"/>
+      <c r="P303" s="12"/>
+      <c r="R303" s="10"/>
     </row>
     <row r="304" spans="15:18">
-      <c r="O304" s="7"/>
-      <c r="P304" s="13"/>
-      <c r="R304" s="11"/>
+      <c r="O304" s="6"/>
+      <c r="P304" s="12"/>
+      <c r="R304" s="10"/>
     </row>
     <row r="305" spans="15:18">
-      <c r="O305" s="7"/>
-      <c r="P305" s="13"/>
-      <c r="R305" s="11"/>
+      <c r="O305" s="6"/>
+      <c r="P305" s="12"/>
+      <c r="R305" s="10"/>
     </row>
     <row r="306" spans="15:18">
-      <c r="O306" s="7"/>
-      <c r="P306" s="13"/>
-      <c r="R306" s="11"/>
+      <c r="O306" s="6"/>
+      <c r="P306" s="12"/>
+      <c r="R306" s="10"/>
     </row>
     <row r="307" spans="15:18">
-      <c r="O307" s="7"/>
-      <c r="P307" s="13"/>
-      <c r="R307" s="11"/>
+      <c r="O307" s="6"/>
+      <c r="P307" s="12"/>
+      <c r="R307" s="10"/>
     </row>
     <row r="308" spans="15:18">
-      <c r="O308" s="7"/>
-      <c r="P308" s="13"/>
-      <c r="R308" s="11"/>
+      <c r="O308" s="6"/>
+      <c r="P308" s="12"/>
+      <c r="R308" s="10"/>
     </row>
     <row r="309" spans="15:18">
-      <c r="O309" s="7"/>
-      <c r="P309" s="13"/>
-      <c r="R309" s="11"/>
+      <c r="O309" s="6"/>
+      <c r="P309" s="12"/>
+      <c r="R309" s="10"/>
     </row>
     <row r="310" spans="15:18">
-      <c r="O310" s="7"/>
-      <c r="P310" s="13"/>
-      <c r="R310" s="11"/>
+      <c r="O310" s="6"/>
+      <c r="P310" s="12"/>
+      <c r="R310" s="10"/>
     </row>
     <row r="311" spans="15:18">
-      <c r="O311" s="7"/>
-      <c r="P311" s="13"/>
-      <c r="R311" s="11"/>
+      <c r="O311" s="6"/>
+      <c r="P311" s="12"/>
+      <c r="R311" s="10"/>
     </row>
     <row r="312" spans="15:18">
-      <c r="O312" s="7"/>
-      <c r="P312" s="13"/>
-      <c r="R312" s="11"/>
+      <c r="O312" s="6"/>
+      <c r="P312" s="12"/>
+      <c r="R312" s="10"/>
     </row>
     <row r="313" spans="15:18">
-      <c r="O313" s="7"/>
-      <c r="P313" s="13"/>
-      <c r="R313" s="11"/>
+      <c r="O313" s="6"/>
+      <c r="P313" s="12"/>
+      <c r="R313" s="10"/>
     </row>
     <row r="314" spans="15:18">
-      <c r="O314" s="7"/>
-      <c r="P314" s="13"/>
-      <c r="R314" s="11"/>
+      <c r="O314" s="6"/>
+      <c r="P314" s="12"/>
+      <c r="R314" s="10"/>
     </row>
     <row r="315" spans="15:18">
-      <c r="O315" s="7"/>
-      <c r="P315" s="13"/>
-      <c r="R315" s="11"/>
+      <c r="O315" s="6"/>
+      <c r="P315" s="12"/>
+      <c r="R315" s="10"/>
     </row>
     <row r="316" spans="15:18">
-      <c r="O316" s="7"/>
-      <c r="P316" s="13"/>
-      <c r="R316" s="11"/>
+      <c r="O316" s="6"/>
+      <c r="P316" s="12"/>
+      <c r="R316" s="10"/>
     </row>
     <row r="317" spans="15:18">
-      <c r="O317" s="7"/>
-      <c r="P317" s="13"/>
-      <c r="R317" s="11"/>
+      <c r="O317" s="6"/>
+      <c r="P317" s="12"/>
+      <c r="R317" s="10"/>
     </row>
     <row r="318" spans="15:18">
-      <c r="O318" s="7"/>
-      <c r="P318" s="13"/>
-      <c r="R318" s="11"/>
+      <c r="O318" s="6"/>
+      <c r="P318" s="12"/>
+      <c r="R318" s="10"/>
     </row>
     <row r="319" spans="15:18">
-      <c r="O319" s="7"/>
-      <c r="P319" s="13"/>
-      <c r="R319" s="11"/>
+      <c r="O319" s="6"/>
+      <c r="P319" s="12"/>
+      <c r="R319" s="10"/>
     </row>
     <row r="320" spans="15:18">
-      <c r="O320" s="7"/>
-      <c r="P320" s="13"/>
-      <c r="R320" s="11"/>
+      <c r="O320" s="6"/>
+      <c r="P320" s="12"/>
+      <c r="R320" s="10"/>
     </row>
     <row r="321" spans="15:18">
-      <c r="O321" s="7"/>
-      <c r="P321" s="13"/>
-      <c r="R321" s="11"/>
+      <c r="O321" s="6"/>
+      <c r="P321" s="12"/>
+      <c r="R321" s="10"/>
     </row>
     <row r="322" spans="15:18">
-      <c r="O322" s="7"/>
-      <c r="P322" s="13"/>
-      <c r="R322" s="11"/>
+      <c r="O322" s="6"/>
+      <c r="P322" s="12"/>
+      <c r="R322" s="10"/>
     </row>
     <row r="323" spans="15:18">
-      <c r="O323" s="7"/>
-      <c r="P323" s="13"/>
-      <c r="R323" s="11"/>
+      <c r="O323" s="6"/>
+      <c r="P323" s="12"/>
+      <c r="R323" s="10"/>
     </row>
     <row r="324" spans="15:18">
-      <c r="O324" s="7"/>
-      <c r="P324" s="13"/>
-      <c r="R324" s="11"/>
+      <c r="O324" s="6"/>
+      <c r="P324" s="12"/>
+      <c r="R324" s="10"/>
     </row>
     <row r="325" spans="15:18">
-      <c r="O325" s="7"/>
-      <c r="P325" s="13"/>
-      <c r="R325" s="11"/>
+      <c r="O325" s="6"/>
+      <c r="P325" s="12"/>
+      <c r="R325" s="10"/>
     </row>
     <row r="326" spans="15:18">
-      <c r="O326" s="7"/>
-      <c r="P326" s="13"/>
-      <c r="R326" s="11"/>
+      <c r="O326" s="6"/>
+      <c r="P326" s="12"/>
+      <c r="R326" s="10"/>
     </row>
     <row r="327" spans="15:18">
-      <c r="O327" s="7"/>
-      <c r="P327" s="13"/>
-      <c r="R327" s="11"/>
+      <c r="O327" s="6"/>
+      <c r="P327" s="12"/>
+      <c r="R327" s="10"/>
     </row>
     <row r="328" spans="15:18">
-      <c r="O328" s="7"/>
-      <c r="P328" s="13"/>
-      <c r="R328" s="11"/>
+      <c r="O328" s="6"/>
+      <c r="P328" s="12"/>
+      <c r="R328" s="10"/>
     </row>
     <row r="329" spans="15:18">
-      <c r="O329" s="7"/>
-      <c r="P329" s="13"/>
-      <c r="R329" s="11"/>
+      <c r="O329" s="6"/>
+      <c r="P329" s="12"/>
+      <c r="R329" s="10"/>
     </row>
     <row r="330" spans="15:18">
-      <c r="O330" s="7"/>
-      <c r="P330" s="13"/>
-      <c r="R330" s="11"/>
+      <c r="O330" s="6"/>
+      <c r="P330" s="12"/>
+      <c r="R330" s="10"/>
     </row>
     <row r="331" spans="15:18">
-      <c r="O331" s="7"/>
-      <c r="P331" s="13"/>
-      <c r="R331" s="11"/>
+      <c r="O331" s="6"/>
+      <c r="P331" s="12"/>
+      <c r="R331" s="10"/>
     </row>
     <row r="332" spans="15:18">
-      <c r="O332" s="7"/>
-      <c r="P332" s="13"/>
-      <c r="R332" s="11"/>
+      <c r="O332" s="6"/>
+      <c r="P332" s="12"/>
+      <c r="R332" s="10"/>
     </row>
     <row r="333" spans="15:18">
-      <c r="O333" s="7"/>
-      <c r="P333" s="13"/>
-      <c r="R333" s="11"/>
+      <c r="O333" s="6"/>
+      <c r="P333" s="12"/>
+      <c r="R333" s="10"/>
     </row>
     <row r="334" spans="15:18">
-      <c r="O334" s="7"/>
-      <c r="P334" s="13"/>
-      <c r="R334" s="11"/>
+      <c r="O334" s="6"/>
+      <c r="P334" s="12"/>
+      <c r="R334" s="10"/>
     </row>
     <row r="335" spans="15:18">
-      <c r="O335" s="7"/>
-      <c r="P335" s="13"/>
-      <c r="R335" s="11"/>
+      <c r="O335" s="6"/>
+      <c r="P335" s="12"/>
+      <c r="R335" s="10"/>
     </row>
     <row r="336" spans="15:18">
-      <c r="O336" s="7"/>
-      <c r="P336" s="13"/>
-      <c r="R336" s="11"/>
+      <c r="O336" s="6"/>
+      <c r="P336" s="12"/>
+      <c r="R336" s="10"/>
     </row>
     <row r="337" spans="15:18">
-      <c r="O337" s="7"/>
-      <c r="P337" s="13"/>
-      <c r="R337" s="11"/>
+      <c r="O337" s="6"/>
+      <c r="P337" s="12"/>
+      <c r="R337" s="10"/>
     </row>
     <row r="338" spans="15:18">
-      <c r="O338" s="7"/>
-      <c r="P338" s="13"/>
-      <c r="R338" s="11"/>
+      <c r="O338" s="6"/>
+      <c r="P338" s="12"/>
+      <c r="R338" s="10"/>
     </row>
     <row r="339" spans="15:18">
-      <c r="O339" s="7"/>
-      <c r="P339" s="13"/>
-      <c r="R339" s="11"/>
+      <c r="O339" s="6"/>
+      <c r="P339" s="12"/>
+      <c r="R339" s="10"/>
     </row>
     <row r="340" spans="15:18">
-      <c r="O340" s="7"/>
-      <c r="P340" s="13"/>
-      <c r="R340" s="11"/>
+      <c r="O340" s="6"/>
+      <c r="P340" s="12"/>
+      <c r="R340" s="10"/>
     </row>
     <row r="341" spans="15:18">
-      <c r="O341" s="7"/>
-      <c r="P341" s="13"/>
-      <c r="R341" s="11"/>
+      <c r="O341" s="6"/>
+      <c r="P341" s="12"/>
+      <c r="R341" s="10"/>
     </row>
     <row r="342" spans="15:18">
-      <c r="O342" s="7"/>
-      <c r="P342" s="13"/>
-      <c r="R342" s="11"/>
+      <c r="O342" s="6"/>
+      <c r="P342" s="12"/>
+      <c r="R342" s="10"/>
     </row>
     <row r="343" spans="15:18">
-      <c r="O343" s="7"/>
-      <c r="P343" s="13"/>
-      <c r="R343" s="11"/>
+      <c r="O343" s="6"/>
+      <c r="P343" s="12"/>
+      <c r="R343" s="10"/>
     </row>
     <row r="344" spans="15:18">
-      <c r="O344" s="7"/>
-      <c r="P344" s="13"/>
-      <c r="R344" s="11"/>
+      <c r="O344" s="6"/>
+      <c r="P344" s="12"/>
+      <c r="R344" s="10"/>
     </row>
     <row r="345" spans="15:18">
-      <c r="O345" s="7"/>
-      <c r="P345" s="13"/>
-      <c r="R345" s="11"/>
+      <c r="O345" s="6"/>
+      <c r="P345" s="12"/>
+      <c r="R345" s="10"/>
     </row>
     <row r="346" spans="15:18">
-      <c r="O346" s="7"/>
-      <c r="P346" s="13"/>
-      <c r="R346" s="11"/>
+      <c r="O346" s="6"/>
+      <c r="P346" s="12"/>
+      <c r="R346" s="10"/>
     </row>
     <row r="347" spans="15:18">
-      <c r="O347" s="7"/>
-      <c r="P347" s="13"/>
-      <c r="R347" s="11"/>
+      <c r="O347" s="6"/>
+      <c r="P347" s="12"/>
+      <c r="R347" s="10"/>
     </row>
     <row r="348" spans="15:18">
-      <c r="O348" s="7"/>
-      <c r="P348" s="13"/>
-      <c r="R348" s="11"/>
+      <c r="O348" s="6"/>
+      <c r="P348" s="12"/>
+      <c r="R348" s="10"/>
     </row>
     <row r="349" spans="15:18">
-      <c r="O349" s="7"/>
-      <c r="P349" s="13"/>
-      <c r="R349" s="11"/>
+      <c r="O349" s="6"/>
+      <c r="P349" s="12"/>
+      <c r="R349" s="10"/>
     </row>
     <row r="350" spans="15:18">
-      <c r="O350" s="7"/>
-      <c r="P350" s="13"/>
-      <c r="R350" s="11"/>
+      <c r="O350" s="6"/>
+      <c r="P350" s="12"/>
+      <c r="R350" s="10"/>
     </row>
     <row r="351" spans="15:18">
-      <c r="O351" s="7"/>
-      <c r="P351" s="13"/>
-      <c r="R351" s="11"/>
+      <c r="O351" s="6"/>
+      <c r="P351" s="12"/>
+      <c r="R351" s="10"/>
     </row>
     <row r="352" spans="15:18">
-      <c r="O352" s="7"/>
-      <c r="P352" s="13"/>
-      <c r="R352" s="11"/>
+      <c r="O352" s="6"/>
+      <c r="P352" s="12"/>
+      <c r="R352" s="10"/>
     </row>
     <row r="353" spans="15:18">
-      <c r="O353" s="7"/>
-      <c r="P353" s="13"/>
-      <c r="R353" s="11"/>
+      <c r="O353" s="6"/>
+      <c r="P353" s="12"/>
+      <c r="R353" s="10"/>
     </row>
     <row r="354" spans="15:18">
-      <c r="O354" s="7"/>
-      <c r="P354" s="13"/>
-      <c r="R354" s="11"/>
+      <c r="O354" s="6"/>
+      <c r="P354" s="12"/>
+      <c r="R354" s="10"/>
     </row>
     <row r="355" spans="15:18">
-      <c r="O355" s="7"/>
-      <c r="P355" s="13"/>
-      <c r="R355" s="11"/>
+      <c r="O355" s="6"/>
+      <c r="P355" s="12"/>
+      <c r="R355" s="10"/>
     </row>
     <row r="356" spans="15:18">
-      <c r="O356" s="7"/>
-      <c r="P356" s="13"/>
-      <c r="R356" s="11"/>
+      <c r="O356" s="6"/>
+      <c r="P356" s="12"/>
+      <c r="R356" s="10"/>
     </row>
     <row r="357" spans="15:18">
-      <c r="O357" s="7"/>
-      <c r="P357" s="13"/>
-      <c r="R357" s="11"/>
+      <c r="O357" s="6"/>
+      <c r="P357" s="12"/>
+      <c r="R357" s="10"/>
     </row>
     <row r="358" spans="15:18">
-      <c r="O358" s="7"/>
-      <c r="P358" s="13"/>
-      <c r="R358" s="11"/>
+      <c r="O358" s="6"/>
+      <c r="P358" s="12"/>
+      <c r="R358" s="10"/>
     </row>
     <row r="359" spans="15:18">
-      <c r="O359" s="7"/>
-      <c r="P359" s="13"/>
-      <c r="R359" s="11"/>
+      <c r="O359" s="6"/>
+      <c r="P359" s="12"/>
+      <c r="R359" s="10"/>
     </row>
     <row r="360" spans="15:18">
-      <c r="O360" s="7"/>
-      <c r="P360" s="13"/>
-      <c r="R360" s="11"/>
+      <c r="O360" s="6"/>
+      <c r="P360" s="12"/>
+      <c r="R360" s="10"/>
     </row>
     <row r="361" spans="15:18">
-      <c r="O361" s="7"/>
-      <c r="P361" s="13"/>
-      <c r="R361" s="11"/>
+      <c r="O361" s="6"/>
+      <c r="P361" s="12"/>
+      <c r="R361" s="10"/>
     </row>
     <row r="362" spans="15:18">
-      <c r="O362" s="7"/>
-      <c r="P362" s="13"/>
-      <c r="R362" s="11"/>
+      <c r="O362" s="6"/>
+      <c r="P362" s="12"/>
+      <c r="R362" s="10"/>
     </row>
     <row r="363" spans="15:18">
-      <c r="O363" s="7"/>
-      <c r="P363" s="13"/>
-      <c r="R363" s="11"/>
+      <c r="O363" s="6"/>
+      <c r="P363" s="12"/>
+      <c r="R363" s="10"/>
     </row>
     <row r="364" spans="15:18">
-      <c r="O364" s="7"/>
-      <c r="P364" s="13"/>
-      <c r="R364" s="11"/>
+      <c r="O364" s="6"/>
+      <c r="P364" s="12"/>
+      <c r="R364" s="10"/>
     </row>
     <row r="365" spans="15:18">
-      <c r="O365" s="7"/>
-      <c r="P365" s="13"/>
-      <c r="R365" s="11"/>
+      <c r="O365" s="6"/>
+      <c r="P365" s="12"/>
+      <c r="R365" s="10"/>
     </row>
     <row r="366" spans="15:18">
-      <c r="O366" s="7"/>
-      <c r="P366" s="13"/>
-      <c r="R366" s="11"/>
+      <c r="O366" s="6"/>
+      <c r="P366" s="12"/>
+      <c r="R366" s="10"/>
     </row>
     <row r="367" spans="15:18">
-      <c r="O367" s="7"/>
-      <c r="P367" s="13"/>
-      <c r="R367" s="11"/>
+      <c r="O367" s="6"/>
+      <c r="P367" s="12"/>
+      <c r="R367" s="10"/>
     </row>
     <row r="368" spans="15:18">
-      <c r="O368" s="7"/>
-      <c r="P368" s="13"/>
-      <c r="R368" s="11"/>
+      <c r="O368" s="6"/>
+      <c r="P368" s="12"/>
+      <c r="R368" s="10"/>
     </row>
     <row r="369" spans="15:18">
-      <c r="O369" s="7"/>
-      <c r="P369" s="13"/>
-      <c r="R369" s="11"/>
+      <c r="O369" s="6"/>
+      <c r="P369" s="12"/>
+      <c r="R369" s="10"/>
     </row>
     <row r="370" spans="15:18">
-      <c r="O370" s="7"/>
-      <c r="P370" s="13"/>
-      <c r="R370" s="11"/>
+      <c r="O370" s="6"/>
+      <c r="P370" s="12"/>
+      <c r="R370" s="10"/>
     </row>
     <row r="371" spans="15:18">
-      <c r="O371" s="7"/>
-      <c r="P371" s="13"/>
-      <c r="R371" s="11"/>
+      <c r="O371" s="6"/>
+      <c r="P371" s="12"/>
+      <c r="R371" s="10"/>
     </row>
     <row r="372" spans="15:18">
-      <c r="O372" s="7"/>
-      <c r="P372" s="13"/>
-      <c r="R372" s="11"/>
+      <c r="O372" s="6"/>
+      <c r="P372" s="12"/>
+      <c r="R372" s="10"/>
     </row>
     <row r="373" spans="15:18">
-      <c r="O373" s="7"/>
-      <c r="P373" s="13"/>
-      <c r="R373" s="11"/>
+      <c r="O373" s="6"/>
+      <c r="P373" s="12"/>
+      <c r="R373" s="10"/>
     </row>
     <row r="374" spans="15:18">
-      <c r="O374" s="7"/>
-      <c r="P374" s="13"/>
-      <c r="R374" s="11"/>
+      <c r="O374" s="6"/>
+      <c r="P374" s="12"/>
+      <c r="R374" s="10"/>
     </row>
     <row r="375" spans="15:18">
-      <c r="O375" s="7"/>
-      <c r="P375" s="13"/>
-      <c r="R375" s="11"/>
+      <c r="O375" s="6"/>
+      <c r="P375" s="12"/>
+      <c r="R375" s="10"/>
     </row>
     <row r="376" spans="15:18">
-      <c r="O376" s="7"/>
-      <c r="P376" s="13"/>
-      <c r="R376" s="11"/>
+      <c r="O376" s="6"/>
+      <c r="P376" s="12"/>
+      <c r="R376" s="10"/>
     </row>
     <row r="377" spans="15:18">
-      <c r="O377" s="7"/>
-      <c r="P377" s="13"/>
-      <c r="R377" s="11"/>
+      <c r="O377" s="6"/>
+      <c r="P377" s="12"/>
+      <c r="R377" s="10"/>
     </row>
     <row r="378" spans="15:18">
-      <c r="O378" s="7"/>
-      <c r="P378" s="13"/>
-      <c r="R378" s="11"/>
+      <c r="O378" s="6"/>
+      <c r="P378" s="12"/>
+      <c r="R378" s="10"/>
     </row>
     <row r="379" spans="15:18">
-      <c r="O379" s="7"/>
-      <c r="P379" s="13"/>
-      <c r="R379" s="11"/>
+      <c r="O379" s="6"/>
+      <c r="P379" s="12"/>
+      <c r="R379" s="10"/>
     </row>
     <row r="380" spans="15:18">
-      <c r="O380" s="7"/>
-      <c r="P380" s="13"/>
-      <c r="R380" s="11"/>
+      <c r="O380" s="6"/>
+      <c r="P380" s="12"/>
+      <c r="R380" s="10"/>
     </row>
     <row r="381" spans="15:18">
-      <c r="O381" s="7"/>
-      <c r="P381" s="13"/>
-      <c r="R381" s="11"/>
+      <c r="O381" s="6"/>
+      <c r="P381" s="12"/>
+      <c r="R381" s="10"/>
     </row>
     <row r="382" spans="15:18">
-      <c r="O382" s="7"/>
-      <c r="P382" s="13"/>
-      <c r="R382" s="11"/>
+      <c r="O382" s="6"/>
+      <c r="P382" s="12"/>
+      <c r="R382" s="10"/>
     </row>
     <row r="383" spans="15:18">
-      <c r="O383" s="7"/>
-      <c r="P383" s="13"/>
-      <c r="R383" s="11"/>
+      <c r="O383" s="6"/>
+      <c r="P383" s="12"/>
+      <c r="R383" s="10"/>
     </row>
     <row r="384" spans="15:18">
-      <c r="O384" s="7"/>
-      <c r="P384" s="13"/>
-      <c r="R384" s="11"/>
+      <c r="O384" s="6"/>
+      <c r="P384" s="12"/>
+      <c r="R384" s="10"/>
     </row>
     <row r="385" spans="15:18">
-      <c r="O385" s="7"/>
-      <c r="P385" s="13"/>
-      <c r="R385" s="11"/>
+      <c r="O385" s="6"/>
+      <c r="P385" s="12"/>
+      <c r="R385" s="10"/>
     </row>
     <row r="386" spans="15:18">
-      <c r="O386" s="7"/>
-      <c r="P386" s="13"/>
-      <c r="R386" s="11"/>
+      <c r="O386" s="6"/>
+      <c r="P386" s="12"/>
+      <c r="R386" s="10"/>
     </row>
     <row r="387" spans="15:18">
-      <c r="O387" s="7"/>
-      <c r="P387" s="13"/>
-      <c r="R387" s="11"/>
+      <c r="O387" s="6"/>
+      <c r="P387" s="12"/>
+      <c r="R387" s="10"/>
     </row>
     <row r="388" spans="15:18">
-      <c r="O388" s="7"/>
-      <c r="P388" s="13"/>
-      <c r="R388" s="11"/>
+      <c r="O388" s="6"/>
+      <c r="P388" s="12"/>
+      <c r="R388" s="10"/>
     </row>
     <row r="389" spans="15:18">
-      <c r="O389" s="7"/>
-      <c r="P389" s="13"/>
-      <c r="R389" s="11"/>
+      <c r="O389" s="6"/>
+      <c r="P389" s="12"/>
+      <c r="R389" s="10"/>
     </row>
     <row r="390" spans="15:18">
-      <c r="O390" s="7"/>
-      <c r="P390" s="13"/>
-      <c r="R390" s="11"/>
+      <c r="O390" s="6"/>
+      <c r="P390" s="12"/>
+      <c r="R390" s="10"/>
     </row>
     <row r="391" spans="15:18">
-      <c r="O391" s="7"/>
-      <c r="P391" s="13"/>
-      <c r="R391" s="11"/>
+      <c r="O391" s="6"/>
+      <c r="P391" s="12"/>
+      <c r="R391" s="10"/>
     </row>
     <row r="392" spans="15:18">
-      <c r="O392" s="7"/>
-      <c r="P392" s="13"/>
-      <c r="R392" s="11"/>
+      <c r="O392" s="6"/>
+      <c r="P392" s="12"/>
+      <c r="R392" s="10"/>
     </row>
     <row r="393" spans="15:18">
-      <c r="O393" s="7"/>
-      <c r="P393" s="13"/>
-      <c r="R393" s="11"/>
+      <c r="O393" s="6"/>
+      <c r="P393" s="12"/>
+      <c r="R393" s="10"/>
     </row>
     <row r="394" spans="15:18">
-      <c r="O394" s="7"/>
-      <c r="P394" s="13"/>
-      <c r="R394" s="11"/>
+      <c r="O394" s="6"/>
+      <c r="P394" s="12"/>
+      <c r="R394" s="10"/>
     </row>
     <row r="395" spans="15:18">
-      <c r="O395" s="7"/>
-      <c r="P395" s="13"/>
-      <c r="R395" s="11"/>
+      <c r="O395" s="6"/>
+      <c r="P395" s="12"/>
+      <c r="R395" s="10"/>
     </row>
     <row r="396" spans="15:18">
-      <c r="O396" s="7"/>
-      <c r="P396" s="13"/>
-      <c r="R396" s="11"/>
+      <c r="O396" s="6"/>
+      <c r="P396" s="12"/>
+      <c r="R396" s="10"/>
     </row>
     <row r="397" spans="15:18">
-      <c r="O397" s="7"/>
-      <c r="P397" s="13"/>
-      <c r="R397" s="11"/>
+      <c r="O397" s="6"/>
+      <c r="P397" s="12"/>
+      <c r="R397" s="10"/>
     </row>
     <row r="398" spans="15:18">
-      <c r="O398" s="7"/>
-      <c r="P398" s="13"/>
-      <c r="R398" s="11"/>
+      <c r="O398" s="6"/>
+      <c r="P398" s="12"/>
+      <c r="R398" s="10"/>
     </row>
     <row r="399" spans="15:18">
-      <c r="O399" s="7"/>
-      <c r="P399" s="13"/>
-      <c r="R399" s="11"/>
+      <c r="O399" s="6"/>
+      <c r="P399" s="12"/>
+      <c r="R399" s="10"/>
     </row>
     <row r="400" spans="15:18">
-      <c r="O400" s="7"/>
-      <c r="P400" s="13"/>
-      <c r="R400" s="11"/>
+      <c r="O400" s="6"/>
+      <c r="P400" s="12"/>
+      <c r="R400" s="10"/>
     </row>
     <row r="401" spans="15:18">
-      <c r="O401" s="7"/>
-      <c r="P401" s="13"/>
-      <c r="R401" s="11"/>
+      <c r="O401" s="6"/>
+      <c r="P401" s="12"/>
+      <c r="R401" s="10"/>
     </row>
     <row r="402" spans="15:18">
-      <c r="O402" s="7"/>
-      <c r="P402" s="13"/>
-      <c r="R402" s="11"/>
+      <c r="O402" s="6"/>
+      <c r="P402" s="12"/>
+      <c r="R402" s="10"/>
     </row>
     <row r="403" spans="15:18">
-      <c r="O403" s="7"/>
-      <c r="P403" s="13"/>
-      <c r="R403" s="11"/>
+      <c r="O403" s="6"/>
+      <c r="P403" s="12"/>
+      <c r="R403" s="10"/>
     </row>
     <row r="404" spans="15:18">
-      <c r="O404" s="7"/>
-      <c r="P404" s="13"/>
-      <c r="R404" s="11"/>
+      <c r="O404" s="6"/>
+      <c r="P404" s="12"/>
+      <c r="R404" s="10"/>
     </row>
     <row r="405" spans="15:18">
-      <c r="O405" s="7"/>
-      <c r="P405" s="13"/>
-      <c r="R405" s="11"/>
+      <c r="O405" s="6"/>
+      <c r="P405" s="12"/>
+      <c r="R405" s="10"/>
     </row>
     <row r="406" spans="15:18">
-      <c r="O406" s="7"/>
-      <c r="P406" s="13"/>
-      <c r="R406" s="11"/>
+      <c r="O406" s="6"/>
+      <c r="P406" s="12"/>
+      <c r="R406" s="10"/>
     </row>
     <row r="407" spans="15:18">
-      <c r="O407" s="7"/>
-      <c r="P407" s="13"/>
-      <c r="R407" s="11"/>
+      <c r="O407" s="6"/>
+      <c r="P407" s="12"/>
+      <c r="R407" s="10"/>
     </row>
     <row r="408" spans="15:18">
-      <c r="O408" s="7"/>
-      <c r="P408" s="13"/>
-      <c r="R408" s="11"/>
+      <c r="O408" s="6"/>
+      <c r="P408" s="12"/>
+      <c r="R408" s="10"/>
     </row>
     <row r="409" spans="15:18">
-      <c r="O409" s="7"/>
-      <c r="P409" s="13"/>
-      <c r="R409" s="11"/>
+      <c r="O409" s="6"/>
+      <c r="P409" s="12"/>
+      <c r="R409" s="10"/>
     </row>
     <row r="410" spans="15:18">
-      <c r="O410" s="7"/>
-      <c r="P410" s="13"/>
-      <c r="R410" s="11"/>
+      <c r="O410" s="6"/>
+      <c r="P410" s="12"/>
+      <c r="R410" s="10"/>
     </row>
     <row r="411" spans="15:18">
-      <c r="O411" s="7"/>
-      <c r="P411" s="13"/>
-      <c r="R411" s="11"/>
+      <c r="O411" s="6"/>
+      <c r="P411" s="12"/>
+      <c r="R411" s="10"/>
     </row>
     <row r="412" spans="15:18">
-      <c r="O412" s="7"/>
-      <c r="P412" s="13"/>
-      <c r="R412" s="11"/>
+      <c r="O412" s="6"/>
+      <c r="P412" s="12"/>
+      <c r="R412" s="10"/>
     </row>
     <row r="413" spans="15:18">
-      <c r="O413" s="7"/>
-      <c r="P413" s="13"/>
-      <c r="R413" s="11"/>
+      <c r="O413" s="6"/>
+      <c r="P413" s="12"/>
+      <c r="R413" s="10"/>
     </row>
     <row r="414" spans="15:18">
-      <c r="O414" s="7"/>
-      <c r="P414" s="13"/>
-      <c r="R414" s="11"/>
+      <c r="O414" s="6"/>
+      <c r="P414" s="12"/>
+      <c r="R414" s="10"/>
     </row>
     <row r="415" spans="15:18">
-      <c r="O415" s="7"/>
-      <c r="P415" s="13"/>
-      <c r="R415" s="11"/>
+      <c r="O415" s="6"/>
+      <c r="P415" s="12"/>
+      <c r="R415" s="10"/>
     </row>
     <row r="416" spans="15:18">
-      <c r="O416" s="7"/>
-      <c r="P416" s="13"/>
-      <c r="R416" s="11"/>
+      <c r="O416" s="6"/>
+      <c r="P416" s="12"/>
+      <c r="R416" s="10"/>
     </row>
     <row r="417" spans="15:18">
-      <c r="O417" s="7"/>
-      <c r="P417" s="13"/>
-      <c r="R417" s="11"/>
+      <c r="O417" s="6"/>
+      <c r="P417" s="12"/>
+      <c r="R417" s="10"/>
     </row>
     <row r="418" spans="15:18">
-      <c r="O418" s="7"/>
-      <c r="P418" s="13"/>
-      <c r="R418" s="11"/>
+      <c r="O418" s="6"/>
+      <c r="P418" s="12"/>
+      <c r="R418" s="10"/>
     </row>
     <row r="419" spans="15:18">
-      <c r="O419" s="7"/>
-      <c r="P419" s="13"/>
-      <c r="R419" s="11"/>
+      <c r="O419" s="6"/>
+      <c r="P419" s="12"/>
+      <c r="R419" s="10"/>
     </row>
     <row r="420" spans="15:18">
-      <c r="O420" s="7"/>
-      <c r="P420" s="13"/>
-      <c r="R420" s="11"/>
+      <c r="O420" s="6"/>
+      <c r="P420" s="12"/>
+      <c r="R420" s="10"/>
     </row>
     <row r="421" spans="15:18">
-      <c r="O421" s="7"/>
-      <c r="P421" s="13"/>
-      <c r="R421" s="11"/>
+      <c r="O421" s="6"/>
+      <c r="P421" s="12"/>
+      <c r="R421" s="10"/>
     </row>
     <row r="422" spans="15:18">
-      <c r="O422" s="7"/>
-      <c r="P422" s="13"/>
-      <c r="R422" s="11"/>
+      <c r="O422" s="6"/>
+      <c r="P422" s="12"/>
+      <c r="R422" s="10"/>
     </row>
     <row r="423" spans="15:18">
-      <c r="O423" s="7"/>
-      <c r="P423" s="13"/>
-      <c r="R423" s="11"/>
+      <c r="O423" s="6"/>
+      <c r="P423" s="12"/>
+      <c r="R423" s="10"/>
     </row>
     <row r="424" spans="15:18">
-      <c r="O424" s="7"/>
-      <c r="P424" s="13"/>
-      <c r="R424" s="11"/>
+      <c r="O424" s="6"/>
+      <c r="P424" s="12"/>
+      <c r="R424" s="10"/>
     </row>
     <row r="425" spans="15:18">
-      <c r="O425" s="7"/>
-      <c r="P425" s="13"/>
-      <c r="R425" s="11"/>
+      <c r="O425" s="6"/>
+      <c r="P425" s="12"/>
+      <c r="R425" s="10"/>
     </row>
     <row r="426" spans="15:18">
-      <c r="O426" s="7"/>
-      <c r="P426" s="13"/>
-      <c r="R426" s="11"/>
+      <c r="O426" s="6"/>
+      <c r="P426" s="12"/>
+      <c r="R426" s="10"/>
     </row>
     <row r="427" spans="15:18">
-      <c r="O427" s="7"/>
-      <c r="P427" s="13"/>
-      <c r="R427" s="11"/>
+      <c r="O427" s="6"/>
+      <c r="P427" s="12"/>
+      <c r="R427" s="10"/>
     </row>
     <row r="428" spans="15:18">
-      <c r="O428" s="7"/>
-      <c r="P428" s="13"/>
-      <c r="R428" s="11"/>
+      <c r="O428" s="6"/>
+      <c r="P428" s="12"/>
+      <c r="R428" s="10"/>
     </row>
     <row r="429" spans="15:18">
-      <c r="O429" s="7"/>
-      <c r="P429" s="13"/>
-      <c r="R429" s="11"/>
+      <c r="O429" s="6"/>
+      <c r="P429" s="12"/>
+      <c r="R429" s="10"/>
     </row>
     <row r="430" spans="15:18">
-      <c r="O430" s="7"/>
-      <c r="P430" s="13"/>
-      <c r="R430" s="11"/>
+      <c r="O430" s="6"/>
+      <c r="P430" s="12"/>
+      <c r="R430" s="10"/>
     </row>
     <row r="431" spans="15:18">
-      <c r="O431" s="7"/>
-      <c r="P431" s="13"/>
-      <c r="R431" s="11"/>
+      <c r="O431" s="6"/>
+      <c r="P431" s="12"/>
+      <c r="R431" s="10"/>
     </row>
     <row r="432" spans="15:18">
-      <c r="O432" s="7"/>
-      <c r="P432" s="13"/>
-      <c r="R432" s="11"/>
+      <c r="O432" s="6"/>
+      <c r="P432" s="12"/>
+      <c r="R432" s="10"/>
     </row>
     <row r="433" spans="15:18">
-      <c r="O433" s="7"/>
-      <c r="P433" s="13"/>
-      <c r="R433" s="11"/>
+      <c r="O433" s="6"/>
+      <c r="P433" s="12"/>
+      <c r="R433" s="10"/>
     </row>
     <row r="434" spans="15:18">
-      <c r="O434" s="7"/>
-      <c r="P434" s="13"/>
-      <c r="R434" s="11"/>
+      <c r="O434" s="6"/>
+      <c r="P434" s="12"/>
+      <c r="R434" s="10"/>
     </row>
     <row r="435" spans="15:18">
-      <c r="O435" s="7"/>
-      <c r="P435" s="13"/>
-      <c r="R435" s="11"/>
+      <c r="O435" s="6"/>
+      <c r="P435" s="12"/>
+      <c r="R435" s="10"/>
     </row>
     <row r="436" spans="15:18">
-      <c r="O436" s="7"/>
-      <c r="P436" s="13"/>
-      <c r="R436" s="11"/>
+      <c r="O436" s="6"/>
+      <c r="P436" s="12"/>
+      <c r="R436" s="10"/>
     </row>
     <row r="437" spans="15:18">
-      <c r="O437" s="7"/>
-      <c r="P437" s="13"/>
-      <c r="R437" s="11"/>
+      <c r="O437" s="6"/>
+      <c r="P437" s="12"/>
+      <c r="R437" s="10"/>
     </row>
     <row r="438" spans="15:18">
-      <c r="O438" s="7"/>
-      <c r="P438" s="13"/>
-      <c r="R438" s="11"/>
+      <c r="O438" s="6"/>
+      <c r="P438" s="12"/>
+      <c r="R438" s="10"/>
     </row>
     <row r="439" spans="15:18">
-      <c r="O439" s="7"/>
-      <c r="P439" s="13"/>
-      <c r="R439" s="11"/>
+      <c r="O439" s="6"/>
+      <c r="P439" s="12"/>
+      <c r="R439" s="10"/>
     </row>
     <row r="440" spans="15:18">
-      <c r="O440" s="7"/>
-      <c r="P440" s="13"/>
-      <c r="R440" s="11"/>
+      <c r="O440" s="6"/>
+      <c r="P440" s="12"/>
+      <c r="R440" s="10"/>
     </row>
     <row r="441" spans="15:18">
-      <c r="O441" s="7"/>
-      <c r="P441" s="13"/>
-      <c r="R441" s="11"/>
+      <c r="O441" s="6"/>
+      <c r="P441" s="12"/>
+      <c r="R441" s="10"/>
     </row>
     <row r="442" spans="15:18">
-      <c r="O442" s="7"/>
-      <c r="P442" s="13"/>
-      <c r="R442" s="11"/>
+      <c r="O442" s="6"/>
+      <c r="P442" s="12"/>
+      <c r="R442" s="10"/>
     </row>
     <row r="443" spans="15:18">
-      <c r="O443" s="7"/>
-      <c r="P443" s="13"/>
-      <c r="R443" s="11"/>
+      <c r="O443" s="6"/>
+      <c r="P443" s="12"/>
+      <c r="R443" s="10"/>
     </row>
     <row r="444" spans="15:18">
-      <c r="O444" s="7"/>
-      <c r="P444" s="13"/>
-      <c r="R444" s="11"/>
+      <c r="O444" s="6"/>
+      <c r="P444" s="12"/>
+      <c r="R444" s="10"/>
     </row>
     <row r="445" spans="15:18">
-      <c r="O445" s="7"/>
-      <c r="P445" s="13"/>
-      <c r="R445" s="11"/>
+      <c r="O445" s="6"/>
+      <c r="P445" s="12"/>
+      <c r="R445" s="10"/>
     </row>
     <row r="446" spans="15:18">
-      <c r="O446" s="7"/>
-      <c r="P446" s="13"/>
-      <c r="R446" s="11"/>
+      <c r="O446" s="6"/>
+      <c r="P446" s="12"/>
+      <c r="R446" s="10"/>
     </row>
     <row r="447" spans="15:18">
-      <c r="O447" s="7"/>
-      <c r="P447" s="13"/>
-      <c r="R447" s="11"/>
+      <c r="O447" s="6"/>
+      <c r="P447" s="12"/>
+      <c r="R447" s="10"/>
     </row>
     <row r="448" spans="15:18">
-      <c r="O448" s="7"/>
-      <c r="P448" s="13"/>
-      <c r="R448" s="11"/>
+      <c r="O448" s="6"/>
+      <c r="P448" s="12"/>
+      <c r="R448" s="10"/>
     </row>
     <row r="449" spans="15:18">
-      <c r="O449" s="7"/>
-      <c r="P449" s="13"/>
-      <c r="R449" s="11"/>
+      <c r="O449" s="6"/>
+      <c r="P449" s="12"/>
+      <c r="R449" s="10"/>
     </row>
     <row r="450" spans="15:18">
-      <c r="O450" s="7"/>
-      <c r="P450" s="13"/>
-      <c r="R450" s="11"/>
+      <c r="O450" s="6"/>
+      <c r="P450" s="12"/>
+      <c r="R450" s="10"/>
     </row>
     <row r="451" spans="15:18">
-      <c r="O451" s="7"/>
-      <c r="P451" s="13"/>
-      <c r="R451" s="11"/>
+      <c r="O451" s="6"/>
+      <c r="P451" s="12"/>
+      <c r="R451" s="10"/>
     </row>
     <row r="452" spans="15:18">
-      <c r="O452" s="7"/>
-      <c r="P452" s="13"/>
-      <c r="R452" s="11"/>
+      <c r="O452" s="6"/>
+      <c r="P452" s="12"/>
+      <c r="R452" s="10"/>
     </row>
     <row r="453" spans="15:18">
-      <c r="O453" s="7"/>
-      <c r="P453" s="13"/>
-      <c r="R453" s="11"/>
+      <c r="O453" s="6"/>
+      <c r="P453" s="12"/>
+      <c r="R453" s="10"/>
     </row>
     <row r="454" spans="15:18">
-      <c r="O454" s="7"/>
-      <c r="P454" s="13"/>
-      <c r="R454" s="11"/>
+      <c r="O454" s="6"/>
+      <c r="P454" s="12"/>
+      <c r="R454" s="10"/>
     </row>
     <row r="455" spans="15:18">
-      <c r="O455" s="7"/>
-      <c r="P455" s="13"/>
-      <c r="R455" s="11"/>
+      <c r="O455" s="6"/>
+      <c r="P455" s="12"/>
+      <c r="R455" s="10"/>
     </row>
     <row r="456" spans="15:18">
-      <c r="O456" s="7"/>
-      <c r="P456" s="13"/>
-      <c r="R456" s="11"/>
+      <c r="O456" s="6"/>
+      <c r="P456" s="12"/>
+      <c r="R456" s="10"/>
     </row>
     <row r="457" spans="15:18">
-      <c r="O457" s="7"/>
-      <c r="P457" s="13"/>
-      <c r="R457" s="11"/>
+      <c r="O457" s="6"/>
+      <c r="P457" s="12"/>
+      <c r="R457" s="10"/>
     </row>
     <row r="458" spans="15:18">
-      <c r="O458" s="7"/>
-      <c r="P458" s="13"/>
-      <c r="R458" s="11"/>
+      <c r="O458" s="6"/>
+      <c r="P458" s="12"/>
+      <c r="R458" s="10"/>
     </row>
     <row r="459" spans="15:18">
-      <c r="O459" s="7"/>
-      <c r="P459" s="13"/>
-      <c r="R459" s="11"/>
+      <c r="O459" s="6"/>
+      <c r="P459" s="12"/>
+      <c r="R459" s="10"/>
     </row>
     <row r="460" spans="15:18">
-      <c r="O460" s="7"/>
-      <c r="P460" s="13"/>
-      <c r="R460" s="11"/>
+      <c r="O460" s="6"/>
+      <c r="P460" s="12"/>
+      <c r="R460" s="10"/>
     </row>
     <row r="461" spans="15:18">
-      <c r="O461" s="7"/>
-      <c r="P461" s="13"/>
-      <c r="R461" s="11"/>
+      <c r="O461" s="6"/>
+      <c r="P461" s="12"/>
+      <c r="R461" s="10"/>
     </row>
     <row r="462" spans="15:18">
-      <c r="O462" s="7"/>
-      <c r="P462" s="13"/>
-      <c r="R462" s="11"/>
+      <c r="O462" s="6"/>
+      <c r="P462" s="12"/>
+      <c r="R462" s="10"/>
     </row>
     <row r="463" spans="15:18">
-      <c r="O463" s="7"/>
-      <c r="P463" s="13"/>
-      <c r="R463" s="11"/>
+      <c r="O463" s="6"/>
+      <c r="P463" s="12"/>
+      <c r="R463" s="10"/>
     </row>
     <row r="464" spans="15:18">
-      <c r="O464" s="7"/>
-      <c r="P464" s="13"/>
-      <c r="R464" s="11"/>
+      <c r="O464" s="6"/>
+      <c r="P464" s="12"/>
+      <c r="R464" s="10"/>
     </row>
     <row r="465" spans="15:18">
-      <c r="O465" s="7"/>
-      <c r="P465" s="13"/>
-      <c r="R465" s="11"/>
+      <c r="O465" s="6"/>
+      <c r="P465" s="12"/>
+      <c r="R465" s="10"/>
     </row>
     <row r="466" spans="15:18">
-      <c r="O466" s="7"/>
-      <c r="P466" s="13"/>
-      <c r="R466" s="11"/>
+      <c r="O466" s="6"/>
+      <c r="P466" s="12"/>
+      <c r="R466" s="10"/>
     </row>
     <row r="467" spans="15:18">
-      <c r="O467" s="7"/>
-      <c r="P467" s="13"/>
-      <c r="R467" s="11"/>
+      <c r="O467" s="6"/>
+      <c r="P467" s="12"/>
+      <c r="R467" s="10"/>
     </row>
     <row r="468" spans="15:18">
-      <c r="O468" s="7"/>
-      <c r="P468" s="13"/>
-      <c r="R468" s="11"/>
+      <c r="O468" s="6"/>
+      <c r="P468" s="12"/>
+      <c r="R468" s="10"/>
     </row>
     <row r="469" spans="15:18">
-      <c r="O469" s="7"/>
-      <c r="P469" s="13"/>
-      <c r="R469" s="11"/>
+      <c r="O469" s="6"/>
+      <c r="P469" s="12"/>
+      <c r="R469" s="10"/>
     </row>
     <row r="470" spans="15:18">
-      <c r="O470" s="7"/>
-      <c r="P470" s="13"/>
-      <c r="R470" s="11"/>
+      <c r="O470" s="6"/>
+      <c r="P470" s="12"/>
+      <c r="R470" s="10"/>
     </row>
     <row r="471" spans="15:18">
-      <c r="O471" s="7"/>
-      <c r="P471" s="13"/>
-      <c r="R471" s="11"/>
+      <c r="O471" s="6"/>
+      <c r="P471" s="12"/>
+      <c r="R471" s="10"/>
     </row>
     <row r="472" spans="15:18">
-      <c r="O472" s="7"/>
-      <c r="P472" s="13"/>
-      <c r="R472" s="11"/>
+      <c r="O472" s="6"/>
+      <c r="P472" s="12"/>
+      <c r="R472" s="10"/>
     </row>
     <row r="473" spans="15:18">
-      <c r="O473" s="7"/>
-      <c r="P473" s="13"/>
-      <c r="R473" s="11"/>
+      <c r="O473" s="6"/>
+      <c r="P473" s="12"/>
+      <c r="R473" s="10"/>
     </row>
     <row r="474" spans="15:18">
-      <c r="O474" s="7"/>
-      <c r="P474" s="13"/>
-      <c r="R474" s="11"/>
+      <c r="O474" s="6"/>
+      <c r="P474" s="12"/>
+      <c r="R474" s="10"/>
     </row>
     <row r="475" spans="15:18">
-      <c r="O475" s="7"/>
-      <c r="P475" s="13"/>
-      <c r="R475" s="11"/>
+      <c r="O475" s="6"/>
+      <c r="P475" s="12"/>
+      <c r="R475" s="10"/>
     </row>
     <row r="476" spans="15:18">
-      <c r="O476" s="7"/>
-      <c r="P476" s="13"/>
-      <c r="R476" s="11"/>
+      <c r="O476" s="6"/>
+      <c r="P476" s="12"/>
+      <c r="R476" s="10"/>
     </row>
     <row r="477" spans="15:18">
-      <c r="O477" s="7"/>
-      <c r="P477" s="13"/>
-      <c r="R477" s="11"/>
+      <c r="O477" s="6"/>
+      <c r="P477" s="12"/>
+      <c r="R477" s="10"/>
     </row>
     <row r="478" spans="15:18">
-      <c r="O478" s="7"/>
-      <c r="P478" s="13"/>
-      <c r="R478" s="11"/>
+      <c r="O478" s="6"/>
+      <c r="P478" s="12"/>
+      <c r="R478" s="10"/>
     </row>
     <row r="479" spans="15:18">
-      <c r="O479" s="7"/>
-      <c r="P479" s="13"/>
-      <c r="R479" s="11"/>
+      <c r="O479" s="6"/>
+      <c r="P479" s="12"/>
+      <c r="R479" s="10"/>
     </row>
     <row r="480" spans="15:18">
-      <c r="O480" s="7"/>
-      <c r="P480" s="13"/>
-      <c r="R480" s="11"/>
+      <c r="O480" s="6"/>
+      <c r="P480" s="12"/>
+      <c r="R480" s="10"/>
     </row>
     <row r="481" spans="15:18">
-      <c r="O481" s="7"/>
-      <c r="P481" s="13"/>
-      <c r="R481" s="11"/>
+      <c r="O481" s="6"/>
+      <c r="P481" s="12"/>
+      <c r="R481" s="10"/>
     </row>
     <row r="482" spans="15:18">
-      <c r="O482" s="7"/>
-      <c r="P482" s="13"/>
-      <c r="R482" s="11"/>
+      <c r="O482" s="6"/>
+      <c r="P482" s="12"/>
+      <c r="R482" s="10"/>
     </row>
     <row r="483" spans="15:18">
-      <c r="O483" s="7"/>
-      <c r="P483" s="13"/>
-      <c r="R483" s="11"/>
+      <c r="O483" s="6"/>
+      <c r="P483" s="12"/>
+      <c r="R483" s="10"/>
     </row>
     <row r="484" spans="15:18">
-      <c r="O484" s="7"/>
-      <c r="P484" s="13"/>
-      <c r="R484" s="11"/>
+      <c r="O484" s="6"/>
+      <c r="P484" s="12"/>
+      <c r="R484" s="10"/>
     </row>
     <row r="485" spans="15:18">
-      <c r="O485" s="7"/>
-      <c r="P485" s="13"/>
-      <c r="R485" s="11"/>
+      <c r="O485" s="6"/>
+      <c r="P485" s="12"/>
+      <c r="R485" s="10"/>
     </row>
     <row r="486" spans="15:18">
-      <c r="O486" s="7"/>
-      <c r="P486" s="13"/>
-      <c r="R486" s="11"/>
+      <c r="O486" s="6"/>
+      <c r="P486" s="12"/>
+      <c r="R486" s="10"/>
     </row>
     <row r="487" spans="15:18">
-      <c r="O487" s="7"/>
-      <c r="P487" s="13"/>
-      <c r="R487" s="11"/>
+      <c r="O487" s="6"/>
+      <c r="P487" s="12"/>
+      <c r="R487" s="10"/>
     </row>
     <row r="488" spans="15:18">
-      <c r="O488" s="7"/>
-      <c r="P488" s="13"/>
-      <c r="R488" s="11"/>
+      <c r="O488" s="6"/>
+      <c r="P488" s="12"/>
+      <c r="R488" s="10"/>
     </row>
     <row r="489" spans="15:18">
-      <c r="O489" s="7"/>
-      <c r="P489" s="13"/>
-      <c r="R489" s="11"/>
+      <c r="O489" s="6"/>
+      <c r="P489" s="12"/>
+      <c r="R489" s="10"/>
     </row>
     <row r="490" spans="15:18">
-      <c r="O490" s="7"/>
-      <c r="P490" s="13"/>
-      <c r="R490" s="11"/>
+      <c r="O490" s="6"/>
+      <c r="P490" s="12"/>
+      <c r="R490" s="10"/>
     </row>
     <row r="491" spans="15:18">
-      <c r="O491" s="7"/>
-      <c r="P491" s="13"/>
-      <c r="R491" s="11"/>
+      <c r="O491" s="6"/>
+      <c r="P491" s="12"/>
+      <c r="R491" s="10"/>
     </row>
     <row r="492" spans="15:18">
-      <c r="O492" s="7"/>
-      <c r="P492" s="13"/>
-      <c r="R492" s="11"/>
+      <c r="O492" s="6"/>
+      <c r="P492" s="12"/>
+      <c r="R492" s="10"/>
     </row>
     <row r="493" spans="15:18">
-      <c r="O493" s="7"/>
-      <c r="P493" s="13"/>
-      <c r="R493" s="11"/>
+      <c r="O493" s="6"/>
+      <c r="P493" s="12"/>
+      <c r="R493" s="10"/>
     </row>
     <row r="494" spans="15:18">
-      <c r="O494" s="7"/>
-      <c r="P494" s="13"/>
-      <c r="R494" s="11"/>
+      <c r="O494" s="6"/>
+      <c r="P494" s="12"/>
+      <c r="R494" s="10"/>
     </row>
     <row r="495" spans="15:18">
-      <c r="O495" s="7"/>
-      <c r="P495" s="13"/>
-      <c r="R495" s="11"/>
+      <c r="O495" s="6"/>
+      <c r="P495" s="12"/>
+      <c r="R495" s="10"/>
     </row>
     <row r="496" spans="15:18">
-      <c r="O496" s="7"/>
-      <c r="P496" s="13"/>
-      <c r="R496" s="11"/>
+      <c r="O496" s="6"/>
+      <c r="P496" s="12"/>
+      <c r="R496" s="10"/>
     </row>
     <row r="497" spans="15:18">
-      <c r="O497" s="7"/>
-      <c r="P497" s="13"/>
-      <c r="R497" s="11"/>
+      <c r="O497" s="6"/>
+      <c r="P497" s="12"/>
+      <c r="R497" s="10"/>
     </row>
     <row r="498" spans="15:18">
-      <c r="O498" s="7"/>
-      <c r="P498" s="13"/>
-      <c r="R498" s="11"/>
+      <c r="O498" s="6"/>
+      <c r="P498" s="12"/>
+      <c r="R498" s="10"/>
     </row>
     <row r="499" spans="15:18">
-      <c r="O499" s="7"/>
-      <c r="P499" s="13"/>
-      <c r="R499" s="11"/>
+      <c r="O499" s="6"/>
+      <c r="P499" s="12"/>
+      <c r="R499" s="10"/>
     </row>
     <row r="500" spans="15:18">
-      <c r="O500" s="7"/>
-      <c r="P500" s="13"/>
-      <c r="R500" s="11"/>
+      <c r="O500" s="6"/>
+      <c r="P500" s="12"/>
+      <c r="R500" s="10"/>
     </row>
     <row r="501" spans="15:18">
-      <c r="O501" s="7"/>
-      <c r="P501" s="13"/>
-      <c r="R501" s="11"/>
+      <c r="O501" s="6"/>
+      <c r="P501" s="12"/>
+      <c r="R501" s="10"/>
     </row>
     <row r="502" spans="15:18">
-      <c r="O502" s="7"/>
-      <c r="P502" s="13"/>
-      <c r="R502" s="11"/>
+      <c r="O502" s="6"/>
+      <c r="P502" s="12"/>
+      <c r="R502" s="10"/>
     </row>
     <row r="503" spans="15:18">
-      <c r="O503" s="7"/>
-      <c r="P503" s="13"/>
-      <c r="R503" s="11"/>
+      <c r="O503" s="6"/>
+      <c r="P503" s="12"/>
+      <c r="R503" s="10"/>
     </row>
     <row r="504" spans="15:18">
-      <c r="O504" s="7"/>
-      <c r="P504" s="13"/>
-      <c r="R504" s="11"/>
+      <c r="O504" s="6"/>
+      <c r="P504" s="12"/>
+      <c r="R504" s="10"/>
     </row>
     <row r="505" spans="15:18">
-      <c r="O505" s="7"/>
-      <c r="P505" s="13"/>
-      <c r="R505" s="11"/>
+      <c r="O505" s="6"/>
+      <c r="P505" s="12"/>
+      <c r="R505" s="10"/>
     </row>
     <row r="506" spans="15:18">
-      <c r="O506" s="7"/>
-      <c r="P506" s="13"/>
-      <c r="R506" s="11"/>
+      <c r="O506" s="6"/>
+      <c r="P506" s="12"/>
+      <c r="R506" s="10"/>
     </row>
     <row r="507" spans="15:18">
-      <c r="O507" s="7"/>
-      <c r="P507" s="13"/>
-      <c r="R507" s="11"/>
+      <c r="O507" s="6"/>
+      <c r="P507" s="12"/>
+      <c r="R507" s="10"/>
     </row>
     <row r="508" spans="15:18">
-      <c r="O508" s="7"/>
-      <c r="P508" s="13"/>
-      <c r="R508" s="11"/>
+      <c r="O508" s="6"/>
+      <c r="P508" s="12"/>
+      <c r="R508" s="10"/>
     </row>
     <row r="509" spans="15:18">
-      <c r="O509" s="7"/>
-      <c r="P509" s="13"/>
-      <c r="R509" s="11"/>
+      <c r="O509" s="6"/>
+      <c r="P509" s="12"/>
+      <c r="R509" s="10"/>
     </row>
     <row r="510" spans="15:18">
-      <c r="O510" s="7"/>
-      <c r="P510" s="13"/>
-      <c r="R510" s="11"/>
+      <c r="O510" s="6"/>
+      <c r="P510" s="12"/>
+      <c r="R510" s="10"/>
     </row>
     <row r="511" spans="15:18">
-      <c r="O511" s="7"/>
-      <c r="P511" s="13"/>
-      <c r="R511" s="11"/>
+      <c r="O511" s="6"/>
+      <c r="P511" s="12"/>
+      <c r="R511" s="10"/>
     </row>
     <row r="512" spans="15:18">
-      <c r="O512" s="7"/>
-      <c r="P512" s="13"/>
-      <c r="R512" s="11"/>
+      <c r="O512" s="6"/>
+      <c r="P512" s="12"/>
+      <c r="R512" s="10"/>
     </row>
     <row r="513" spans="15:18">
-      <c r="O513" s="7"/>
-      <c r="P513" s="13"/>
-      <c r="R513" s="11"/>
+      <c r="O513" s="6"/>
+      <c r="P513" s="12"/>
+      <c r="R513" s="10"/>
     </row>
     <row r="514" spans="15:18">
-      <c r="O514" s="7"/>
-      <c r="P514" s="13"/>
-      <c r="R514" s="11"/>
+      <c r="O514" s="6"/>
+      <c r="P514" s="12"/>
+      <c r="R514" s="10"/>
     </row>
     <row r="515" spans="15:18">
-      <c r="O515" s="7"/>
-      <c r="P515" s="13"/>
-      <c r="R515" s="11"/>
+      <c r="O515" s="6"/>
+      <c r="P515" s="12"/>
+      <c r="R515" s="10"/>
     </row>
     <row r="516" spans="15:18">
-      <c r="O516" s="7"/>
-      <c r="P516" s="13"/>
-      <c r="R516" s="11"/>
+      <c r="O516" s="6"/>
+      <c r="P516" s="12"/>
+      <c r="R516" s="10"/>
     </row>
     <row r="517" spans="15:18">
-      <c r="O517" s="7"/>
-      <c r="P517" s="13"/>
-      <c r="R517" s="11"/>
+      <c r="O517" s="6"/>
+      <c r="P517" s="12"/>
+      <c r="R517" s="10"/>
     </row>
     <row r="518" spans="15:18">
-      <c r="O518" s="7"/>
-      <c r="P518" s="13"/>
-      <c r="R518" s="11"/>
+      <c r="O518" s="6"/>
+      <c r="P518" s="12"/>
+      <c r="R518" s="10"/>
     </row>
     <row r="519" spans="15:18">
-      <c r="P519" s="13"/>
-      <c r="R519" s="11"/>
+      <c r="P519" s="12"/>
+      <c r="R519" s="10"/>
     </row>
     <row r="520" spans="15:18">
-      <c r="P520" s="13"/>
-      <c r="R520" s="11"/>
+      <c r="P520" s="12"/>
+      <c r="R520" s="10"/>
     </row>
     <row r="521" spans="15:18">
-      <c r="R521" s="11"/>
+      <c r="R521" s="10"/>
     </row>
     <row r="522" spans="15:18">
-      <c r="R522" s="11"/>
+      <c r="R522" s="10"/>
     </row>
     <row r="523" spans="15:18">
-      <c r="R523" s="11"/>
+      <c r="R523" s="10"/>
     </row>
     <row r="524" spans="15:18">
-      <c r="R524" s="11"/>
+      <c r="R524" s="10"/>
     </row>
     <row r="525" spans="15:18">
-      <c r="R525" s="11"/>
+      <c r="R525" s="10"/>
     </row>
     <row r="526" spans="15:18">
-      <c r="R526" s="11"/>
+      <c r="R526" s="10"/>
     </row>
     <row r="527" spans="15:18">
-      <c r="R527" s="11"/>
+      <c r="R527" s="10"/>
     </row>
     <row r="528" spans="15:18">
-      <c r="R528" s="11"/>
+      <c r="R528" s="10"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="6">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R527:R528" xr:uid="{709BC68A-C242-4787-A4C8-EA4F2DF4203E}">
       <formula1>IF($O527="Tiktok", R527&lt;&gt;"", TRUE)</formula1>

--- a/public/Ananbay_template.xlsx
+++ b/public/Ananbay_template.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vscode\teb-express\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C6A995-9972-4D83-9FDF-EFB37AF65754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0411E34A-2DBD-4995-9346-52AA88E8FC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>Order ID</t>
   </si>
@@ -96,9 +83,6 @@
   </si>
   <si>
     <t>Số lượng item</t>
-  </si>
-  <si>
-    <t>Giá tiền</t>
   </si>
   <si>
     <t>321075232</t>
@@ -191,13 +175,20 @@
   <si>
     <t>YES</t>
   </si>
+  <si>
+    <t>Tổng giá tiền</t>
+  </si>
+  <si>
+    <t>Bảo hiểm hàng 
+(10% giá trị cột W)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="General\,"/>
+    <numFmt numFmtId="164" formatCode="General\,"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -291,56 +282,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -620,135 +608,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V528"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <dimension ref="A1:W528"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="11.21875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="19.21875" style="5" customWidth="1"/>
-    <col min="13" max="13" width="8.6640625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9.21875" style="5" customWidth="1"/>
-    <col min="16" max="16" width="13.21875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="32.109375" style="17" customWidth="1"/>
-    <col min="18" max="18" width="16.44140625" style="5" customWidth="1"/>
-    <col min="19" max="19" width="6.21875" style="4" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14" style="5" customWidth="1"/>
-    <col min="22" max="22" width="8" style="5" customWidth="1"/>
-    <col min="23" max="1023" width="8.6640625" style="5"/>
-    <col min="1024" max="1024" width="11.5546875" style="5" customWidth="1"/>
-    <col min="1025" max="16384" width="8.6640625" style="5"/>
+    <col min="1" max="1" width="22.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="9.28515625" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" customWidth="1"/>
+    <col min="17" max="17" width="32.140625" style="14" customWidth="1"/>
+    <col min="18" max="18" width="16.42578125" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" style="4" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" style="4" customWidth="1"/>
+    <col min="21" max="21" width="30.5703125" style="4" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" customWidth="1"/>
+    <col min="1024" max="1024" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="22" customFormat="1">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:23" s="19" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="R1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="T1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="22" t="s">
+      <c r="U1" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="V1" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="22" t="s">
+      <c r="W1" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="11" t="s">
+      <c r="B2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="L2" s="3">
         <v>120</v>
@@ -763,36 +753,35 @@
         <v>5</v>
       </c>
       <c r="P2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="4"/>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="15.6" customHeight="1">
+      <c r="A3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="4"/>
-      <c r="U2" s="5">
-        <v>1</v>
-      </c>
-      <c r="V2" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="7"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" t="s">
         <v>34</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="L3" s="3">
         <v>90</v>
@@ -807,2639 +796,2630 @@
         <v>7</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="13" t="s">
         <v>36</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>37</v>
       </c>
       <c r="R3" s="4"/>
       <c r="T3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U3" s="5">
+        <v>37</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3">
         <v>2</v>
       </c>
-      <c r="V3" s="5">
+      <c r="W3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="11"/>
+    <row r="4" spans="1:23">
       <c r="P4" s="2"/>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="11"/>
+    <row r="5" spans="1:23">
       <c r="P5" s="2"/>
-      <c r="Q5" s="15"/>
+      <c r="Q5" s="12"/>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="11"/>
+    <row r="6" spans="1:23">
       <c r="P6" s="2"/>
-      <c r="Q6" s="15"/>
+      <c r="Q6" s="12"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="11"/>
+    <row r="7" spans="1:23">
       <c r="P7" s="2"/>
-      <c r="Q7" s="15"/>
+      <c r="Q7" s="12"/>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:23">
       <c r="P8" s="2"/>
-      <c r="Q8" s="15"/>
+      <c r="Q8" s="12"/>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:23">
       <c r="P9" s="2"/>
-      <c r="Q9" s="15"/>
+      <c r="Q9" s="12"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="P10" s="2"/>
-      <c r="Q10" s="15"/>
+      <c r="Q10" s="12"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="P11" s="2"/>
-      <c r="Q11" s="15"/>
+      <c r="Q11" s="12"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:23">
       <c r="P12" s="2"/>
-      <c r="Q12" s="15"/>
+      <c r="Q12" s="12"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:23">
       <c r="P13" s="2"/>
-      <c r="Q13" s="15"/>
+      <c r="Q13" s="12"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:23">
       <c r="P14" s="2"/>
-      <c r="Q14" s="15"/>
+      <c r="Q14" s="12"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:23">
       <c r="P15" s="2"/>
-      <c r="Q15" s="15"/>
+      <c r="Q15" s="12"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:23">
       <c r="P16" s="2"/>
-      <c r="Q16" s="15"/>
+      <c r="Q16" s="12"/>
       <c r="R16" s="4"/>
     </row>
     <row r="17" spans="16:18">
       <c r="P17" s="2"/>
-      <c r="Q17" s="15"/>
+      <c r="Q17" s="12"/>
       <c r="R17" s="4"/>
     </row>
     <row r="18" spans="16:18">
       <c r="P18" s="2"/>
-      <c r="Q18" s="15"/>
+      <c r="Q18" s="12"/>
       <c r="R18" s="4"/>
     </row>
     <row r="19" spans="16:18">
       <c r="P19" s="2"/>
-      <c r="Q19" s="15"/>
+      <c r="Q19" s="12"/>
       <c r="R19" s="4"/>
     </row>
     <row r="20" spans="16:18">
       <c r="P20" s="2"/>
-      <c r="Q20" s="15"/>
+      <c r="Q20" s="12"/>
       <c r="R20" s="4"/>
     </row>
     <row r="21" spans="16:18">
       <c r="P21" s="2"/>
-      <c r="Q21" s="15"/>
+      <c r="Q21" s="12"/>
       <c r="R21" s="4"/>
     </row>
     <row r="22" spans="16:18">
       <c r="P22" s="2"/>
-      <c r="Q22" s="15"/>
+      <c r="Q22" s="12"/>
       <c r="R22" s="4"/>
     </row>
     <row r="23" spans="16:18">
       <c r="P23" s="2"/>
-      <c r="Q23" s="15"/>
+      <c r="Q23" s="12"/>
       <c r="R23" s="4"/>
     </row>
     <row r="24" spans="16:18">
       <c r="P24" s="2"/>
-      <c r="Q24" s="15"/>
+      <c r="Q24" s="12"/>
       <c r="R24" s="4"/>
     </row>
     <row r="25" spans="16:18">
       <c r="P25" s="2"/>
-      <c r="Q25" s="15"/>
+      <c r="Q25" s="12"/>
       <c r="R25" s="4"/>
     </row>
     <row r="26" spans="16:18">
       <c r="P26" s="2"/>
-      <c r="Q26" s="15"/>
+      <c r="Q26" s="12"/>
       <c r="R26" s="4"/>
     </row>
     <row r="27" spans="16:18">
       <c r="P27" s="2"/>
-      <c r="Q27" s="15"/>
+      <c r="Q27" s="12"/>
       <c r="R27" s="4"/>
     </row>
     <row r="28" spans="16:18">
       <c r="P28" s="2"/>
-      <c r="Q28" s="15"/>
+      <c r="Q28" s="12"/>
       <c r="R28" s="4"/>
     </row>
     <row r="29" spans="16:18">
       <c r="P29" s="2"/>
-      <c r="Q29" s="15"/>
+      <c r="Q29" s="12"/>
       <c r="R29" s="4"/>
     </row>
     <row r="30" spans="16:18">
       <c r="P30" s="2"/>
-      <c r="Q30" s="15"/>
+      <c r="Q30" s="12"/>
       <c r="R30" s="4"/>
     </row>
     <row r="31" spans="16:18">
       <c r="P31" s="2"/>
-      <c r="Q31" s="15"/>
+      <c r="Q31" s="12"/>
       <c r="R31" s="4"/>
     </row>
     <row r="32" spans="16:18">
       <c r="P32" s="2"/>
-      <c r="Q32" s="15"/>
+      <c r="Q32" s="12"/>
       <c r="R32" s="4"/>
     </row>
     <row r="33" spans="16:18">
       <c r="P33" s="2"/>
-      <c r="Q33" s="15"/>
+      <c r="Q33" s="12"/>
       <c r="R33" s="4"/>
     </row>
     <row r="34" spans="16:18">
       <c r="P34" s="2"/>
-      <c r="Q34" s="15"/>
+      <c r="Q34" s="12"/>
       <c r="R34" s="4"/>
     </row>
     <row r="35" spans="16:18">
       <c r="P35" s="2"/>
-      <c r="Q35" s="15"/>
+      <c r="Q35" s="12"/>
       <c r="R35" s="4"/>
     </row>
     <row r="36" spans="16:18">
       <c r="P36" s="2"/>
-      <c r="Q36" s="15"/>
+      <c r="Q36" s="12"/>
       <c r="R36" s="4"/>
     </row>
     <row r="37" spans="16:18">
       <c r="P37" s="2"/>
-      <c r="Q37" s="15"/>
+      <c r="Q37" s="12"/>
       <c r="R37" s="4"/>
     </row>
     <row r="38" spans="16:18">
       <c r="P38" s="2"/>
-      <c r="Q38" s="15"/>
+      <c r="Q38" s="12"/>
       <c r="R38" s="4"/>
     </row>
     <row r="39" spans="16:18">
       <c r="P39" s="2"/>
-      <c r="Q39" s="15"/>
+      <c r="Q39" s="12"/>
       <c r="R39" s="4"/>
     </row>
     <row r="40" spans="16:18">
       <c r="P40" s="2"/>
-      <c r="Q40" s="15"/>
+      <c r="Q40" s="12"/>
       <c r="R40" s="4"/>
     </row>
     <row r="41" spans="16:18">
       <c r="P41" s="2"/>
-      <c r="Q41" s="15"/>
+      <c r="Q41" s="12"/>
       <c r="R41" s="4"/>
     </row>
     <row r="42" spans="16:18">
       <c r="P42" s="2"/>
-      <c r="Q42" s="15"/>
+      <c r="Q42" s="12"/>
       <c r="R42" s="4"/>
     </row>
     <row r="43" spans="16:18">
       <c r="P43" s="2"/>
-      <c r="Q43" s="15"/>
+      <c r="Q43" s="12"/>
       <c r="R43" s="4"/>
     </row>
     <row r="44" spans="16:18">
       <c r="P44" s="2"/>
-      <c r="Q44" s="15"/>
+      <c r="Q44" s="12"/>
       <c r="R44" s="4"/>
     </row>
     <row r="45" spans="16:18">
       <c r="P45" s="2"/>
-      <c r="Q45" s="15"/>
+      <c r="Q45" s="12"/>
       <c r="R45" s="4"/>
     </row>
     <row r="46" spans="16:18">
       <c r="P46" s="2"/>
-      <c r="Q46" s="15"/>
+      <c r="Q46" s="12"/>
       <c r="R46" s="4"/>
     </row>
     <row r="47" spans="16:18">
       <c r="P47" s="2"/>
-      <c r="Q47" s="15"/>
+      <c r="Q47" s="12"/>
       <c r="R47" s="4"/>
     </row>
     <row r="48" spans="16:18">
       <c r="P48" s="2"/>
-      <c r="Q48" s="15"/>
+      <c r="Q48" s="12"/>
       <c r="R48" s="4"/>
     </row>
     <row r="49" spans="16:18">
       <c r="P49" s="2"/>
-      <c r="Q49" s="15"/>
+      <c r="Q49" s="12"/>
       <c r="R49" s="4"/>
     </row>
     <row r="50" spans="16:18">
       <c r="P50" s="2"/>
-      <c r="Q50" s="15"/>
+      <c r="Q50" s="12"/>
       <c r="R50" s="4"/>
     </row>
     <row r="51" spans="16:18">
       <c r="P51" s="2"/>
-      <c r="Q51" s="15"/>
+      <c r="Q51" s="12"/>
       <c r="R51" s="4"/>
     </row>
     <row r="52" spans="16:18">
       <c r="P52" s="2"/>
-      <c r="Q52" s="15"/>
+      <c r="Q52" s="12"/>
       <c r="R52" s="4"/>
     </row>
     <row r="53" spans="16:18">
       <c r="P53" s="2"/>
-      <c r="Q53" s="15"/>
+      <c r="Q53" s="12"/>
       <c r="R53" s="4"/>
     </row>
     <row r="54" spans="16:18">
       <c r="P54" s="2"/>
-      <c r="Q54" s="15"/>
+      <c r="Q54" s="12"/>
       <c r="R54" s="4"/>
     </row>
     <row r="55" spans="16:18">
       <c r="P55" s="2"/>
-      <c r="Q55" s="15"/>
+      <c r="Q55" s="12"/>
       <c r="R55" s="4"/>
     </row>
     <row r="56" spans="16:18">
       <c r="P56" s="2"/>
-      <c r="Q56" s="15"/>
+      <c r="Q56" s="12"/>
       <c r="R56" s="4"/>
     </row>
     <row r="57" spans="16:18">
       <c r="P57" s="2"/>
-      <c r="Q57" s="15"/>
+      <c r="Q57" s="12"/>
       <c r="R57" s="4"/>
     </row>
     <row r="58" spans="16:18">
       <c r="P58" s="2"/>
-      <c r="Q58" s="15"/>
+      <c r="Q58" s="12"/>
       <c r="R58" s="4"/>
     </row>
     <row r="59" spans="16:18">
       <c r="P59" s="2"/>
-      <c r="Q59" s="15"/>
+      <c r="Q59" s="12"/>
       <c r="R59" s="4"/>
     </row>
     <row r="60" spans="16:18">
       <c r="P60" s="2"/>
-      <c r="Q60" s="15"/>
+      <c r="Q60" s="12"/>
       <c r="R60" s="4"/>
     </row>
     <row r="61" spans="16:18">
       <c r="P61" s="2"/>
-      <c r="Q61" s="15"/>
+      <c r="Q61" s="12"/>
       <c r="R61" s="4"/>
     </row>
     <row r="62" spans="16:18">
       <c r="P62" s="2"/>
-      <c r="Q62" s="15"/>
+      <c r="Q62" s="12"/>
       <c r="R62" s="4"/>
     </row>
     <row r="63" spans="16:18">
       <c r="P63" s="2"/>
-      <c r="Q63" s="15"/>
+      <c r="Q63" s="12"/>
       <c r="R63" s="4"/>
     </row>
     <row r="64" spans="16:18">
       <c r="P64" s="2"/>
-      <c r="Q64" s="15"/>
+      <c r="Q64" s="12"/>
       <c r="R64" s="4"/>
     </row>
     <row r="65" spans="16:18">
       <c r="P65" s="2"/>
-      <c r="Q65" s="15"/>
+      <c r="Q65" s="12"/>
       <c r="R65" s="4"/>
     </row>
     <row r="66" spans="16:18">
       <c r="P66" s="2"/>
-      <c r="Q66" s="15"/>
+      <c r="Q66" s="12"/>
       <c r="R66" s="4"/>
     </row>
     <row r="67" spans="16:18">
       <c r="P67" s="2"/>
-      <c r="Q67" s="15"/>
+      <c r="Q67" s="12"/>
       <c r="R67" s="4"/>
     </row>
     <row r="68" spans="16:18">
       <c r="P68" s="2"/>
-      <c r="Q68" s="15"/>
+      <c r="Q68" s="12"/>
       <c r="R68" s="4"/>
     </row>
     <row r="69" spans="16:18">
       <c r="P69" s="2"/>
-      <c r="Q69" s="15"/>
+      <c r="Q69" s="12"/>
       <c r="R69" s="4"/>
     </row>
     <row r="70" spans="16:18">
       <c r="P70" s="2"/>
-      <c r="Q70" s="15"/>
+      <c r="Q70" s="12"/>
       <c r="R70" s="4"/>
     </row>
     <row r="71" spans="16:18">
       <c r="P71" s="2"/>
-      <c r="Q71" s="15"/>
+      <c r="Q71" s="12"/>
       <c r="R71" s="4"/>
     </row>
     <row r="72" spans="16:18">
       <c r="P72" s="2"/>
-      <c r="Q72" s="15"/>
+      <c r="Q72" s="12"/>
       <c r="R72" s="4"/>
     </row>
     <row r="73" spans="16:18">
       <c r="P73" s="2"/>
-      <c r="Q73" s="15"/>
+      <c r="Q73" s="12"/>
       <c r="R73" s="4"/>
     </row>
     <row r="74" spans="16:18">
       <c r="P74" s="2"/>
-      <c r="Q74" s="15"/>
+      <c r="Q74" s="12"/>
       <c r="R74" s="4"/>
     </row>
     <row r="75" spans="16:18">
       <c r="P75" s="2"/>
-      <c r="Q75" s="15"/>
+      <c r="Q75" s="12"/>
       <c r="R75" s="4"/>
     </row>
     <row r="76" spans="16:18">
       <c r="P76" s="2"/>
-      <c r="Q76" s="15"/>
+      <c r="Q76" s="12"/>
       <c r="R76" s="4"/>
     </row>
     <row r="77" spans="16:18">
       <c r="P77" s="2"/>
-      <c r="Q77" s="15"/>
+      <c r="Q77" s="12"/>
       <c r="R77" s="4"/>
     </row>
     <row r="78" spans="16:18">
       <c r="P78" s="2"/>
-      <c r="Q78" s="15"/>
+      <c r="Q78" s="12"/>
       <c r="R78" s="4"/>
     </row>
     <row r="79" spans="16:18">
       <c r="P79" s="2"/>
-      <c r="Q79" s="15"/>
+      <c r="Q79" s="12"/>
       <c r="R79" s="4"/>
     </row>
     <row r="80" spans="16:18">
       <c r="P80" s="2"/>
-      <c r="Q80" s="15"/>
+      <c r="Q80" s="12"/>
       <c r="R80" s="4"/>
     </row>
     <row r="81" spans="16:18">
       <c r="P81" s="2"/>
-      <c r="Q81" s="15"/>
+      <c r="Q81" s="12"/>
       <c r="R81" s="4"/>
     </row>
     <row r="82" spans="16:18">
       <c r="P82" s="2"/>
-      <c r="Q82" s="15"/>
+      <c r="Q82" s="12"/>
       <c r="R82" s="4"/>
     </row>
     <row r="83" spans="16:18">
       <c r="P83" s="2"/>
-      <c r="Q83" s="15"/>
+      <c r="Q83" s="12"/>
       <c r="R83" s="4"/>
     </row>
     <row r="84" spans="16:18">
       <c r="P84" s="2"/>
-      <c r="Q84" s="15"/>
+      <c r="Q84" s="12"/>
       <c r="R84" s="4"/>
     </row>
     <row r="85" spans="16:18">
       <c r="P85" s="2"/>
-      <c r="Q85" s="15"/>
+      <c r="Q85" s="12"/>
       <c r="R85" s="4"/>
     </row>
     <row r="86" spans="16:18">
       <c r="P86" s="2"/>
-      <c r="Q86" s="15"/>
+      <c r="Q86" s="12"/>
       <c r="R86" s="4"/>
     </row>
     <row r="87" spans="16:18">
       <c r="P87" s="2"/>
-      <c r="Q87" s="15"/>
+      <c r="Q87" s="12"/>
       <c r="R87" s="4"/>
     </row>
     <row r="88" spans="16:18">
       <c r="P88" s="2"/>
-      <c r="Q88" s="15"/>
+      <c r="Q88" s="12"/>
       <c r="R88" s="4"/>
     </row>
     <row r="89" spans="16:18">
       <c r="P89" s="2"/>
-      <c r="Q89" s="15"/>
+      <c r="Q89" s="12"/>
       <c r="R89" s="4"/>
     </row>
     <row r="90" spans="16:18">
       <c r="P90" s="2"/>
-      <c r="Q90" s="15"/>
+      <c r="Q90" s="12"/>
       <c r="R90" s="4"/>
     </row>
     <row r="91" spans="16:18">
       <c r="P91" s="2"/>
-      <c r="Q91" s="15"/>
+      <c r="Q91" s="12"/>
       <c r="R91" s="4"/>
     </row>
     <row r="92" spans="16:18">
       <c r="P92" s="2"/>
-      <c r="Q92" s="15"/>
+      <c r="Q92" s="12"/>
       <c r="R92" s="4"/>
     </row>
     <row r="93" spans="16:18">
       <c r="P93" s="2"/>
-      <c r="Q93" s="15"/>
+      <c r="Q93" s="12"/>
       <c r="R93" s="4"/>
     </row>
     <row r="94" spans="16:18">
       <c r="P94" s="2"/>
-      <c r="Q94" s="15"/>
+      <c r="Q94" s="12"/>
       <c r="R94" s="4"/>
     </row>
     <row r="95" spans="16:18">
       <c r="P95" s="2"/>
-      <c r="Q95" s="15"/>
+      <c r="Q95" s="12"/>
       <c r="R95" s="4"/>
     </row>
     <row r="96" spans="16:18">
       <c r="P96" s="2"/>
-      <c r="Q96" s="15"/>
+      <c r="Q96" s="12"/>
       <c r="R96" s="4"/>
     </row>
     <row r="97" spans="16:18">
       <c r="P97" s="2"/>
-      <c r="Q97" s="15"/>
+      <c r="Q97" s="12"/>
       <c r="R97" s="4"/>
     </row>
     <row r="98" spans="16:18">
       <c r="P98" s="2"/>
-      <c r="Q98" s="15"/>
+      <c r="Q98" s="12"/>
       <c r="R98" s="4"/>
     </row>
     <row r="99" spans="16:18">
       <c r="P99" s="2"/>
-      <c r="Q99" s="15"/>
+      <c r="Q99" s="12"/>
       <c r="R99" s="4"/>
     </row>
     <row r="100" spans="16:18">
       <c r="P100" s="2"/>
-      <c r="Q100" s="15"/>
+      <c r="Q100" s="12"/>
       <c r="R100" s="4"/>
     </row>
     <row r="101" spans="16:18">
       <c r="P101" s="2"/>
-      <c r="Q101" s="15"/>
+      <c r="Q101" s="12"/>
       <c r="R101" s="4"/>
     </row>
     <row r="102" spans="16:18">
       <c r="P102" s="2"/>
-      <c r="Q102" s="15"/>
+      <c r="Q102" s="12"/>
       <c r="R102" s="4"/>
     </row>
     <row r="103" spans="16:18">
       <c r="P103" s="2"/>
-      <c r="Q103" s="15"/>
+      <c r="Q103" s="12"/>
       <c r="R103" s="4"/>
     </row>
     <row r="104" spans="16:18">
       <c r="P104" s="2"/>
-      <c r="Q104" s="15"/>
+      <c r="Q104" s="12"/>
       <c r="R104" s="4"/>
     </row>
     <row r="105" spans="16:18">
       <c r="P105" s="2"/>
-      <c r="Q105" s="15"/>
+      <c r="Q105" s="12"/>
       <c r="R105" s="4"/>
     </row>
     <row r="106" spans="16:18">
       <c r="P106" s="2"/>
-      <c r="Q106" s="15"/>
+      <c r="Q106" s="12"/>
       <c r="R106" s="4"/>
     </row>
     <row r="107" spans="16:18">
       <c r="P107" s="2"/>
-      <c r="Q107" s="15"/>
+      <c r="Q107" s="12"/>
       <c r="R107" s="4"/>
     </row>
     <row r="108" spans="16:18">
       <c r="P108" s="2"/>
-      <c r="Q108" s="15"/>
+      <c r="Q108" s="12"/>
       <c r="R108" s="4"/>
     </row>
     <row r="109" spans="16:18">
       <c r="P109" s="2"/>
-      <c r="Q109" s="15"/>
+      <c r="Q109" s="12"/>
       <c r="R109" s="4"/>
     </row>
     <row r="110" spans="16:18">
       <c r="P110" s="2"/>
-      <c r="Q110" s="15"/>
+      <c r="Q110" s="12"/>
       <c r="R110" s="4"/>
     </row>
     <row r="111" spans="16:18">
       <c r="P111" s="2"/>
-      <c r="Q111" s="15"/>
+      <c r="Q111" s="12"/>
       <c r="R111" s="4"/>
     </row>
     <row r="112" spans="16:18">
       <c r="P112" s="2"/>
-      <c r="Q112" s="15"/>
+      <c r="Q112" s="12"/>
       <c r="R112" s="4"/>
     </row>
     <row r="113" spans="16:18">
       <c r="P113" s="2"/>
-      <c r="Q113" s="15"/>
+      <c r="Q113" s="12"/>
       <c r="R113" s="4"/>
     </row>
     <row r="114" spans="16:18">
       <c r="P114" s="2"/>
-      <c r="Q114" s="15"/>
+      <c r="Q114" s="12"/>
       <c r="R114" s="4"/>
     </row>
     <row r="115" spans="16:18">
       <c r="P115" s="2"/>
-      <c r="Q115" s="15"/>
+      <c r="Q115" s="12"/>
       <c r="R115" s="4"/>
     </row>
     <row r="116" spans="16:18">
       <c r="P116" s="2"/>
-      <c r="Q116" s="15"/>
+      <c r="Q116" s="12"/>
       <c r="R116" s="4"/>
     </row>
     <row r="117" spans="16:18">
       <c r="P117" s="2"/>
-      <c r="Q117" s="15"/>
+      <c r="Q117" s="12"/>
       <c r="R117" s="4"/>
     </row>
     <row r="118" spans="16:18">
       <c r="P118" s="2"/>
-      <c r="Q118" s="15"/>
+      <c r="Q118" s="12"/>
       <c r="R118" s="4"/>
     </row>
     <row r="119" spans="16:18">
       <c r="P119" s="2"/>
-      <c r="Q119" s="15"/>
+      <c r="Q119" s="12"/>
       <c r="R119" s="4"/>
     </row>
     <row r="120" spans="16:18">
       <c r="P120" s="2"/>
-      <c r="Q120" s="15"/>
+      <c r="Q120" s="12"/>
       <c r="R120" s="4"/>
     </row>
     <row r="121" spans="16:18">
       <c r="P121" s="2"/>
-      <c r="Q121" s="15"/>
+      <c r="Q121" s="12"/>
       <c r="R121" s="4"/>
     </row>
     <row r="122" spans="16:18">
       <c r="P122" s="2"/>
-      <c r="Q122" s="15"/>
+      <c r="Q122" s="12"/>
       <c r="R122" s="4"/>
     </row>
     <row r="123" spans="16:18">
       <c r="P123" s="2"/>
-      <c r="Q123" s="15"/>
+      <c r="Q123" s="12"/>
       <c r="R123" s="4"/>
     </row>
     <row r="124" spans="16:18">
       <c r="P124" s="2"/>
-      <c r="Q124" s="15"/>
+      <c r="Q124" s="12"/>
       <c r="R124" s="4"/>
     </row>
     <row r="125" spans="16:18">
       <c r="P125" s="2"/>
-      <c r="Q125" s="15"/>
+      <c r="Q125" s="12"/>
       <c r="R125" s="4"/>
     </row>
     <row r="126" spans="16:18">
       <c r="P126" s="2"/>
-      <c r="Q126" s="15"/>
+      <c r="Q126" s="12"/>
       <c r="R126" s="4"/>
     </row>
     <row r="127" spans="16:18">
       <c r="P127" s="2"/>
-      <c r="Q127" s="15"/>
+      <c r="Q127" s="12"/>
       <c r="R127" s="4"/>
     </row>
     <row r="128" spans="16:18">
       <c r="P128" s="2"/>
-      <c r="Q128" s="15"/>
+      <c r="Q128" s="12"/>
       <c r="R128" s="4"/>
     </row>
     <row r="129" spans="16:18">
       <c r="P129" s="2"/>
-      <c r="Q129" s="15"/>
+      <c r="Q129" s="12"/>
       <c r="R129" s="4"/>
     </row>
     <row r="130" spans="16:18">
       <c r="P130" s="2"/>
-      <c r="Q130" s="15"/>
+      <c r="Q130" s="12"/>
       <c r="R130" s="4"/>
     </row>
     <row r="131" spans="16:18">
       <c r="P131" s="2"/>
-      <c r="Q131" s="15"/>
+      <c r="Q131" s="12"/>
       <c r="R131" s="4"/>
     </row>
     <row r="132" spans="16:18">
       <c r="P132" s="2"/>
-      <c r="Q132" s="15"/>
+      <c r="Q132" s="12"/>
       <c r="R132" s="4"/>
     </row>
     <row r="133" spans="16:18">
       <c r="P133" s="2"/>
-      <c r="Q133" s="15"/>
+      <c r="Q133" s="12"/>
       <c r="R133" s="4"/>
     </row>
     <row r="134" spans="16:18">
       <c r="P134" s="2"/>
-      <c r="Q134" s="15"/>
+      <c r="Q134" s="12"/>
       <c r="R134" s="4"/>
     </row>
     <row r="135" spans="16:18">
       <c r="P135" s="2"/>
-      <c r="Q135" s="15"/>
+      <c r="Q135" s="12"/>
       <c r="R135" s="4"/>
     </row>
     <row r="136" spans="16:18">
       <c r="P136" s="2"/>
-      <c r="Q136" s="15"/>
+      <c r="Q136" s="12"/>
       <c r="R136" s="4"/>
     </row>
     <row r="137" spans="16:18">
       <c r="P137" s="2"/>
-      <c r="Q137" s="15"/>
+      <c r="Q137" s="12"/>
       <c r="R137" s="4"/>
     </row>
     <row r="138" spans="16:18">
       <c r="P138" s="2"/>
-      <c r="Q138" s="15"/>
+      <c r="Q138" s="12"/>
       <c r="R138" s="4"/>
     </row>
     <row r="139" spans="16:18">
       <c r="P139" s="2"/>
-      <c r="Q139" s="15"/>
+      <c r="Q139" s="12"/>
       <c r="R139" s="4"/>
     </row>
     <row r="140" spans="16:18">
       <c r="P140" s="2"/>
-      <c r="Q140" s="15"/>
+      <c r="Q140" s="12"/>
       <c r="R140" s="4"/>
     </row>
     <row r="141" spans="16:18">
       <c r="P141" s="2"/>
-      <c r="Q141" s="15"/>
+      <c r="Q141" s="12"/>
       <c r="R141" s="4"/>
     </row>
     <row r="142" spans="16:18">
       <c r="P142" s="2"/>
-      <c r="Q142" s="15"/>
+      <c r="Q142" s="12"/>
       <c r="R142" s="4"/>
     </row>
     <row r="143" spans="16:18">
       <c r="P143" s="2"/>
-      <c r="Q143" s="15"/>
+      <c r="Q143" s="12"/>
       <c r="R143" s="4"/>
     </row>
     <row r="144" spans="16:18">
       <c r="P144" s="2"/>
-      <c r="Q144" s="15"/>
+      <c r="Q144" s="12"/>
       <c r="R144" s="4"/>
     </row>
     <row r="145" spans="16:18">
       <c r="P145" s="2"/>
-      <c r="Q145" s="15"/>
+      <c r="Q145" s="12"/>
       <c r="R145" s="4"/>
     </row>
     <row r="146" spans="16:18">
       <c r="P146" s="2"/>
-      <c r="Q146" s="15"/>
+      <c r="Q146" s="12"/>
       <c r="R146" s="4"/>
     </row>
     <row r="147" spans="16:18">
       <c r="P147" s="2"/>
-      <c r="Q147" s="15"/>
+      <c r="Q147" s="12"/>
       <c r="R147" s="4"/>
     </row>
     <row r="148" spans="16:18">
       <c r="P148" s="2"/>
-      <c r="Q148" s="15"/>
+      <c r="Q148" s="12"/>
       <c r="R148" s="4"/>
     </row>
     <row r="149" spans="16:18">
       <c r="P149" s="2"/>
-      <c r="Q149" s="15"/>
+      <c r="Q149" s="12"/>
       <c r="R149" s="4"/>
     </row>
     <row r="150" spans="16:18">
       <c r="P150" s="2"/>
-      <c r="Q150" s="15"/>
+      <c r="Q150" s="12"/>
       <c r="R150" s="4"/>
     </row>
     <row r="151" spans="16:18">
       <c r="P151" s="2"/>
-      <c r="Q151" s="15"/>
+      <c r="Q151" s="12"/>
       <c r="R151" s="4"/>
     </row>
     <row r="152" spans="16:18">
       <c r="P152" s="2"/>
-      <c r="Q152" s="15"/>
+      <c r="Q152" s="12"/>
       <c r="R152" s="4"/>
     </row>
     <row r="153" spans="16:18">
       <c r="P153" s="2"/>
-      <c r="Q153" s="15"/>
+      <c r="Q153" s="12"/>
       <c r="R153" s="4"/>
     </row>
     <row r="154" spans="16:18">
       <c r="P154" s="2"/>
-      <c r="Q154" s="15"/>
+      <c r="Q154" s="12"/>
       <c r="R154" s="4"/>
     </row>
     <row r="155" spans="16:18">
       <c r="P155" s="2"/>
-      <c r="Q155" s="15"/>
+      <c r="Q155" s="12"/>
       <c r="R155" s="4"/>
     </row>
     <row r="156" spans="16:18">
       <c r="P156" s="2"/>
-      <c r="Q156" s="15"/>
+      <c r="Q156" s="12"/>
       <c r="R156" s="4"/>
     </row>
     <row r="157" spans="16:18">
       <c r="P157" s="2"/>
-      <c r="Q157" s="15"/>
+      <c r="Q157" s="12"/>
       <c r="R157" s="4"/>
     </row>
     <row r="158" spans="16:18">
       <c r="P158" s="2"/>
-      <c r="Q158" s="15"/>
+      <c r="Q158" s="12"/>
       <c r="R158" s="4"/>
     </row>
     <row r="159" spans="16:18">
       <c r="P159" s="2"/>
-      <c r="Q159" s="15"/>
+      <c r="Q159" s="12"/>
       <c r="R159" s="4"/>
     </row>
     <row r="160" spans="16:18">
       <c r="P160" s="2"/>
-      <c r="Q160" s="15"/>
+      <c r="Q160" s="12"/>
       <c r="R160" s="4"/>
     </row>
     <row r="161" spans="16:18">
       <c r="P161" s="2"/>
-      <c r="Q161" s="15"/>
+      <c r="Q161" s="12"/>
       <c r="R161" s="4"/>
     </row>
     <row r="162" spans="16:18">
       <c r="P162" s="2"/>
-      <c r="Q162" s="15"/>
+      <c r="Q162" s="12"/>
       <c r="R162" s="4"/>
     </row>
     <row r="163" spans="16:18">
       <c r="P163" s="2"/>
-      <c r="Q163" s="15"/>
+      <c r="Q163" s="12"/>
       <c r="R163" s="4"/>
     </row>
     <row r="164" spans="16:18">
       <c r="P164" s="2"/>
-      <c r="Q164" s="15"/>
+      <c r="Q164" s="12"/>
       <c r="R164" s="4"/>
     </row>
     <row r="165" spans="16:18">
       <c r="P165" s="2"/>
-      <c r="Q165" s="15"/>
+      <c r="Q165" s="12"/>
       <c r="R165" s="4"/>
     </row>
     <row r="166" spans="16:18">
       <c r="P166" s="2"/>
-      <c r="Q166" s="15"/>
+      <c r="Q166" s="12"/>
       <c r="R166" s="4"/>
     </row>
     <row r="167" spans="16:18">
       <c r="P167" s="2"/>
-      <c r="Q167" s="15"/>
+      <c r="Q167" s="12"/>
       <c r="R167" s="4"/>
     </row>
     <row r="168" spans="16:18">
       <c r="P168" s="2"/>
-      <c r="Q168" s="15"/>
+      <c r="Q168" s="12"/>
       <c r="R168" s="4"/>
     </row>
     <row r="169" spans="16:18">
       <c r="P169" s="2"/>
-      <c r="Q169" s="15"/>
+      <c r="Q169" s="12"/>
       <c r="R169" s="4"/>
     </row>
     <row r="170" spans="16:18">
       <c r="P170" s="2"/>
-      <c r="Q170" s="15"/>
+      <c r="Q170" s="12"/>
       <c r="R170" s="4"/>
     </row>
     <row r="171" spans="16:18">
       <c r="P171" s="2"/>
-      <c r="Q171" s="15"/>
+      <c r="Q171" s="12"/>
       <c r="R171" s="4"/>
     </row>
     <row r="172" spans="16:18">
       <c r="P172" s="2"/>
-      <c r="Q172" s="15"/>
+      <c r="Q172" s="12"/>
       <c r="R172" s="4"/>
     </row>
     <row r="173" spans="16:18">
       <c r="P173" s="2"/>
-      <c r="Q173" s="15"/>
+      <c r="Q173" s="12"/>
       <c r="R173" s="4"/>
     </row>
     <row r="174" spans="16:18">
       <c r="P174" s="2"/>
-      <c r="Q174" s="15"/>
+      <c r="Q174" s="12"/>
       <c r="R174" s="4"/>
     </row>
     <row r="175" spans="16:18">
       <c r="P175" s="2"/>
-      <c r="Q175" s="15"/>
+      <c r="Q175" s="12"/>
       <c r="R175" s="4"/>
     </row>
     <row r="176" spans="16:18">
       <c r="P176" s="2"/>
-      <c r="Q176" s="15"/>
+      <c r="Q176" s="12"/>
       <c r="R176" s="4"/>
     </row>
     <row r="177" spans="16:18">
       <c r="P177" s="2"/>
-      <c r="Q177" s="15"/>
+      <c r="Q177" s="12"/>
       <c r="R177" s="4"/>
     </row>
     <row r="178" spans="16:18">
       <c r="P178" s="2"/>
-      <c r="Q178" s="15"/>
+      <c r="Q178" s="12"/>
       <c r="R178" s="4"/>
     </row>
     <row r="179" spans="16:18">
       <c r="P179" s="2"/>
-      <c r="Q179" s="15"/>
+      <c r="Q179" s="12"/>
       <c r="R179" s="4"/>
     </row>
     <row r="180" spans="16:18">
       <c r="P180" s="2"/>
-      <c r="Q180" s="15"/>
+      <c r="Q180" s="12"/>
       <c r="R180" s="4"/>
     </row>
     <row r="181" spans="16:18">
       <c r="P181" s="2"/>
-      <c r="Q181" s="15"/>
+      <c r="Q181" s="12"/>
       <c r="R181" s="4"/>
     </row>
     <row r="182" spans="16:18">
       <c r="P182" s="2"/>
-      <c r="Q182" s="15"/>
+      <c r="Q182" s="12"/>
       <c r="R182" s="4"/>
     </row>
     <row r="183" spans="16:18">
       <c r="P183" s="2"/>
-      <c r="Q183" s="15"/>
+      <c r="Q183" s="12"/>
       <c r="R183" s="4"/>
     </row>
     <row r="184" spans="16:18">
       <c r="P184" s="2"/>
-      <c r="Q184" s="15"/>
+      <c r="Q184" s="12"/>
       <c r="R184" s="4"/>
     </row>
     <row r="185" spans="16:18">
       <c r="P185" s="2"/>
-      <c r="Q185" s="15"/>
+      <c r="Q185" s="12"/>
       <c r="R185" s="4"/>
     </row>
     <row r="186" spans="16:18">
       <c r="P186" s="2"/>
-      <c r="Q186" s="15"/>
+      <c r="Q186" s="12"/>
       <c r="R186" s="4"/>
     </row>
     <row r="187" spans="16:18">
       <c r="P187" s="2"/>
-      <c r="Q187" s="15"/>
+      <c r="Q187" s="12"/>
       <c r="R187" s="4"/>
     </row>
     <row r="188" spans="16:18">
       <c r="P188" s="2"/>
-      <c r="Q188" s="15"/>
+      <c r="Q188" s="12"/>
       <c r="R188" s="4"/>
     </row>
     <row r="189" spans="16:18">
       <c r="P189" s="2"/>
-      <c r="Q189" s="15"/>
+      <c r="Q189" s="12"/>
       <c r="R189" s="4"/>
     </row>
     <row r="190" spans="16:18">
       <c r="P190" s="2"/>
-      <c r="Q190" s="15"/>
+      <c r="Q190" s="12"/>
       <c r="R190" s="4"/>
     </row>
     <row r="191" spans="16:18">
       <c r="P191" s="2"/>
-      <c r="Q191" s="15"/>
+      <c r="Q191" s="12"/>
       <c r="R191" s="4"/>
     </row>
     <row r="192" spans="16:18">
       <c r="P192" s="2"/>
-      <c r="Q192" s="15"/>
+      <c r="Q192" s="12"/>
       <c r="R192" s="4"/>
     </row>
     <row r="193" spans="16:18">
       <c r="P193" s="2"/>
-      <c r="Q193" s="15"/>
+      <c r="Q193" s="12"/>
       <c r="R193" s="4"/>
     </row>
     <row r="194" spans="16:18">
       <c r="P194" s="2"/>
-      <c r="Q194" s="15"/>
+      <c r="Q194" s="12"/>
       <c r="R194" s="4"/>
     </row>
     <row r="195" spans="16:18">
       <c r="P195" s="2"/>
-      <c r="Q195" s="15"/>
+      <c r="Q195" s="12"/>
       <c r="R195" s="4"/>
     </row>
     <row r="196" spans="16:18">
       <c r="P196" s="2"/>
-      <c r="Q196" s="15"/>
+      <c r="Q196" s="12"/>
       <c r="R196" s="4"/>
     </row>
     <row r="197" spans="16:18">
       <c r="P197" s="2"/>
-      <c r="Q197" s="15"/>
+      <c r="Q197" s="12"/>
       <c r="R197" s="4"/>
     </row>
     <row r="198" spans="16:18">
       <c r="P198" s="2"/>
-      <c r="Q198" s="15"/>
+      <c r="Q198" s="12"/>
       <c r="R198" s="4"/>
     </row>
     <row r="199" spans="16:18">
       <c r="P199" s="2"/>
-      <c r="Q199" s="15"/>
+      <c r="Q199" s="12"/>
       <c r="R199" s="4"/>
     </row>
     <row r="200" spans="16:18">
       <c r="P200" s="2"/>
-      <c r="Q200" s="15"/>
+      <c r="Q200" s="12"/>
       <c r="R200" s="4"/>
     </row>
     <row r="201" spans="16:18">
       <c r="P201" s="2"/>
-      <c r="Q201" s="15"/>
+      <c r="Q201" s="12"/>
       <c r="R201" s="4"/>
     </row>
     <row r="202" spans="16:18">
       <c r="P202" s="2"/>
-      <c r="Q202" s="15"/>
+      <c r="Q202" s="12"/>
       <c r="R202" s="4"/>
     </row>
     <row r="203" spans="16:18">
       <c r="P203" s="2"/>
-      <c r="Q203" s="15"/>
+      <c r="Q203" s="12"/>
       <c r="R203" s="4"/>
     </row>
     <row r="204" spans="16:18">
       <c r="P204" s="2"/>
-      <c r="Q204" s="15"/>
+      <c r="Q204" s="12"/>
       <c r="R204" s="4"/>
     </row>
     <row r="205" spans="16:18">
       <c r="P205" s="2"/>
-      <c r="Q205" s="15"/>
+      <c r="Q205" s="12"/>
       <c r="R205" s="4"/>
     </row>
     <row r="206" spans="16:18">
       <c r="P206" s="2"/>
-      <c r="Q206" s="15"/>
+      <c r="Q206" s="12"/>
       <c r="R206" s="4"/>
     </row>
     <row r="207" spans="16:18">
       <c r="P207" s="2"/>
-      <c r="Q207" s="15"/>
+      <c r="Q207" s="12"/>
       <c r="R207" s="4"/>
     </row>
     <row r="208" spans="16:18">
       <c r="P208" s="2"/>
-      <c r="Q208" s="15"/>
+      <c r="Q208" s="12"/>
       <c r="R208" s="4"/>
     </row>
     <row r="209" spans="16:18">
       <c r="P209" s="2"/>
-      <c r="Q209" s="15"/>
+      <c r="Q209" s="12"/>
       <c r="R209" s="4"/>
     </row>
     <row r="210" spans="16:18">
       <c r="P210" s="2"/>
-      <c r="Q210" s="15"/>
+      <c r="Q210" s="12"/>
       <c r="R210" s="4"/>
     </row>
     <row r="211" spans="16:18">
       <c r="P211" s="2"/>
-      <c r="Q211" s="15"/>
+      <c r="Q211" s="12"/>
       <c r="R211" s="4"/>
     </row>
     <row r="212" spans="16:18">
       <c r="P212" s="2"/>
-      <c r="Q212" s="15"/>
+      <c r="Q212" s="12"/>
       <c r="R212" s="4"/>
     </row>
     <row r="213" spans="16:18">
       <c r="P213" s="2"/>
-      <c r="Q213" s="15"/>
+      <c r="Q213" s="12"/>
       <c r="R213" s="4"/>
     </row>
     <row r="214" spans="16:18">
       <c r="P214" s="2"/>
-      <c r="Q214" s="15"/>
+      <c r="Q214" s="12"/>
       <c r="R214" s="4"/>
     </row>
     <row r="215" spans="16:18">
       <c r="P215" s="2"/>
-      <c r="Q215" s="15"/>
+      <c r="Q215" s="12"/>
       <c r="R215" s="4"/>
     </row>
     <row r="216" spans="16:18">
       <c r="P216" s="2"/>
-      <c r="Q216" s="15"/>
+      <c r="Q216" s="12"/>
       <c r="R216" s="4"/>
     </row>
     <row r="217" spans="16:18">
       <c r="P217" s="2"/>
-      <c r="Q217" s="15"/>
+      <c r="Q217" s="12"/>
       <c r="R217" s="4"/>
     </row>
     <row r="218" spans="16:18">
       <c r="P218" s="2"/>
-      <c r="Q218" s="15"/>
+      <c r="Q218" s="12"/>
       <c r="R218" s="4"/>
     </row>
     <row r="219" spans="16:18">
       <c r="P219" s="2"/>
-      <c r="Q219" s="15"/>
+      <c r="Q219" s="12"/>
       <c r="R219" s="4"/>
     </row>
     <row r="220" spans="16:18">
       <c r="P220" s="2"/>
-      <c r="Q220" s="15"/>
+      <c r="Q220" s="12"/>
       <c r="R220" s="4"/>
     </row>
     <row r="221" spans="16:18">
       <c r="P221" s="2"/>
-      <c r="Q221" s="15"/>
+      <c r="Q221" s="12"/>
       <c r="R221" s="4"/>
     </row>
     <row r="222" spans="16:18">
       <c r="P222" s="2"/>
-      <c r="Q222" s="15"/>
+      <c r="Q222" s="12"/>
       <c r="R222" s="4"/>
     </row>
     <row r="223" spans="16:18">
       <c r="P223" s="2"/>
-      <c r="Q223" s="15"/>
+      <c r="Q223" s="12"/>
       <c r="R223" s="4"/>
     </row>
     <row r="224" spans="16:18">
       <c r="P224" s="2"/>
-      <c r="Q224" s="15"/>
+      <c r="Q224" s="12"/>
       <c r="R224" s="4"/>
     </row>
     <row r="225" spans="16:18">
       <c r="P225" s="2"/>
-      <c r="Q225" s="15"/>
+      <c r="Q225" s="12"/>
       <c r="R225" s="4"/>
     </row>
     <row r="226" spans="16:18">
       <c r="P226" s="2"/>
-      <c r="Q226" s="15"/>
+      <c r="Q226" s="12"/>
       <c r="R226" s="4"/>
     </row>
     <row r="227" spans="16:18">
       <c r="P227" s="2"/>
-      <c r="Q227" s="15"/>
+      <c r="Q227" s="12"/>
       <c r="R227" s="4"/>
     </row>
     <row r="228" spans="16:18">
       <c r="P228" s="2"/>
-      <c r="Q228" s="15"/>
+      <c r="Q228" s="12"/>
       <c r="R228" s="4"/>
     </row>
     <row r="229" spans="16:18">
       <c r="P229" s="2"/>
-      <c r="Q229" s="15"/>
+      <c r="Q229" s="12"/>
       <c r="R229" s="4"/>
     </row>
     <row r="230" spans="16:18">
       <c r="P230" s="2"/>
-      <c r="Q230" s="15"/>
+      <c r="Q230" s="12"/>
       <c r="R230" s="4"/>
     </row>
     <row r="231" spans="16:18">
       <c r="P231" s="2"/>
-      <c r="Q231" s="15"/>
+      <c r="Q231" s="12"/>
       <c r="R231" s="4"/>
     </row>
     <row r="232" spans="16:18">
       <c r="P232" s="2"/>
-      <c r="Q232" s="15"/>
+      <c r="Q232" s="12"/>
       <c r="R232" s="4"/>
     </row>
     <row r="233" spans="16:18">
       <c r="P233" s="2"/>
-      <c r="Q233" s="15"/>
+      <c r="Q233" s="12"/>
       <c r="R233" s="4"/>
     </row>
     <row r="234" spans="16:18">
       <c r="P234" s="2"/>
-      <c r="Q234" s="15"/>
+      <c r="Q234" s="12"/>
       <c r="R234" s="4"/>
     </row>
     <row r="235" spans="16:18">
       <c r="P235" s="2"/>
-      <c r="Q235" s="15"/>
+      <c r="Q235" s="12"/>
       <c r="R235" s="4"/>
     </row>
     <row r="236" spans="16:18">
       <c r="P236" s="2"/>
-      <c r="Q236" s="15"/>
+      <c r="Q236" s="12"/>
       <c r="R236" s="4"/>
     </row>
     <row r="237" spans="16:18">
       <c r="P237" s="2"/>
-      <c r="Q237" s="15"/>
+      <c r="Q237" s="12"/>
       <c r="R237" s="4"/>
     </row>
     <row r="238" spans="16:18">
       <c r="P238" s="2"/>
-      <c r="Q238" s="15"/>
+      <c r="Q238" s="12"/>
       <c r="R238" s="4"/>
     </row>
     <row r="239" spans="16:18">
       <c r="P239" s="2"/>
-      <c r="Q239" s="15"/>
+      <c r="Q239" s="12"/>
       <c r="R239" s="4"/>
     </row>
     <row r="240" spans="16:18">
       <c r="P240" s="2"/>
-      <c r="Q240" s="15"/>
+      <c r="Q240" s="12"/>
       <c r="R240" s="4"/>
     </row>
     <row r="241" spans="16:18">
       <c r="P241" s="2"/>
-      <c r="Q241" s="15"/>
+      <c r="Q241" s="12"/>
       <c r="R241" s="4"/>
     </row>
     <row r="242" spans="16:18">
       <c r="P242" s="2"/>
-      <c r="Q242" s="15"/>
+      <c r="Q242" s="12"/>
       <c r="R242" s="4"/>
     </row>
     <row r="243" spans="16:18">
       <c r="P243" s="2"/>
-      <c r="Q243" s="15"/>
+      <c r="Q243" s="12"/>
       <c r="R243" s="4"/>
     </row>
     <row r="244" spans="16:18">
       <c r="P244" s="2"/>
-      <c r="Q244" s="15"/>
+      <c r="Q244" s="12"/>
       <c r="R244" s="4"/>
     </row>
     <row r="245" spans="16:18">
       <c r="P245" s="2"/>
-      <c r="Q245" s="15"/>
+      <c r="Q245" s="12"/>
       <c r="R245" s="4"/>
     </row>
     <row r="246" spans="16:18">
       <c r="P246" s="2"/>
-      <c r="Q246" s="15"/>
+      <c r="Q246" s="12"/>
       <c r="R246" s="4"/>
     </row>
     <row r="247" spans="16:18">
       <c r="P247" s="2"/>
-      <c r="Q247" s="15"/>
+      <c r="Q247" s="12"/>
       <c r="R247" s="4"/>
     </row>
     <row r="248" spans="16:18">
       <c r="P248" s="2"/>
-      <c r="Q248" s="15"/>
+      <c r="Q248" s="12"/>
       <c r="R248" s="4"/>
     </row>
     <row r="249" spans="16:18">
       <c r="P249" s="2"/>
-      <c r="Q249" s="15"/>
+      <c r="Q249" s="12"/>
       <c r="R249" s="4"/>
     </row>
     <row r="250" spans="16:18">
       <c r="P250" s="2"/>
-      <c r="Q250" s="15"/>
+      <c r="Q250" s="12"/>
       <c r="R250" s="4"/>
     </row>
     <row r="251" spans="16:18">
       <c r="P251" s="2"/>
-      <c r="Q251" s="15"/>
+      <c r="Q251" s="12"/>
       <c r="R251" s="4"/>
     </row>
     <row r="252" spans="16:18">
       <c r="P252" s="2"/>
-      <c r="Q252" s="15"/>
+      <c r="Q252" s="12"/>
       <c r="R252" s="4"/>
     </row>
     <row r="253" spans="16:18">
       <c r="P253" s="2"/>
-      <c r="Q253" s="15"/>
+      <c r="Q253" s="12"/>
       <c r="R253" s="4"/>
     </row>
     <row r="254" spans="16:18">
       <c r="P254" s="2"/>
-      <c r="Q254" s="15"/>
+      <c r="Q254" s="12"/>
       <c r="R254" s="4"/>
     </row>
     <row r="255" spans="16:18">
       <c r="P255" s="2"/>
-      <c r="Q255" s="15"/>
+      <c r="Q255" s="12"/>
       <c r="R255" s="4"/>
     </row>
     <row r="256" spans="16:18">
       <c r="P256" s="2"/>
-      <c r="Q256" s="15"/>
+      <c r="Q256" s="12"/>
       <c r="R256" s="4"/>
     </row>
     <row r="257" spans="16:18">
       <c r="P257" s="2"/>
-      <c r="Q257" s="15"/>
+      <c r="Q257" s="12"/>
       <c r="R257" s="4"/>
     </row>
     <row r="258" spans="16:18">
       <c r="P258" s="2"/>
-      <c r="Q258" s="15"/>
+      <c r="Q258" s="12"/>
       <c r="R258" s="4"/>
     </row>
     <row r="259" spans="16:18">
       <c r="P259" s="2"/>
-      <c r="Q259" s="15"/>
+      <c r="Q259" s="12"/>
       <c r="R259" s="4"/>
     </row>
     <row r="260" spans="16:18">
       <c r="P260" s="2"/>
-      <c r="Q260" s="15"/>
+      <c r="Q260" s="12"/>
       <c r="R260" s="4"/>
     </row>
     <row r="261" spans="16:18">
       <c r="P261" s="2"/>
-      <c r="Q261" s="15"/>
+      <c r="Q261" s="12"/>
       <c r="R261" s="4"/>
     </row>
     <row r="262" spans="16:18">
       <c r="P262" s="2"/>
-      <c r="Q262" s="15"/>
+      <c r="Q262" s="12"/>
       <c r="R262" s="4"/>
     </row>
     <row r="263" spans="16:18">
       <c r="P263" s="2"/>
-      <c r="Q263" s="15"/>
+      <c r="Q263" s="12"/>
       <c r="R263" s="4"/>
     </row>
     <row r="264" spans="16:18">
       <c r="P264" s="2"/>
-      <c r="Q264" s="15"/>
+      <c r="Q264" s="12"/>
       <c r="R264" s="4"/>
     </row>
     <row r="265" spans="16:18">
       <c r="P265" s="2"/>
-      <c r="Q265" s="15"/>
+      <c r="Q265" s="12"/>
       <c r="R265" s="4"/>
     </row>
     <row r="266" spans="16:18">
       <c r="P266" s="2"/>
-      <c r="Q266" s="15"/>
+      <c r="Q266" s="12"/>
       <c r="R266" s="4"/>
     </row>
     <row r="267" spans="16:18">
       <c r="P267" s="2"/>
-      <c r="Q267" s="15"/>
+      <c r="Q267" s="12"/>
       <c r="R267" s="4"/>
     </row>
     <row r="268" spans="16:18">
       <c r="P268" s="2"/>
-      <c r="Q268" s="15"/>
+      <c r="Q268" s="12"/>
       <c r="R268" s="4"/>
     </row>
     <row r="269" spans="16:18">
       <c r="P269" s="2"/>
-      <c r="Q269" s="15"/>
+      <c r="Q269" s="12"/>
       <c r="R269" s="4"/>
     </row>
     <row r="270" spans="16:18">
       <c r="P270" s="2"/>
-      <c r="Q270" s="15"/>
+      <c r="Q270" s="12"/>
       <c r="R270" s="4"/>
     </row>
     <row r="271" spans="16:18">
       <c r="P271" s="2"/>
-      <c r="Q271" s="15"/>
+      <c r="Q271" s="12"/>
       <c r="R271" s="4"/>
     </row>
     <row r="272" spans="16:18">
       <c r="P272" s="2"/>
-      <c r="Q272" s="15"/>
+      <c r="Q272" s="12"/>
       <c r="R272" s="4"/>
     </row>
     <row r="273" spans="16:18">
       <c r="P273" s="2"/>
-      <c r="Q273" s="15"/>
+      <c r="Q273" s="12"/>
       <c r="R273" s="4"/>
     </row>
     <row r="274" spans="16:18">
       <c r="P274" s="2"/>
-      <c r="Q274" s="15"/>
+      <c r="Q274" s="12"/>
       <c r="R274" s="4"/>
     </row>
     <row r="275" spans="16:18">
       <c r="P275" s="2"/>
-      <c r="Q275" s="15"/>
+      <c r="Q275" s="12"/>
       <c r="R275" s="4"/>
     </row>
     <row r="276" spans="16:18">
       <c r="P276" s="2"/>
-      <c r="Q276" s="15"/>
+      <c r="Q276" s="12"/>
       <c r="R276" s="4"/>
     </row>
     <row r="277" spans="16:18">
       <c r="P277" s="2"/>
-      <c r="Q277" s="15"/>
+      <c r="Q277" s="12"/>
       <c r="R277" s="4"/>
     </row>
     <row r="278" spans="16:18">
       <c r="P278" s="2"/>
-      <c r="Q278" s="15"/>
+      <c r="Q278" s="12"/>
       <c r="R278" s="4"/>
     </row>
     <row r="279" spans="16:18">
       <c r="P279" s="2"/>
-      <c r="Q279" s="15"/>
+      <c r="Q279" s="12"/>
       <c r="R279" s="4"/>
     </row>
     <row r="280" spans="16:18">
       <c r="P280" s="2"/>
-      <c r="Q280" s="15"/>
+      <c r="Q280" s="12"/>
       <c r="R280" s="4"/>
     </row>
     <row r="281" spans="16:18">
       <c r="P281" s="2"/>
-      <c r="Q281" s="15"/>
+      <c r="Q281" s="12"/>
       <c r="R281" s="4"/>
     </row>
     <row r="282" spans="16:18">
       <c r="P282" s="2"/>
-      <c r="Q282" s="15"/>
+      <c r="Q282" s="12"/>
       <c r="R282" s="4"/>
     </row>
     <row r="283" spans="16:18">
       <c r="P283" s="2"/>
-      <c r="Q283" s="15"/>
+      <c r="Q283" s="12"/>
       <c r="R283" s="4"/>
     </row>
     <row r="284" spans="16:18">
       <c r="P284" s="2"/>
-      <c r="Q284" s="15"/>
+      <c r="Q284" s="12"/>
       <c r="R284" s="4"/>
     </row>
     <row r="285" spans="16:18">
       <c r="P285" s="2"/>
-      <c r="Q285" s="15"/>
+      <c r="Q285" s="12"/>
       <c r="R285" s="4"/>
     </row>
     <row r="286" spans="16:18">
       <c r="P286" s="2"/>
-      <c r="Q286" s="15"/>
+      <c r="Q286" s="12"/>
       <c r="R286" s="4"/>
     </row>
     <row r="287" spans="16:18">
       <c r="P287" s="2"/>
-      <c r="Q287" s="15"/>
+      <c r="Q287" s="12"/>
       <c r="R287" s="4"/>
     </row>
     <row r="288" spans="16:18">
       <c r="P288" s="2"/>
-      <c r="Q288" s="15"/>
+      <c r="Q288" s="12"/>
       <c r="R288" s="4"/>
     </row>
     <row r="289" spans="16:18">
       <c r="P289" s="2"/>
-      <c r="Q289" s="15"/>
+      <c r="Q289" s="12"/>
       <c r="R289" s="4"/>
     </row>
     <row r="290" spans="16:18">
       <c r="P290" s="2"/>
-      <c r="Q290" s="15"/>
+      <c r="Q290" s="12"/>
       <c r="R290" s="4"/>
     </row>
     <row r="291" spans="16:18">
       <c r="P291" s="2"/>
-      <c r="Q291" s="15"/>
+      <c r="Q291" s="12"/>
       <c r="R291" s="4"/>
     </row>
     <row r="292" spans="16:18">
       <c r="P292" s="2"/>
-      <c r="Q292" s="15"/>
+      <c r="Q292" s="12"/>
       <c r="R292" s="4"/>
     </row>
     <row r="293" spans="16:18">
       <c r="P293" s="2"/>
-      <c r="Q293" s="15"/>
+      <c r="Q293" s="12"/>
       <c r="R293" s="4"/>
     </row>
     <row r="294" spans="16:18">
       <c r="P294" s="2"/>
-      <c r="Q294" s="15"/>
+      <c r="Q294" s="12"/>
       <c r="R294" s="4"/>
     </row>
     <row r="295" spans="16:18">
       <c r="P295" s="2"/>
-      <c r="Q295" s="15"/>
+      <c r="Q295" s="12"/>
       <c r="R295" s="4"/>
     </row>
     <row r="296" spans="16:18">
       <c r="P296" s="2"/>
-      <c r="Q296" s="15"/>
+      <c r="Q296" s="12"/>
       <c r="R296" s="4"/>
     </row>
     <row r="297" spans="16:18">
       <c r="P297" s="2"/>
-      <c r="Q297" s="15"/>
+      <c r="Q297" s="12"/>
       <c r="R297" s="4"/>
     </row>
     <row r="298" spans="16:18">
       <c r="P298" s="2"/>
-      <c r="Q298" s="15"/>
+      <c r="Q298" s="12"/>
       <c r="R298" s="4"/>
     </row>
     <row r="299" spans="16:18">
       <c r="P299" s="2"/>
-      <c r="Q299" s="15"/>
+      <c r="Q299" s="12"/>
       <c r="R299" s="4"/>
     </row>
     <row r="300" spans="16:18">
       <c r="P300" s="2"/>
-      <c r="Q300" s="15"/>
+      <c r="Q300" s="12"/>
       <c r="R300" s="4"/>
     </row>
     <row r="301" spans="16:18">
       <c r="P301" s="2"/>
-      <c r="Q301" s="15"/>
+      <c r="Q301" s="12"/>
       <c r="R301" s="4"/>
     </row>
     <row r="302" spans="16:18">
       <c r="P302" s="2"/>
-      <c r="Q302" s="15"/>
+      <c r="Q302" s="12"/>
       <c r="R302" s="4"/>
     </row>
     <row r="303" spans="16:18">
       <c r="P303" s="2"/>
-      <c r="Q303" s="15"/>
+      <c r="Q303" s="12"/>
       <c r="R303" s="4"/>
     </row>
     <row r="304" spans="16:18">
       <c r="P304" s="2"/>
-      <c r="Q304" s="15"/>
+      <c r="Q304" s="12"/>
       <c r="R304" s="4"/>
     </row>
     <row r="305" spans="16:18">
       <c r="P305" s="2"/>
-      <c r="Q305" s="15"/>
+      <c r="Q305" s="12"/>
       <c r="R305" s="4"/>
     </row>
     <row r="306" spans="16:18">
       <c r="P306" s="2"/>
-      <c r="Q306" s="15"/>
+      <c r="Q306" s="12"/>
       <c r="R306" s="4"/>
     </row>
     <row r="307" spans="16:18">
       <c r="P307" s="2"/>
-      <c r="Q307" s="15"/>
+      <c r="Q307" s="12"/>
       <c r="R307" s="4"/>
     </row>
     <row r="308" spans="16:18">
       <c r="P308" s="2"/>
-      <c r="Q308" s="15"/>
+      <c r="Q308" s="12"/>
       <c r="R308" s="4"/>
     </row>
     <row r="309" spans="16:18">
       <c r="P309" s="2"/>
-      <c r="Q309" s="15"/>
+      <c r="Q309" s="12"/>
       <c r="R309" s="4"/>
     </row>
     <row r="310" spans="16:18">
       <c r="P310" s="2"/>
-      <c r="Q310" s="15"/>
+      <c r="Q310" s="12"/>
       <c r="R310" s="4"/>
     </row>
     <row r="311" spans="16:18">
       <c r="P311" s="2"/>
-      <c r="Q311" s="15"/>
+      <c r="Q311" s="12"/>
       <c r="R311" s="4"/>
     </row>
     <row r="312" spans="16:18">
       <c r="P312" s="2"/>
-      <c r="Q312" s="15"/>
+      <c r="Q312" s="12"/>
       <c r="R312" s="4"/>
     </row>
     <row r="313" spans="16:18">
       <c r="P313" s="2"/>
-      <c r="Q313" s="15"/>
+      <c r="Q313" s="12"/>
       <c r="R313" s="4"/>
     </row>
     <row r="314" spans="16:18">
       <c r="P314" s="2"/>
-      <c r="Q314" s="15"/>
+      <c r="Q314" s="12"/>
       <c r="R314" s="4"/>
     </row>
     <row r="315" spans="16:18">
       <c r="P315" s="2"/>
-      <c r="Q315" s="15"/>
+      <c r="Q315" s="12"/>
       <c r="R315" s="4"/>
     </row>
     <row r="316" spans="16:18">
       <c r="P316" s="2"/>
-      <c r="Q316" s="15"/>
+      <c r="Q316" s="12"/>
       <c r="R316" s="4"/>
     </row>
     <row r="317" spans="16:18">
       <c r="P317" s="2"/>
-      <c r="Q317" s="15"/>
+      <c r="Q317" s="12"/>
       <c r="R317" s="4"/>
     </row>
     <row r="318" spans="16:18">
       <c r="P318" s="2"/>
-      <c r="Q318" s="15"/>
+      <c r="Q318" s="12"/>
       <c r="R318" s="4"/>
     </row>
     <row r="319" spans="16:18">
       <c r="P319" s="2"/>
-      <c r="Q319" s="15"/>
+      <c r="Q319" s="12"/>
       <c r="R319" s="4"/>
     </row>
     <row r="320" spans="16:18">
       <c r="P320" s="2"/>
-      <c r="Q320" s="15"/>
+      <c r="Q320" s="12"/>
       <c r="R320" s="4"/>
     </row>
     <row r="321" spans="16:18">
       <c r="P321" s="2"/>
-      <c r="Q321" s="15"/>
+      <c r="Q321" s="12"/>
       <c r="R321" s="4"/>
     </row>
     <row r="322" spans="16:18">
       <c r="P322" s="2"/>
-      <c r="Q322" s="15"/>
+      <c r="Q322" s="12"/>
       <c r="R322" s="4"/>
     </row>
     <row r="323" spans="16:18">
       <c r="P323" s="2"/>
-      <c r="Q323" s="15"/>
+      <c r="Q323" s="12"/>
       <c r="R323" s="4"/>
     </row>
     <row r="324" spans="16:18">
       <c r="P324" s="2"/>
-      <c r="Q324" s="15"/>
+      <c r="Q324" s="12"/>
       <c r="R324" s="4"/>
     </row>
     <row r="325" spans="16:18">
       <c r="P325" s="2"/>
-      <c r="Q325" s="15"/>
+      <c r="Q325" s="12"/>
       <c r="R325" s="4"/>
     </row>
     <row r="326" spans="16:18">
       <c r="P326" s="2"/>
-      <c r="Q326" s="15"/>
+      <c r="Q326" s="12"/>
       <c r="R326" s="4"/>
     </row>
     <row r="327" spans="16:18">
       <c r="P327" s="2"/>
-      <c r="Q327" s="15"/>
+      <c r="Q327" s="12"/>
       <c r="R327" s="4"/>
     </row>
     <row r="328" spans="16:18">
       <c r="P328" s="2"/>
-      <c r="Q328" s="15"/>
+      <c r="Q328" s="12"/>
       <c r="R328" s="4"/>
     </row>
     <row r="329" spans="16:18">
       <c r="P329" s="2"/>
-      <c r="Q329" s="15"/>
+      <c r="Q329" s="12"/>
       <c r="R329" s="4"/>
     </row>
     <row r="330" spans="16:18">
       <c r="P330" s="2"/>
-      <c r="Q330" s="15"/>
+      <c r="Q330" s="12"/>
       <c r="R330" s="4"/>
     </row>
     <row r="331" spans="16:18">
       <c r="P331" s="2"/>
-      <c r="Q331" s="15"/>
+      <c r="Q331" s="12"/>
       <c r="R331" s="4"/>
     </row>
     <row r="332" spans="16:18">
       <c r="P332" s="2"/>
-      <c r="Q332" s="15"/>
+      <c r="Q332" s="12"/>
       <c r="R332" s="4"/>
     </row>
     <row r="333" spans="16:18">
       <c r="P333" s="2"/>
-      <c r="Q333" s="15"/>
+      <c r="Q333" s="12"/>
       <c r="R333" s="4"/>
     </row>
     <row r="334" spans="16:18">
       <c r="P334" s="2"/>
-      <c r="Q334" s="15"/>
+      <c r="Q334" s="12"/>
       <c r="R334" s="4"/>
     </row>
     <row r="335" spans="16:18">
       <c r="P335" s="2"/>
-      <c r="Q335" s="15"/>
+      <c r="Q335" s="12"/>
       <c r="R335" s="4"/>
     </row>
     <row r="336" spans="16:18">
       <c r="P336" s="2"/>
-      <c r="Q336" s="15"/>
+      <c r="Q336" s="12"/>
       <c r="R336" s="4"/>
     </row>
     <row r="337" spans="16:18">
       <c r="P337" s="2"/>
-      <c r="Q337" s="15"/>
+      <c r="Q337" s="12"/>
       <c r="R337" s="4"/>
     </row>
     <row r="338" spans="16:18">
       <c r="P338" s="2"/>
-      <c r="Q338" s="15"/>
+      <c r="Q338" s="12"/>
       <c r="R338" s="4"/>
     </row>
     <row r="339" spans="16:18">
       <c r="P339" s="2"/>
-      <c r="Q339" s="15"/>
+      <c r="Q339" s="12"/>
       <c r="R339" s="4"/>
     </row>
     <row r="340" spans="16:18">
       <c r="P340" s="2"/>
-      <c r="Q340" s="15"/>
+      <c r="Q340" s="12"/>
       <c r="R340" s="4"/>
     </row>
     <row r="341" spans="16:18">
       <c r="P341" s="2"/>
-      <c r="Q341" s="15"/>
+      <c r="Q341" s="12"/>
       <c r="R341" s="4"/>
     </row>
     <row r="342" spans="16:18">
       <c r="P342" s="2"/>
-      <c r="Q342" s="15"/>
+      <c r="Q342" s="12"/>
       <c r="R342" s="4"/>
     </row>
     <row r="343" spans="16:18">
       <c r="P343" s="2"/>
-      <c r="Q343" s="15"/>
+      <c r="Q343" s="12"/>
       <c r="R343" s="4"/>
     </row>
     <row r="344" spans="16:18">
       <c r="P344" s="2"/>
-      <c r="Q344" s="15"/>
+      <c r="Q344" s="12"/>
       <c r="R344" s="4"/>
     </row>
     <row r="345" spans="16:18">
       <c r="P345" s="2"/>
-      <c r="Q345" s="15"/>
+      <c r="Q345" s="12"/>
       <c r="R345" s="4"/>
     </row>
     <row r="346" spans="16:18">
       <c r="P346" s="2"/>
-      <c r="Q346" s="15"/>
+      <c r="Q346" s="12"/>
       <c r="R346" s="4"/>
     </row>
     <row r="347" spans="16:18">
       <c r="P347" s="2"/>
-      <c r="Q347" s="15"/>
+      <c r="Q347" s="12"/>
       <c r="R347" s="4"/>
     </row>
     <row r="348" spans="16:18">
       <c r="P348" s="2"/>
-      <c r="Q348" s="15"/>
+      <c r="Q348" s="12"/>
       <c r="R348" s="4"/>
     </row>
     <row r="349" spans="16:18">
       <c r="P349" s="2"/>
-      <c r="Q349" s="15"/>
+      <c r="Q349" s="12"/>
       <c r="R349" s="4"/>
     </row>
     <row r="350" spans="16:18">
       <c r="P350" s="2"/>
-      <c r="Q350" s="15"/>
+      <c r="Q350" s="12"/>
       <c r="R350" s="4"/>
     </row>
     <row r="351" spans="16:18">
       <c r="P351" s="2"/>
-      <c r="Q351" s="15"/>
+      <c r="Q351" s="12"/>
       <c r="R351" s="4"/>
     </row>
     <row r="352" spans="16:18">
       <c r="P352" s="2"/>
-      <c r="Q352" s="15"/>
+      <c r="Q352" s="12"/>
       <c r="R352" s="4"/>
     </row>
     <row r="353" spans="16:18">
       <c r="P353" s="2"/>
-      <c r="Q353" s="15"/>
+      <c r="Q353" s="12"/>
       <c r="R353" s="4"/>
     </row>
     <row r="354" spans="16:18">
       <c r="P354" s="2"/>
-      <c r="Q354" s="15"/>
+      <c r="Q354" s="12"/>
       <c r="R354" s="4"/>
     </row>
     <row r="355" spans="16:18">
       <c r="P355" s="2"/>
-      <c r="Q355" s="15"/>
+      <c r="Q355" s="12"/>
       <c r="R355" s="4"/>
     </row>
     <row r="356" spans="16:18">
       <c r="P356" s="2"/>
-      <c r="Q356" s="15"/>
+      <c r="Q356" s="12"/>
       <c r="R356" s="4"/>
     </row>
     <row r="357" spans="16:18">
       <c r="P357" s="2"/>
-      <c r="Q357" s="15"/>
+      <c r="Q357" s="12"/>
       <c r="R357" s="4"/>
     </row>
     <row r="358" spans="16:18">
       <c r="P358" s="2"/>
-      <c r="Q358" s="15"/>
+      <c r="Q358" s="12"/>
       <c r="R358" s="4"/>
     </row>
     <row r="359" spans="16:18">
       <c r="P359" s="2"/>
-      <c r="Q359" s="15"/>
+      <c r="Q359" s="12"/>
       <c r="R359" s="4"/>
     </row>
     <row r="360" spans="16:18">
       <c r="P360" s="2"/>
-      <c r="Q360" s="15"/>
+      <c r="Q360" s="12"/>
       <c r="R360" s="4"/>
     </row>
     <row r="361" spans="16:18">
       <c r="P361" s="2"/>
-      <c r="Q361" s="15"/>
+      <c r="Q361" s="12"/>
       <c r="R361" s="4"/>
     </row>
     <row r="362" spans="16:18">
       <c r="P362" s="2"/>
-      <c r="Q362" s="15"/>
+      <c r="Q362" s="12"/>
       <c r="R362" s="4"/>
     </row>
     <row r="363" spans="16:18">
       <c r="P363" s="2"/>
-      <c r="Q363" s="15"/>
+      <c r="Q363" s="12"/>
       <c r="R363" s="4"/>
     </row>
     <row r="364" spans="16:18">
       <c r="P364" s="2"/>
-      <c r="Q364" s="15"/>
+      <c r="Q364" s="12"/>
       <c r="R364" s="4"/>
     </row>
     <row r="365" spans="16:18">
       <c r="P365" s="2"/>
-      <c r="Q365" s="15"/>
+      <c r="Q365" s="12"/>
       <c r="R365" s="4"/>
     </row>
     <row r="366" spans="16:18">
       <c r="P366" s="2"/>
-      <c r="Q366" s="15"/>
+      <c r="Q366" s="12"/>
       <c r="R366" s="4"/>
     </row>
     <row r="367" spans="16:18">
       <c r="P367" s="2"/>
-      <c r="Q367" s="15"/>
+      <c r="Q367" s="12"/>
       <c r="R367" s="4"/>
     </row>
     <row r="368" spans="16:18">
       <c r="P368" s="2"/>
-      <c r="Q368" s="15"/>
+      <c r="Q368" s="12"/>
       <c r="R368" s="4"/>
     </row>
     <row r="369" spans="16:18">
       <c r="P369" s="2"/>
-      <c r="Q369" s="15"/>
+      <c r="Q369" s="12"/>
       <c r="R369" s="4"/>
     </row>
     <row r="370" spans="16:18">
       <c r="P370" s="2"/>
-      <c r="Q370" s="15"/>
+      <c r="Q370" s="12"/>
       <c r="R370" s="4"/>
     </row>
     <row r="371" spans="16:18">
       <c r="P371" s="2"/>
-      <c r="Q371" s="15"/>
+      <c r="Q371" s="12"/>
       <c r="R371" s="4"/>
     </row>
     <row r="372" spans="16:18">
       <c r="P372" s="2"/>
-      <c r="Q372" s="15"/>
+      <c r="Q372" s="12"/>
       <c r="R372" s="4"/>
     </row>
     <row r="373" spans="16:18">
       <c r="P373" s="2"/>
-      <c r="Q373" s="15"/>
+      <c r="Q373" s="12"/>
       <c r="R373" s="4"/>
     </row>
     <row r="374" spans="16:18">
       <c r="P374" s="2"/>
-      <c r="Q374" s="15"/>
+      <c r="Q374" s="12"/>
       <c r="R374" s="4"/>
     </row>
     <row r="375" spans="16:18">
       <c r="P375" s="2"/>
-      <c r="Q375" s="15"/>
+      <c r="Q375" s="12"/>
       <c r="R375" s="4"/>
     </row>
     <row r="376" spans="16:18">
       <c r="P376" s="2"/>
-      <c r="Q376" s="15"/>
+      <c r="Q376" s="12"/>
       <c r="R376" s="4"/>
     </row>
     <row r="377" spans="16:18">
       <c r="P377" s="2"/>
-      <c r="Q377" s="15"/>
+      <c r="Q377" s="12"/>
       <c r="R377" s="4"/>
     </row>
     <row r="378" spans="16:18">
       <c r="P378" s="2"/>
-      <c r="Q378" s="15"/>
+      <c r="Q378" s="12"/>
       <c r="R378" s="4"/>
     </row>
     <row r="379" spans="16:18">
       <c r="P379" s="2"/>
-      <c r="Q379" s="15"/>
+      <c r="Q379" s="12"/>
       <c r="R379" s="4"/>
     </row>
     <row r="380" spans="16:18">
       <c r="P380" s="2"/>
-      <c r="Q380" s="15"/>
+      <c r="Q380" s="12"/>
       <c r="R380" s="4"/>
     </row>
     <row r="381" spans="16:18">
       <c r="P381" s="2"/>
-      <c r="Q381" s="15"/>
+      <c r="Q381" s="12"/>
       <c r="R381" s="4"/>
     </row>
     <row r="382" spans="16:18">
       <c r="P382" s="2"/>
-      <c r="Q382" s="15"/>
+      <c r="Q382" s="12"/>
       <c r="R382" s="4"/>
     </row>
     <row r="383" spans="16:18">
       <c r="P383" s="2"/>
-      <c r="Q383" s="15"/>
+      <c r="Q383" s="12"/>
       <c r="R383" s="4"/>
     </row>
     <row r="384" spans="16:18">
       <c r="P384" s="2"/>
-      <c r="Q384" s="15"/>
+      <c r="Q384" s="12"/>
       <c r="R384" s="4"/>
     </row>
     <row r="385" spans="16:18">
       <c r="P385" s="2"/>
-      <c r="Q385" s="15"/>
+      <c r="Q385" s="12"/>
       <c r="R385" s="4"/>
     </row>
     <row r="386" spans="16:18">
       <c r="P386" s="2"/>
-      <c r="Q386" s="15"/>
+      <c r="Q386" s="12"/>
       <c r="R386" s="4"/>
     </row>
     <row r="387" spans="16:18">
       <c r="P387" s="2"/>
-      <c r="Q387" s="15"/>
+      <c r="Q387" s="12"/>
       <c r="R387" s="4"/>
     </row>
     <row r="388" spans="16:18">
       <c r="P388" s="2"/>
-      <c r="Q388" s="15"/>
+      <c r="Q388" s="12"/>
       <c r="R388" s="4"/>
     </row>
     <row r="389" spans="16:18">
       <c r="P389" s="2"/>
-      <c r="Q389" s="15"/>
+      <c r="Q389" s="12"/>
       <c r="R389" s="4"/>
     </row>
     <row r="390" spans="16:18">
       <c r="P390" s="2"/>
-      <c r="Q390" s="15"/>
+      <c r="Q390" s="12"/>
       <c r="R390" s="4"/>
     </row>
     <row r="391" spans="16:18">
       <c r="P391" s="2"/>
-      <c r="Q391" s="15"/>
+      <c r="Q391" s="12"/>
       <c r="R391" s="4"/>
     </row>
     <row r="392" spans="16:18">
       <c r="P392" s="2"/>
-      <c r="Q392" s="15"/>
+      <c r="Q392" s="12"/>
       <c r="R392" s="4"/>
     </row>
     <row r="393" spans="16:18">
       <c r="P393" s="2"/>
-      <c r="Q393" s="15"/>
+      <c r="Q393" s="12"/>
       <c r="R393" s="4"/>
     </row>
     <row r="394" spans="16:18">
       <c r="P394" s="2"/>
-      <c r="Q394" s="15"/>
+      <c r="Q394" s="12"/>
       <c r="R394" s="4"/>
     </row>
     <row r="395" spans="16:18">
       <c r="P395" s="2"/>
-      <c r="Q395" s="15"/>
+      <c r="Q395" s="12"/>
       <c r="R395" s="4"/>
     </row>
     <row r="396" spans="16:18">
       <c r="P396" s="2"/>
-      <c r="Q396" s="15"/>
+      <c r="Q396" s="12"/>
       <c r="R396" s="4"/>
     </row>
     <row r="397" spans="16:18">
       <c r="P397" s="2"/>
-      <c r="Q397" s="15"/>
+      <c r="Q397" s="12"/>
       <c r="R397" s="4"/>
     </row>
     <row r="398" spans="16:18">
       <c r="P398" s="2"/>
-      <c r="Q398" s="15"/>
+      <c r="Q398" s="12"/>
       <c r="R398" s="4"/>
     </row>
     <row r="399" spans="16:18">
       <c r="P399" s="2"/>
-      <c r="Q399" s="15"/>
+      <c r="Q399" s="12"/>
       <c r="R399" s="4"/>
     </row>
     <row r="400" spans="16:18">
       <c r="P400" s="2"/>
-      <c r="Q400" s="15"/>
+      <c r="Q400" s="12"/>
       <c r="R400" s="4"/>
     </row>
     <row r="401" spans="16:18">
       <c r="P401" s="2"/>
-      <c r="Q401" s="15"/>
+      <c r="Q401" s="12"/>
       <c r="R401" s="4"/>
     </row>
     <row r="402" spans="16:18">
       <c r="P402" s="2"/>
-      <c r="Q402" s="15"/>
+      <c r="Q402" s="12"/>
       <c r="R402" s="4"/>
     </row>
     <row r="403" spans="16:18">
       <c r="P403" s="2"/>
-      <c r="Q403" s="15"/>
+      <c r="Q403" s="12"/>
       <c r="R403" s="4"/>
     </row>
     <row r="404" spans="16:18">
       <c r="P404" s="2"/>
-      <c r="Q404" s="15"/>
+      <c r="Q404" s="12"/>
       <c r="R404" s="4"/>
     </row>
     <row r="405" spans="16:18">
       <c r="P405" s="2"/>
-      <c r="Q405" s="15"/>
+      <c r="Q405" s="12"/>
       <c r="R405" s="4"/>
     </row>
     <row r="406" spans="16:18">
       <c r="P406" s="2"/>
-      <c r="Q406" s="15"/>
+      <c r="Q406" s="12"/>
       <c r="R406" s="4"/>
     </row>
     <row r="407" spans="16:18">
       <c r="P407" s="2"/>
-      <c r="Q407" s="15"/>
+      <c r="Q407" s="12"/>
       <c r="R407" s="4"/>
     </row>
     <row r="408" spans="16:18">
       <c r="P408" s="2"/>
-      <c r="Q408" s="15"/>
+      <c r="Q408" s="12"/>
       <c r="R408" s="4"/>
     </row>
     <row r="409" spans="16:18">
       <c r="P409" s="2"/>
-      <c r="Q409" s="15"/>
+      <c r="Q409" s="12"/>
       <c r="R409" s="4"/>
     </row>
     <row r="410" spans="16:18">
       <c r="P410" s="2"/>
-      <c r="Q410" s="15"/>
+      <c r="Q410" s="12"/>
       <c r="R410" s="4"/>
     </row>
     <row r="411" spans="16:18">
       <c r="P411" s="2"/>
-      <c r="Q411" s="15"/>
+      <c r="Q411" s="12"/>
       <c r="R411" s="4"/>
     </row>
     <row r="412" spans="16:18">
       <c r="P412" s="2"/>
-      <c r="Q412" s="15"/>
+      <c r="Q412" s="12"/>
       <c r="R412" s="4"/>
     </row>
     <row r="413" spans="16:18">
       <c r="P413" s="2"/>
-      <c r="Q413" s="15"/>
+      <c r="Q413" s="12"/>
       <c r="R413" s="4"/>
     </row>
     <row r="414" spans="16:18">
       <c r="P414" s="2"/>
-      <c r="Q414" s="15"/>
+      <c r="Q414" s="12"/>
       <c r="R414" s="4"/>
     </row>
     <row r="415" spans="16:18">
       <c r="P415" s="2"/>
-      <c r="Q415" s="15"/>
+      <c r="Q415" s="12"/>
       <c r="R415" s="4"/>
     </row>
     <row r="416" spans="16:18">
       <c r="P416" s="2"/>
-      <c r="Q416" s="15"/>
+      <c r="Q416" s="12"/>
       <c r="R416" s="4"/>
     </row>
     <row r="417" spans="16:18">
       <c r="P417" s="2"/>
-      <c r="Q417" s="15"/>
+      <c r="Q417" s="12"/>
       <c r="R417" s="4"/>
     </row>
     <row r="418" spans="16:18">
       <c r="P418" s="2"/>
-      <c r="Q418" s="15"/>
+      <c r="Q418" s="12"/>
       <c r="R418" s="4"/>
     </row>
     <row r="419" spans="16:18">
       <c r="P419" s="2"/>
-      <c r="Q419" s="15"/>
+      <c r="Q419" s="12"/>
       <c r="R419" s="4"/>
     </row>
     <row r="420" spans="16:18">
       <c r="P420" s="2"/>
-      <c r="Q420" s="15"/>
+      <c r="Q420" s="12"/>
       <c r="R420" s="4"/>
     </row>
     <row r="421" spans="16:18">
       <c r="P421" s="2"/>
-      <c r="Q421" s="15"/>
+      <c r="Q421" s="12"/>
       <c r="R421" s="4"/>
     </row>
     <row r="422" spans="16:18">
       <c r="P422" s="2"/>
-      <c r="Q422" s="15"/>
+      <c r="Q422" s="12"/>
       <c r="R422" s="4"/>
     </row>
     <row r="423" spans="16:18">
       <c r="P423" s="2"/>
-      <c r="Q423" s="15"/>
+      <c r="Q423" s="12"/>
       <c r="R423" s="4"/>
     </row>
     <row r="424" spans="16:18">
       <c r="P424" s="2"/>
-      <c r="Q424" s="15"/>
+      <c r="Q424" s="12"/>
       <c r="R424" s="4"/>
     </row>
     <row r="425" spans="16:18">
       <c r="P425" s="2"/>
-      <c r="Q425" s="15"/>
+      <c r="Q425" s="12"/>
       <c r="R425" s="4"/>
     </row>
     <row r="426" spans="16:18">
       <c r="P426" s="2"/>
-      <c r="Q426" s="15"/>
+      <c r="Q426" s="12"/>
       <c r="R426" s="4"/>
     </row>
     <row r="427" spans="16:18">
       <c r="P427" s="2"/>
-      <c r="Q427" s="15"/>
+      <c r="Q427" s="12"/>
       <c r="R427" s="4"/>
     </row>
     <row r="428" spans="16:18">
       <c r="P428" s="2"/>
-      <c r="Q428" s="15"/>
+      <c r="Q428" s="12"/>
       <c r="R428" s="4"/>
     </row>
     <row r="429" spans="16:18">
       <c r="P429" s="2"/>
-      <c r="Q429" s="15"/>
+      <c r="Q429" s="12"/>
       <c r="R429" s="4"/>
     </row>
     <row r="430" spans="16:18">
       <c r="P430" s="2"/>
-      <c r="Q430" s="15"/>
+      <c r="Q430" s="12"/>
       <c r="R430" s="4"/>
     </row>
     <row r="431" spans="16:18">
       <c r="P431" s="2"/>
-      <c r="Q431" s="15"/>
+      <c r="Q431" s="12"/>
       <c r="R431" s="4"/>
     </row>
     <row r="432" spans="16:18">
       <c r="P432" s="2"/>
-      <c r="Q432" s="15"/>
+      <c r="Q432" s="12"/>
       <c r="R432" s="4"/>
     </row>
     <row r="433" spans="16:18">
       <c r="P433" s="2"/>
-      <c r="Q433" s="15"/>
+      <c r="Q433" s="12"/>
       <c r="R433" s="4"/>
     </row>
     <row r="434" spans="16:18">
       <c r="P434" s="2"/>
-      <c r="Q434" s="15"/>
+      <c r="Q434" s="12"/>
       <c r="R434" s="4"/>
     </row>
     <row r="435" spans="16:18">
       <c r="P435" s="2"/>
-      <c r="Q435" s="15"/>
+      <c r="Q435" s="12"/>
       <c r="R435" s="4"/>
     </row>
     <row r="436" spans="16:18">
       <c r="P436" s="2"/>
-      <c r="Q436" s="15"/>
+      <c r="Q436" s="12"/>
       <c r="R436" s="4"/>
     </row>
     <row r="437" spans="16:18">
       <c r="P437" s="2"/>
-      <c r="Q437" s="15"/>
+      <c r="Q437" s="12"/>
       <c r="R437" s="4"/>
     </row>
     <row r="438" spans="16:18">
       <c r="P438" s="2"/>
-      <c r="Q438" s="15"/>
+      <c r="Q438" s="12"/>
       <c r="R438" s="4"/>
     </row>
     <row r="439" spans="16:18">
       <c r="P439" s="2"/>
-      <c r="Q439" s="15"/>
+      <c r="Q439" s="12"/>
       <c r="R439" s="4"/>
     </row>
     <row r="440" spans="16:18">
       <c r="P440" s="2"/>
-      <c r="Q440" s="15"/>
+      <c r="Q440" s="12"/>
       <c r="R440" s="4"/>
     </row>
     <row r="441" spans="16:18">
       <c r="P441" s="2"/>
-      <c r="Q441" s="15"/>
+      <c r="Q441" s="12"/>
       <c r="R441" s="4"/>
     </row>
     <row r="442" spans="16:18">
       <c r="P442" s="2"/>
-      <c r="Q442" s="15"/>
+      <c r="Q442" s="12"/>
       <c r="R442" s="4"/>
     </row>
     <row r="443" spans="16:18">
       <c r="P443" s="2"/>
-      <c r="Q443" s="15"/>
+      <c r="Q443" s="12"/>
       <c r="R443" s="4"/>
     </row>
     <row r="444" spans="16:18">
       <c r="P444" s="2"/>
-      <c r="Q444" s="15"/>
+      <c r="Q444" s="12"/>
       <c r="R444" s="4"/>
     </row>
     <row r="445" spans="16:18">
       <c r="P445" s="2"/>
-      <c r="Q445" s="15"/>
+      <c r="Q445" s="12"/>
       <c r="R445" s="4"/>
     </row>
     <row r="446" spans="16:18">
       <c r="P446" s="2"/>
-      <c r="Q446" s="15"/>
+      <c r="Q446" s="12"/>
       <c r="R446" s="4"/>
     </row>
     <row r="447" spans="16:18">
       <c r="P447" s="2"/>
-      <c r="Q447" s="15"/>
+      <c r="Q447" s="12"/>
       <c r="R447" s="4"/>
     </row>
     <row r="448" spans="16:18">
       <c r="P448" s="2"/>
-      <c r="Q448" s="15"/>
+      <c r="Q448" s="12"/>
       <c r="R448" s="4"/>
     </row>
     <row r="449" spans="16:18">
       <c r="P449" s="2"/>
-      <c r="Q449" s="15"/>
+      <c r="Q449" s="12"/>
       <c r="R449" s="4"/>
     </row>
     <row r="450" spans="16:18">
       <c r="P450" s="2"/>
-      <c r="Q450" s="15"/>
+      <c r="Q450" s="12"/>
       <c r="R450" s="4"/>
     </row>
     <row r="451" spans="16:18">
       <c r="P451" s="2"/>
-      <c r="Q451" s="15"/>
+      <c r="Q451" s="12"/>
       <c r="R451" s="4"/>
     </row>
     <row r="452" spans="16:18">
       <c r="P452" s="2"/>
-      <c r="Q452" s="15"/>
+      <c r="Q452" s="12"/>
       <c r="R452" s="4"/>
     </row>
     <row r="453" spans="16:18">
       <c r="P453" s="2"/>
-      <c r="Q453" s="15"/>
+      <c r="Q453" s="12"/>
       <c r="R453" s="4"/>
     </row>
     <row r="454" spans="16:18">
       <c r="P454" s="2"/>
-      <c r="Q454" s="15"/>
+      <c r="Q454" s="12"/>
       <c r="R454" s="4"/>
     </row>
     <row r="455" spans="16:18">
       <c r="P455" s="2"/>
-      <c r="Q455" s="15"/>
+      <c r="Q455" s="12"/>
       <c r="R455" s="4"/>
     </row>
     <row r="456" spans="16:18">
       <c r="P456" s="2"/>
-      <c r="Q456" s="15"/>
+      <c r="Q456" s="12"/>
       <c r="R456" s="4"/>
     </row>
     <row r="457" spans="16:18">
       <c r="P457" s="2"/>
-      <c r="Q457" s="15"/>
+      <c r="Q457" s="12"/>
       <c r="R457" s="4"/>
     </row>
     <row r="458" spans="16:18">
       <c r="P458" s="2"/>
-      <c r="Q458" s="15"/>
+      <c r="Q458" s="12"/>
       <c r="R458" s="4"/>
     </row>
     <row r="459" spans="16:18">
       <c r="P459" s="2"/>
-      <c r="Q459" s="15"/>
+      <c r="Q459" s="12"/>
       <c r="R459" s="4"/>
     </row>
     <row r="460" spans="16:18">
       <c r="P460" s="2"/>
-      <c r="Q460" s="15"/>
+      <c r="Q460" s="12"/>
       <c r="R460" s="4"/>
     </row>
     <row r="461" spans="16:18">
       <c r="P461" s="2"/>
-      <c r="Q461" s="15"/>
+      <c r="Q461" s="12"/>
       <c r="R461" s="4"/>
     </row>
     <row r="462" spans="16:18">
       <c r="P462" s="2"/>
-      <c r="Q462" s="15"/>
+      <c r="Q462" s="12"/>
       <c r="R462" s="4"/>
     </row>
     <row r="463" spans="16:18">
       <c r="P463" s="2"/>
-      <c r="Q463" s="15"/>
+      <c r="Q463" s="12"/>
       <c r="R463" s="4"/>
     </row>
     <row r="464" spans="16:18">
       <c r="P464" s="2"/>
-      <c r="Q464" s="15"/>
+      <c r="Q464" s="12"/>
       <c r="R464" s="4"/>
     </row>
     <row r="465" spans="16:18">
       <c r="P465" s="2"/>
-      <c r="Q465" s="15"/>
+      <c r="Q465" s="12"/>
       <c r="R465" s="4"/>
     </row>
     <row r="466" spans="16:18">
       <c r="P466" s="2"/>
-      <c r="Q466" s="15"/>
+      <c r="Q466" s="12"/>
       <c r="R466" s="4"/>
     </row>
     <row r="467" spans="16:18">
       <c r="P467" s="2"/>
-      <c r="Q467" s="15"/>
+      <c r="Q467" s="12"/>
       <c r="R467" s="4"/>
     </row>
     <row r="468" spans="16:18">
       <c r="P468" s="2"/>
-      <c r="Q468" s="15"/>
+      <c r="Q468" s="12"/>
       <c r="R468" s="4"/>
     </row>
     <row r="469" spans="16:18">
       <c r="P469" s="2"/>
-      <c r="Q469" s="15"/>
+      <c r="Q469" s="12"/>
       <c r="R469" s="4"/>
     </row>
     <row r="470" spans="16:18">
       <c r="P470" s="2"/>
-      <c r="Q470" s="15"/>
+      <c r="Q470" s="12"/>
       <c r="R470" s="4"/>
     </row>
     <row r="471" spans="16:18">
       <c r="P471" s="2"/>
-      <c r="Q471" s="15"/>
+      <c r="Q471" s="12"/>
       <c r="R471" s="4"/>
     </row>
     <row r="472" spans="16:18">
       <c r="P472" s="2"/>
-      <c r="Q472" s="15"/>
+      <c r="Q472" s="12"/>
       <c r="R472" s="4"/>
     </row>
     <row r="473" spans="16:18">
       <c r="P473" s="2"/>
-      <c r="Q473" s="15"/>
+      <c r="Q473" s="12"/>
       <c r="R473" s="4"/>
     </row>
     <row r="474" spans="16:18">
       <c r="P474" s="2"/>
-      <c r="Q474" s="15"/>
+      <c r="Q474" s="12"/>
       <c r="R474" s="4"/>
     </row>
     <row r="475" spans="16:18">
       <c r="P475" s="2"/>
-      <c r="Q475" s="15"/>
+      <c r="Q475" s="12"/>
       <c r="R475" s="4"/>
     </row>
     <row r="476" spans="16:18">
       <c r="P476" s="2"/>
-      <c r="Q476" s="15"/>
+      <c r="Q476" s="12"/>
       <c r="R476" s="4"/>
     </row>
     <row r="477" spans="16:18">
       <c r="P477" s="2"/>
-      <c r="Q477" s="15"/>
+      <c r="Q477" s="12"/>
       <c r="R477" s="4"/>
     </row>
     <row r="478" spans="16:18">
       <c r="P478" s="2"/>
-      <c r="Q478" s="15"/>
+      <c r="Q478" s="12"/>
       <c r="R478" s="4"/>
     </row>
     <row r="479" spans="16:18">
       <c r="P479" s="2"/>
-      <c r="Q479" s="15"/>
+      <c r="Q479" s="12"/>
       <c r="R479" s="4"/>
     </row>
     <row r="480" spans="16:18">
       <c r="P480" s="2"/>
-      <c r="Q480" s="15"/>
+      <c r="Q480" s="12"/>
       <c r="R480" s="4"/>
     </row>
     <row r="481" spans="16:18">
       <c r="P481" s="2"/>
-      <c r="Q481" s="15"/>
+      <c r="Q481" s="12"/>
       <c r="R481" s="4"/>
     </row>
     <row r="482" spans="16:18">
       <c r="P482" s="2"/>
-      <c r="Q482" s="15"/>
+      <c r="Q482" s="12"/>
       <c r="R482" s="4"/>
     </row>
     <row r="483" spans="16:18">
       <c r="P483" s="2"/>
-      <c r="Q483" s="15"/>
+      <c r="Q483" s="12"/>
       <c r="R483" s="4"/>
     </row>
     <row r="484" spans="16:18">
       <c r="P484" s="2"/>
-      <c r="Q484" s="15"/>
+      <c r="Q484" s="12"/>
       <c r="R484" s="4"/>
     </row>
     <row r="485" spans="16:18">
       <c r="P485" s="2"/>
-      <c r="Q485" s="15"/>
+      <c r="Q485" s="12"/>
       <c r="R485" s="4"/>
     </row>
     <row r="486" spans="16:18">
       <c r="P486" s="2"/>
-      <c r="Q486" s="15"/>
+      <c r="Q486" s="12"/>
       <c r="R486" s="4"/>
     </row>
     <row r="487" spans="16:18">
       <c r="P487" s="2"/>
-      <c r="Q487" s="15"/>
+      <c r="Q487" s="12"/>
       <c r="R487" s="4"/>
     </row>
     <row r="488" spans="16:18">
       <c r="P488" s="2"/>
-      <c r="Q488" s="15"/>
+      <c r="Q488" s="12"/>
       <c r="R488" s="4"/>
     </row>
     <row r="489" spans="16:18">
       <c r="P489" s="2"/>
-      <c r="Q489" s="15"/>
+      <c r="Q489" s="12"/>
       <c r="R489" s="4"/>
     </row>
     <row r="490" spans="16:18">
       <c r="P490" s="2"/>
-      <c r="Q490" s="15"/>
+      <c r="Q490" s="12"/>
       <c r="R490" s="4"/>
     </row>
     <row r="491" spans="16:18">
       <c r="P491" s="2"/>
-      <c r="Q491" s="15"/>
+      <c r="Q491" s="12"/>
       <c r="R491" s="4"/>
     </row>
     <row r="492" spans="16:18">
       <c r="P492" s="2"/>
-      <c r="Q492" s="15"/>
+      <c r="Q492" s="12"/>
       <c r="R492" s="4"/>
     </row>
     <row r="493" spans="16:18">
       <c r="P493" s="2"/>
-      <c r="Q493" s="15"/>
+      <c r="Q493" s="12"/>
       <c r="R493" s="4"/>
     </row>
     <row r="494" spans="16:18">
       <c r="P494" s="2"/>
-      <c r="Q494" s="15"/>
+      <c r="Q494" s="12"/>
       <c r="R494" s="4"/>
     </row>
     <row r="495" spans="16:18">
       <c r="P495" s="2"/>
-      <c r="Q495" s="15"/>
+      <c r="Q495" s="12"/>
       <c r="R495" s="4"/>
     </row>
     <row r="496" spans="16:18">
       <c r="P496" s="2"/>
-      <c r="Q496" s="15"/>
+      <c r="Q496" s="12"/>
       <c r="R496" s="4"/>
     </row>
     <row r="497" spans="16:18">
       <c r="P497" s="2"/>
-      <c r="Q497" s="15"/>
+      <c r="Q497" s="12"/>
       <c r="R497" s="4"/>
     </row>
     <row r="498" spans="16:18">
       <c r="P498" s="2"/>
-      <c r="Q498" s="15"/>
+      <c r="Q498" s="12"/>
       <c r="R498" s="4"/>
     </row>
     <row r="499" spans="16:18">
       <c r="P499" s="2"/>
-      <c r="Q499" s="15"/>
+      <c r="Q499" s="12"/>
       <c r="R499" s="4"/>
     </row>
     <row r="500" spans="16:18">
       <c r="P500" s="2"/>
-      <c r="Q500" s="15"/>
+      <c r="Q500" s="12"/>
       <c r="R500" s="4"/>
     </row>
     <row r="501" spans="16:18">
       <c r="P501" s="2"/>
-      <c r="Q501" s="15"/>
+      <c r="Q501" s="12"/>
       <c r="R501" s="4"/>
     </row>
     <row r="502" spans="16:18">
       <c r="P502" s="2"/>
-      <c r="Q502" s="15"/>
+      <c r="Q502" s="12"/>
       <c r="R502" s="4"/>
     </row>
     <row r="503" spans="16:18">
       <c r="P503" s="2"/>
-      <c r="Q503" s="15"/>
+      <c r="Q503" s="12"/>
       <c r="R503" s="4"/>
     </row>
     <row r="504" spans="16:18">
       <c r="P504" s="2"/>
-      <c r="Q504" s="15"/>
+      <c r="Q504" s="12"/>
       <c r="R504" s="4"/>
     </row>
     <row r="505" spans="16:18">
       <c r="P505" s="2"/>
-      <c r="Q505" s="15"/>
+      <c r="Q505" s="12"/>
       <c r="R505" s="4"/>
     </row>
     <row r="506" spans="16:18">
       <c r="P506" s="2"/>
-      <c r="Q506" s="15"/>
+      <c r="Q506" s="12"/>
       <c r="R506" s="4"/>
     </row>
     <row r="507" spans="16:18">
       <c r="P507" s="2"/>
-      <c r="Q507" s="15"/>
+      <c r="Q507" s="12"/>
       <c r="R507" s="4"/>
     </row>
     <row r="508" spans="16:18">
       <c r="P508" s="2"/>
-      <c r="Q508" s="15"/>
+      <c r="Q508" s="12"/>
       <c r="R508" s="4"/>
     </row>
     <row r="509" spans="16:18">
       <c r="P509" s="2"/>
-      <c r="Q509" s="15"/>
+      <c r="Q509" s="12"/>
       <c r="R509" s="4"/>
     </row>
     <row r="510" spans="16:18">
       <c r="P510" s="2"/>
-      <c r="Q510" s="15"/>
+      <c r="Q510" s="12"/>
       <c r="R510" s="4"/>
     </row>
     <row r="511" spans="16:18">
       <c r="P511" s="2"/>
-      <c r="Q511" s="15"/>
+      <c r="Q511" s="12"/>
       <c r="R511" s="4"/>
     </row>
     <row r="512" spans="16:18">
       <c r="P512" s="2"/>
-      <c r="Q512" s="15"/>
+      <c r="Q512" s="12"/>
       <c r="R512" s="4"/>
     </row>
     <row r="513" spans="16:18">
       <c r="P513" s="2"/>
-      <c r="Q513" s="15"/>
+      <c r="Q513" s="12"/>
       <c r="R513" s="4"/>
     </row>
     <row r="514" spans="16:18">
       <c r="P514" s="2"/>
-      <c r="Q514" s="15"/>
+      <c r="Q514" s="12"/>
       <c r="R514" s="4"/>
     </row>
     <row r="515" spans="16:18">
       <c r="P515" s="2"/>
-      <c r="Q515" s="15"/>
+      <c r="Q515" s="12"/>
       <c r="R515" s="4"/>
     </row>
     <row r="516" spans="16:18">
       <c r="P516" s="2"/>
-      <c r="Q516" s="15"/>
+      <c r="Q516" s="12"/>
       <c r="R516" s="4"/>
     </row>
     <row r="517" spans="16:18">
       <c r="P517" s="2"/>
-      <c r="Q517" s="15"/>
+      <c r="Q517" s="12"/>
       <c r="R517" s="4"/>
     </row>
     <row r="518" spans="16:18">
       <c r="P518" s="2"/>
-      <c r="Q518" s="15"/>
+      <c r="Q518" s="12"/>
       <c r="R518" s="4"/>
     </row>
     <row r="519" spans="16:18">
-      <c r="Q519" s="15"/>
+      <c r="Q519" s="12"/>
       <c r="R519" s="4"/>
     </row>
     <row r="520" spans="16:18">
-      <c r="Q520" s="15"/>
+      <c r="Q520" s="12"/>
       <c r="R520" s="4"/>
     </row>
     <row r="521" spans="16:18">
-      <c r="Q521" s="15"/>
+      <c r="Q521" s="12"/>
     </row>
     <row r="522" spans="16:18">
-      <c r="Q522" s="15"/>
+      <c r="Q522" s="12"/>
     </row>
     <row r="523" spans="16:18">
-      <c r="Q523" s="15"/>
+      <c r="Q523" s="12"/>
     </row>
     <row r="524" spans="16:18">
-      <c r="Q524" s="15"/>
+      <c r="Q524" s="12"/>
     </row>
     <row r="525" spans="16:18">
-      <c r="Q525" s="15"/>
+      <c r="Q525" s="12"/>
     </row>
     <row r="526" spans="16:18">
-      <c r="Q526" s="15"/>
+      <c r="Q526" s="12"/>
     </row>
     <row r="527" spans="16:18">
-      <c r="Q527" s="15"/>
+      <c r="Q527" s="12"/>
     </row>
     <row r="528" spans="16:18">
-      <c r="Q528" s="15"/>
+      <c r="Q528" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -3458,7 +3438,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R520 S2:S3 S5:S1048576" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"YES, NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T6 T8:T1048576" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:U6 T8:U1048576" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>", YES, NO"</formula1>
     </dataValidation>
   </dataValidations>
